--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -36068,6 +36068,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1553">
+      <c r="A1553" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B1553" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1553" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D1553" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E1553" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F1553" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G1553" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1554" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1554" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="D1554" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="E1554" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="F1554" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="G1554" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -36114,6 +36114,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1555">
+      <c r="A1555" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1555" t="n">
+        <v>7280</v>
+      </c>
+      <c r="C1555" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="D1555" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="E1555" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F1555" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="G1555" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -36137,6 +36137,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1556">
+      <c r="A1556" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1556" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C1556" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="D1556" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="E1556" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="F1556" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="G1556" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -36160,6 +36160,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1557">
+      <c r="A1557" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1557" t="n">
+        <v>16291</v>
+      </c>
+      <c r="C1557" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="D1557" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="E1557" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="F1557" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="G1557" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -36001,22 +36001,22 @@
     </row>
     <row r="1550">
       <c r="A1550" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1550" t="n">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="C1550" t="n">
-        <v>6.5</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="D1550" t="n">
-        <v>6.44999980926514</v>
+        <v>6.34999990463257</v>
       </c>
       <c r="E1550" t="n">
-        <v>6.44999980926514</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="F1550" t="n">
-        <v>6.5</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="G1550" t="s">
         <v>7</v>
@@ -36024,13 +36024,13 @@
     </row>
     <row r="1551">
       <c r="A1551" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1551" t="n">
-        <v>11052</v>
+        <v>2000</v>
       </c>
       <c r="C1551" t="n">
-        <v>6.55000019073486</v>
+        <v>6.5</v>
       </c>
       <c r="D1551" t="n">
         <v>6.44999980926514</v>
@@ -36039,7 +36039,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="F1551" t="n">
-        <v>6.55000019073486</v>
+        <v>6.5</v>
       </c>
       <c r="G1551" t="s">
         <v>7</v>
@@ -36047,22 +36047,22 @@
     </row>
     <row r="1552">
       <c r="A1552" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1552" t="n">
-        <v>8581</v>
+        <v>11052</v>
       </c>
       <c r="C1552" t="n">
         <v>6.55000019073486</v>
       </c>
       <c r="D1552" t="n">
-        <v>6.40000009536743</v>
+        <v>6.44999980926514</v>
       </c>
       <c r="E1552" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="F1552" t="n">
         <v>6.55000019073486</v>
-      </c>
-      <c r="F1552" t="n">
-        <v>6.5</v>
       </c>
       <c r="G1552" t="s">
         <v>7</v>
@@ -36070,19 +36070,19 @@
     </row>
     <row r="1553">
       <c r="A1553" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1553" t="n">
-        <v>0</v>
+        <v>8581</v>
       </c>
       <c r="C1553" t="n">
-        <v>6.5</v>
+        <v>6.55000019073486</v>
       </c>
       <c r="D1553" t="n">
-        <v>6.5</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="E1553" t="n">
-        <v>6.5</v>
+        <v>6.55000019073486</v>
       </c>
       <c r="F1553" t="n">
         <v>6.5</v>
@@ -36093,22 +36093,22 @@
     </row>
     <row r="1554">
       <c r="A1554" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1554" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="C1554" t="n">
-        <v>6.55000019073486</v>
+        <v>6.5</v>
       </c>
       <c r="D1554" t="n">
-        <v>6.40000009536743</v>
+        <v>6.5</v>
       </c>
       <c r="E1554" t="n">
-        <v>6.55000019073486</v>
+        <v>6.5</v>
       </c>
       <c r="F1554" t="n">
-        <v>6.55000019073486</v>
+        <v>6.5</v>
       </c>
       <c r="G1554" t="s">
         <v>7</v>
@@ -36116,10 +36116,10 @@
     </row>
     <row r="1555">
       <c r="A1555" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1555" t="n">
-        <v>7280</v>
+        <v>5000</v>
       </c>
       <c r="C1555" t="n">
         <v>6.55000019073486</v>
@@ -36128,7 +36128,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="E1555" t="n">
-        <v>6.5</v>
+        <v>6.55000019073486</v>
       </c>
       <c r="F1555" t="n">
         <v>6.55000019073486</v>
@@ -36139,10 +36139,10 @@
     </row>
     <row r="1556">
       <c r="A1556" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1556" t="n">
-        <v>7500</v>
+        <v>7280</v>
       </c>
       <c r="C1556" t="n">
         <v>6.55000019073486</v>
@@ -36151,7 +36151,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="E1556" t="n">
-        <v>6.55000019073486</v>
+        <v>6.5</v>
       </c>
       <c r="F1556" t="n">
         <v>6.55000019073486</v>
@@ -36162,24 +36162,47 @@
     </row>
     <row r="1557">
       <c r="A1557" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1557" t="n">
-        <v>16291</v>
+        <v>7500</v>
       </c>
       <c r="C1557" t="n">
         <v>6.55000019073486</v>
       </c>
       <c r="D1557" t="n">
-        <v>6.25</v>
+        <v>6.40000009536743</v>
       </c>
       <c r="E1557" t="n">
         <v>6.55000019073486</v>
       </c>
       <c r="F1557" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="G1557" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1558" t="n">
+        <v>3557</v>
+      </c>
+      <c r="C1558" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D1558" t="n">
         <v>6.44999980926514</v>
       </c>
-      <c r="G1557" t="s">
+      <c r="E1558" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="F1558" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G1558" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -551,7 +551,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G9" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G10" t="n">
-        <v>4.19595146179199</v>
+        <v>4.19595193862915</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G15" t="n">
-        <v>4.11463499069214</v>
+        <v>4.11463451385498</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>4.11463499069214</v>
+        <v>4.11463451385498</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>4.11463499069214</v>
+        <v>4.11463451385498</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.17968797683716</v>
+        <v>4.17968893051147</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>4.26100540161133</v>
+        <v>4.26100492477417</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>4.26100540161133</v>
+        <v>4.26100492477417</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.11463499069214</v>
+        <v>4.11463451385498</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>4.17968797683716</v>
+        <v>4.17968893051147</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G47" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G49" t="n">
-        <v>4.05771350860596</v>
+        <v>4.05771255493164</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.9845278263092</v>
+        <v>3.98452830314636</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200133323669</v>
+        <v>3.95200157165527</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.9438693523407</v>
+        <v>3.94386959075928</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.75</v>
       </c>
       <c r="G57" t="n">
-        <v>3.86255264282227</v>
+        <v>3.86255216598511</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442066192627</v>
+        <v>3.85442090034485</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.88694858551025</v>
+        <v>3.8869481086731</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.82189393043518</v>
+        <v>3.82189416885376</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057698249817</v>
+        <v>3.74057674407959</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057698249817</v>
+        <v>3.74057674407959</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>3.82189393043518</v>
+        <v>3.82189416885376</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>3.71618175506592</v>
+        <v>3.71618270874023</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.67552375793457</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.64299726486206</v>
+        <v>3.6429967880249</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926003456116</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926003456116</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>3.67552375793457</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69178676605225</v>
+        <v>3.6917872428894</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.773104429245</v>
+        <v>3.77310347557068</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>3.67552375793457</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G81" t="n">
-        <v>4.19595146179199</v>
+        <v>4.19595193862915</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>4.11463499069214</v>
+        <v>4.11463451385498</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>4.17968797683716</v>
+        <v>4.17968893051147</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G85" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G87" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737628936768</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.45616626739502</v>
+        <v>4.45616579055786</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111185073853</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111185073853</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G100" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G101" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869276046753</v>
+        <v>4.48869323730469</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869276046753</v>
+        <v>4.48869323730469</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.47242879867554</v>
+        <v>4.47243022918701</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495672225952</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495672225952</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>4.5212197303772</v>
+        <v>4.52121925354004</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G114" t="n">
-        <v>4.35858535766602</v>
+        <v>4.35858583450317</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G119" t="n">
-        <v>4.35858535766602</v>
+        <v>4.35858583450317</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737628936768</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>4.34232234954834</v>
+        <v>4.3423228263855</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111185073853</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>4.91154050827026</v>
+        <v>4.91154003143311</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791091918945</v>
+        <v>5.05791044235229</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801832199097</v>
+        <v>5.18801736831665</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043836593628</v>
+        <v>5.09043788909912</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>4.8790135383606</v>
+        <v>4.87901401519775</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791091918945</v>
+        <v>5.05791044235229</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G152" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538394927979</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>5.10670185089111</v>
+        <v>5.10670137405396</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043836593628</v>
+        <v>5.09043788909912</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>4.9765944480896</v>
+        <v>4.97659397125244</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>4.94406747817993</v>
+        <v>4.94406700134277</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G165" t="n">
-        <v>4.92780447006226</v>
+        <v>4.92780351638794</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G168" t="n">
-        <v>4.92780447006226</v>
+        <v>4.92780351638794</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.94406747817993</v>
+        <v>4.94406700134277</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>4.91154050827026</v>
+        <v>4.91154003143311</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>4.8790135383606</v>
+        <v>4.87901401519775</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G175" t="n">
-        <v>4.83022308349609</v>
+        <v>4.83022403717041</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>5.25307178497314</v>
+        <v>5.25307130813599</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.36691570281982</v>
+        <v>5.36691522598267</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.5</v>
       </c>
       <c r="G185" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.5</v>
       </c>
       <c r="G186" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>6.5</v>
       </c>
       <c r="G187" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.5</v>
       </c>
       <c r="G188" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922786712646</v>
+        <v>5.13922834396362</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538394927979</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G194" t="n">
-        <v>5.20428228378296</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>5.00475692749023</v>
+        <v>5.00475597381592</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G201" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G205" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368719100952</v>
+        <v>5.45368814468384</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>5.38717937469482</v>
+        <v>5.38717985153198</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368719100952</v>
+        <v>5.45368814468384</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G217" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333108901978</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G222" t="n">
-        <v>5.78623008728027</v>
+        <v>5.78622961044312</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>5.75297546386719</v>
+        <v>5.75297594070435</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>5.78623008728027</v>
+        <v>5.78622961044312</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G229" t="n">
-        <v>5.96912813186646</v>
+        <v>5.9691276550293</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G231" t="n">
-        <v>5.80285739898682</v>
+        <v>5.80285692214966</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>5.78623008728027</v>
+        <v>5.78622961044312</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>5.80285739898682</v>
+        <v>5.80285692214966</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G252" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G255" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333108901978</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G267" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333108901978</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G272" t="n">
-        <v>5.52019596099854</v>
+        <v>5.52019643783569</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>5.75297546386719</v>
+        <v>5.75297594070435</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G290" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G294" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333108901978</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>5.43706083297729</v>
+        <v>5.43706035614014</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G302" t="n">
-        <v>5.38717937469482</v>
+        <v>5.38717985153198</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>5.38717937469482</v>
+        <v>5.38717985153198</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>5.38717937469482</v>
+        <v>5.38717985153198</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G307" t="n">
-        <v>5.38717937469482</v>
+        <v>5.38717985153198</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G319" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G323" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G324" t="n">
-        <v>5.20428228378296</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G325" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G327" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G332" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G333" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G334" t="n">
-        <v>5.20428228378296</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G335" t="n">
-        <v>5.20428228378296</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G336" t="n">
-        <v>5.20428228378296</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G337" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G338" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G339" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G340" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G347" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G349" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G353" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>5.07126474380493</v>
+        <v>5.07126426696777</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G364" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G365" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G368" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G375" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G386" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G387" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G394" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G395" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G396" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97150230407715</v>
+        <v>4.97150182723999</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G401" t="n">
-        <v>4.92162084579468</v>
+        <v>4.92162132263184</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>4.67221450805664</v>
+        <v>4.67221403121948</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>4.48931646347046</v>
+        <v>4.4893159866333</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G409" t="n">
-        <v>4.68884086608887</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>4.43943548202515</v>
+        <v>4.43943500518799</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>4.48931646347046</v>
+        <v>4.4893159866333</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>4.47268962860107</v>
+        <v>4.47268915176392</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>4.35629892349243</v>
+        <v>4.35629940032959</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G420" t="n">
-        <v>4.45606184005737</v>
+        <v>4.45606231689453</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>4.67221450805664</v>
+        <v>4.67221403121948</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>4.60570573806763</v>
+        <v>4.60570621490479</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>4.55582523345947</v>
+        <v>4.55582475662231</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>4.52257013320923</v>
+        <v>4.52257061004639</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G429" t="n">
-        <v>4.68884086608887</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.5</v>
       </c>
       <c r="G431" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>5.5</v>
       </c>
       <c r="G433" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5.5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>4.68884086608887</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G439" t="n">
-        <v>4.75534963607788</v>
+        <v>4.75535011291504</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504903793335</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504903793335</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G460" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G461" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G462" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G463" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>6</v>
       </c>
       <c r="G472" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G475" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G479" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504903793335</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G484" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G495" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G498" t="n">
-        <v>4.41524505615234</v>
+        <v>4.41524457931519</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G499" t="n">
-        <v>4.41524505615234</v>
+        <v>4.41524457931519</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G500" t="n">
-        <v>4.41524505615234</v>
+        <v>4.41524457931519</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G501" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G502" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G503" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G506" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G514" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G515" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.89256858825684</v>
+        <v>4.89256906509399</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.89256858825684</v>
+        <v>4.89256906509399</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G521" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G524" t="n">
-        <v>4.99485206604004</v>
+        <v>4.9948525428772</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G532" t="n">
-        <v>4.92666292190552</v>
+        <v>4.92666339874268</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.5</v>
       </c>
       <c r="G547" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.48343467712402</v>
+        <v>4.48343420028687</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>4.48343467712402</v>
+        <v>4.48343420028687</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G559" t="n">
-        <v>4.53457546234131</v>
+        <v>4.53457593917847</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G563" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G567" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G568" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G569" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G570" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G571" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G572" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G582" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.5</v>
       </c>
       <c r="G595" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G600" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>5.5</v>
       </c>
       <c r="G612" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G616" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G617" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G621" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G624" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504903793335</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G645" t="n">
-        <v>5.30170297622681</v>
+        <v>5.30170345306396</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G647" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6</v>
       </c>
       <c r="G648" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>5.13123083114624</v>
+        <v>5.13123035430908</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6</v>
       </c>
       <c r="G654" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>5.18237161636353</v>
+        <v>5.18237209320068</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>6</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6</v>
       </c>
       <c r="G658" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6</v>
       </c>
       <c r="G660" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G662" t="n">
-        <v>5.18237161636353</v>
+        <v>5.18237209320068</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>5.13123083114624</v>
+        <v>5.13123035430908</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>5.18237161636353</v>
+        <v>5.18237209320068</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>5.18237161636353</v>
+        <v>5.18237209320068</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6</v>
       </c>
       <c r="G679" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>6</v>
       </c>
       <c r="G681" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6</v>
       </c>
       <c r="G684" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G685" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6</v>
       </c>
       <c r="G687" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6</v>
       </c>
       <c r="G691" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6</v>
       </c>
       <c r="G692" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6</v>
       </c>
       <c r="G693" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G695" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G699" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>6</v>
       </c>
       <c r="G704" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G707" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G708" t="n">
-        <v>5.20235919952393</v>
+        <v>5.20235872268677</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>5.20235919952393</v>
+        <v>5.20235872268677</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.20235919952393</v>
+        <v>5.20235872268677</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>5.20235919952393</v>
+        <v>5.20235872268677</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G715" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.75</v>
       </c>
       <c r="G717" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.75</v>
       </c>
       <c r="G718" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.75</v>
       </c>
       <c r="G719" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.75</v>
       </c>
       <c r="G720" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.75</v>
       </c>
       <c r="G721" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G724" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.75</v>
       </c>
       <c r="G725" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>5.75</v>
       </c>
       <c r="G726" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.75</v>
       </c>
       <c r="G727" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.89374494552612</v>
+        <v>4.89374446868896</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G770" t="n">
-        <v>4.89374494552612</v>
+        <v>4.89374446868896</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G793" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>4.89374494552612</v>
+        <v>4.89374446868896</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>4.98191976547241</v>
+        <v>4.98192024230957</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>4.39114379882812</v>
+        <v>4.39114332199097</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G809" t="n">
-        <v>4.39114379882812</v>
+        <v>4.39114332199097</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G822" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G835" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G847" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G848" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G849" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.0913462638855</v>
+        <v>4.09134674072266</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.00317096710205</v>
+        <v>4.00317049026489</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G854" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>4.00317096710205</v>
+        <v>4.00317049026489</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G860" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G861" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G868" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G877" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86208987236023</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>3.72100901603699</v>
+        <v>3.72100877761841</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>3.68573904037476</v>
+        <v>3.68573880195618</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G886" t="n">
-        <v>3.73864436149597</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G893" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>3.826819896698</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73864436149597</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>3.826819896698</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86208987236023</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>3.826819896698</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86208987236023</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G919" t="n">
-        <v>3.826819896698</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G924" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>4.07371139526367</v>
+        <v>4.07371091842651</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G937" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G944" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G949" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G955" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>4.33823776245117</v>
+        <v>4.33823823928833</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -40917,7 +40917,7 @@
         <v>5500</v>
       </c>
       <c r="C1560" t="n">
-        <v>6.59999990463257</v>
+        <v>6.65000009536743</v>
       </c>
       <c r="D1560" t="n">
         <v>6.5</v>
@@ -40932,6 +40932,32 @@
         <v>6.65000009536743</v>
       </c>
       <c r="H1560" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1561" t="n">
+        <v>16236</v>
+      </c>
+      <c r="C1561" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="D1561" t="n">
+        <v>6.40000009536743</v>
+      </c>
+      <c r="E1561" t="n">
+        <v>6.65000009536743</v>
+      </c>
+      <c r="F1561" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="G1561" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="H1561" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -551,7 +551,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G15" t="n">
-        <v>4.11463451385498</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>4.11463451385498</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>4.11463451385498</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.17968893051147</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474239349365</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.27726936340332</v>
+        <v>4.277268409729</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>4.27726936340332</v>
+        <v>4.277268409729</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>4.26100492477417</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>4.26100492477417</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.11463451385498</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>4.17968893051147</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G49" t="n">
-        <v>4.05771255493164</v>
+        <v>4.0577130317688</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.98452830314636</v>
+        <v>3.98452806472778</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200157165527</v>
+        <v>3.95200109481812</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639632225037</v>
+        <v>3.97639656066895</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639632225037</v>
+        <v>3.97639656066895</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94386959075928</v>
+        <v>3.9438693523407</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321135520935</v>
+        <v>3.90321063995361</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321135520935</v>
+        <v>3.90321063995361</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.75</v>
       </c>
       <c r="G57" t="n">
-        <v>3.86255216598511</v>
+        <v>3.86255264282227</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442090034485</v>
+        <v>3.85442042350769</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.8869481086731</v>
+        <v>3.88694763183594</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.82189416885376</v>
+        <v>3.82189393043518</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057674407959</v>
+        <v>3.74057722091675</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057674407959</v>
+        <v>3.74057722091675</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>3.82189416885376</v>
+        <v>3.82189393043518</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991874694824</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>3.71618270874023</v>
+        <v>3.7161819934845</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.6429967880249</v>
+        <v>3.64299726486206</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926051139832</v>
+        <v>3.65926027297974</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991874694824</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926051139832</v>
+        <v>3.65926027297974</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.77310347557068</v>
+        <v>3.773104429245</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991874694824</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>4.11463451385498</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>4.17968893051147</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G85" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474239349365</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G87" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474239349365</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>4.39111185073853</v>
+        <v>4.39111280441284</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.39111185073853</v>
+        <v>4.39111280441284</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G100" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474239349365</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G101" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474239349365</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869323730469</v>
+        <v>4.48869276046753</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869323730469</v>
+        <v>4.48869276046753</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.47243022918701</v>
+        <v>4.4724292755127</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495672225952</v>
+        <v>4.50495576858521</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495672225952</v>
+        <v>4.50495576858521</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>4.52121925354004</v>
+        <v>4.52122020721436</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>4.43990278244019</v>
+        <v>4.43990230560303</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G114" t="n">
-        <v>4.35858583450317</v>
+        <v>4.35858631134033</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G119" t="n">
-        <v>4.35858583450317</v>
+        <v>4.35858631134033</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>4.3423228263855</v>
+        <v>4.34232234954834</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.39111185073853</v>
+        <v>4.39111280441284</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G130" t="n">
-        <v>4.61879968643188</v>
+        <v>4.61880016326904</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>4.76517057418823</v>
+        <v>4.76517009735107</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791044235229</v>
+        <v>5.05791139602661</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>5.1554913520813</v>
+        <v>5.15549087524414</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>5.1554913520813</v>
+        <v>5.15549087524414</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801736831665</v>
+        <v>5.18801832199097</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164743423462</v>
+        <v>5.04164695739746</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791044235229</v>
+        <v>5.05791139602661</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538394927979</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>4.97659397125244</v>
+        <v>4.97659349441528</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164743423462</v>
+        <v>5.04164695739746</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G162" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G163" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G165" t="n">
-        <v>4.92780351638794</v>
+        <v>4.9278039932251</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G167" t="n">
-        <v>4.89527750015259</v>
+        <v>4.89527702331543</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G168" t="n">
-        <v>4.92780351638794</v>
+        <v>4.9278039932251</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.89527750015259</v>
+        <v>4.89527702331543</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>5.38317823410034</v>
+        <v>5.3831787109375</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922834396362</v>
+        <v>5.13922739028931</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538394927979</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G194" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>5.00475597381592</v>
+        <v>5.00475645065308</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G201" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G205" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368719100952</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>5.38717985153198</v>
+        <v>5.38718032836914</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368719100952</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G217" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634910583496</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66984033584595</v>
+        <v>5.66984081268311</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>5.75297594070435</v>
+        <v>5.75297546386719</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7</v>
       </c>
       <c r="G225" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G228" t="n">
-        <v>5.88599252700806</v>
+        <v>5.88599300384521</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>7</v>
       </c>
       <c r="G235" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7</v>
       </c>
       <c r="G236" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>5.83611106872559</v>
+        <v>5.83611154556274</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7</v>
       </c>
       <c r="G240" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7</v>
       </c>
       <c r="G241" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G245" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G247" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66984033584595</v>
+        <v>5.66984081268311</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G252" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G255" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G258" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G265" t="n">
-        <v>5.61995887756348</v>
+        <v>5.61995935440063</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634910583496</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634910583496</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>5.75297594070435</v>
+        <v>5.75297546386719</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634910583496</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634910583496</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G283" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G290" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G302" t="n">
-        <v>5.38717985153198</v>
+        <v>5.38718032836914</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>5.38717985153198</v>
+        <v>5.38718032836914</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>5.38717985153198</v>
+        <v>5.38718032836914</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G307" t="n">
-        <v>5.38717985153198</v>
+        <v>5.38718032836914</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15439939498901</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>5.12114572525024</v>
+        <v>5.1211462020874</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G319" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G323" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G324" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G325" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G327" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G332" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G334" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G335" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G336" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G337" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G339" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G340" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G347" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G349" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G350" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G351" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G352" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15439939498901</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>5.07126426696777</v>
+        <v>5.07126522064209</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G364" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G369" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G381" t="n">
-        <v>5.12114572525024</v>
+        <v>5.1211462020874</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G382" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G386" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G387" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G391" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15439939498901</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15439939498901</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>5.23753595352173</v>
+        <v>5.23753643035889</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G394" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G395" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G396" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G397" t="n">
-        <v>5.08789205551147</v>
+        <v>5.08789253234863</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G398" t="n">
-        <v>5.08789205551147</v>
+        <v>5.08789253234863</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G401" t="n">
-        <v>4.92162132263184</v>
+        <v>4.92162084579468</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>4.88836717605591</v>
+        <v>4.88836669921875</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>4.4893159866333</v>
+        <v>4.48931646347046</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>4.80523157119751</v>
+        <v>4.80523109436035</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>4.43943500518799</v>
+        <v>4.4394359588623</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>4.4893159866333</v>
+        <v>4.48931646347046</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>4.47268915176392</v>
+        <v>4.47268867492676</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>4.35629940032959</v>
+        <v>4.35629892349243</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G424" t="n">
-        <v>4.80523157119751</v>
+        <v>4.80523109436035</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>4.55582475662231</v>
+        <v>4.55582523345947</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G440" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504903793335</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504903793335</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>5.06304121017456</v>
+        <v>5.06304168701172</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>5.06304121017456</v>
+        <v>5.06304168701172</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>6</v>
       </c>
       <c r="G472" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G475" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>4.58571767807007</v>
+        <v>4.58571720123291</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G479" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504903793335</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G484" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G488" t="n">
-        <v>4.43229198455811</v>
+        <v>4.43229150772095</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G489" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>4.58571767807007</v>
+        <v>4.58571720123291</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G491" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G492" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G493" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G495" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G497" t="n">
-        <v>4.31296110153198</v>
+        <v>4.31296062469482</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G504" t="n">
-        <v>4.58571767807007</v>
+        <v>4.58571720123291</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G506" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G514" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G515" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.89256906509399</v>
+        <v>4.89256811141968</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.89256906509399</v>
+        <v>4.89256811141968</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G524" t="n">
-        <v>4.9948525428772</v>
+        <v>4.99485206604004</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008813858032</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G532" t="n">
-        <v>4.92666339874268</v>
+        <v>4.92666292190552</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.97780466079712</v>
+        <v>4.97780513763428</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.5</v>
       </c>
       <c r="G547" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G548" t="n">
-        <v>4.58571767807007</v>
+        <v>4.58571720123291</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>4.55162334442139</v>
+        <v>4.55162382125854</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.55162334442139</v>
+        <v>4.55162382125854</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G554" t="n">
-        <v>4.44933891296387</v>
+        <v>4.44933938980103</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G558" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G564" t="n">
-        <v>4.43229198455811</v>
+        <v>4.43229150772095</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G565" t="n">
-        <v>4.43229198455811</v>
+        <v>4.43229150772095</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G566" t="n">
-        <v>4.43229198455811</v>
+        <v>4.43229150772095</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.56867027282715</v>
+        <v>4.56867074966431</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.5</v>
       </c>
       <c r="G595" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>5.5</v>
       </c>
       <c r="G612" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G616" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G617" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G621" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G624" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504903793335</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>5.25056076049805</v>
+        <v>5.25056123733521</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G644" t="n">
-        <v>5.35284519195557</v>
+        <v>5.35284471511841</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G645" t="n">
-        <v>5.30170345306396</v>
+        <v>5.30170297622681</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6</v>
       </c>
       <c r="G648" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6</v>
       </c>
       <c r="G654" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>6</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6</v>
       </c>
       <c r="G658" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6</v>
       </c>
       <c r="G660" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008813858032</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>5.06304121017456</v>
+        <v>5.06304168701172</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>5.06304121017456</v>
+        <v>5.06304168701172</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6</v>
       </c>
       <c r="G679" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>6</v>
       </c>
       <c r="G681" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6</v>
       </c>
       <c r="G684" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G685" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6</v>
       </c>
       <c r="G687" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6</v>
       </c>
       <c r="G691" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6</v>
       </c>
       <c r="G692" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6</v>
       </c>
       <c r="G693" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G695" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G699" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>6</v>
       </c>
       <c r="G704" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G707" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G715" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G724" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G728" t="n">
-        <v>4.93783187866211</v>
+        <v>4.93783235549927</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.93783187866211</v>
+        <v>4.93783235549927</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G793" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>4.98192024230957</v>
+        <v>4.98191976547241</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.25</v>
       </c>
       <c r="G799" t="n">
-        <v>4.62921762466431</v>
+        <v>4.62921810150146</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>4.02080631256104</v>
+        <v>4.02080583572388</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>4.02080631256104</v>
+        <v>4.02080583572388</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G832" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G835" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G845" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G846" t="n">
-        <v>4.25006294250488</v>
+        <v>4.25006246566772</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G847" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G848" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G849" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.00317049026489</v>
+        <v>4.00317096710205</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G854" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>4.00317049026489</v>
+        <v>4.00317096710205</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>4.02080631256104</v>
+        <v>4.02080583572388</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G860" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.5</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96790099143982</v>
+        <v>3.96790075302124</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.5</v>
       </c>
       <c r="G872" t="n">
-        <v>3.96790099143982</v>
+        <v>3.96790075302124</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.96790099143982</v>
+        <v>3.96790075302124</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.5</v>
       </c>
       <c r="G876" t="n">
-        <v>3.96790099143982</v>
+        <v>3.96790075302124</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>3.8973605632782</v>
+        <v>3.89736032485962</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209058761597</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G883" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918478965759</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>3.72100877761841</v>
+        <v>3.72100925445557</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G886" t="n">
-        <v>3.73864412307739</v>
+        <v>3.73864436149597</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918478965759</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>3.8973605632782</v>
+        <v>3.89736032485962</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G899" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>3.79154968261719</v>
+        <v>3.79154992103577</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G901" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73864412307739</v>
+        <v>3.73864436149597</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G904" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918478965759</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G905" t="n">
-        <v>3.79154968261719</v>
+        <v>3.79154992103577</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G906" t="n">
-        <v>3.79154968261719</v>
+        <v>3.79154992103577</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209058761597</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G908" t="n">
-        <v>3.79154968261719</v>
+        <v>3.79154992103577</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G910" t="n">
-        <v>3.79154968261719</v>
+        <v>3.79154992103577</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209058761597</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G915" t="n">
-        <v>3.8973605632782</v>
+        <v>3.89736032485962</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G919" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G924" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G934" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>4.07371091842651</v>
+        <v>4.07371139526367</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G936" t="n">
-        <v>4.25006294250488</v>
+        <v>4.25006246566772</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G937" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G938" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G940" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G943" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G944" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G949" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G955" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>5</v>
       </c>
       <c r="G957" t="n">
-        <v>4.40877819061279</v>
+        <v>4.40877866744995</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G967" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>4.45847797393799</v>
+        <v>4.45847749710083</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.31169652938843</v>
+        <v>4.31169605255127</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.31169652938843</v>
+        <v>4.31169605255127</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.0364818572998</v>
+        <v>4.03648138046265</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.0364818572998</v>
+        <v>4.03648138046265</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.9630913734436</v>
+        <v>3.96309113502502</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.88970065116882</v>
+        <v>3.88970017433167</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.9630913734436</v>
+        <v>3.96309113502502</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.88970065116882</v>
+        <v>3.88970017433167</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1091" t="n">
-        <v>4.0364818572998</v>
+        <v>4.03648138046265</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.0364818572998</v>
+        <v>4.03648138046265</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.9630913734436</v>
+        <v>3.96309113502502</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.9630913734436</v>
+        <v>3.96309113502502</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1133" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.31169652938843</v>
+        <v>4.31169605255127</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.31169652938843</v>
+        <v>4.31169605255127</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.45847797393799</v>
+        <v>4.45847749710083</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -40958,6 +40958,32 @@
         <v>6.80000019073486</v>
       </c>
       <c r="H1561" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1562" t="n">
+        <v>10528</v>
+      </c>
+      <c r="C1562" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="D1562" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="E1562" t="n">
+        <v>6.65000009536743</v>
+      </c>
+      <c r="F1562" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="G1562" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="H1562" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -551,7 +551,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G9" t="n">
-        <v>4.16342496871948</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G10" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.17968797683716</v>
+        <v>4.17968845367432</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>4.24474239349365</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.277268409729</v>
+        <v>4.27726936340332</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>4.277268409729</v>
+        <v>4.27726936340332</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>4.17968797683716</v>
+        <v>4.17968845367432</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G47" t="n">
-        <v>4.16342496871948</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>4.16342496871948</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G49" t="n">
-        <v>4.0577130317688</v>
+        <v>4.05771255493164</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.98452806472778</v>
+        <v>3.98452830314636</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200109481812</v>
+        <v>3.95200133323669</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639656066895</v>
+        <v>3.97639584541321</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639656066895</v>
+        <v>3.97639584541321</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321063995361</v>
+        <v>3.90321111679077</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321063995361</v>
+        <v>3.90321111679077</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442042350769</v>
+        <v>3.85442113876343</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.88694763183594</v>
+        <v>3.8869481086731</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.82189393043518</v>
+        <v>3.82189416885376</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057722091675</v>
+        <v>3.74057698249817</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057722091675</v>
+        <v>3.74057698249817</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>3.82189393043518</v>
+        <v>3.82189416885376</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>3.7161819934845</v>
+        <v>3.71618270874023</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.64299726486206</v>
+        <v>3.6429967880249</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926027297974</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926027297974</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.6917872428894</v>
+        <v>3.69178748130798</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.773104429245</v>
+        <v>3.77310371398926</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16342496871948</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G81" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>4.17968797683716</v>
+        <v>4.17968845367432</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G85" t="n">
-        <v>4.24474239349365</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G87" t="n">
-        <v>4.24474239349365</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.42363929748535</v>
+        <v>4.42363882064819</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.45616579055786</v>
+        <v>4.45616626739502</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.42363929748535</v>
+        <v>4.42363882064819</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111232757568</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111232757568</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G100" t="n">
-        <v>4.24474239349365</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G101" t="n">
-        <v>4.24474239349365</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.32605934143066</v>
+        <v>4.32605886459351</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>4.52122020721436</v>
+        <v>4.5212197303772</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>4.43990230560303</v>
+        <v>4.43990325927734</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G112" t="n">
-        <v>4.32605934143066</v>
+        <v>4.32605886459351</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G114" t="n">
-        <v>4.35858631134033</v>
+        <v>4.35858583450317</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G119" t="n">
-        <v>4.35858631134033</v>
+        <v>4.35858583450317</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111232757568</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>4.76517009735107</v>
+        <v>4.76517057418823</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>4.91154003143311</v>
+        <v>4.91154050827026</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791139602661</v>
+        <v>5.05791044235229</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>5.15549087524414</v>
+        <v>5.1554913520813</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>5.15549087524414</v>
+        <v>5.1554913520813</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801832199097</v>
+        <v>5.18801784515381</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043836593628</v>
+        <v>5.09043788909912</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164695739746</v>
+        <v>5.04164791107178</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791139602661</v>
+        <v>5.05791044235229</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538347244263</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>5.10670137405396</v>
+        <v>5.1067008972168</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043836593628</v>
+        <v>5.09043788909912</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164695739746</v>
+        <v>5.04164791107178</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G162" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G163" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>4.94406700134277</v>
+        <v>4.94406795501709</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G167" t="n">
-        <v>4.89527702331543</v>
+        <v>4.89527750015259</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.94406700134277</v>
+        <v>4.94406795501709</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.89527702331543</v>
+        <v>4.89527750015259</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>4.91154003143311</v>
+        <v>4.91154050827026</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G175" t="n">
-        <v>4.83022403717041</v>
+        <v>4.83022356033325</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>5.25307130813599</v>
+        <v>5.25307178497314</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G178" t="n">
-        <v>5.23680830001831</v>
+        <v>5.23680877685547</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>5.3831787109375</v>
+        <v>5.38317823410034</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922739028931</v>
+        <v>5.13922834396362</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538347244263</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368719100952</v>
+        <v>5.45368814468384</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>5.38718032836914</v>
+        <v>5.38717937469482</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368719100952</v>
+        <v>5.45368814468384</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G217" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>5.60333108901978</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>5.73634910583496</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G222" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>5.75297546386719</v>
+        <v>5.7529764175415</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>5.9026198387146</v>
+        <v>5.90261936187744</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G228" t="n">
-        <v>5.88599300384521</v>
+        <v>5.88599252700806</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>5.9026198387146</v>
+        <v>5.90261936187744</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>5.9026198387146</v>
+        <v>5.90261936187744</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>5.85273838043213</v>
+        <v>5.85273885726929</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G244" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G245" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G247" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G252" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682279586792</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682279586792</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G255" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G258" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>5.60333108901978</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G267" t="n">
-        <v>5.60333108901978</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>5.73634910583496</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>5.73634910583496</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>5.75297546386719</v>
+        <v>5.7529764175415</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>5.73634910583496</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>5.73634910583496</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G283" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G290" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682279586792</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G294" t="n">
-        <v>5.60333108901978</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682279586792</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>5.43706035614014</v>
+        <v>5.43706083297729</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G302" t="n">
-        <v>5.38718032836914</v>
+        <v>5.38717937469482</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>5.38718032836914</v>
+        <v>5.38717937469482</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>5.38718032836914</v>
+        <v>5.38717937469482</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G307" t="n">
-        <v>5.38718032836914</v>
+        <v>5.38717937469482</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.15439939498901</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>5.1211462020874</v>
+        <v>5.12114572525024</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G319" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G327" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G349" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G350" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G351" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G352" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463838577271</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>5.15439939498901</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463838577271</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463838577271</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463838577271</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>5.07126522064209</v>
+        <v>5.07126474380493</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G364" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G369" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G381" t="n">
-        <v>5.1211462020874</v>
+        <v>5.12114572525024</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G382" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G391" t="n">
-        <v>5.15439939498901</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.15439939498901</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G394" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G395" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G396" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G397" t="n">
-        <v>5.08789253234863</v>
+        <v>5.08789157867432</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G398" t="n">
-        <v>5.08789253234863</v>
+        <v>5.08789157867432</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97150182723999</v>
+        <v>4.97150230407715</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>4.82185840606689</v>
+        <v>4.82185888290405</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>4.67221403121948</v>
+        <v>4.6722149848938</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G410" t="n">
-        <v>4.78860425949097</v>
+        <v>4.78860378265381</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>4.80523109436035</v>
+        <v>4.80523157119751</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>4.4394359588623</v>
+        <v>4.43943548202515</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>4.47268867492676</v>
+        <v>4.47268962860107</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>4.35629892349243</v>
+        <v>4.35629940032959</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G424" t="n">
-        <v>4.80523109436035</v>
+        <v>4.80523157119751</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>4.67221403121948</v>
+        <v>4.6722149848938</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>4.52257061004639</v>
+        <v>4.52257013320923</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>4.78860425949097</v>
+        <v>4.78860378265381</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G439" t="n">
-        <v>4.75535011291504</v>
+        <v>4.75534963607788</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G440" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G449" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G458" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>5.06304168701172</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>5.06304168701172</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G475" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G478" t="n">
-        <v>4.58571720123291</v>
+        <v>4.58571767807007</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G479" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G484" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>4.61981201171875</v>
+        <v>4.61981248855591</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G488" t="n">
-        <v>4.43229150772095</v>
+        <v>4.43229198455811</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G489" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>4.58571720123291</v>
+        <v>4.58571767807007</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G491" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G492" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G493" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G495" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G497" t="n">
-        <v>4.31296062469482</v>
+        <v>4.31296110153198</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G498" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524410247803</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G499" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524410247803</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G500" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524410247803</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G503" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G504" t="n">
-        <v>4.58571720123291</v>
+        <v>4.58571767807007</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G506" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G513" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G514" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G515" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.89256811141968</v>
+        <v>4.89256858825684</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.89256811141968</v>
+        <v>4.89256858825684</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008813858032</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G539" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G543" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G548" t="n">
-        <v>4.58571720123291</v>
+        <v>4.58571767807007</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>4.36410284042358</v>
+        <v>4.36410331726074</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G554" t="n">
-        <v>4.44933938980103</v>
+        <v>4.44933891296387</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G558" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G564" t="n">
-        <v>4.43229150772095</v>
+        <v>4.43229198455811</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G565" t="n">
-        <v>4.43229150772095</v>
+        <v>4.43229198455811</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G566" t="n">
-        <v>4.43229150772095</v>
+        <v>4.43229198455811</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G567" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G568" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G569" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G570" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G571" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G572" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.56867074966431</v>
+        <v>4.56867027282715</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G577" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G578" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G584" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G586" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G588" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G598" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G599" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G604" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G607" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G608" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G609" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G616" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G617" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G620" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G621" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G624" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G630" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G631" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G635" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>5.25056123733521</v>
+        <v>5.25056076049805</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>5.16532468795776</v>
+        <v>5.16532516479492</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008813858032</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>5.06304168701172</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>5.06304168701172</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G685" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G695" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.986328125</v>
+        <v>4.98632860183716</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.986328125</v>
+        <v>4.98632860183716</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G699" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G708" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.75</v>
       </c>
       <c r="G717" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.75</v>
       </c>
       <c r="G718" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.75</v>
       </c>
       <c r="G719" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.75</v>
       </c>
       <c r="G720" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.75</v>
       </c>
       <c r="G721" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.75</v>
       </c>
       <c r="G725" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>5.75</v>
       </c>
       <c r="G726" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.75</v>
       </c>
       <c r="G727" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G728" t="n">
-        <v>4.93783235549927</v>
+        <v>4.93783187866211</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.93783235549927</v>
+        <v>4.93783187866211</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G770" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.25</v>
       </c>
       <c r="G799" t="n">
-        <v>4.62921810150146</v>
+        <v>4.62921762466431</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>4.39114332199097</v>
+        <v>4.39114379882812</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G809" t="n">
-        <v>4.39114332199097</v>
+        <v>4.39114379882812</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G822" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>4.02080583572388</v>
+        <v>4.02080631256104</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>4.02080583572388</v>
+        <v>4.02080631256104</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G832" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G846" t="n">
-        <v>4.25006246566772</v>
+        <v>4.25006294250488</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.09134674072266</v>
+        <v>4.0913462638855</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>4.02080583572388</v>
+        <v>4.02080631256104</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G861" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.5</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G868" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.5</v>
       </c>
       <c r="G872" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.5</v>
       </c>
       <c r="G876" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G877" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>3.89736032485962</v>
+        <v>3.8973605632782</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86209058761597</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G883" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>3.72100925445557</v>
+        <v>3.72100901603699</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>3.68573880195618</v>
+        <v>3.68573904037476</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>3.89736032485962</v>
+        <v>3.8973605632782</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G893" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G899" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G901" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G904" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G905" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G906" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86209058761597</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G908" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G910" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86209058761597</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G915" t="n">
-        <v>3.89736032485962</v>
+        <v>3.8973605632782</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G934" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G936" t="n">
-        <v>4.25006246566772</v>
+        <v>4.25006294250488</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G937" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G938" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G940" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G943" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G949" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G955" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>4.33823823928833</v>
+        <v>4.33823776245117</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>5</v>
       </c>
       <c r="G957" t="n">
-        <v>4.40877866744995</v>
+        <v>4.40877819061279</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G967" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>4.45847749710083</v>
+        <v>4.45847797393799</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.88970017433167</v>
+        <v>3.88970065116882</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.88970017433167</v>
+        <v>3.88970065116882</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1091" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1133" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.45847749710083</v>
+        <v>4.45847797393799</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -40984,6 +40984,32 @@
         <v>6.44999980926514</v>
       </c>
       <c r="H1562" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1563" t="n">
+        <v>33763</v>
+      </c>
+      <c r="C1563" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="D1563" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="E1563" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="F1563" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="G1563" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="H1563" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -551,7 +551,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G49" t="n">
-        <v>4.05771255493164</v>
+        <v>4.05771350860596</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.98452830314636</v>
+        <v>3.9845278263092</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200133323669</v>
+        <v>3.95200085639954</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321111679077</v>
+        <v>3.90321135520935</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321111679077</v>
+        <v>3.90321135520935</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442113876343</v>
+        <v>3.85442066192627</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.82189416885376</v>
+        <v>3.82189345359802</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>3.82189416885376</v>
+        <v>3.82189345359802</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991874694824</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>3.71618270874023</v>
+        <v>3.71618223190308</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552375793457</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.6429967880249</v>
+        <v>3.64299726486206</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926051139832</v>
+        <v>3.65926003456116</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991874694824</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926051139832</v>
+        <v>3.65926003456116</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552375793457</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69178748130798</v>
+        <v>3.69178676605225</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.77310371398926</v>
+        <v>3.773104429245</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991874694824</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552375793457</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.42363882064819</v>
+        <v>4.42363929748535</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.42363882064819</v>
+        <v>4.42363929748535</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>4.39111232757568</v>
+        <v>4.39111280441284</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.39111232757568</v>
+        <v>4.39111280441284</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.32605886459351</v>
+        <v>4.32605934143066</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.4724292755127</v>
+        <v>4.47242879867554</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495624542236</v>
+        <v>4.50495576858521</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495624542236</v>
+        <v>4.50495576858521</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>4.43990325927734</v>
+        <v>4.43990278244019</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G112" t="n">
-        <v>4.32605886459351</v>
+        <v>4.32605934143066</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G114" t="n">
-        <v>4.35858583450317</v>
+        <v>4.35858535766602</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G119" t="n">
-        <v>4.35858583450317</v>
+        <v>4.35858535766602</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.39111232757568</v>
+        <v>4.39111280441284</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G130" t="n">
-        <v>4.61880016326904</v>
+        <v>4.61879968643188</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>4.76517057418823</v>
+        <v>4.76517105102539</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791044235229</v>
+        <v>5.05791091918945</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801784515381</v>
+        <v>5.18801832199097</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164791107178</v>
+        <v>5.04164743423462</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>4.87901401519775</v>
+        <v>4.87901306152344</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791044235229</v>
+        <v>5.05791091918945</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G152" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538347244263</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>5.1067008972168</v>
+        <v>5.10670137405396</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>4.97659349441528</v>
+        <v>4.97659397125244</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164791107178</v>
+        <v>5.04164743423462</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>4.94406795501709</v>
+        <v>4.94406700134277</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G165" t="n">
-        <v>4.9278039932251</v>
+        <v>4.92780447006226</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G168" t="n">
-        <v>4.9278039932251</v>
+        <v>4.92780447006226</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.94406795501709</v>
+        <v>4.94406700134277</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>4.87901401519775</v>
+        <v>4.87901306152344</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G178" t="n">
-        <v>5.23680877685547</v>
+        <v>5.23680830001831</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.5</v>
       </c>
       <c r="G185" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.5</v>
       </c>
       <c r="G186" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>6.5</v>
       </c>
       <c r="G187" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.5</v>
       </c>
       <c r="G188" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922834396362</v>
+        <v>5.13922786712646</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538347244263</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G194" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>5.00475645065308</v>
+        <v>5.00475692749023</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>5.35392570495605</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.35392570495605</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368719100952</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368719100952</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G217" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66984033584595</v>
+        <v>5.66984081268311</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>5.7529764175415</v>
+        <v>5.75297546386719</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7</v>
       </c>
       <c r="G225" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G229" t="n">
-        <v>5.9691276550293</v>
+        <v>5.96912813186646</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G231" t="n">
-        <v>5.80285692214966</v>
+        <v>5.80285739898682</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>5.85273885726929</v>
+        <v>5.85273838043213</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>7</v>
       </c>
       <c r="G235" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7</v>
       </c>
       <c r="G236" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>5.83611154556274</v>
+        <v>5.83611106872559</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>5.80285692214966</v>
+        <v>5.80285739898682</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7</v>
       </c>
       <c r="G240" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7</v>
       </c>
       <c r="G241" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G244" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66984033584595</v>
+        <v>5.66984081268311</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G252" t="n">
-        <v>5.53682279586792</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>5.53682279586792</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G255" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G265" t="n">
-        <v>5.61995935440063</v>
+        <v>5.61995887756348</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G267" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G272" t="n">
-        <v>5.52019643783569</v>
+        <v>5.52019596099854</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>5.7529764175415</v>
+        <v>5.75297546386719</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G290" t="n">
-        <v>5.53682279586792</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G294" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>5.53682279586792</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>5.35392570495605</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G319" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G324" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G327" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G333" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G334" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G335" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G336" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G338" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777351379395</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G349" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G353" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777351379395</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463838577271</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463838577271</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463838577271</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463838577271</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G364" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G365" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777351379395</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G368" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777351379395</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G375" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G391" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G394" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G395" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G396" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G397" t="n">
-        <v>5.08789157867432</v>
+        <v>5.08789205551147</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G398" t="n">
-        <v>5.08789157867432</v>
+        <v>5.08789205551147</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>4.82185888290405</v>
+        <v>4.82185840606689</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>4.88836669921875</v>
+        <v>4.88836717605591</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>4.6722149848938</v>
+        <v>4.67221450805664</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G409" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884086608887</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G410" t="n">
-        <v>4.78860378265381</v>
+        <v>4.78860425949097</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>4.35629940032959</v>
+        <v>4.35629892349243</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G420" t="n">
-        <v>4.45606231689453</v>
+        <v>4.45606184005737</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>4.6722149848938</v>
+        <v>4.67221450805664</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>4.60570621490479</v>
+        <v>4.60570573806763</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G429" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884086608887</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>5.5</v>
       </c>
       <c r="G431" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>5.5</v>
       </c>
       <c r="G433" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5.5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884086608887</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>4.78860378265381</v>
+        <v>4.78860425949097</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5.5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G449" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G458" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G460" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G461" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G462" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G463" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G475" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G479" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G484" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>4.61981248855591</v>
+        <v>4.61981201171875</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G495" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G498" t="n">
-        <v>4.41524410247803</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G499" t="n">
-        <v>4.41524410247803</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G500" t="n">
-        <v>4.41524410247803</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G501" t="n">
-        <v>4.46638631820679</v>
+        <v>4.46638584136963</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G502" t="n">
-        <v>4.46638631820679</v>
+        <v>4.46638584136963</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G506" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G513" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G514" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G515" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G521" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.97780513763428</v>
+        <v>4.97780466079712</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G539" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G543" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.48343420028687</v>
+        <v>4.48343467712402</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>4.55162382125854</v>
+        <v>4.55162334442139</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>4.48343420028687</v>
+        <v>4.48343467712402</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.55162382125854</v>
+        <v>4.55162334442139</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>4.36410331726074</v>
+        <v>4.36410284042358</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G559" t="n">
-        <v>4.53457593917847</v>
+        <v>4.53457546234131</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G563" t="n">
-        <v>4.46638631820679</v>
+        <v>4.46638584136963</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G577" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G578" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G582" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G584" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G586" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G588" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G598" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G599" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G600" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G604" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G607" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G608" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G609" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G616" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G617" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G620" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G621" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G624" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G630" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G631" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G635" t="n">
-        <v>4.84142684936523</v>
+        <v>4.84142637252808</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G644" t="n">
-        <v>5.35284471511841</v>
+        <v>5.35284519195557</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.1994194984436</v>
+        <v>5.19941997528076</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G647" t="n">
-        <v>5.1994194984436</v>
+        <v>5.19941997528076</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>5.1994194984436</v>
+        <v>5.19941997528076</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>5.13123035430908</v>
+        <v>5.13123083114624</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>5.16532516479492</v>
+        <v>5.16532468795776</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G662" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>5.13123035430908</v>
+        <v>5.13123083114624</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G685" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G695" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.98632860183716</v>
+        <v>4.986328125</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.98632860183716</v>
+        <v>4.986328125</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G699" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -41010,6 +41010,32 @@
         <v>6.15000009536743</v>
       </c>
       <c r="H1563" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1564" t="n">
+        <v>17127</v>
+      </c>
+      <c r="C1564" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D1564" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="E1564" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F1564" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="G1564" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="H1564" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -603,7 +603,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G9" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0495810508728</v>
+        <v>4.04958152770996</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G15" t="n">
-        <v>4.11463451385498</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>4.11463451385498</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>4.11463451385498</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.08210849761963</v>
+        <v>4.08210802078247</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.27726936340332</v>
+        <v>4.27726984024048</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>4.27726936340332</v>
+        <v>4.27726984024048</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>4.26100492477417</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>4.26100492477417</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.11463451385498</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G38" t="n">
-        <v>4.08210849761963</v>
+        <v>4.08210802078247</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G43" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G44" t="n">
-        <v>4.29353284835815</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G45" t="n">
-        <v>4.29353284835815</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G47" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.9845278263092</v>
+        <v>3.98452806472778</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200157165527</v>
+        <v>3.95200133323669</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639560699463</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639560699463</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94386911392212</v>
+        <v>3.9438693523407</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321135520935</v>
+        <v>3.90321087837219</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321135520935</v>
+        <v>3.90321087837219</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442042350769</v>
+        <v>3.85442090034485</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.8869481086731</v>
+        <v>3.88694834709167</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057722091675</v>
+        <v>3.74057674407959</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057722091675</v>
+        <v>3.74057674407959</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.6999192237854</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552375793457</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.64299750328064</v>
+        <v>3.64299702644348</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926003456116</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.6999192237854</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926003456116</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552375793457</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69178700447083</v>
+        <v>3.69178676605225</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.773104429245</v>
+        <v>3.77310419082642</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.6999192237854</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552375793457</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>4.11463451385498</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G93" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.42363929748535</v>
+        <v>4.42363882064819</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.45616674423218</v>
+        <v>4.45616626739502</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.42363929748535</v>
+        <v>4.42363882064819</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111232757568</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111232757568</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869323730469</v>
+        <v>4.48869228363037</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869323730469</v>
+        <v>4.48869228363037</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.47242975234985</v>
+        <v>4.4724292755127</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>4.52121925354004</v>
+        <v>4.5212197303772</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>4.43990230560303</v>
+        <v>4.43990278244019</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>4.29353284835815</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G115" t="n">
-        <v>4.29353284835815</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29353284835815</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>4.34232234954834</v>
+        <v>4.3423228263855</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111232757568</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G130" t="n">
-        <v>4.61879968643188</v>
+        <v>4.61880016326904</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>4.76517009735107</v>
+        <v>4.76516962051392</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>4.91154050827026</v>
+        <v>4.91154098510742</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791044235229</v>
+        <v>5.05791091918945</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801784515381</v>
+        <v>5.18801832199097</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>4.87901401519775</v>
+        <v>4.8790135383606</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791044235229</v>
+        <v>5.05791091918945</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G152" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538394927979</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>5.10670137405396</v>
+        <v>5.1067008972168</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>4.97659397125244</v>
+        <v>4.9765944480896</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>4.94406747817993</v>
+        <v>4.94406652450562</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G165" t="n">
-        <v>4.92780351638794</v>
+        <v>4.9278039932251</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G167" t="n">
-        <v>4.89527750015259</v>
+        <v>4.89527797698975</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G168" t="n">
-        <v>4.92780351638794</v>
+        <v>4.9278039932251</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.94406747817993</v>
+        <v>4.94406652450562</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.89527750015259</v>
+        <v>4.89527797698975</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>4.91154050827026</v>
+        <v>4.91154098510742</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>4.87901401519775</v>
+        <v>4.8790135383606</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G175" t="n">
-        <v>4.83022356033325</v>
+        <v>4.83022403717041</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>5.25307130813599</v>
+        <v>5.25307178497314</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G178" t="n">
-        <v>5.23680877685547</v>
+        <v>5.23680830001831</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.36691570281982</v>
+        <v>5.36691522598267</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.5</v>
       </c>
       <c r="G185" t="n">
-        <v>5.28559875488281</v>
+        <v>5.2855978012085</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.5</v>
       </c>
       <c r="G186" t="n">
-        <v>5.28559875488281</v>
+        <v>5.2855978012085</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>6.5</v>
       </c>
       <c r="G187" t="n">
-        <v>5.28559875488281</v>
+        <v>5.2855978012085</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.5</v>
       </c>
       <c r="G188" t="n">
-        <v>5.28559875488281</v>
+        <v>5.2855978012085</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922834396362</v>
+        <v>5.13922786712646</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538394927979</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G191" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G192" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G194" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>5.00475597381592</v>
+        <v>5.00475692749023</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.5</v>
       </c>
       <c r="G210" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380620956421</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>6.5</v>
       </c>
       <c r="G211" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380620956421</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368766784668</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.5</v>
       </c>
       <c r="G214" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380620956421</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368766784668</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634910583496</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G228" t="n">
-        <v>5.8859920501709</v>
+        <v>5.88599252700806</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>5.93587398529053</v>
+        <v>5.93587350845337</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>5.85273838043213</v>
+        <v>5.85273885726929</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G250" t="n">
-        <v>5.58670473098755</v>
+        <v>5.58670425415039</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G254" t="n">
-        <v>5.58670473098755</v>
+        <v>5.58670425415039</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G265" t="n">
-        <v>5.61995887756348</v>
+        <v>5.61995935440063</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G267" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G269" t="n">
-        <v>5.50356960296631</v>
+        <v>5.50356912612915</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>5.57007694244385</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.57007694244385</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634910583496</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634910583496</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634910583496</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634910583496</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>5.57007694244385</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>5.50356960296631</v>
+        <v>5.50356912612915</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>5.57007694244385</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G294" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>6.5</v>
       </c>
       <c r="G301" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380620956421</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>5.27079010009766</v>
+        <v>5.27079057693481</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090816497803</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G319" t="n">
-        <v>5.27079010009766</v>
+        <v>5.27079057693481</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G323" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090816497803</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G324" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G325" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090816497803</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G327" t="n">
-        <v>5.27079010009766</v>
+        <v>5.27079057693481</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.27079010009766</v>
+        <v>5.27079057693481</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G332" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090816497803</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G334" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G335" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G336" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G339" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090816497803</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G340" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090816497803</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.27079010009766</v>
+        <v>5.27079057693481</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.27079010009766</v>
+        <v>5.27079057693481</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G349" t="n">
-        <v>5.27079010009766</v>
+        <v>5.27079057693481</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>5.07126474380493</v>
+        <v>5.07126522064209</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090816497803</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090816497803</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G364" t="n">
-        <v>5.27079010009766</v>
+        <v>5.27079057693481</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G386" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090816497803</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G387" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090816497803</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090816497803</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G394" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G395" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G396" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G397" t="n">
-        <v>5.08789157867432</v>
+        <v>5.08789205551147</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G398" t="n">
-        <v>5.08789157867432</v>
+        <v>5.08789205551147</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97150182723999</v>
+        <v>4.97150230407715</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>4.48931694030762</v>
+        <v>4.48931646347046</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G409" t="n">
-        <v>4.68884181976318</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G414" t="n">
-        <v>4.58907890319824</v>
+        <v>4.58907842636108</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>4.43943500518799</v>
+        <v>4.43943548202515</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>4.48931694030762</v>
+        <v>4.48931646347046</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>4.47268915176392</v>
+        <v>4.47268962860107</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>4.60570526123047</v>
+        <v>4.60570573806763</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>4.55582475662231</v>
+        <v>4.55582523345947</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G429" t="n">
-        <v>4.68884181976318</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>4.68884181976318</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G439" t="n">
-        <v>4.75535011291504</v>
+        <v>4.75534963607788</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G440" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G449" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G457" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G458" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>5.0630407333374</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>5.0630407333374</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>6</v>
       </c>
       <c r="G472" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>4.61981201171875</v>
+        <v>4.61981248855591</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G503" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G513" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.89256858825684</v>
+        <v>4.89256811141968</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.89256858825684</v>
+        <v>4.89256811141968</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G524" t="n">
-        <v>4.99485206604004</v>
+        <v>4.99485158920288</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G532" t="n">
-        <v>4.92666339874268</v>
+        <v>4.92666292190552</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.97780466079712</v>
+        <v>4.97780513763428</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G539" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G543" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.5</v>
       </c>
       <c r="G547" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>4.55162286758423</v>
+        <v>4.55162334442139</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.55162286758423</v>
+        <v>4.55162334442139</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>4.36410236358643</v>
+        <v>4.36410284042358</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G567" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G568" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G569" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G570" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G571" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G572" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G577" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G578" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G584" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G586" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G588" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.5</v>
       </c>
       <c r="G595" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G598" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G599" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G604" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G605" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G606" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G607" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G608" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G609" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>5.5</v>
       </c>
       <c r="G612" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G620" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G630" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G631" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G635" t="n">
-        <v>4.84142637252808</v>
+        <v>4.84142684936523</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G644" t="n">
-        <v>5.35284519195557</v>
+        <v>5.35284471511841</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G645" t="n">
-        <v>5.30170345306396</v>
+        <v>5.30170297622681</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6</v>
       </c>
       <c r="G648" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>5.16532468795776</v>
+        <v>5.16532516479492</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6</v>
       </c>
       <c r="G654" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>6</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6</v>
       </c>
       <c r="G658" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6</v>
       </c>
       <c r="G660" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>5.0630407333374</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>5.0630407333374</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6</v>
       </c>
       <c r="G679" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>6</v>
       </c>
       <c r="G681" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6</v>
       </c>
       <c r="G684" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6</v>
       </c>
       <c r="G687" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6</v>
       </c>
       <c r="G691" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6</v>
       </c>
       <c r="G692" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6</v>
       </c>
       <c r="G693" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.986328125</v>
+        <v>4.98632860183716</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.986328125</v>
+        <v>4.98632860183716</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>6</v>
       </c>
       <c r="G704" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G707" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G708" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G715" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>5.75</v>
       </c>
       <c r="G717" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.75</v>
       </c>
       <c r="G718" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>5.75</v>
       </c>
       <c r="G719" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>5.75</v>
       </c>
       <c r="G720" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.75</v>
       </c>
       <c r="G721" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G724" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.75</v>
       </c>
       <c r="G725" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>5.75</v>
       </c>
       <c r="G726" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>5.75</v>
       </c>
       <c r="G727" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G770" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G793" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>4.98192024230957</v>
+        <v>4.98191976547241</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>4.39114332199097</v>
+        <v>4.39114379882812</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G809" t="n">
-        <v>4.39114332199097</v>
+        <v>4.39114379882812</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G822" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G835" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G847" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G848" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G849" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.09134674072266</v>
+        <v>4.0913462638855</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.00317049026489</v>
+        <v>4.00317096710205</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G854" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>4.00317049026489</v>
+        <v>4.00317096710205</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G860" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G861" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G868" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G877" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>3.72100877761841</v>
+        <v>3.72100901603699</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>3.68573880195618</v>
+        <v>3.68573904037476</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G886" t="n">
-        <v>3.73864412307739</v>
+        <v>3.73864436149597</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G893" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73864412307739</v>
+        <v>3.73864436149597</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G919" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G924" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>4.07371091842651</v>
+        <v>4.07371139526367</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G937" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G944" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G949" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G955" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>4.33823823928833</v>
+        <v>4.33823776245117</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -41088,6 +41088,32 @@
         <v>6.15000009536743</v>
       </c>
       <c r="H1566" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1567" t="n">
+        <v>3273</v>
+      </c>
+      <c r="C1567" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="D1567" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="E1567" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="F1567" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G1567" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="H1567" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -36475,8 +36475,31 @@
       <c r="E1570" t="n">
         <v>6</v>
       </c>
-      <c r="F1570"/>
+      <c r="F1570" t="n">
+        <v>6</v>
+      </c>
       <c r="G1570" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1571" t="n">
+        <v>38153</v>
+      </c>
+      <c r="C1571" t="n">
+        <v>6.30000019073486</v>
+      </c>
+      <c r="D1571" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1571" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="F1571"/>
+      <c r="G1571" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -36498,8 +36498,31 @@
       <c r="E1571" t="n">
         <v>6.09999990463257</v>
       </c>
-      <c r="F1571"/>
+      <c r="F1571" t="n">
+        <v>6.19999980926514</v>
+      </c>
       <c r="G1571" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1572" t="n">
+        <v>4170</v>
+      </c>
+      <c r="C1572" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="D1572" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="E1572" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F1572"/>
+      <c r="G1572" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -36521,8 +36521,31 @@
       <c r="E1572" t="n">
         <v>6.19999980926514</v>
       </c>
-      <c r="F1572"/>
+      <c r="F1572" t="n">
+        <v>6.19999980926514</v>
+      </c>
       <c r="G1572" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1573" t="n">
+        <v>7217</v>
+      </c>
+      <c r="C1573" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D1573" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="E1573" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F1573"/>
+      <c r="G1573" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -36544,8 +36544,31 @@
       <c r="E1573" t="n">
         <v>6.05000019073486</v>
       </c>
-      <c r="F1573"/>
+      <c r="F1573" t="n">
+        <v>6.09999990463257</v>
+      </c>
       <c r="G1573" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1574" t="n">
+        <v>10329</v>
+      </c>
+      <c r="C1574" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="D1574" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="E1574" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="F1574"/>
+      <c r="G1574" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -36574,6 +36574,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1575">
+      <c r="A1575" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1575" t="n">
+        <v>3959</v>
+      </c>
+      <c r="C1575" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D1575" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="F1575" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G1575" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -551,7 +551,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G9" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>4.04958200454712</v>
+        <v>4.04958152770996</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G36" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G43" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G44" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G45" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G47" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.98452854156494</v>
+        <v>3.98452830314636</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200181007385</v>
+        <v>3.95200157165527</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639608383179</v>
+        <v>3.97639584541321</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639608383179</v>
+        <v>3.97639584541321</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.9438693523407</v>
+        <v>3.94387006759644</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321135520935</v>
+        <v>3.90321087837219</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321135520935</v>
+        <v>3.90321087837219</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442066192627</v>
+        <v>3.85442042350769</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.88694787025452</v>
+        <v>3.8869481086731</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057722091675</v>
+        <v>3.74057698249817</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057722091675</v>
+        <v>3.74057698249817</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>3.71618247032166</v>
+        <v>3.7161819934845</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.64299654960632</v>
+        <v>3.64299726486206</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926027297974</v>
+        <v>3.65926003456116</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926027297974</v>
+        <v>3.65926003456116</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G85" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G87" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G93" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G100" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G101" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869228363037</v>
+        <v>4.48869323730469</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869228363037</v>
+        <v>4.48869323730469</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495624542236</v>
+        <v>4.50495576858521</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495624542236</v>
+        <v>4.50495576858521</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>4.52121877670288</v>
+        <v>4.52121925354004</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.55374574661255</v>
+        <v>4.55374622344971</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G115" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>4.3423228263855</v>
+        <v>4.34232187271118</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.55374574661255</v>
+        <v>4.55374622344971</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G130" t="n">
-        <v>4.61879920959473</v>
+        <v>4.61879968643188</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>4.91154050827026</v>
+        <v>4.91154003143311</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>5.07417440414429</v>
+        <v>5.07417392730713</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>5.07417440414429</v>
+        <v>5.07417392730713</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801832199097</v>
+        <v>5.18801736831665</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164743423462</v>
+        <v>5.04164791107178</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>5.07417440414429</v>
+        <v>5.07417392730713</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538394927979</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>4.9765944480896</v>
+        <v>4.97659397125244</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164743423462</v>
+        <v>5.04164791107178</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G162" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G163" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>4.91154050827026</v>
+        <v>4.91154003143311</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G175" t="n">
-        <v>4.83022451400757</v>
+        <v>4.83022356033325</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>5.2530722618103</v>
+        <v>5.25307130813599</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G178" t="n">
-        <v>5.23680782318115</v>
+        <v>5.23680830001831</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>5.38317823410034</v>
+        <v>5.3831787109375</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.36691474914551</v>
+        <v>5.36691570281982</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.5</v>
       </c>
       <c r="G185" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.5</v>
       </c>
       <c r="G186" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>6.5</v>
       </c>
       <c r="G187" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.5</v>
       </c>
       <c r="G188" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922786712646</v>
+        <v>5.13922834396362</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538394927979</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>5.00475645065308</v>
+        <v>5.00475597381592</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067203521729</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067203521729</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.5</v>
       </c>
       <c r="G210" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>6.5</v>
       </c>
       <c r="G211" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368766784668</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G213" t="n">
-        <v>5.38717937469482</v>
+        <v>5.38717985153198</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.5</v>
       </c>
       <c r="G214" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694276809692</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368766784668</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G217" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694276809692</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694276809692</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>5.73634910583496</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66983985900879</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>5.7529764175415</v>
+        <v>5.75297594070435</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>5.93587398529053</v>
+        <v>5.93587446212769</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G231" t="n">
-        <v>5.80285739898682</v>
+        <v>5.80285692214966</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>5.8361120223999</v>
+        <v>5.83611154556274</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>5.80285739898682</v>
+        <v>5.80285692214966</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G244" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309400558472</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G245" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G247" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66983985900879</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G258" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309400558472</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694276809692</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G269" t="n">
-        <v>5.50356912612915</v>
+        <v>5.50356960296631</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>5.73634910583496</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>5.73634910583496</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>5.7529764175415</v>
+        <v>5.75297594070435</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>5.73634910583496</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>5.73634910583496</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G283" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309400558472</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>5.50356912612915</v>
+        <v>5.50356960296631</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694276809692</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694276809692</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694276809692</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694276809692</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>5.43706083297729</v>
+        <v>5.43706130981445</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694276809692</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>6.5</v>
       </c>
       <c r="G301" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G302" t="n">
-        <v>5.38717937469482</v>
+        <v>5.38717985153198</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067203521729</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067203521729</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G305" t="n">
-        <v>5.38717937469482</v>
+        <v>5.38717985153198</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G306" t="n">
-        <v>5.38717937469482</v>
+        <v>5.38717985153198</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G307" t="n">
-        <v>5.38717937469482</v>
+        <v>5.38717985153198</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067203521729</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067203521729</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G323" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G325" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067203521729</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G332" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G333" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G338" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G339" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G340" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G353" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>5.07126522064209</v>
+        <v>5.07126474380493</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G365" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G368" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067203521729</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G375" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G386" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G387" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G391" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G394" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G395" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G396" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G397" t="n">
-        <v>5.08789205551147</v>
+        <v>5.08789157867432</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G398" t="n">
-        <v>5.08789205551147</v>
+        <v>5.08789157867432</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>4.82185792922974</v>
+        <v>4.82185888290405</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G401" t="n">
-        <v>4.92162084579468</v>
+        <v>4.92162132263184</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>4.83848571777344</v>
+        <v>4.83848524093628</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>4.88836669921875</v>
+        <v>4.88836717605591</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G405" t="n">
-        <v>4.83848571777344</v>
+        <v>4.83848524093628</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>4.4893159866333</v>
+        <v>4.48931646347046</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G410" t="n">
-        <v>4.78860378265381</v>
+        <v>4.78860425949097</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G414" t="n">
-        <v>4.58907842636108</v>
+        <v>4.58907890319824</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>4.43943548202515</v>
+        <v>4.43943452835083</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>4.4893159866333</v>
+        <v>4.48931646347046</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>4.47268962860107</v>
+        <v>4.47268915176392</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>4.35629892349243</v>
+        <v>4.35629940032959</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>4.60570621490479</v>
+        <v>4.60570573806763</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>4.78860378265381</v>
+        <v>4.78860425949097</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G440" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G449" t="n">
-        <v>4.72209501266479</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G460" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G461" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G462" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>6</v>
       </c>
       <c r="G472" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G474" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G479" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G484" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>4.61981248855591</v>
+        <v>4.61981201171875</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G488" t="n">
-        <v>4.43229150772095</v>
+        <v>4.43229198455811</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G495" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G498" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G499" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G500" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G501" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G502" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.89256811141968</v>
+        <v>4.89256858825684</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.89256811141968</v>
+        <v>4.89256858825684</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G522" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008813858032</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90961599349976</v>
+        <v>4.90961647033691</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>4.87552118301392</v>
+        <v>4.87552070617676</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.48343467712402</v>
+        <v>4.48343420028687</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>4.48343467712402</v>
+        <v>4.48343420028687</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>4.36410284042358</v>
+        <v>4.36410236358643</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G559" t="n">
-        <v>4.53457546234131</v>
+        <v>4.53457593917847</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G563" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G564" t="n">
-        <v>4.43229150772095</v>
+        <v>4.43229198455811</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G565" t="n">
-        <v>4.43229150772095</v>
+        <v>4.43229198455811</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G566" t="n">
-        <v>4.43229150772095</v>
+        <v>4.43229198455811</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.80733203887939</v>
+        <v>4.80733251571655</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G582" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G600" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>4.80733203887939</v>
+        <v>4.80733251571655</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G636" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G637" t="n">
-        <v>5.01189947128296</v>
+        <v>5.01189994812012</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G638" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G640" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>5.01189947128296</v>
+        <v>5.01189994812012</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>5.25056076049805</v>
+        <v>5.25056171417236</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G644" t="n">
-        <v>5.35284471511841</v>
+        <v>5.35284566879272</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G647" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6</v>
       </c>
       <c r="G648" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>5.21646642684937</v>
+        <v>5.21646690368652</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G650" t="n">
-        <v>5.21646642684937</v>
+        <v>5.21646690368652</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>5.16532516479492</v>
+        <v>5.16532468795776</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6</v>
       </c>
       <c r="G654" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>5.21646642684937</v>
+        <v>5.21646690368652</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>6</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>6</v>
       </c>
       <c r="G658" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>6</v>
       </c>
       <c r="G660" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008813858032</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G672" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G673" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>6</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6</v>
       </c>
       <c r="G679" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>6</v>
       </c>
       <c r="G681" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>6</v>
       </c>
       <c r="G684" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>6</v>
       </c>
       <c r="G687" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>6</v>
       </c>
       <c r="G691" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>6</v>
       </c>
       <c r="G692" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>6</v>
       </c>
       <c r="G693" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>6</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.98632860183716</v>
+        <v>4.986328125</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.98632860183716</v>
+        <v>4.986328125</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>6</v>
       </c>
       <c r="G704" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G728" t="n">
-        <v>4.93783187866211</v>
+        <v>4.93783235549927</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.93783187866211</v>
+        <v>4.93783235549927</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G741" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G755" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G762" t="n">
-        <v>4.5410418510437</v>
+        <v>4.54104232788086</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G765" t="n">
-        <v>4.5410418510437</v>
+        <v>4.54104232788086</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G766" t="n">
-        <v>4.45286703109741</v>
+        <v>4.45286655426025</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G777" t="n">
-        <v>4.5410418510437</v>
+        <v>4.54104232788086</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>4.98192024230957</v>
+        <v>4.98191976547241</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.25</v>
       </c>
       <c r="G799" t="n">
-        <v>4.62921810150146</v>
+        <v>4.62921762466431</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G800" t="n">
-        <v>4.5410418510437</v>
+        <v>4.54104232788086</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G801" t="n">
-        <v>4.5410418510437</v>
+        <v>4.54104232788086</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G821" t="n">
-        <v>4.21479225158691</v>
+        <v>4.21479272842407</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G828" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G835" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G838" t="n">
-        <v>4.21479225158691</v>
+        <v>4.21479272842407</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G839" t="n">
-        <v>4.21479225158691</v>
+        <v>4.21479272842407</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G841" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G844" t="n">
-        <v>4.21479225158691</v>
+        <v>4.21479272842407</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G845" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.0913462638855</v>
+        <v>4.09134674072266</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G859" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G868" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G877" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G878" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G879" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G880" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G883" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>3.68573880195618</v>
+        <v>3.6857385635376</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G886" t="n">
-        <v>3.73864388465881</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G893" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G894" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G895" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G897" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G899" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G901" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73864388465881</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G904" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G912" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G917" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G919" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G921" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G922" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G929" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G934" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G944" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>4.33823776245117</v>
+        <v>4.33823823928833</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G960" t="n">
-        <v>4.5410418510437</v>
+        <v>4.54104232788086</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>4.45286703109741</v>
+        <v>4.45286655426025</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G962" t="n">
-        <v>4.5410418510437</v>
+        <v>4.54104232788086</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G967" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>4.45847749710083</v>
+        <v>4.45847797393799</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.88970017433167</v>
+        <v>3.88970065116882</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.88970017433167</v>
+        <v>3.88970065116882</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1091" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1133" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.45847749710083</v>
+        <v>4.45847797393799</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -41374,6 +41374,32 @@
         <v>6.09999990463257</v>
       </c>
       <c r="H1577" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1578" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C1578" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D1578" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G1578" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="H1578" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -525,7 +525,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G9" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G10" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>4.04958152770996</v>
+        <v>4.0495810508728</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G15" t="n">
-        <v>4.11463499069214</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>4.11463499069214</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>4.11463499069214</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.27726936340332</v>
+        <v>4.27726888656616</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>4.27726936340332</v>
+        <v>4.27726888656616</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>4.26100492477417</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>4.26100492477417</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G27" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>4.09837198257446</v>
+        <v>4.09837245941162</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.11463499069214</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>4.09837198257446</v>
+        <v>4.09837245941162</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G36" t="n">
-        <v>4.09837198257446</v>
+        <v>4.09837245941162</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G41" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.21221494674683</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G43" t="n">
-        <v>4.21221494674683</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G44" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G45" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G47" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G49" t="n">
-        <v>4.05771255493164</v>
+        <v>4.05771350860596</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200157165527</v>
+        <v>3.95200133323669</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94387006759644</v>
+        <v>3.94386982917786</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321087837219</v>
+        <v>3.90321111679077</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321087837219</v>
+        <v>3.90321111679077</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>4.75</v>
       </c>
       <c r="G57" t="n">
-        <v>3.86255264282227</v>
+        <v>3.86255288124084</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>3.7161819934845</v>
+        <v>3.71618247032166</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.64299726486206</v>
+        <v>3.6429967880249</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926003456116</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926003456116</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69178700447083</v>
+        <v>3.69178748130798</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.77310371398926</v>
+        <v>3.77310419082642</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>4.09837198257446</v>
+        <v>4.09837245941162</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G81" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>4.11463499069214</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G88" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G93" t="n">
-        <v>4.21221494674683</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737628936768</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.42363929748535</v>
+        <v>4.42363882064819</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.45616579055786</v>
+        <v>4.45616626739502</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.42363929748535</v>
+        <v>4.42363882064819</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869323730469</v>
+        <v>4.48869276046753</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869323730469</v>
+        <v>4.48869276046753</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.47242975234985</v>
+        <v>4.4724292755127</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G115" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737628936768</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>4.34232187271118</v>
+        <v>4.3423228263855</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.63506317138672</v>
+        <v>4.63506269454956</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.63506317138672</v>
+        <v>4.63506269454956</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.63506317138672</v>
+        <v>4.63506269454956</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.63506317138672</v>
+        <v>4.63506269454956</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.63506317138672</v>
+        <v>4.63506269454956</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>4.76517057418823</v>
+        <v>4.76517009735107</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>4.91154003143311</v>
+        <v>4.91154050827026</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801736831665</v>
+        <v>5.18801784515381</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164791107178</v>
+        <v>5.04164743423462</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>4.87901401519775</v>
+        <v>4.8790135383606</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538394927979</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>5.10670137405396</v>
+        <v>5.10670185089111</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164791107178</v>
+        <v>5.04164743423462</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G162" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G163" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G167" t="n">
-        <v>4.89527750015259</v>
+        <v>4.89527702331543</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.89527750015259</v>
+        <v>4.89527702331543</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>4.91154003143311</v>
+        <v>4.91154050827026</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.96033096313477</v>
+        <v>4.96033048629761</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>4.87901401519775</v>
+        <v>4.8790135383606</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>5.25307130813599</v>
+        <v>5.25307178497314</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>6.5</v>
       </c>
       <c r="G185" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>6.5</v>
       </c>
       <c r="G186" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>6.5</v>
       </c>
       <c r="G187" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>6.5</v>
       </c>
       <c r="G188" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538394927979</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G191" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G192" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>5.00475597381592</v>
+        <v>5.00475692749023</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G201" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067203521729</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G205" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067203521729</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>5.35392570495605</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.35392570495605</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>6.5</v>
       </c>
       <c r="G210" t="n">
-        <v>5.40380716323853</v>
+        <v>5.40380668640137</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>6.5</v>
       </c>
       <c r="G211" t="n">
-        <v>5.40380716323853</v>
+        <v>5.40380668640137</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368766784668</v>
+        <v>5.45368814468384</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>6.5</v>
       </c>
       <c r="G214" t="n">
-        <v>5.40380716323853</v>
+        <v>5.40380668640137</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>5.48694276809692</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368766784668</v>
+        <v>5.45368814468384</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G217" t="n">
-        <v>5.48694276809692</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.48694276809692</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7</v>
       </c>
       <c r="G225" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G228" t="n">
-        <v>5.88599252700806</v>
+        <v>5.88599300384521</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>5.93587446212769</v>
+        <v>5.93587350845337</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G231" t="n">
-        <v>5.80285692214966</v>
+        <v>5.80285739898682</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>5.85273838043213</v>
+        <v>5.85273790359497</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>7</v>
       </c>
       <c r="G235" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7</v>
       </c>
       <c r="G236" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>5.83611154556274</v>
+        <v>5.83611106872559</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>5.80285692214966</v>
+        <v>5.80285739898682</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7</v>
       </c>
       <c r="G240" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7</v>
       </c>
       <c r="G241" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G243" t="n">
-        <v>5.76960325241089</v>
+        <v>5.76960277557373</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G244" t="n">
-        <v>5.70309400558472</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G250" t="n">
-        <v>5.58670425415039</v>
+        <v>5.58670473098755</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G254" t="n">
-        <v>5.58670425415039</v>
+        <v>5.58670473098755</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70309400558472</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G267" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.48694276809692</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G271" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G272" t="n">
-        <v>5.52019643783569</v>
+        <v>5.52019596099854</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>5.70309400558472</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.48694276809692</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G294" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.48694276809692</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>5.48694276809692</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.48694276809692</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>5.43706130981445</v>
+        <v>5.43706035614014</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>5.48694276809692</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>6.5</v>
       </c>
       <c r="G301" t="n">
-        <v>5.40380716323853</v>
+        <v>5.40380668640137</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067203521729</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067203521729</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>5.35392570495605</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067203521729</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>5.12114572525024</v>
+        <v>5.1211462020874</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G319" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067203521729</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G323" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G325" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G327" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067203521729</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>5.33729839324951</v>
+        <v>5.33729887008667</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G332" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G333" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G337" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G339" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G340" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G347" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G349" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>5.07126474380493</v>
+        <v>5.07126426696777</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G364" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G365" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067203521729</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G375" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G381" t="n">
-        <v>5.12114572525024</v>
+        <v>5.1211462020874</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G386" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G387" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G391" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G397" t="n">
-        <v>5.08789157867432</v>
+        <v>5.08789205551147</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G398" t="n">
-        <v>5.08789157867432</v>
+        <v>5.08789205551147</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>4.82185888290405</v>
+        <v>4.82185792922974</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G401" t="n">
-        <v>4.92162132263184</v>
+        <v>4.92162084579468</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>4.90499401092529</v>
+        <v>4.90499448776245</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>4.88836717605591</v>
+        <v>4.88836765289307</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G409" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884181976318</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G410" t="n">
-        <v>4.78860425949097</v>
+        <v>4.78860473632812</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>4.43943452835083</v>
+        <v>4.43943500518799</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>4.55582475662231</v>
+        <v>4.55582523345947</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>4.52257061004639</v>
+        <v>4.52257013320923</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G429" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884181976318</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884181976318</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>4.78860425949097</v>
+        <v>4.78860473632812</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>5.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G524" t="n">
-        <v>4.9948525428772</v>
+        <v>4.99485206604004</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008813858032</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.97780466079712</v>
+        <v>4.97780513763428</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>4.87552070617676</v>
+        <v>4.87552118301392</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.5</v>
       </c>
       <c r="G547" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.56867027282715</v>
+        <v>4.56867074966431</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.5</v>
       </c>
       <c r="G595" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>5.5</v>
       </c>
       <c r="G612" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G636" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G638" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>5.25056171417236</v>
+        <v>5.25056123733521</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>5.21646690368652</v>
+        <v>5.21646642684937</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G650" t="n">
-        <v>5.21646690368652</v>
+        <v>5.21646642684937</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>5.21646690368652</v>
+        <v>5.21646642684937</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008813858032</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G671" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G672" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G673" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -41400,6 +41400,32 @@
         <v>6.09999990463257</v>
       </c>
       <c r="H1578" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1579" t="n">
+        <v>21676</v>
+      </c>
+      <c r="C1579" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="D1579" t="n">
+        <v>5.94999980926514</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="G1579" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="H1579" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -543,7 +543,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H6" t="n">
         <v>18626</v>
@@ -630,7 +630,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G9" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H9" t="n">
         <v>5755</v>
@@ -659,7 +659,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G10" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H10" t="n">
         <v>1712</v>
@@ -775,7 +775,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>4.04958152770996</v>
+        <v>4.0495810508728</v>
       </c>
       <c r="H14" t="n">
         <v>810</v>
@@ -804,7 +804,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463451385498</v>
       </c>
       <c r="H15" t="n">
         <v>1464</v>
@@ -833,7 +833,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463451385498</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463451385498</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.08210802078247</v>
+        <v>4.08210849761963</v>
       </c>
       <c r="H18" t="n">
         <v>970</v>
@@ -949,7 +949,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H20" t="n">
         <v>3268</v>
@@ -978,7 +978,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.27726888656616</v>
+        <v>4.27726936340332</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1036,7 +1036,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>4.27726888656616</v>
+        <v>4.27726936340332</v>
       </c>
       <c r="H23" t="n">
         <v>3200</v>
@@ -1065,7 +1065,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>4.26100540161133</v>
+        <v>4.26100492477417</v>
       </c>
       <c r="H24" t="n">
         <v>2429</v>
@@ -1094,7 +1094,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>4.26100540161133</v>
+        <v>4.26100492477417</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H26" t="n">
         <v>1926</v>
@@ -1152,7 +1152,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G27" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H27" t="n">
         <v>651</v>
@@ -1239,7 +1239,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H30" t="n">
         <v>4377</v>
@@ -1268,7 +1268,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H31" t="n">
         <v>6330</v>
@@ -1297,7 +1297,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H32" t="n">
         <v>1096</v>
@@ -1326,7 +1326,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463451385498</v>
       </c>
       <c r="H33" t="n">
         <v>2550</v>
@@ -1355,7 +1355,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H34" t="n">
         <v>3736</v>
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H35" t="n">
         <v>500</v>
@@ -1413,7 +1413,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G36" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H36" t="n">
         <v>550</v>
@@ -1442,7 +1442,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H37" t="n">
         <v>1422</v>
@@ -1471,7 +1471,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G38" t="n">
-        <v>4.08210802078247</v>
+        <v>4.08210849761963</v>
       </c>
       <c r="H38" t="n">
         <v>950</v>
@@ -1529,7 +1529,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H40" t="n">
         <v>1276</v>
@@ -1558,7 +1558,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G41" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H41" t="n">
         <v>470</v>
@@ -1587,7 +1587,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H42" t="n">
         <v>450</v>
@@ -1616,7 +1616,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G43" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H43" t="n">
         <v>450</v>
@@ -1645,7 +1645,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G44" t="n">
-        <v>4.29353284835815</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H44" t="n">
         <v>3940</v>
@@ -1674,7 +1674,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G45" t="n">
-        <v>4.29353284835815</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G47" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H47" t="n">
         <v>1066</v>
@@ -1761,7 +1761,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H48" t="n">
         <v>400</v>
@@ -1790,7 +1790,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G49" t="n">
-        <v>4.05771350860596</v>
+        <v>4.05771255493164</v>
       </c>
       <c r="H49" t="n">
         <v>5985</v>
@@ -1819,7 +1819,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.98452806472778</v>
+        <v>3.9845278263092</v>
       </c>
       <c r="H50" t="n">
         <v>6262</v>
@@ -1848,7 +1848,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200109481812</v>
+        <v>3.95200157165527</v>
       </c>
       <c r="H51" t="n">
         <v>4885</v>
@@ -1877,7 +1877,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639632225037</v>
+        <v>3.97639584541321</v>
       </c>
       <c r="H52" t="n">
         <v>1056</v>
@@ -1906,7 +1906,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639632225037</v>
+        <v>3.97639584541321</v>
       </c>
       <c r="H53" t="n">
         <v>504</v>
@@ -1935,7 +1935,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94386887550354</v>
+        <v>3.94386911392212</v>
       </c>
       <c r="H54" t="n">
         <v>2108</v>
@@ -1964,7 +1964,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321063995361</v>
+        <v>3.90321135520935</v>
       </c>
       <c r="H55" t="n">
         <v>1248</v>
@@ -1993,7 +1993,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321063995361</v>
+        <v>3.90321135520935</v>
       </c>
       <c r="H56" t="n">
         <v>400</v>
@@ -2080,7 +2080,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.8869481086731</v>
+        <v>3.88694834709167</v>
       </c>
       <c r="H59" t="n">
         <v>1153</v>
@@ -2109,7 +2109,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.82189393043518</v>
+        <v>3.82189416885376</v>
       </c>
       <c r="H60" t="n">
         <v>400</v>
@@ -2138,7 +2138,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057674407959</v>
+        <v>3.74057722091675</v>
       </c>
       <c r="H61" t="n">
         <v>2000</v>
@@ -2167,7 +2167,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057674407959</v>
+        <v>3.74057722091675</v>
       </c>
       <c r="H62" t="n">
         <v>1245</v>
@@ -2196,7 +2196,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>3.82189393043518</v>
+        <v>3.82189416885376</v>
       </c>
       <c r="H63" t="n">
         <v>1994</v>
@@ -2225,7 +2225,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>3.63486504554749</v>
+        <v>3.63486528396606</v>
       </c>
       <c r="H64" t="n">
         <v>2884</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991850852966</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H65" t="n">
         <v>4762</v>
@@ -2283,7 +2283,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>3.71618223190308</v>
+        <v>3.71618175506592</v>
       </c>
       <c r="H66" t="n">
         <v>23931</v>
@@ -2341,7 +2341,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.64299702644348</v>
+        <v>3.64299750328064</v>
       </c>
       <c r="H68" t="n">
         <v>7900</v>
@@ -2399,7 +2399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991850852966</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H70" t="n">
         <v>12720</v>
@@ -2486,7 +2486,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.6917872428894</v>
+        <v>3.69178700447083</v>
       </c>
       <c r="H73" t="n">
         <v>281949</v>
@@ -2515,7 +2515,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.773104429245</v>
+        <v>3.77310419082642</v>
       </c>
       <c r="H74" t="n">
         <v>7850</v>
@@ -2544,7 +2544,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991850852966</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H75" t="n">
         <v>12819</v>
@@ -2602,7 +2602,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H77" t="n">
         <v>35243</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H78" t="n">
         <v>15007</v>
@@ -2660,7 +2660,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H79" t="n">
         <v>61552</v>
@@ -2689,7 +2689,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342544555664</v>
       </c>
       <c r="H80" t="n">
         <v>8198</v>
@@ -2718,7 +2718,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G81" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H81" t="n">
         <v>4817</v>
@@ -2747,7 +2747,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463451385498</v>
       </c>
       <c r="H82" t="n">
         <v>8365</v>
@@ -2834,7 +2834,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G85" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H85" t="n">
         <v>4943</v>
@@ -2892,7 +2892,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G87" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H87" t="n">
         <v>1000</v>
@@ -2921,7 +2921,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G88" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H88" t="n">
         <v>4736</v>
@@ -2979,7 +2979,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H90" t="n">
         <v>11784</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H91" t="n">
         <v>30633</v>
@@ -3037,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H92" t="n">
         <v>124660</v>
@@ -3066,7 +3066,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G93" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H93" t="n">
         <v>37142</v>
@@ -3095,7 +3095,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737533569336</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H94" t="n">
         <v>35821</v>
@@ -3124,7 +3124,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.42363882064819</v>
+        <v>4.42363929748535</v>
       </c>
       <c r="H95" t="n">
         <v>35724</v>
@@ -3182,7 +3182,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.42363882064819</v>
+        <v>4.42363929748535</v>
       </c>
       <c r="H97" t="n">
         <v>12350</v>
@@ -3211,7 +3211,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>4.39111232757568</v>
+        <v>4.39111328125</v>
       </c>
       <c r="H98" t="n">
         <v>10150</v>
@@ -3240,7 +3240,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.39111232757568</v>
+        <v>4.39111328125</v>
       </c>
       <c r="H99" t="n">
         <v>5600</v>
@@ -3269,7 +3269,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G100" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H100" t="n">
         <v>13735</v>
@@ -3298,7 +3298,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G101" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H101" t="n">
         <v>17485</v>
@@ -3356,7 +3356,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869228363037</v>
+        <v>4.48869323730469</v>
       </c>
       <c r="H103" t="n">
         <v>18889</v>
@@ -3385,7 +3385,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869228363037</v>
+        <v>4.48869323730469</v>
       </c>
       <c r="H104" t="n">
         <v>6100</v>
@@ -3443,7 +3443,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H106" t="n">
         <v>11075</v>
@@ -3472,7 +3472,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H107" t="n">
         <v>9254</v>
@@ -3588,7 +3588,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>4.29353284835815</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H111" t="n">
         <v>9209</v>
@@ -3646,7 +3646,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H113" t="n">
         <v>32551</v>
@@ -3675,7 +3675,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G114" t="n">
-        <v>4.35858631134033</v>
+        <v>4.35858583450317</v>
       </c>
       <c r="H114" t="n">
         <v>39778</v>
@@ -3704,7 +3704,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G115" t="n">
-        <v>4.29353284835815</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H115" t="n">
         <v>9983</v>
@@ -3733,7 +3733,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29353284835815</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H116" t="n">
         <v>12350</v>
@@ -3820,7 +3820,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G119" t="n">
-        <v>4.35858631134033</v>
+        <v>4.35858583450317</v>
       </c>
       <c r="H119" t="n">
         <v>76765</v>
@@ -3849,7 +3849,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737533569336</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H120" t="n">
         <v>50907</v>
@@ -3965,7 +3965,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.39111232757568</v>
+        <v>4.39111328125</v>
       </c>
       <c r="H124" t="n">
         <v>37196</v>
@@ -3994,7 +3994,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H125" t="n">
         <v>59141</v>
@@ -4052,7 +4052,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H127" t="n">
         <v>19970</v>
@@ -4081,7 +4081,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H128" t="n">
         <v>22395</v>
@@ -4110,7 +4110,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H129" t="n">
         <v>7536</v>
@@ -4168,7 +4168,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H131" t="n">
         <v>37064</v>
@@ -4255,7 +4255,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>4.91154050827026</v>
+        <v>4.91154098510742</v>
       </c>
       <c r="H134" t="n">
         <v>14070</v>
@@ -4284,7 +4284,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>5.07417440414429</v>
+        <v>5.07417392730713</v>
       </c>
       <c r="H135" t="n">
         <v>34938</v>
@@ -4313,7 +4313,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791091918945</v>
+        <v>5.05791044235229</v>
       </c>
       <c r="H136" t="n">
         <v>24382</v>
@@ -4371,7 +4371,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>5.1554913520813</v>
+        <v>5.15549182891846</v>
       </c>
       <c r="H138" t="n">
         <v>14771</v>
@@ -4400,7 +4400,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>5.1554913520813</v>
+        <v>5.15549182891846</v>
       </c>
       <c r="H139" t="n">
         <v>5761</v>
@@ -4429,7 +4429,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>5.07417440414429</v>
+        <v>5.07417392730713</v>
       </c>
       <c r="H140" t="n">
         <v>18825</v>
@@ -4458,7 +4458,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>5.12296533584595</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H141" t="n">
         <v>13207</v>
@@ -4487,7 +4487,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801784515381</v>
+        <v>5.18801736831665</v>
       </c>
       <c r="H142" t="n">
         <v>16197</v>
@@ -4516,7 +4516,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H143" t="n">
         <v>11836</v>
@@ -4545,7 +4545,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>5.12296533584595</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H144" t="n">
         <v>4290</v>
@@ -4574,7 +4574,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H145" t="n">
         <v>16119</v>
@@ -4603,7 +4603,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H146" t="n">
         <v>2211</v>
@@ -4632,7 +4632,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>5.12296533584595</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H147" t="n">
         <v>10023</v>
@@ -4661,7 +4661,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164743423462</v>
+        <v>5.04164791107178</v>
       </c>
       <c r="H148" t="n">
         <v>9600</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>4.87901449203491</v>
+        <v>4.87901401519775</v>
       </c>
       <c r="H149" t="n">
         <v>16280</v>
@@ -4719,7 +4719,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791091918945</v>
+        <v>5.05791044235229</v>
       </c>
       <c r="H150" t="n">
         <v>6072</v>
@@ -4748,7 +4748,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.12296533584595</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H151" t="n">
         <v>10138</v>
@@ -4777,7 +4777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G152" t="n">
-        <v>5.12296533584595</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H152" t="n">
         <v>7104</v>
@@ -4806,7 +4806,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>5.12296533584595</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H153" t="n">
         <v>5444</v>
@@ -4835,7 +4835,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>5.07417440414429</v>
+        <v>5.07417392730713</v>
       </c>
       <c r="H154" t="n">
         <v>9966</v>
@@ -4864,7 +4864,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538394927979</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H155" t="n">
         <v>13422</v>
@@ -4922,7 +4922,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>5.12296533584595</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H157" t="n">
         <v>4698</v>
@@ -4951,7 +4951,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H158" t="n">
         <v>9550</v>
@@ -4980,7 +4980,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H159" t="n">
         <v>11350</v>
@@ -5009,7 +5009,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>4.97659397125244</v>
+        <v>4.9765944480896</v>
       </c>
       <c r="H160" t="n">
         <v>12705</v>
@@ -5038,7 +5038,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164743423462</v>
+        <v>5.04164791107178</v>
       </c>
       <c r="H161" t="n">
         <v>3098</v>
@@ -5067,7 +5067,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G162" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H162" t="n">
         <v>7250</v>
@@ -5096,7 +5096,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G163" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H163" t="n">
         <v>7961</v>
@@ -5183,7 +5183,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H166" t="n">
         <v>16468</v>
@@ -5328,7 +5328,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>4.91154050827026</v>
+        <v>4.91154098510742</v>
       </c>
       <c r="H171" t="n">
         <v>16947</v>
@@ -5357,7 +5357,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H172" t="n">
         <v>2308</v>
@@ -5415,7 +5415,7 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>4.87901449203491</v>
+        <v>4.87901401519775</v>
       </c>
       <c r="H174" t="n">
         <v>7490</v>
@@ -5444,7 +5444,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G175" t="n">
-        <v>4.83022403717041</v>
+        <v>4.83022356033325</v>
       </c>
       <c r="H175" t="n">
         <v>11057</v>
@@ -5473,7 +5473,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H176" t="n">
         <v>18455</v>
@@ -5502,7 +5502,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>5.25307178497314</v>
+        <v>5.25307130813599</v>
       </c>
       <c r="H177" t="n">
         <v>49926</v>
@@ -5531,7 +5531,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G178" t="n">
-        <v>5.23680877685547</v>
+        <v>5.23680830001831</v>
       </c>
       <c r="H178" t="n">
         <v>49204</v>
@@ -5676,7 +5676,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>5.3831787109375</v>
+        <v>5.38317823410034</v>
       </c>
       <c r="H183" t="n">
         <v>5662</v>
@@ -5705,7 +5705,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.36691474914551</v>
+        <v>5.36691570281982</v>
       </c>
       <c r="H184" t="n">
         <v>16090</v>
@@ -5734,7 +5734,7 @@
         <v>6.5</v>
       </c>
       <c r="G185" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H185" t="n">
         <v>14887</v>
@@ -5763,7 +5763,7 @@
         <v>6.5</v>
       </c>
       <c r="G186" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H186" t="n">
         <v>11690</v>
@@ -5792,7 +5792,7 @@
         <v>6.5</v>
       </c>
       <c r="G187" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>6.5</v>
       </c>
       <c r="G188" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H188" t="n">
         <v>10480</v>
@@ -5879,7 +5879,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538394927979</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H190" t="n">
         <v>5989</v>
@@ -5908,7 +5908,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G191" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H191" t="n">
         <v>110919</v>
@@ -5937,7 +5937,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G192" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H192" t="n">
         <v>2290</v>
@@ -5995,7 +5995,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G194" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H194" t="n">
         <v>2077</v>
@@ -6082,7 +6082,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G197" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H197" t="n">
         <v>40911</v>
@@ -6111,7 +6111,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G198" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H198" t="n">
         <v>13457</v>
@@ -6140,7 +6140,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H199" t="n">
         <v>6894</v>
@@ -6169,7 +6169,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H200" t="n">
         <v>28649</v>
@@ -6198,7 +6198,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G201" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H201" t="n">
         <v>8833</v>
@@ -6227,7 +6227,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H202" t="n">
         <v>680</v>
@@ -6285,7 +6285,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H204" t="n">
         <v>3896</v>
@@ -6314,7 +6314,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G205" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H205" t="n">
         <v>1300</v>
@@ -6343,7 +6343,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H206" t="n">
         <v>4898</v>
@@ -6459,7 +6459,7 @@
         <v>6.5</v>
       </c>
       <c r="G210" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H210" t="n">
         <v>8091</v>
@@ -6488,7 +6488,7 @@
         <v>6.5</v>
       </c>
       <c r="G211" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H211" t="n">
         <v>5361</v>
@@ -6575,7 +6575,7 @@
         <v>6.5</v>
       </c>
       <c r="G214" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H214" t="n">
         <v>24252</v>
@@ -6604,7 +6604,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H215" t="n">
         <v>22458</v>
@@ -6662,7 +6662,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G217" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H217" t="n">
         <v>7967</v>
@@ -6691,7 +6691,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H218" t="n">
         <v>6727</v>
@@ -6807,7 +6807,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G222" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H222" t="n">
         <v>8191</v>
@@ -6836,7 +6836,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H223" t="n">
         <v>3507</v>
@@ -6923,7 +6923,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H226" t="n">
         <v>20880</v>
@@ -6952,7 +6952,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>5.9026198387146</v>
+        <v>5.90261936187744</v>
       </c>
       <c r="H227" t="n">
         <v>38319</v>
@@ -7010,7 +7010,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G229" t="n">
-        <v>5.96912717819214</v>
+        <v>5.9691276550293</v>
       </c>
       <c r="H229" t="n">
         <v>37060</v>
@@ -7039,7 +7039,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>5.93587398529053</v>
+        <v>5.93587350845337</v>
       </c>
       <c r="H230" t="n">
         <v>14060</v>
@@ -7068,7 +7068,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G231" t="n">
-        <v>5.80285692214966</v>
+        <v>5.80285739898682</v>
       </c>
       <c r="H231" t="n">
         <v>11590</v>
@@ -7097,7 +7097,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>5.9026198387146</v>
+        <v>5.90261936187744</v>
       </c>
       <c r="H232" t="n">
         <v>6952</v>
@@ -7126,7 +7126,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>5.9026198387146</v>
+        <v>5.90261936187744</v>
       </c>
       <c r="H233" t="n">
         <v>4553</v>
@@ -7155,7 +7155,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>5.85273838043213</v>
+        <v>5.85273885726929</v>
       </c>
       <c r="H234" t="n">
         <v>12940</v>
@@ -7242,7 +7242,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H237" t="n">
         <v>8720</v>
@@ -7271,7 +7271,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>5.83611154556274</v>
+        <v>5.83611106872559</v>
       </c>
       <c r="H238" t="n">
         <v>2340</v>
@@ -7300,7 +7300,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>5.80285692214966</v>
+        <v>5.80285739898682</v>
       </c>
       <c r="H239" t="n">
         <v>8443</v>
@@ -7590,7 +7590,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H249" t="n">
         <v>6312</v>
@@ -7648,7 +7648,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H251" t="n">
         <v>1386</v>
@@ -7822,7 +7822,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H257" t="n">
         <v>3560</v>
@@ -7909,7 +7909,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H260" t="n">
         <v>1200</v>
@@ -7996,7 +7996,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H263" t="n">
         <v>8019</v>
@@ -8083,7 +8083,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H266" t="n">
         <v>9438</v>
@@ -8141,7 +8141,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H268" t="n">
         <v>1450</v>
@@ -8170,7 +8170,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G269" t="n">
-        <v>5.50356912612915</v>
+        <v>5.50356960296631</v>
       </c>
       <c r="H269" t="n">
         <v>22096</v>
@@ -8199,7 +8199,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H270" t="n">
         <v>5650</v>
@@ -8228,7 +8228,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G271" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H271" t="n">
         <v>23690</v>
@@ -8315,7 +8315,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H274" t="n">
         <v>4619</v>
@@ -8344,7 +8344,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H275" t="n">
         <v>428</v>
@@ -8373,7 +8373,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H276" t="n">
         <v>7400</v>
@@ -8634,7 +8634,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H285" t="n">
         <v>15427</v>
@@ -8663,7 +8663,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H286" t="n">
         <v>32500</v>
@@ -8721,7 +8721,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H288" t="n">
         <v>1973</v>
@@ -8750,7 +8750,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>5.50356912612915</v>
+        <v>5.50356960296631</v>
       </c>
       <c r="H289" t="n">
         <v>10165</v>
@@ -8808,7 +8808,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H291" t="n">
         <v>4539</v>
@@ -8837,7 +8837,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H292" t="n">
         <v>31220</v>
@@ -8866,7 +8866,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H293" t="n">
         <v>14001</v>
@@ -8924,7 +8924,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H295" t="n">
         <v>22500</v>
@@ -8982,7 +8982,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H297" t="n">
         <v>7700</v>
@@ -9011,7 +9011,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H298" t="n">
         <v>17311</v>
@@ -9040,7 +9040,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>5.43706035614014</v>
+        <v>5.43706130981445</v>
       </c>
       <c r="H299" t="n">
         <v>4580</v>
@@ -9069,7 +9069,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H300" t="n">
         <v>4728</v>
@@ -9098,7 +9098,7 @@
         <v>6.5</v>
       </c>
       <c r="G301" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H301" t="n">
         <v>21147</v>
@@ -9359,7 +9359,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H310" t="n">
         <v>27369</v>
@@ -9388,7 +9388,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H311" t="n">
         <v>15780</v>
@@ -9446,7 +9446,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G313" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H313" t="n">
         <v>14039</v>
@@ -9475,7 +9475,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H314" t="n">
         <v>5258</v>
@@ -9504,7 +9504,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H315" t="n">
         <v>3276</v>
@@ -9562,7 +9562,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>5.12114572525024</v>
+        <v>5.12114524841309</v>
       </c>
       <c r="H317" t="n">
         <v>4420</v>
@@ -9591,7 +9591,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G318" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H318" t="n">
         <v>5508</v>
@@ -9620,7 +9620,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G319" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H319" t="n">
         <v>1750</v>
@@ -9649,7 +9649,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G320" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H320" t="n">
         <v>7080</v>
@@ -9707,7 +9707,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H322" t="n">
         <v>6754</v>
@@ -9736,7 +9736,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G323" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H323" t="n">
         <v>11714</v>
@@ -9765,7 +9765,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G324" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H324" t="n">
         <v>4701</v>
@@ -9794,7 +9794,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G325" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H325" t="n">
         <v>3556</v>
@@ -9823,7 +9823,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H326" t="n">
         <v>4390</v>
@@ -9852,7 +9852,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G327" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H327" t="n">
         <v>10600</v>
@@ -9881,7 +9881,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H328" t="n">
         <v>6860</v>
@@ -9910,7 +9910,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H329" t="n">
         <v>24800</v>
@@ -9968,7 +9968,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>5.33729839324951</v>
+        <v>5.33729887008667</v>
       </c>
       <c r="H331" t="n">
         <v>11425</v>
@@ -9997,7 +9997,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G332" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H332" t="n">
         <v>8128</v>
@@ -10026,7 +10026,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G333" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H333" t="n">
         <v>1126</v>
@@ -10055,7 +10055,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G334" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H334" t="n">
         <v>10830</v>
@@ -10084,7 +10084,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G335" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H335" t="n">
         <v>11568</v>
@@ -10113,7 +10113,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G336" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G337" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H337" t="n">
         <v>15623</v>
@@ -10171,7 +10171,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G338" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H338" t="n">
         <v>2453</v>
@@ -10200,7 +10200,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G339" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H339" t="n">
         <v>2836</v>
@@ -10229,7 +10229,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G340" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H340" t="n">
         <v>2000</v>
@@ -10258,7 +10258,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H341" t="n">
         <v>13173</v>
@@ -10287,7 +10287,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H342" t="n">
         <v>2043</v>
@@ -10316,7 +10316,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H343" t="n">
         <v>13845</v>
@@ -10345,7 +10345,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H344" t="n">
         <v>13660</v>
@@ -10374,7 +10374,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H345" t="n">
         <v>8254</v>
@@ -10403,7 +10403,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G347" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H347" t="n">
         <v>5755</v>
@@ -10461,7 +10461,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H348" t="n">
         <v>3489</v>
@@ -10490,7 +10490,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G349" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H349" t="n">
         <v>8775</v>
@@ -10519,7 +10519,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G350" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H350" t="n">
         <v>10077</v>
@@ -10548,7 +10548,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G351" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H351" t="n">
         <v>51065</v>
@@ -10577,7 +10577,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G352" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H352" t="n">
         <v>20290</v>
@@ -10606,7 +10606,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G353" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H353" t="n">
         <v>6420</v>
@@ -10635,7 +10635,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H354" t="n">
         <v>7088</v>
@@ -10693,7 +10693,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H356" t="n">
         <v>2400</v>
@@ -10722,7 +10722,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H358" t="n">
         <v>4600</v>
@@ -10780,7 +10780,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>5.07126522064209</v>
+        <v>5.07126474380493</v>
       </c>
       <c r="H359" t="n">
         <v>3000</v>
@@ -10838,7 +10838,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H361" t="n">
         <v>1507</v>
@@ -10867,7 +10867,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H362" t="n">
         <v>1294</v>
@@ -10896,7 +10896,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H363" t="n">
         <v>4848</v>
@@ -10925,7 +10925,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G364" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H364" t="n">
         <v>2203</v>
@@ -10954,7 +10954,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G365" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H365" t="n">
         <v>1500</v>
@@ -10983,7 +10983,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H366" t="n">
         <v>710</v>
@@ -11012,7 +11012,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H367" t="n">
         <v>112</v>
@@ -11041,7 +11041,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G368" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G369" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H369" t="n">
         <v>9188</v>
@@ -11099,7 +11099,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G370" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -11128,7 +11128,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G371" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H371" t="n">
         <v>27645</v>
@@ -11157,7 +11157,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H372" t="n">
         <v>8315</v>
@@ -11215,7 +11215,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G374" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H374" t="n">
         <v>3307</v>
@@ -11244,7 +11244,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G375" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H375" t="n">
         <v>2615</v>
@@ -11273,7 +11273,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G376" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H376" t="n">
         <v>2515</v>
@@ -11302,7 +11302,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G377" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H377" t="n">
         <v>5705</v>
@@ -11331,7 +11331,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H378" t="n">
         <v>112</v>
@@ -11360,7 +11360,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G381" t="n">
-        <v>5.12114572525024</v>
+        <v>5.12114524841309</v>
       </c>
       <c r="H381" t="n">
         <v>1071</v>
@@ -11447,7 +11447,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G382" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H382" t="n">
         <v>4400</v>
@@ -11476,7 +11476,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H383" t="n">
         <v>5263</v>
@@ -11505,7 +11505,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11563,7 +11563,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G386" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H386" t="n">
         <v>400</v>
@@ -11592,7 +11592,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G387" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G388" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H388" t="n">
         <v>500</v>
@@ -11650,7 +11650,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G389" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H389" t="n">
         <v>2640</v>
@@ -11679,7 +11679,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>5.22090911865234</v>
+        <v>5.22090864181519</v>
       </c>
       <c r="H390" t="n">
         <v>1000</v>
@@ -11766,7 +11766,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G393" t="n">
-        <v>5.23753643035889</v>
+        <v>5.23753595352173</v>
       </c>
       <c r="H393" t="n">
         <v>260</v>
@@ -11882,7 +11882,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G397" t="n">
-        <v>5.08789205551147</v>
+        <v>5.08789157867432</v>
       </c>
       <c r="H397" t="n">
         <v>1898</v>
@@ -11911,7 +11911,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G398" t="n">
-        <v>5.08789205551147</v>
+        <v>5.08789157867432</v>
       </c>
       <c r="H398" t="n">
         <v>2425</v>
@@ -11998,7 +11998,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G401" t="n">
-        <v>4.92162132263184</v>
+        <v>4.92162084579468</v>
       </c>
       <c r="H401" t="n">
         <v>1890</v>
@@ -12085,7 +12085,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>4.88836669921875</v>
+        <v>4.88836717605591</v>
       </c>
       <c r="H404" t="n">
         <v>32</v>
@@ -12143,7 +12143,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>4.67221450805664</v>
+        <v>4.67221403121948</v>
       </c>
       <c r="H406" t="n">
         <v>19716</v>
@@ -12288,7 +12288,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G411" t="n">
-        <v>4.70546865463257</v>
+        <v>4.70546817779541</v>
       </c>
       <c r="H411" t="n">
         <v>826</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>4.80523109436035</v>
+        <v>4.80523157119751</v>
       </c>
       <c r="H412" t="n">
         <v>200</v>
@@ -12433,7 +12433,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>4.4394359588623</v>
+        <v>4.43943500518799</v>
       </c>
       <c r="H416" t="n">
         <v>3039</v>
@@ -12520,7 +12520,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>4.35629940032959</v>
+        <v>4.35629987716675</v>
       </c>
       <c r="H419" t="n">
         <v>5206</v>
@@ -12578,7 +12578,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H421" t="n">
         <v>1908</v>
@@ -12636,7 +12636,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H423" t="n">
         <v>3457</v>
@@ -12665,7 +12665,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G424" t="n">
-        <v>4.80523109436035</v>
+        <v>4.80523157119751</v>
       </c>
       <c r="H424" t="n">
         <v>3714</v>
@@ -12694,7 +12694,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>4.67221450805664</v>
+        <v>4.67221403121948</v>
       </c>
       <c r="H425" t="n">
         <v>5049</v>
@@ -12723,7 +12723,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>4.60570621490479</v>
+        <v>4.60570573806763</v>
       </c>
       <c r="H426" t="n">
         <v>6617</v>
@@ -13042,7 +13042,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H437" t="n">
         <v>6066</v>
@@ -13071,7 +13071,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H438" t="n">
         <v>1719</v>
@@ -13245,7 +13245,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H444" t="n">
         <v>3000</v>
@@ -13303,7 +13303,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13332,7 +13332,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H447" t="n">
         <v>1000</v>
@@ -13361,7 +13361,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H450" t="n">
         <v>1700</v>
@@ -13535,7 +13535,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H454" t="n">
         <v>4800</v>
@@ -13564,7 +13564,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H455" t="n">
         <v>5500</v>
@@ -13593,7 +13593,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H459" t="n">
         <v>510</v>
@@ -13709,7 +13709,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G460" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G461" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H461" t="n">
         <v>686</v>
@@ -13767,7 +13767,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G462" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>5.06304121017456</v>
+        <v>5.0630407333374</v>
       </c>
       <c r="H464" t="n">
         <v>1994</v>
@@ -13883,7 +13883,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>5.06304121017456</v>
+        <v>5.0630407333374</v>
       </c>
       <c r="H466" t="n">
         <v>991</v>
@@ -13912,7 +13912,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H467" t="n">
         <v>1464</v>
@@ -13941,7 +13941,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H468" t="n">
         <v>810</v>
@@ -13970,7 +13970,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H469" t="n">
         <v>646</v>
@@ -13999,7 +13999,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H470" t="n">
         <v>1000</v>
@@ -14028,7 +14028,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G475" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H475" t="n">
         <v>1701</v>
@@ -14202,7 +14202,7 @@
         <v>5.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H477" t="n">
         <v>350</v>
@@ -14347,7 +14347,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H482" t="n">
         <v>1405</v>
@@ -14376,7 +14376,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G498" t="n">
-        <v>4.41524505615234</v>
+        <v>4.41524457931519</v>
       </c>
       <c r="H498" t="n">
         <v>3223</v>
@@ -14840,7 +14840,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G499" t="n">
-        <v>4.41524505615234</v>
+        <v>4.41524457931519</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G500" t="n">
-        <v>4.41524505615234</v>
+        <v>4.41524457931519</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G501" t="n">
-        <v>4.46638679504395</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H501" t="n">
         <v>705</v>
@@ -14927,7 +14927,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G502" t="n">
-        <v>4.46638679504395</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G506" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H506" t="n">
         <v>55</v>
@@ -15072,7 +15072,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H507" t="n">
         <v>3700</v>
@@ -15101,7 +15101,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H511" t="n">
         <v>2505</v>
@@ -15217,7 +15217,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H512" t="n">
         <v>2050</v>
@@ -15275,7 +15275,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G514" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H514" t="n">
         <v>1247</v>
@@ -15304,7 +15304,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G515" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H515" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15362,7 +15362,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H523" t="n">
         <v>1285</v>
@@ -15594,7 +15594,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H525" t="n">
         <v>235</v>
@@ -15623,7 +15623,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H526" t="n">
         <v>1325</v>
@@ -15652,7 +15652,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008813858032</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H530" t="n">
         <v>1270</v>
@@ -15768,7 +15768,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H531" t="n">
         <v>1390</v>
@@ -15797,7 +15797,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G532" t="n">
-        <v>4.92666292190552</v>
+        <v>4.92666339874268</v>
       </c>
       <c r="H532" t="n">
         <v>374</v>
@@ -15884,7 +15884,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H535" t="n">
         <v>2280</v>
@@ -15913,7 +15913,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H536" t="n">
         <v>2123</v>
@@ -15942,7 +15942,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H537" t="n">
         <v>1000</v>
@@ -15971,7 +15971,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H538" t="n">
         <v>1776</v>
@@ -16029,7 +16029,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H540" t="n">
         <v>350</v>
@@ -16058,7 +16058,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H542" t="n">
         <v>2760</v>
@@ -16116,7 +16116,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G543" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16174,7 +16174,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H545" t="n">
         <v>2895</v>
@@ -16232,7 +16232,7 @@
         <v>5.5</v>
       </c>
       <c r="G547" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H547" t="n">
         <v>2535</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.48343420028687</v>
+        <v>4.48343467712402</v>
       </c>
       <c r="H549" t="n">
         <v>1022</v>
@@ -16319,7 +16319,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>4.55162382125854</v>
+        <v>4.55162286758423</v>
       </c>
       <c r="H550" t="n">
         <v>360</v>
@@ -16348,7 +16348,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>4.48343420028687</v>
+        <v>4.48343467712402</v>
       </c>
       <c r="H551" t="n">
         <v>1200</v>
@@ -16377,7 +16377,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.55162382125854</v>
+        <v>4.55162286758423</v>
       </c>
       <c r="H552" t="n">
         <v>450</v>
@@ -16435,7 +16435,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G554" t="n">
-        <v>4.44933938980103</v>
+        <v>4.44933891296387</v>
       </c>
       <c r="H554" t="n">
         <v>608</v>
@@ -16580,7 +16580,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G559" t="n">
-        <v>4.53457593917847</v>
+        <v>4.53457546234131</v>
       </c>
       <c r="H559" t="n">
         <v>750</v>
@@ -16696,7 +16696,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G563" t="n">
-        <v>4.46638679504395</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H563" t="n">
         <v>2000</v>
@@ -16986,7 +16986,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G573" t="n">
-        <v>4.56867074966431</v>
+        <v>4.56867027282715</v>
       </c>
       <c r="H573" t="n">
         <v>2280</v>
@@ -17044,7 +17044,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H575" t="n">
         <v>20</v>
@@ -17073,7 +17073,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H579" t="n">
         <v>4350</v>
@@ -17218,7 +17218,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H581" t="n">
         <v>1495</v>
@@ -17247,7 +17247,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G582" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H582" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H583" t="n">
         <v>1150</v>
@@ -17334,7 +17334,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H585" t="n">
         <v>360</v>
@@ -17392,7 +17392,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H587" t="n">
         <v>1750</v>
@@ -17450,7 +17450,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H589" t="n">
         <v>710</v>
@@ -17479,7 +17479,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H590" t="n">
         <v>900</v>
@@ -17508,7 +17508,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H591" t="n">
         <v>2311</v>
@@ -17537,7 +17537,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H592" t="n">
         <v>901</v>
@@ -17566,7 +17566,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H593" t="n">
         <v>2905</v>
@@ -17595,7 +17595,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>5.5</v>
       </c>
       <c r="G595" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H595" t="n">
         <v>6710</v>
@@ -17682,7 +17682,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H597" t="n">
         <v>607</v>
@@ -17711,7 +17711,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G598" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H598" t="n">
         <v>65</v>
@@ -17769,7 +17769,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G600" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H600" t="n">
         <v>2186</v>
@@ -17798,7 +17798,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H603" t="n">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H610" t="n">
         <v>1351</v>
@@ -18088,7 +18088,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H611" t="n">
         <v>510</v>
@@ -18117,7 +18117,7 @@
         <v>5.5</v>
       </c>
       <c r="G612" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H612" t="n">
         <v>34</v>
@@ -18146,7 +18146,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H613" t="n">
         <v>186</v>
@@ -18175,7 +18175,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H614" t="n">
         <v>186</v>
@@ -18204,7 +18204,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G616" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -18262,7 +18262,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G617" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18320,7 +18320,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H619" t="n">
         <v>675</v>
@@ -18378,7 +18378,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G621" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H621" t="n">
         <v>200</v>
@@ -18407,7 +18407,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H622" t="n">
         <v>0</v>
@@ -18436,7 +18436,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G624" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18523,7 +18523,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H626" t="n">
         <v>110</v>
@@ -18552,7 +18552,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H627" t="n">
         <v>10</v>
@@ -18581,7 +18581,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H628" t="n">
         <v>400</v>
@@ -18610,7 +18610,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H629" t="n">
         <v>110</v>
@@ -18697,7 +18697,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H632" t="n">
         <v>872</v>
@@ -18755,7 +18755,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H634" t="n">
         <v>10</v>
@@ -18813,7 +18813,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G636" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H636" t="n">
         <v>1898</v>
@@ -18842,7 +18842,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G637" t="n">
-        <v>5.01189947128296</v>
+        <v>5.01189994812012</v>
       </c>
       <c r="H637" t="n">
         <v>67041</v>
@@ -18900,7 +18900,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H639" t="n">
         <v>800</v>
@@ -18958,7 +18958,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>5.01189947128296</v>
+        <v>5.01189994812012</v>
       </c>
       <c r="H641" t="n">
         <v>3920</v>
@@ -18987,7 +18987,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H642" t="n">
         <v>5765</v>
@@ -19074,7 +19074,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G645" t="n">
-        <v>5.30170249938965</v>
+        <v>5.30170345306396</v>
       </c>
       <c r="H645" t="n">
         <v>2953</v>
@@ -19103,7 +19103,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.1994194984436</v>
+        <v>5.19941997528076</v>
       </c>
       <c r="H646" t="n">
         <v>12764</v>
@@ -19132,7 +19132,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G647" t="n">
-        <v>5.1994194984436</v>
+        <v>5.19941997528076</v>
       </c>
       <c r="H647" t="n">
         <v>1345</v>
@@ -19190,7 +19190,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>5.21646642684937</v>
+        <v>5.21646690368652</v>
       </c>
       <c r="H649" t="n">
         <v>560</v>
@@ -19219,7 +19219,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G650" t="n">
-        <v>5.21646642684937</v>
+        <v>5.21646690368652</v>
       </c>
       <c r="H650" t="n">
         <v>4700</v>
@@ -19248,7 +19248,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>5.1994194984436</v>
+        <v>5.19941997528076</v>
       </c>
       <c r="H651" t="n">
         <v>2400</v>
@@ -19277,7 +19277,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>5.13123035430908</v>
+        <v>5.13123083114624</v>
       </c>
       <c r="H652" t="n">
         <v>317</v>
@@ -19364,7 +19364,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H655" t="n">
         <v>1585</v>
@@ -19393,7 +19393,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>5.21646642684937</v>
+        <v>5.21646690368652</v>
       </c>
       <c r="H656" t="n">
         <v>815</v>
@@ -19567,7 +19567,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G662" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H662" t="n">
         <v>4300</v>
@@ -19596,7 +19596,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008813858032</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H663" t="n">
         <v>300</v>
@@ -19625,7 +19625,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>5.13123035430908</v>
+        <v>5.13123083114624</v>
       </c>
       <c r="H664" t="n">
         <v>5303</v>
@@ -19654,7 +19654,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H665" t="n">
         <v>3800</v>
@@ -19683,7 +19683,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H666" t="n">
         <v>0</v>
@@ -19712,7 +19712,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>5.06304121017456</v>
+        <v>5.0630407333374</v>
       </c>
       <c r="H667" t="n">
         <v>1000</v>
@@ -19741,7 +19741,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>5.06304121017456</v>
+        <v>5.0630407333374</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G671" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H671" t="n">
         <v>2756</v>
@@ -19944,7 +19944,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H675" t="n">
         <v>2151</v>
@@ -20234,7 +20234,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G685" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H685" t="n">
         <v>298</v>
@@ -20263,7 +20263,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H686" t="n">
         <v>1900</v>
@@ -20321,7 +20321,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H688" t="n">
         <v>3796</v>
@@ -20495,7 +20495,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H694" t="n">
         <v>2751</v>
@@ -20524,7 +20524,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G695" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H695" t="n">
         <v>331</v>
@@ -20582,7 +20582,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G697" t="n">
-        <v>4.98632860183716</v>
+        <v>4.986328125</v>
       </c>
       <c r="H697" t="n">
         <v>100</v>
@@ -20611,7 +20611,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>4.98632860183716</v>
+        <v>4.986328125</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -20640,7 +20640,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G699" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H699" t="n">
         <v>380</v>
@@ -20698,7 +20698,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H701" t="n">
         <v>150</v>
@@ -20727,7 +20727,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -20756,7 +20756,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H703" t="n">
         <v>200</v>
@@ -20872,7 +20872,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G707" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H707" t="n">
         <v>1585</v>
@@ -21104,7 +21104,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G715" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H715" t="n">
         <v>3214</v>
@@ -21133,7 +21133,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H716" t="n">
         <v>1000</v>
@@ -21365,7 +21365,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G724" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H724" t="n">
         <v>500</v>
@@ -21481,7 +21481,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G728" t="n">
-        <v>4.93783235549927</v>
+        <v>4.93783187866211</v>
       </c>
       <c r="H728" t="n">
         <v>2930</v>
@@ -21510,7 +21510,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.93783235549927</v>
+        <v>4.93783187866211</v>
       </c>
       <c r="H729" t="n">
         <v>6873</v>
@@ -23366,7 +23366,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G793" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H793" t="n">
         <v>1992</v>
@@ -23424,7 +23424,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>4.98191976547241</v>
+        <v>4.98192024230957</v>
       </c>
       <c r="H795" t="n">
         <v>144</v>
@@ -23540,7 +23540,7 @@
         <v>5.25</v>
       </c>
       <c r="G799" t="n">
-        <v>4.62921810150146</v>
+        <v>4.62921762466431</v>
       </c>
       <c r="H799" t="n">
         <v>495</v>
@@ -23946,7 +23946,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H813" t="n">
         <v>1618</v>
@@ -23975,7 +23975,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24004,7 +24004,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H815" t="n">
         <v>1188</v>
@@ -24033,7 +24033,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H816" t="n">
         <v>10</v>
@@ -24091,7 +24091,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H818" t="n">
         <v>700</v>
@@ -24120,7 +24120,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H819" t="n">
         <v>166</v>
@@ -24149,7 +24149,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>4.02080583572388</v>
+        <v>4.02080631256104</v>
       </c>
       <c r="H823" t="n">
         <v>4500</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H827" t="n">
         <v>2876</v>
@@ -24410,7 +24410,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>4.02080583572388</v>
+        <v>4.02080631256104</v>
       </c>
       <c r="H829" t="n">
         <v>1007</v>
@@ -24497,7 +24497,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G832" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H832" t="n">
         <v>207</v>
@@ -24526,7 +24526,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H833" t="n">
         <v>1050</v>
@@ -24555,7 +24555,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G835" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H835" t="n">
         <v>1</v>
@@ -24613,7 +24613,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H836" t="n">
         <v>1974</v>
@@ -24787,7 +24787,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H842" t="n">
         <v>2500</v>
@@ -24816,7 +24816,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H843" t="n">
         <v>1253</v>
@@ -24874,7 +24874,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H845" t="n">
         <v>796</v>
@@ -24903,7 +24903,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G846" t="n">
-        <v>4.25006246566772</v>
+        <v>4.25006294250488</v>
       </c>
       <c r="H846" t="n">
         <v>3297</v>
@@ -24932,7 +24932,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G847" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H847" t="n">
         <v>3500</v>
@@ -24961,7 +24961,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G848" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H848" t="n">
         <v>1250</v>
@@ -24990,7 +24990,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G849" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -25019,7 +25019,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -25077,7 +25077,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.00317096710205</v>
+        <v>4.00317049026489</v>
       </c>
       <c r="H852" t="n">
         <v>21572</v>
@@ -25135,7 +25135,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G854" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H854" t="n">
         <v>56826</v>
@@ -25164,7 +25164,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>4.00317096710205</v>
+        <v>4.00317049026489</v>
       </c>
       <c r="H855" t="n">
         <v>5901</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H856" t="n">
         <v>3097</v>
@@ -25222,7 +25222,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>4.02080583572388</v>
+        <v>4.02080631256104</v>
       </c>
       <c r="H857" t="n">
         <v>1400</v>
@@ -25309,7 +25309,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G860" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H860" t="n">
         <v>5097</v>
@@ -25483,7 +25483,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H866" t="n">
         <v>20519</v>
@@ -25512,7 +25512,7 @@
         <v>4.5</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H867" t="n">
         <v>14414</v>
@@ -25657,7 +25657,7 @@
         <v>4.5</v>
       </c>
       <c r="G872" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H872" t="n">
         <v>2450</v>
@@ -25715,7 +25715,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H874" t="n">
         <v>3098</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H875" t="n">
         <v>3194</v>
@@ -25773,7 +25773,7 @@
         <v>4.5</v>
       </c>
       <c r="G876" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H876" t="n">
         <v>2457</v>
@@ -25918,7 +25918,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>3.89736032485962</v>
+        <v>3.8973605632782</v>
       </c>
       <c r="H881" t="n">
         <v>30875</v>
@@ -25947,7 +25947,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86209058761597</v>
+        <v>3.86208987236023</v>
       </c>
       <c r="H882" t="n">
         <v>15378</v>
@@ -25976,7 +25976,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G883" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H883" t="n">
         <v>18373</v>
@@ -26005,7 +26005,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>3.72100925445557</v>
+        <v>3.72100877761841</v>
       </c>
       <c r="H884" t="n">
         <v>9694</v>
@@ -26063,7 +26063,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G886" t="n">
-        <v>3.73864436149597</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H886" t="n">
         <v>2531</v>
@@ -26092,7 +26092,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H887" t="n">
         <v>5091</v>
@@ -26121,7 +26121,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H888" t="n">
         <v>8519</v>
@@ -26150,7 +26150,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H889" t="n">
         <v>14342</v>
@@ -26179,7 +26179,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H890" t="n">
         <v>20433</v>
@@ -26208,7 +26208,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H891" t="n">
         <v>58437</v>
@@ -26237,7 +26237,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>3.89736032485962</v>
+        <v>3.8973605632782</v>
       </c>
       <c r="H892" t="n">
         <v>25887</v>
@@ -26353,7 +26353,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>3.826819896698</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H896" t="n">
         <v>7640</v>
@@ -26440,7 +26440,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G899" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H899" t="n">
         <v>25714</v>
@@ -26469,7 +26469,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H900" t="n">
         <v>21083</v>
@@ -26498,7 +26498,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G901" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H901" t="n">
         <v>17900</v>
@@ -26527,7 +26527,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73864436149597</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H902" t="n">
         <v>44451</v>
@@ -26556,7 +26556,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>3.826819896698</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H903" t="n">
         <v>25646</v>
@@ -26585,7 +26585,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G904" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H904" t="n">
         <v>39491</v>
@@ -26614,7 +26614,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G905" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H905" t="n">
         <v>14849</v>
@@ -26643,7 +26643,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G906" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H906" t="n">
         <v>5341</v>
@@ -26672,7 +26672,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86209058761597</v>
+        <v>3.86208987236023</v>
       </c>
       <c r="H907" t="n">
         <v>7190</v>
@@ -26701,7 +26701,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G908" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H908" t="n">
         <v>400</v>
@@ -26730,7 +26730,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H909" t="n">
         <v>700</v>
@@ -26759,7 +26759,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G910" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H910" t="n">
         <v>15870</v>
@@ -26788,7 +26788,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>3.826819896698</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H911" t="n">
         <v>85</v>
@@ -26875,7 +26875,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86209058761597</v>
+        <v>3.86208987236023</v>
       </c>
       <c r="H914" t="n">
         <v>1050</v>
@@ -26904,7 +26904,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G915" t="n">
-        <v>3.89736032485962</v>
+        <v>3.8973605632782</v>
       </c>
       <c r="H915" t="n">
         <v>2945</v>
@@ -26933,7 +26933,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H916" t="n">
         <v>35</v>
@@ -27020,7 +27020,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G919" t="n">
-        <v>3.826819896698</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H919" t="n">
         <v>1905</v>
@@ -27049,7 +27049,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H920" t="n">
         <v>8574</v>
@@ -27165,7 +27165,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G924" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H924" t="n">
         <v>2250</v>
@@ -27194,7 +27194,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H925" t="n">
         <v>2087</v>
@@ -27223,7 +27223,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H930" t="n">
         <v>125</v>
@@ -27397,7 +27397,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H932" t="n">
         <v>468</v>
@@ -27426,7 +27426,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H933" t="n">
         <v>7761</v>
@@ -27455,7 +27455,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G934" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H934" t="n">
         <v>5727</v>
@@ -27484,7 +27484,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>4.07371139526367</v>
+        <v>4.07371091842651</v>
       </c>
       <c r="H935" t="n">
         <v>2555</v>
@@ -27513,7 +27513,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G936" t="n">
-        <v>4.25006246566772</v>
+        <v>4.25006294250488</v>
       </c>
       <c r="H936" t="n">
         <v>38360</v>
@@ -27542,7 +27542,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G937" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H937" t="n">
         <v>8262</v>
@@ -27571,7 +27571,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G938" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H938" t="n">
         <v>10491</v>
@@ -27629,7 +27629,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G940" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H940" t="n">
         <v>194</v>
@@ -27658,7 +27658,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H941" t="n">
         <v>430</v>
@@ -27716,7 +27716,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G943" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H943" t="n">
         <v>1635</v>
@@ -27745,7 +27745,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G944" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H944" t="n">
         <v>8544</v>
@@ -27774,7 +27774,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H945" t="n">
         <v>3230</v>
@@ -27890,7 +27890,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G949" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H949" t="n">
         <v>1750</v>
@@ -28064,7 +28064,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G955" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H955" t="n">
         <v>4302</v>
@@ -28122,7 +28122,7 @@
         <v>5</v>
       </c>
       <c r="G957" t="n">
-        <v>4.40877866744995</v>
+        <v>4.40877819061279</v>
       </c>
       <c r="H957" t="n">
         <v>2700</v>
@@ -28412,7 +28412,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G967" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H967" t="n">
         <v>1977</v>
@@ -29282,7 +29282,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>4.45847749710083</v>
+        <v>4.45847797393799</v>
       </c>
       <c r="H997" t="n">
         <v>700</v>
@@ -29543,7 +29543,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1006" t="n">
         <v>2585</v>
@@ -29572,7 +29572,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1007" t="n">
         <v>2103</v>
@@ -29601,7 +29601,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1008" t="n">
         <v>1200</v>
@@ -29630,7 +29630,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1009" t="n">
         <v>600</v>
@@ -29659,7 +29659,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1011" t="n">
         <v>300</v>
@@ -30790,7 +30790,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1049" t="n">
         <v>2020</v>
@@ -30819,7 +30819,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1050" t="n">
         <v>1250</v>
@@ -31080,7 +31080,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1059" t="n">
         <v>4001</v>
@@ -31109,7 +31109,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.88970017433167</v>
+        <v>3.88970065116882</v>
       </c>
       <c r="H1060" t="n">
         <v>14640</v>
@@ -31196,7 +31196,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1063" t="n">
         <v>6269</v>
@@ -31370,7 +31370,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.88970017433167</v>
+        <v>3.88970065116882</v>
       </c>
       <c r="H1069" t="n">
         <v>861</v>
@@ -32008,7 +32008,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1091" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1091" t="n">
         <v>7006</v>
@@ -32037,7 +32037,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1092" t="n">
         <v>10055</v>
@@ -32124,7 +32124,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1095" t="n">
         <v>1998</v>
@@ -32153,7 +32153,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1096" t="n">
         <v>0</v>
@@ -33226,7 +33226,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1133" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1133" t="n">
         <v>1360</v>
@@ -33255,7 +33255,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1134" t="n">
         <v>2035</v>
@@ -33516,7 +33516,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1143" t="n">
         <v>500</v>
@@ -33661,7 +33661,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.45847749710083</v>
+        <v>4.45847797393799</v>
       </c>
       <c r="H1148" t="n">
         <v>12871</v>
@@ -46166,6 +46166,64 @@
         <v>21676</v>
       </c>
       <c r="I1579" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1580" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1580" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="D1580" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="G1580" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="H1580" t="n">
+        <v>960</v>
+      </c>
+      <c r="I1580" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1581" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1581" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="D1581" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="E1581" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F1581" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G1581" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="H1581" t="n">
+        <v>442</v>
+      </c>
+      <c r="I1581" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -572,7 +572,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H7" t="n">
         <v>5900</v>
@@ -601,7 +601,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H8" t="n">
         <v>1000</v>
@@ -630,7 +630,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G9" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H9" t="n">
         <v>5755</v>
@@ -659,7 +659,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G10" t="n">
-        <v>4.19595146179199</v>
+        <v>4.19595193862915</v>
       </c>
       <c r="H10" t="n">
         <v>1712</v>
@@ -775,7 +775,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0495810508728</v>
+        <v>4.04958200454712</v>
       </c>
       <c r="H14" t="n">
         <v>810</v>
@@ -804,7 +804,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G15" t="n">
-        <v>4.11463451385498</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H15" t="n">
         <v>1464</v>
@@ -833,7 +833,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>4.11463451385498</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>4.11463451385498</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H20" t="n">
         <v>3268</v>
@@ -1007,7 +1007,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H22" t="n">
         <v>3365</v>
@@ -1181,7 +1181,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H28" t="n">
         <v>350</v>
@@ -1239,7 +1239,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H30" t="n">
         <v>4377</v>
@@ -1326,7 +1326,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.11463451385498</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H33" t="n">
         <v>2550</v>
@@ -1355,7 +1355,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H34" t="n">
         <v>3736</v>
@@ -1413,7 +1413,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G36" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H36" t="n">
         <v>550</v>
@@ -1645,7 +1645,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G44" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H44" t="n">
         <v>3940</v>
@@ -1674,7 +1674,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G45" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G47" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H47" t="n">
         <v>1066</v>
@@ -1761,7 +1761,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H48" t="n">
         <v>400</v>
@@ -1790,7 +1790,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G49" t="n">
-        <v>4.05771255493164</v>
+        <v>4.0577130317688</v>
       </c>
       <c r="H49" t="n">
         <v>5985</v>
@@ -1819,7 +1819,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.9845278263092</v>
+        <v>3.98452830314636</v>
       </c>
       <c r="H50" t="n">
         <v>6262</v>
@@ -1848,7 +1848,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200157165527</v>
+        <v>3.95200133323669</v>
       </c>
       <c r="H51" t="n">
         <v>4885</v>
@@ -1877,7 +1877,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H52" t="n">
         <v>1056</v>
@@ -1906,7 +1906,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H53" t="n">
         <v>504</v>
@@ -1935,7 +1935,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94386911392212</v>
+        <v>3.94386982917786</v>
       </c>
       <c r="H54" t="n">
         <v>2108</v>
@@ -2022,7 +2022,7 @@
         <v>4.75</v>
       </c>
       <c r="G57" t="n">
-        <v>3.86255264282227</v>
+        <v>3.86255311965942</v>
       </c>
       <c r="H57" t="n">
         <v>4200</v>
@@ -2080,7 +2080,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.88694834709167</v>
+        <v>3.88694763183594</v>
       </c>
       <c r="H59" t="n">
         <v>1153</v>
@@ -2109,7 +2109,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.82189416885376</v>
+        <v>3.82189440727234</v>
       </c>
       <c r="H60" t="n">
         <v>400</v>
@@ -2138,7 +2138,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057722091675</v>
+        <v>3.74057698249817</v>
       </c>
       <c r="H61" t="n">
         <v>2000</v>
@@ -2167,7 +2167,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057722091675</v>
+        <v>3.74057698249817</v>
       </c>
       <c r="H62" t="n">
         <v>1245</v>
@@ -2196,7 +2196,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>3.82189416885376</v>
+        <v>3.82189440727234</v>
       </c>
       <c r="H63" t="n">
         <v>1994</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991874694824</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H65" t="n">
         <v>4762</v>
@@ -2283,7 +2283,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>3.71618175506592</v>
+        <v>3.71618247032166</v>
       </c>
       <c r="H66" t="n">
         <v>23931</v>
@@ -2312,7 +2312,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.67552375793457</v>
+        <v>3.67552447319031</v>
       </c>
       <c r="H67" t="n">
         <v>5250</v>
@@ -2370,7 +2370,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926027297974</v>
+        <v>3.65926003456116</v>
       </c>
       <c r="H69" t="n">
         <v>14000</v>
@@ -2399,7 +2399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991874694824</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H70" t="n">
         <v>12720</v>
@@ -2428,7 +2428,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926027297974</v>
+        <v>3.65926003456116</v>
       </c>
       <c r="H71" t="n">
         <v>11150</v>
@@ -2457,7 +2457,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>3.67552375793457</v>
+        <v>3.67552447319031</v>
       </c>
       <c r="H72" t="n">
         <v>6400</v>
@@ -2486,7 +2486,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69178700447083</v>
+        <v>3.6917872428894</v>
       </c>
       <c r="H73" t="n">
         <v>281949</v>
@@ -2515,7 +2515,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.77310419082642</v>
+        <v>3.77310371398926</v>
       </c>
       <c r="H74" t="n">
         <v>7850</v>
@@ -2544,7 +2544,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991874694824</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H75" t="n">
         <v>12819</v>
@@ -2573,7 +2573,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>3.67552375793457</v>
+        <v>3.67552447319031</v>
       </c>
       <c r="H76" t="n">
         <v>24183</v>
@@ -2660,7 +2660,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H79" t="n">
         <v>61552</v>
@@ -2689,7 +2689,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16342544555664</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H80" t="n">
         <v>8198</v>
@@ -2718,7 +2718,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G81" t="n">
-        <v>4.19595146179199</v>
+        <v>4.19595193862915</v>
       </c>
       <c r="H81" t="n">
         <v>4817</v>
@@ -2747,7 +2747,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>4.11463451385498</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H82" t="n">
         <v>8365</v>
@@ -2834,7 +2834,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G85" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H85" t="n">
         <v>4943</v>
@@ -2863,7 +2863,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -2892,7 +2892,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G87" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H87" t="n">
         <v>1000</v>
@@ -3095,7 +3095,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H94" t="n">
         <v>35821</v>
@@ -3211,7 +3211,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>4.39111328125</v>
+        <v>4.39111280441284</v>
       </c>
       <c r="H98" t="n">
         <v>10150</v>
@@ -3240,7 +3240,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.39111328125</v>
+        <v>4.39111280441284</v>
       </c>
       <c r="H99" t="n">
         <v>5600</v>
@@ -3269,7 +3269,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G100" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H100" t="n">
         <v>13735</v>
@@ -3298,7 +3298,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G101" t="n">
-        <v>4.24474143981934</v>
+        <v>4.24474191665649</v>
       </c>
       <c r="H101" t="n">
         <v>17485</v>
@@ -3443,7 +3443,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495624542236</v>
+        <v>4.50495576858521</v>
       </c>
       <c r="H106" t="n">
         <v>11075</v>
@@ -3472,7 +3472,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495624542236</v>
+        <v>4.50495576858521</v>
       </c>
       <c r="H107" t="n">
         <v>9254</v>
@@ -3501,7 +3501,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>4.5212197303772</v>
+        <v>4.52121925354004</v>
       </c>
       <c r="H108" t="n">
         <v>11295</v>
@@ -3588,7 +3588,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H111" t="n">
         <v>9209</v>
@@ -3704,7 +3704,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G115" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H115" t="n">
         <v>9983</v>
@@ -3733,7 +3733,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H116" t="n">
         <v>12350</v>
@@ -3762,7 +3762,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H117" t="n">
         <v>20886</v>
@@ -3791,7 +3791,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H118" t="n">
         <v>47283</v>
@@ -3849,7 +3849,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H120" t="n">
         <v>50907</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H121" t="n">
         <v>5333</v>
@@ -3907,7 +3907,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>4.3423228263855</v>
+        <v>4.34232234954834</v>
       </c>
       <c r="H122" t="n">
         <v>510822</v>
@@ -3936,7 +3936,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H123" t="n">
         <v>30275</v>
@@ -3965,7 +3965,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.39111328125</v>
+        <v>4.39111280441284</v>
       </c>
       <c r="H124" t="n">
         <v>37196</v>
@@ -4139,7 +4139,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G130" t="n">
-        <v>4.61880016326904</v>
+        <v>4.61879968643188</v>
       </c>
       <c r="H130" t="n">
         <v>12487</v>
@@ -4255,7 +4255,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>4.91154098510742</v>
+        <v>4.91154003143311</v>
       </c>
       <c r="H134" t="n">
         <v>14070</v>
@@ -4313,7 +4313,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791044235229</v>
+        <v>5.05791091918945</v>
       </c>
       <c r="H136" t="n">
         <v>24382</v>
@@ -4342,7 +4342,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H137" t="n">
         <v>12072</v>
@@ -4371,7 +4371,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>5.15549182891846</v>
+        <v>5.1554913520813</v>
       </c>
       <c r="H138" t="n">
         <v>14771</v>
@@ -4400,7 +4400,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>5.15549182891846</v>
+        <v>5.1554913520813</v>
       </c>
       <c r="H139" t="n">
         <v>5761</v>
@@ -4458,7 +4458,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H141" t="n">
         <v>13207</v>
@@ -4487,7 +4487,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801736831665</v>
+        <v>5.18801832199097</v>
       </c>
       <c r="H142" t="n">
         <v>16197</v>
@@ -4516,7 +4516,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043836593628</v>
+        <v>5.09043788909912</v>
       </c>
       <c r="H143" t="n">
         <v>11836</v>
@@ -4545,7 +4545,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H144" t="n">
         <v>4290</v>
@@ -4632,7 +4632,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H147" t="n">
         <v>10023</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>4.87901401519775</v>
+        <v>4.8790135383606</v>
       </c>
       <c r="H149" t="n">
         <v>16280</v>
@@ -4719,7 +4719,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791044235229</v>
+        <v>5.05791091918945</v>
       </c>
       <c r="H150" t="n">
         <v>6072</v>
@@ -4748,7 +4748,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H151" t="n">
         <v>10138</v>
@@ -4777,7 +4777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G152" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H152" t="n">
         <v>7104</v>
@@ -4806,7 +4806,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H153" t="n">
         <v>5444</v>
@@ -4864,7 +4864,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538347244263</v>
       </c>
       <c r="H155" t="n">
         <v>13422</v>
@@ -4922,7 +4922,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H157" t="n">
         <v>4698</v>
@@ -4980,7 +4980,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043836593628</v>
+        <v>5.09043788909912</v>
       </c>
       <c r="H159" t="n">
         <v>11350</v>
@@ -5009,7 +5009,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>4.9765944480896</v>
+        <v>4.97659397125244</v>
       </c>
       <c r="H160" t="n">
         <v>12705</v>
@@ -5125,7 +5125,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>4.94406700134277</v>
+        <v>4.94406747817993</v>
       </c>
       <c r="H164" t="n">
         <v>28419</v>
@@ -5212,7 +5212,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G167" t="n">
-        <v>4.89527702331543</v>
+        <v>4.89527750015259</v>
       </c>
       <c r="H167" t="n">
         <v>20850</v>
@@ -5270,7 +5270,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.94406700134277</v>
+        <v>4.94406747817993</v>
       </c>
       <c r="H169" t="n">
         <v>2656</v>
@@ -5299,7 +5299,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.89527702331543</v>
+        <v>4.89527750015259</v>
       </c>
       <c r="H170" t="n">
         <v>15167</v>
@@ -5328,7 +5328,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>4.91154098510742</v>
+        <v>4.91154003143311</v>
       </c>
       <c r="H171" t="n">
         <v>16947</v>
@@ -5415,7 +5415,7 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>4.87901401519775</v>
+        <v>4.8790135383606</v>
       </c>
       <c r="H174" t="n">
         <v>7490</v>
@@ -5560,7 +5560,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H179" t="n">
         <v>12820</v>
@@ -5589,7 +5589,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H180" t="n">
         <v>11620</v>
@@ -5618,7 +5618,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H181" t="n">
         <v>5800</v>
@@ -5647,7 +5647,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065126419067</v>
       </c>
       <c r="H182" t="n">
         <v>7541</v>
@@ -5676,7 +5676,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>5.38317823410034</v>
+        <v>5.3831787109375</v>
       </c>
       <c r="H183" t="n">
         <v>5662</v>
@@ -5705,7 +5705,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.36691570281982</v>
+        <v>5.36691522598267</v>
       </c>
       <c r="H184" t="n">
         <v>16090</v>
@@ -5850,7 +5850,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922786712646</v>
+        <v>5.13922834396362</v>
       </c>
       <c r="H189" t="n">
         <v>10921</v>
@@ -5879,7 +5879,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538347244263</v>
       </c>
       <c r="H190" t="n">
         <v>5989</v>
@@ -5966,7 +5966,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H193" t="n">
         <v>4766</v>
@@ -6024,7 +6024,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>5.00475645065308</v>
+        <v>5.00475692749023</v>
       </c>
       <c r="H195" t="n">
         <v>15185</v>
@@ -6140,7 +6140,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H199" t="n">
         <v>6894</v>
@@ -6169,7 +6169,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H200" t="n">
         <v>28649</v>
@@ -6227,7 +6227,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H202" t="n">
         <v>680</v>
@@ -6285,7 +6285,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H204" t="n">
         <v>3896</v>
@@ -6401,7 +6401,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>5.35392570495605</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H208" t="n">
         <v>3971</v>
@@ -6430,7 +6430,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.35392570495605</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H209" t="n">
         <v>6644</v>
@@ -6720,7 +6720,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H219" t="n">
         <v>20185</v>
@@ -6778,7 +6778,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H221" t="n">
         <v>22001</v>
@@ -6836,7 +6836,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66984033584595</v>
+        <v>5.66984081268311</v>
       </c>
       <c r="H223" t="n">
         <v>3507</v>
@@ -6865,7 +6865,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>5.75297546386719</v>
+        <v>5.75297594070435</v>
       </c>
       <c r="H224" t="n">
         <v>500</v>
@@ -6894,7 +6894,7 @@
         <v>7</v>
       </c>
       <c r="G225" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H225" t="n">
         <v>7539</v>
@@ -7010,7 +7010,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G229" t="n">
-        <v>5.9691276550293</v>
+        <v>5.96912813186646</v>
       </c>
       <c r="H229" t="n">
         <v>37060</v>
@@ -7155,7 +7155,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>5.85273885726929</v>
+        <v>5.85273838043213</v>
       </c>
       <c r="H234" t="n">
         <v>12940</v>
@@ -7184,7 +7184,7 @@
         <v>7</v>
       </c>
       <c r="G235" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H235" t="n">
         <v>7545</v>
@@ -7213,7 +7213,7 @@
         <v>7</v>
       </c>
       <c r="G236" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H236" t="n">
         <v>2000</v>
@@ -7271,7 +7271,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>5.83611106872559</v>
+        <v>5.83611154556274</v>
       </c>
       <c r="H238" t="n">
         <v>2340</v>
@@ -7329,7 +7329,7 @@
         <v>7</v>
       </c>
       <c r="G240" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H240" t="n">
         <v>3750</v>
@@ -7358,7 +7358,7 @@
         <v>7</v>
       </c>
       <c r="G241" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H241" t="n">
         <v>4000</v>
@@ -7445,7 +7445,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G244" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H244" t="n">
         <v>4011</v>
@@ -7590,7 +7590,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H249" t="n">
         <v>6312</v>
@@ -7648,7 +7648,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66984033584595</v>
+        <v>5.66984081268311</v>
       </c>
       <c r="H251" t="n">
         <v>1386</v>
@@ -7822,7 +7822,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H257" t="n">
         <v>3560</v>
@@ -7909,7 +7909,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H260" t="n">
         <v>1200</v>
@@ -7967,7 +7967,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H262" t="n">
         <v>500</v>
@@ -7996,7 +7996,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H263" t="n">
         <v>8019</v>
@@ -8025,7 +8025,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H264" t="n">
         <v>1211</v>
@@ -8054,7 +8054,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G265" t="n">
-        <v>5.61995935440063</v>
+        <v>5.61995887756348</v>
       </c>
       <c r="H265" t="n">
         <v>1620</v>
@@ -8083,7 +8083,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H266" t="n">
         <v>9438</v>
@@ -8112,7 +8112,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G267" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H267" t="n">
         <v>175</v>
@@ -8228,7 +8228,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G271" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H271" t="n">
         <v>23690</v>
@@ -8257,7 +8257,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G272" t="n">
-        <v>5.52019643783569</v>
+        <v>5.52019596099854</v>
       </c>
       <c r="H272" t="n">
         <v>2848</v>
@@ -8344,7 +8344,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H275" t="n">
         <v>428</v>
@@ -8373,7 +8373,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H276" t="n">
         <v>7400</v>
@@ -8402,7 +8402,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H277" t="n">
         <v>4450</v>
@@ -8431,7 +8431,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H278" t="n">
         <v>3400</v>
@@ -8460,7 +8460,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>5.75297546386719</v>
+        <v>5.75297594070435</v>
       </c>
       <c r="H279" t="n">
         <v>13700</v>
@@ -8489,7 +8489,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H280" t="n">
         <v>5210</v>
@@ -8547,7 +8547,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H282" t="n">
         <v>6500</v>
@@ -8605,7 +8605,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H284" t="n">
         <v>6060</v>
@@ -8634,7 +8634,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H285" t="n">
         <v>15427</v>
@@ -8663,7 +8663,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H286" t="n">
         <v>32500</v>
@@ -8866,7 +8866,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H293" t="n">
         <v>14001</v>
@@ -8895,7 +8895,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G294" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H294" t="n">
         <v>31744</v>
@@ -9040,7 +9040,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>5.43706130981445</v>
+        <v>5.43706035614014</v>
       </c>
       <c r="H299" t="n">
         <v>4580</v>
@@ -9301,7 +9301,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>5.35392570495605</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H308" t="n">
         <v>7755</v>
@@ -9504,7 +9504,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H315" t="n">
         <v>3276</v>
@@ -9533,7 +9533,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H316" t="n">
         <v>29455</v>
@@ -9562,7 +9562,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>5.12114524841309</v>
+        <v>5.12114572525024</v>
       </c>
       <c r="H317" t="n">
         <v>4420</v>
@@ -9910,7 +9910,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H329" t="n">
         <v>24800</v>
@@ -9968,7 +9968,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>5.33729887008667</v>
+        <v>5.33729839324951</v>
       </c>
       <c r="H331" t="n">
         <v>11425</v>
@@ -10026,7 +10026,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G333" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H333" t="n">
         <v>1126</v>
@@ -10258,7 +10258,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H341" t="n">
         <v>13173</v>
@@ -10461,7 +10461,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H348" t="n">
         <v>3489</v>
@@ -10635,7 +10635,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H354" t="n">
         <v>7088</v>
@@ -10664,7 +10664,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H355" t="n">
         <v>1170</v>
@@ -10693,7 +10693,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H356" t="n">
         <v>2400</v>
@@ -10722,7 +10722,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H358" t="n">
         <v>4600</v>
@@ -10954,7 +10954,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G365" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H365" t="n">
         <v>1500</v>
@@ -11244,7 +11244,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G375" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H375" t="n">
         <v>2615</v>
@@ -11418,7 +11418,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G381" t="n">
-        <v>5.12114524841309</v>
+        <v>5.12114572525024</v>
       </c>
       <c r="H381" t="n">
         <v>1071</v>
@@ -11476,7 +11476,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H383" t="n">
         <v>5263</v>
@@ -11505,7 +11505,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G391" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H391" t="n">
         <v>6720</v>
@@ -11737,7 +11737,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G397" t="n">
-        <v>5.08789157867432</v>
+        <v>5.08789205551147</v>
       </c>
       <c r="H397" t="n">
         <v>1898</v>
@@ -11911,7 +11911,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G398" t="n">
-        <v>5.08789157867432</v>
+        <v>5.08789205551147</v>
       </c>
       <c r="H398" t="n">
         <v>2425</v>
@@ -11940,7 +11940,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97150182723999</v>
+        <v>4.97150278091431</v>
       </c>
       <c r="H399" t="n">
         <v>5742</v>
@@ -11969,7 +11969,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>4.82185888290405</v>
+        <v>4.82185840606689</v>
       </c>
       <c r="H400" t="n">
         <v>7273</v>
@@ -12056,7 +12056,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>4.83848571777344</v>
+        <v>4.83848524093628</v>
       </c>
       <c r="H403" t="n">
         <v>339</v>
@@ -12114,7 +12114,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G405" t="n">
-        <v>4.83848571777344</v>
+        <v>4.83848524093628</v>
       </c>
       <c r="H405" t="n">
         <v>5440</v>
@@ -12143,7 +12143,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>4.67221403121948</v>
+        <v>4.67221450805664</v>
       </c>
       <c r="H406" t="n">
         <v>19716</v>
@@ -12172,7 +12172,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H407" t="n">
         <v>9154</v>
@@ -12230,7 +12230,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G409" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884086608887</v>
       </c>
       <c r="H409" t="n">
         <v>700</v>
@@ -12288,7 +12288,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G411" t="n">
-        <v>4.70546817779541</v>
+        <v>4.70546865463257</v>
       </c>
       <c r="H411" t="n">
         <v>826</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>4.80523157119751</v>
+        <v>4.80523204803467</v>
       </c>
       <c r="H412" t="n">
         <v>200</v>
@@ -12375,7 +12375,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G414" t="n">
-        <v>4.58907890319824</v>
+        <v>4.5890793800354</v>
       </c>
       <c r="H414" t="n">
         <v>4253</v>
@@ -12404,7 +12404,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H415" t="n">
         <v>970</v>
@@ -12491,7 +12491,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>4.47268915176392</v>
+        <v>4.47268962860107</v>
       </c>
       <c r="H418" t="n">
         <v>25169</v>
@@ -12520,7 +12520,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>4.35629987716675</v>
+        <v>4.35629892349243</v>
       </c>
       <c r="H419" t="n">
         <v>5206</v>
@@ -12665,7 +12665,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G424" t="n">
-        <v>4.80523157119751</v>
+        <v>4.80523204803467</v>
       </c>
       <c r="H424" t="n">
         <v>3714</v>
@@ -12694,7 +12694,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>4.67221403121948</v>
+        <v>4.67221450805664</v>
       </c>
       <c r="H425" t="n">
         <v>5049</v>
@@ -12781,7 +12781,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>4.52257061004639</v>
+        <v>4.52257013320923</v>
       </c>
       <c r="H428" t="n">
         <v>8580</v>
@@ -12810,7 +12810,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G429" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884086608887</v>
       </c>
       <c r="H429" t="n">
         <v>3246</v>
@@ -12839,7 +12839,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H430" t="n">
         <v>7925</v>
@@ -12868,7 +12868,7 @@
         <v>5.5</v>
       </c>
       <c r="G431" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H431" t="n">
         <v>2128</v>
@@ -12897,7 +12897,7 @@
         <v>5.5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>5.5</v>
       </c>
       <c r="G433" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H433" t="n">
         <v>2400</v>
@@ -12955,7 +12955,7 @@
         <v>5.5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884086608887</v>
       </c>
       <c r="H435" t="n">
         <v>2711</v>
@@ -13100,7 +13100,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G439" t="n">
-        <v>4.75535011291504</v>
+        <v>4.75534963607788</v>
       </c>
       <c r="H439" t="n">
         <v>4000</v>
@@ -13187,7 +13187,7 @@
         <v>5.5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H442" t="n">
         <v>700</v>
@@ -13419,7 +13419,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H450" t="n">
         <v>1700</v>
@@ -13477,7 +13477,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H452" t="n">
         <v>500</v>
@@ -13506,7 +13506,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H459" t="n">
         <v>510</v>
@@ -13709,7 +13709,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G460" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G461" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H461" t="n">
         <v>686</v>
@@ -13767,7 +13767,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G462" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>5.0630407333374</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H464" t="n">
         <v>1994</v>
@@ -13883,7 +13883,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G466" t="n">
-        <v>5.0630407333374</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H466" t="n">
         <v>991</v>
@@ -13912,7 +13912,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H467" t="n">
         <v>1464</v>
@@ -13941,7 +13941,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H468" t="n">
         <v>810</v>
@@ -13970,7 +13970,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H469" t="n">
         <v>646</v>
@@ -13999,7 +13999,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H470" t="n">
         <v>1000</v>
@@ -14028,7 +14028,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -14202,7 +14202,7 @@
         <v>5.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H477" t="n">
         <v>350</v>
@@ -14318,7 +14318,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H481" t="n">
         <v>500</v>
@@ -14347,7 +14347,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028415679932</v>
       </c>
       <c r="H482" t="n">
         <v>1405</v>
@@ -14376,7 +14376,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028415679932</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>4.61981201171875</v>
+        <v>4.61981248855591</v>
       </c>
       <c r="H486" t="n">
         <v>4252</v>
@@ -14782,7 +14782,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G497" t="n">
-        <v>4.31296110153198</v>
+        <v>4.31296062469482</v>
       </c>
       <c r="H497" t="n">
         <v>5800</v>
@@ -14811,7 +14811,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G498" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H498" t="n">
         <v>3223</v>
@@ -14840,7 +14840,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G499" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G500" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14898,7 +14898,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G501" t="n">
-        <v>4.46638631820679</v>
+        <v>4.46638584136963</v>
       </c>
       <c r="H501" t="n">
         <v>705</v>
@@ -14927,7 +14927,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G502" t="n">
-        <v>4.46638631820679</v>
+        <v>4.46638584136963</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H512" t="n">
         <v>2050</v>
@@ -15362,7 +15362,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028415679932</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028415679932</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15536,7 +15536,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H523" t="n">
         <v>1285</v>
@@ -15594,7 +15594,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H525" t="n">
         <v>235</v>
@@ -15623,7 +15623,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H526" t="n">
         <v>1325</v>
@@ -15652,7 +15652,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H528" t="n">
         <v>700</v>
@@ -15710,7 +15710,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008909225464</v>
       </c>
       <c r="H530" t="n">
         <v>1270</v>
@@ -15768,7 +15768,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H531" t="n">
         <v>1390</v>
@@ -15797,7 +15797,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G532" t="n">
-        <v>4.92666339874268</v>
+        <v>4.92666292190552</v>
       </c>
       <c r="H532" t="n">
         <v>374</v>
@@ -15826,7 +15826,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.97780466079712</v>
+        <v>4.97780513763428</v>
       </c>
       <c r="H533" t="n">
         <v>524</v>
@@ -15884,7 +15884,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028415679932</v>
       </c>
       <c r="H535" t="n">
         <v>2280</v>
@@ -15913,7 +15913,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028415679932</v>
       </c>
       <c r="H536" t="n">
         <v>2123</v>
@@ -16145,7 +16145,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>4.87552118301392</v>
+        <v>4.87552165985107</v>
       </c>
       <c r="H544" t="n">
         <v>421</v>
@@ -16232,7 +16232,7 @@
         <v>5.5</v>
       </c>
       <c r="G547" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H547" t="n">
         <v>2535</v>
@@ -16319,7 +16319,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>4.55162286758423</v>
+        <v>4.55162334442139</v>
       </c>
       <c r="H550" t="n">
         <v>360</v>
@@ -16377,7 +16377,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.55162286758423</v>
+        <v>4.55162334442139</v>
       </c>
       <c r="H552" t="n">
         <v>450</v>
@@ -16406,7 +16406,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>4.36410236358643</v>
+        <v>4.36410284042358</v>
       </c>
       <c r="H553" t="n">
         <v>4928</v>
@@ -16696,7 +16696,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G563" t="n">
-        <v>4.46638631820679</v>
+        <v>4.46638584136963</v>
       </c>
       <c r="H563" t="n">
         <v>2000</v>
@@ -17160,7 +17160,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H579" t="n">
         <v>4350</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.80733203887939</v>
+        <v>4.80733251571655</v>
       </c>
       <c r="H580" t="n">
         <v>3158</v>
@@ -17218,7 +17218,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H581" t="n">
         <v>1495</v>
@@ -17247,7 +17247,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G582" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H582" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H583" t="n">
         <v>1150</v>
@@ -17334,7 +17334,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H585" t="n">
         <v>360</v>
@@ -17392,7 +17392,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H587" t="n">
         <v>1750</v>
@@ -17450,7 +17450,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H589" t="n">
         <v>710</v>
@@ -17479,7 +17479,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H590" t="n">
         <v>900</v>
@@ -17508,7 +17508,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H591" t="n">
         <v>2311</v>
@@ -17537,7 +17537,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H592" t="n">
         <v>901</v>
@@ -17566,7 +17566,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H593" t="n">
         <v>2905</v>
@@ -17595,7 +17595,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>5.5</v>
       </c>
       <c r="G595" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H595" t="n">
         <v>6710</v>
@@ -17769,7 +17769,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G600" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H600" t="n">
         <v>2186</v>
@@ -17798,7 +17798,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H603" t="n">
         <v>0</v>
@@ -18088,7 +18088,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028415679932</v>
       </c>
       <c r="H611" t="n">
         <v>510</v>
@@ -18117,7 +18117,7 @@
         <v>5.5</v>
       </c>
       <c r="G612" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H612" t="n">
         <v>34</v>
@@ -18320,7 +18320,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H619" t="n">
         <v>675</v>
@@ -18494,7 +18494,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>4.80733203887939</v>
+        <v>4.80733251571655</v>
       </c>
       <c r="H625" t="n">
         <v>1866</v>
@@ -18523,7 +18523,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H626" t="n">
         <v>110</v>
@@ -18552,7 +18552,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H627" t="n">
         <v>10</v>
@@ -18581,7 +18581,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H628" t="n">
         <v>400</v>
@@ -18610,7 +18610,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H629" t="n">
         <v>110</v>
@@ -18726,7 +18726,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H633" t="n">
         <v>1703</v>
@@ -18813,7 +18813,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G636" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028415679932</v>
       </c>
       <c r="H636" t="n">
         <v>1898</v>
@@ -18871,7 +18871,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G638" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H638" t="n">
         <v>3800</v>
@@ -18900,7 +18900,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H639" t="n">
         <v>800</v>
@@ -18987,7 +18987,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H642" t="n">
         <v>5765</v>
@@ -19074,7 +19074,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G645" t="n">
-        <v>5.30170345306396</v>
+        <v>5.30170297622681</v>
       </c>
       <c r="H645" t="n">
         <v>2953</v>
@@ -19190,7 +19190,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>5.21646690368652</v>
+        <v>5.21646642684937</v>
       </c>
       <c r="H649" t="n">
         <v>560</v>
@@ -19219,7 +19219,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G650" t="n">
-        <v>5.21646690368652</v>
+        <v>5.21646642684937</v>
       </c>
       <c r="H650" t="n">
         <v>4700</v>
@@ -19393,7 +19393,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>5.21646690368652</v>
+        <v>5.21646642684937</v>
       </c>
       <c r="H656" t="n">
         <v>815</v>
@@ -19596,7 +19596,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008909225464</v>
       </c>
       <c r="H663" t="n">
         <v>300</v>
@@ -19712,7 +19712,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>5.0630407333374</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H667" t="n">
         <v>1000</v>
@@ -19741,7 +19741,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>5.0630407333374</v>
+        <v>5.06304121017456</v>
       </c>
       <c r="H668" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G671" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H671" t="n">
         <v>2756</v>
@@ -19857,7 +19857,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G672" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H672" t="n">
         <v>1371</v>
@@ -19886,7 +19886,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G673" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19944,7 +19944,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>5.04599380493164</v>
+        <v>5.0459942817688</v>
       </c>
       <c r="H675" t="n">
         <v>2151</v>
@@ -19973,7 +19973,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H676" t="n">
         <v>3802</v>
@@ -20002,7 +20002,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H677" t="n">
         <v>1377</v>
@@ -20031,7 +20031,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20089,7 +20089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H680" t="n">
         <v>893</v>
@@ -20147,7 +20147,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H682" t="n">
         <v>6283</v>
@@ -20350,7 +20350,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H689" t="n">
         <v>820</v>
@@ -20379,7 +20379,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H690" t="n">
         <v>700</v>
@@ -20669,7 +20669,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H700" t="n">
         <v>807</v>
@@ -46209,7 +46209,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="D1581" t="n">
-        <v>6.05000019073486</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="E1581" t="n">
         <v>6.05000019073486</v>
@@ -46224,6 +46224,35 @@
         <v>442</v>
       </c>
       <c r="I1581" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1582" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1582" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="D1582" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="E1582" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F1582" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G1582" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="H1582" t="n">
+        <v>5717</v>
+      </c>
+      <c r="I1582" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H2" t="n">
         <v>425</v>
@@ -456,7 +456,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H3" t="n">
         <v>650</v>
@@ -485,7 +485,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H5" t="n">
         <v>1105</v>
@@ -543,7 +543,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.22847890853882</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H6" t="n">
         <v>18626</v>
@@ -659,7 +659,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G10" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H10" t="n">
         <v>1712</v>
@@ -688,7 +688,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H11" t="n">
         <v>6680</v>
@@ -717,7 +717,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>4.04958200454712</v>
+        <v>4.04958152770996</v>
       </c>
       <c r="H14" t="n">
         <v>810</v>
@@ -891,7 +891,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.08210849761963</v>
+        <v>4.08210897445679</v>
       </c>
       <c r="H18" t="n">
         <v>970</v>
@@ -920,7 +920,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.17968797683716</v>
+        <v>4.17968845367432</v>
       </c>
       <c r="H19" t="n">
         <v>3229</v>
@@ -1065,7 +1065,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>4.26100492477417</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H24" t="n">
         <v>2429</v>
@@ -1094,7 +1094,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>4.26100492477417</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.22847890853882</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H26" t="n">
         <v>1926</v>
@@ -1152,7 +1152,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G27" t="n">
-        <v>4.22847890853882</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H27" t="n">
         <v>651</v>
@@ -1210,7 +1210,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H29" t="n">
         <v>1969</v>
@@ -1239,7 +1239,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H30" t="n">
         <v>4377</v>
@@ -1268,7 +1268,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H31" t="n">
         <v>6330</v>
@@ -1297,7 +1297,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H32" t="n">
         <v>1096</v>
@@ -1355,7 +1355,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H34" t="n">
         <v>3736</v>
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H35" t="n">
         <v>500</v>
@@ -1413,7 +1413,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G36" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H36" t="n">
         <v>550</v>
@@ -1471,7 +1471,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G38" t="n">
-        <v>4.08210849761963</v>
+        <v>4.08210897445679</v>
       </c>
       <c r="H38" t="n">
         <v>950</v>
@@ -1500,7 +1500,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H39" t="n">
         <v>300</v>
@@ -1529,7 +1529,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>4.22847890853882</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H40" t="n">
         <v>1276</v>
@@ -1558,7 +1558,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G41" t="n">
-        <v>4.22847890853882</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H41" t="n">
         <v>470</v>
@@ -1587,7 +1587,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.21221494674683</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H42" t="n">
         <v>450</v>
@@ -1616,7 +1616,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G43" t="n">
-        <v>4.21221494674683</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H43" t="n">
         <v>450</v>
@@ -1703,7 +1703,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>4.17968797683716</v>
+        <v>4.17968845367432</v>
       </c>
       <c r="H46" t="n">
         <v>980</v>
@@ -1877,7 +1877,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639632225037</v>
+        <v>3.97639584541321</v>
       </c>
       <c r="H52" t="n">
         <v>1056</v>
@@ -1906,7 +1906,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639632225037</v>
+        <v>3.97639584541321</v>
       </c>
       <c r="H53" t="n">
         <v>504</v>
@@ -1935,7 +1935,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94386982917786</v>
+        <v>3.9438693523407</v>
       </c>
       <c r="H54" t="n">
         <v>2108</v>
@@ -1964,7 +1964,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321135520935</v>
+        <v>3.90321111679077</v>
       </c>
       <c r="H55" t="n">
         <v>1248</v>
@@ -1993,7 +1993,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321135520935</v>
+        <v>3.90321111679077</v>
       </c>
       <c r="H56" t="n">
         <v>400</v>
@@ -2051,7 +2051,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442042350769</v>
+        <v>3.85442066192627</v>
       </c>
       <c r="H58" t="n">
         <v>450</v>
@@ -2080,7 +2080,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.88694763183594</v>
+        <v>3.88694858551025</v>
       </c>
       <c r="H59" t="n">
         <v>1153</v>
@@ -2109,7 +2109,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.82189440727234</v>
+        <v>3.82189416885376</v>
       </c>
       <c r="H60" t="n">
         <v>400</v>
@@ -2138,7 +2138,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057698249817</v>
+        <v>3.74057674407959</v>
       </c>
       <c r="H61" t="n">
         <v>2000</v>
@@ -2167,7 +2167,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057698249817</v>
+        <v>3.74057674407959</v>
       </c>
       <c r="H62" t="n">
         <v>1245</v>
@@ -2196,7 +2196,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>3.82189440727234</v>
+        <v>3.82189416885376</v>
       </c>
       <c r="H63" t="n">
         <v>1994</v>
@@ -2225,7 +2225,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>3.63486528396606</v>
+        <v>3.63486504554749</v>
       </c>
       <c r="H64" t="n">
         <v>2884</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991946220398</v>
       </c>
       <c r="H65" t="n">
         <v>4762</v>
@@ -2312,7 +2312,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.67552447319031</v>
+        <v>3.67552328109741</v>
       </c>
       <c r="H67" t="n">
         <v>5250</v>
@@ -2370,7 +2370,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926003456116</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H69" t="n">
         <v>14000</v>
@@ -2399,7 +2399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991946220398</v>
       </c>
       <c r="H70" t="n">
         <v>12720</v>
@@ -2428,7 +2428,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926003456116</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H71" t="n">
         <v>11150</v>
@@ -2457,7 +2457,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>3.67552447319031</v>
+        <v>3.67552328109741</v>
       </c>
       <c r="H72" t="n">
         <v>6400</v>
@@ -2486,7 +2486,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.6917872428894</v>
+        <v>3.69178676605225</v>
       </c>
       <c r="H73" t="n">
         <v>281949</v>
@@ -2515,7 +2515,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.77310371398926</v>
+        <v>3.77310395240784</v>
       </c>
       <c r="H74" t="n">
         <v>7850</v>
@@ -2544,7 +2544,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991946220398</v>
       </c>
       <c r="H75" t="n">
         <v>12819</v>
@@ -2573,7 +2573,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>3.67552447319031</v>
+        <v>3.67552328109741</v>
       </c>
       <c r="H76" t="n">
         <v>24183</v>
@@ -2660,7 +2660,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H79" t="n">
         <v>61552</v>
@@ -2718,7 +2718,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G81" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H81" t="n">
         <v>4817</v>
@@ -2776,7 +2776,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G83" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H83" t="n">
         <v>11228</v>
@@ -2805,7 +2805,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>4.17968797683716</v>
+        <v>4.17968845367432</v>
       </c>
       <c r="H84" t="n">
         <v>8061</v>
@@ -2921,7 +2921,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G88" t="n">
-        <v>4.22847890853882</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H88" t="n">
         <v>4736</v>
@@ -2950,7 +2950,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H89" t="n">
         <v>8400</v>
@@ -2979,7 +2979,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H90" t="n">
         <v>11784</v>
@@ -3037,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H92" t="n">
         <v>124660</v>
@@ -3066,7 +3066,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G93" t="n">
-        <v>4.21221494674683</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H93" t="n">
         <v>37142</v>
@@ -3095,7 +3095,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737628936768</v>
+        <v>4.40737676620483</v>
       </c>
       <c r="H94" t="n">
         <v>35821</v>
@@ -3153,7 +3153,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.45616626739502</v>
+        <v>4.45616579055786</v>
       </c>
       <c r="H96" t="n">
         <v>5000</v>
@@ -3211,7 +3211,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G98" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111232757568</v>
       </c>
       <c r="H98" t="n">
         <v>10150</v>
@@ -3240,7 +3240,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G99" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111232757568</v>
       </c>
       <c r="H99" t="n">
         <v>5600</v>
@@ -3327,7 +3327,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.32605886459351</v>
+        <v>4.32605838775635</v>
       </c>
       <c r="H102" t="n">
         <v>20579</v>
@@ -3356,7 +3356,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869323730469</v>
+        <v>4.48869228363037</v>
       </c>
       <c r="H103" t="n">
         <v>18889</v>
@@ -3385,7 +3385,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869323730469</v>
+        <v>4.48869228363037</v>
       </c>
       <c r="H104" t="n">
         <v>6100</v>
@@ -3501,7 +3501,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>4.52121925354004</v>
+        <v>4.5212197303772</v>
       </c>
       <c r="H108" t="n">
         <v>11295</v>
@@ -3530,7 +3530,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.55374622344971</v>
+        <v>4.55374574661255</v>
       </c>
       <c r="H109" t="n">
         <v>6650</v>
@@ -3559,7 +3559,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>4.43990278244019</v>
+        <v>4.43990230560303</v>
       </c>
       <c r="H110" t="n">
         <v>13298</v>
@@ -3617,7 +3617,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G112" t="n">
-        <v>4.32605886459351</v>
+        <v>4.32605838775635</v>
       </c>
       <c r="H112" t="n">
         <v>8648</v>
@@ -3646,7 +3646,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>4.22847890853882</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H113" t="n">
         <v>32551</v>
@@ -3849,7 +3849,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737628936768</v>
+        <v>4.40737676620483</v>
       </c>
       <c r="H120" t="n">
         <v>50907</v>
@@ -3965,7 +3965,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G124" t="n">
-        <v>4.39111280441284</v>
+        <v>4.39111232757568</v>
       </c>
       <c r="H124" t="n">
         <v>37196</v>
@@ -4023,7 +4023,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.55374622344971</v>
+        <v>4.55374574661255</v>
       </c>
       <c r="H126" t="n">
         <v>89802</v>
@@ -4139,7 +4139,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G130" t="n">
-        <v>4.61879968643188</v>
+        <v>4.61879920959473</v>
       </c>
       <c r="H130" t="n">
         <v>12487</v>
@@ -4226,7 +4226,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>4.86275053024292</v>
+        <v>4.86275100708008</v>
       </c>
       <c r="H133" t="n">
         <v>5321</v>
@@ -4255,7 +4255,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>4.91154003143311</v>
+        <v>4.91154098510742</v>
       </c>
       <c r="H134" t="n">
         <v>14070</v>
@@ -4342,7 +4342,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H137" t="n">
         <v>12072</v>
@@ -4458,7 +4458,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H141" t="n">
         <v>13207</v>
@@ -4516,7 +4516,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H143" t="n">
         <v>11836</v>
@@ -4545,7 +4545,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H144" t="n">
         <v>4290</v>
@@ -4632,7 +4632,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H147" t="n">
         <v>10023</v>
@@ -4661,7 +4661,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164791107178</v>
+        <v>5.04164695739746</v>
       </c>
       <c r="H148" t="n">
         <v>9600</v>
@@ -4748,7 +4748,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H151" t="n">
         <v>10138</v>
@@ -4777,7 +4777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G152" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H152" t="n">
         <v>7104</v>
@@ -4806,7 +4806,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H153" t="n">
         <v>5444</v>
@@ -4864,7 +4864,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538347244263</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H155" t="n">
         <v>13422</v>
@@ -4922,7 +4922,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H157" t="n">
         <v>4698</v>
@@ -4980,7 +4980,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H159" t="n">
         <v>11350</v>
@@ -5038,7 +5038,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164791107178</v>
+        <v>5.04164695739746</v>
       </c>
       <c r="H161" t="n">
         <v>3098</v>
@@ -5125,7 +5125,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>4.94406747817993</v>
+        <v>4.94406700134277</v>
       </c>
       <c r="H164" t="n">
         <v>28419</v>
@@ -5212,7 +5212,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G167" t="n">
-        <v>4.89527750015259</v>
+        <v>4.89527702331543</v>
       </c>
       <c r="H167" t="n">
         <v>20850</v>
@@ -5270,7 +5270,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.94406747817993</v>
+        <v>4.94406700134277</v>
       </c>
       <c r="H169" t="n">
         <v>2656</v>
@@ -5299,7 +5299,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.89527750015259</v>
+        <v>4.89527702331543</v>
       </c>
       <c r="H170" t="n">
         <v>15167</v>
@@ -5328,7 +5328,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>4.91154003143311</v>
+        <v>4.91154098510742</v>
       </c>
       <c r="H171" t="n">
         <v>16947</v>
@@ -5386,7 +5386,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.96033048629761</v>
+        <v>4.96033096313477</v>
       </c>
       <c r="H173" t="n">
         <v>5030</v>
@@ -5502,7 +5502,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>5.25307130813599</v>
+        <v>5.25307178497314</v>
       </c>
       <c r="H177" t="n">
         <v>49926</v>
@@ -5560,7 +5560,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H179" t="n">
         <v>12820</v>
@@ -5589,7 +5589,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H180" t="n">
         <v>11620</v>
@@ -5618,7 +5618,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H181" t="n">
         <v>5800</v>
@@ -5647,7 +5647,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>5.35065126419067</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H182" t="n">
         <v>7541</v>
@@ -5676,7 +5676,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>5.3831787109375</v>
+        <v>5.38317823410034</v>
       </c>
       <c r="H183" t="n">
         <v>5662</v>
@@ -5705,7 +5705,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.36691522598267</v>
+        <v>5.36691474914551</v>
       </c>
       <c r="H184" t="n">
         <v>16090</v>
@@ -5850,7 +5850,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922834396362</v>
+        <v>5.13922739028931</v>
       </c>
       <c r="H189" t="n">
         <v>10921</v>
@@ -5879,7 +5879,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538347244263</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H190" t="n">
         <v>5989</v>
@@ -5966,7 +5966,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H193" t="n">
         <v>4766</v>
@@ -5995,7 +5995,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G194" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H194" t="n">
         <v>2077</v>
@@ -6053,7 +6053,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765354156494</v>
       </c>
       <c r="H196" t="n">
         <v>5900</v>
@@ -6140,7 +6140,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H199" t="n">
         <v>6894</v>
@@ -6169,7 +6169,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H200" t="n">
         <v>28649</v>
@@ -6227,7 +6227,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H202" t="n">
         <v>680</v>
@@ -6256,7 +6256,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067060470581</v>
       </c>
       <c r="H203" t="n">
         <v>5722</v>
@@ -6285,7 +6285,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H204" t="n">
         <v>3896</v>
@@ -6372,7 +6372,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067060470581</v>
       </c>
       <c r="H207" t="n">
         <v>5465</v>
@@ -6459,7 +6459,7 @@
         <v>6.5</v>
       </c>
       <c r="G210" t="n">
-        <v>5.40380716323853</v>
+        <v>5.40380668640137</v>
       </c>
       <c r="H210" t="n">
         <v>8091</v>
@@ -6488,7 +6488,7 @@
         <v>6.5</v>
       </c>
       <c r="G211" t="n">
-        <v>5.40380716323853</v>
+        <v>5.40380668640137</v>
       </c>
       <c r="H211" t="n">
         <v>5361</v>
@@ -6517,7 +6517,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368766784668</v>
       </c>
       <c r="H212" t="n">
         <v>6658</v>
@@ -6575,7 +6575,7 @@
         <v>6.5</v>
       </c>
       <c r="G214" t="n">
-        <v>5.40380716323853</v>
+        <v>5.40380668640137</v>
       </c>
       <c r="H214" t="n">
         <v>24252</v>
@@ -6604,7 +6604,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H215" t="n">
         <v>22458</v>
@@ -6633,7 +6633,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368766784668</v>
       </c>
       <c r="H216" t="n">
         <v>10530</v>
@@ -6662,7 +6662,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G217" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H217" t="n">
         <v>7967</v>
@@ -6691,7 +6691,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H218" t="n">
         <v>6727</v>
@@ -6749,7 +6749,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H220" t="n">
         <v>4090</v>
@@ -6778,7 +6778,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H221" t="n">
         <v>22001</v>
@@ -7155,7 +7155,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>5.85273838043213</v>
+        <v>5.85273790359497</v>
       </c>
       <c r="H234" t="n">
         <v>12940</v>
@@ -7271,7 +7271,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>5.83611154556274</v>
+        <v>5.83611106872559</v>
       </c>
       <c r="H238" t="n">
         <v>2340</v>
@@ -7387,7 +7387,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G242" t="n">
-        <v>5.71972179412842</v>
+        <v>5.71972227096558</v>
       </c>
       <c r="H242" t="n">
         <v>6410</v>
@@ -7416,7 +7416,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G243" t="n">
-        <v>5.76960277557373</v>
+        <v>5.76960229873657</v>
       </c>
       <c r="H243" t="n">
         <v>1500</v>
@@ -7445,7 +7445,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G244" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H244" t="n">
         <v>4011</v>
@@ -7474,7 +7474,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G245" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H245" t="n">
         <v>4200</v>
@@ -7503,7 +7503,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G246" t="n">
-        <v>5.71972179412842</v>
+        <v>5.71972227096558</v>
       </c>
       <c r="H246" t="n">
         <v>2137</v>
@@ -7532,7 +7532,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G247" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H247" t="n">
         <v>5180</v>
@@ -7561,7 +7561,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G248" t="n">
-        <v>5.71972179412842</v>
+        <v>5.71972227096558</v>
       </c>
       <c r="H248" t="n">
         <v>2125</v>
@@ -7677,7 +7677,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G252" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H252" t="n">
         <v>8006</v>
@@ -7706,7 +7706,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H253" t="n">
         <v>472</v>
@@ -7764,7 +7764,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G255" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H255" t="n">
         <v>1900</v>
@@ -7793,7 +7793,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G258" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H258" t="n">
         <v>4652</v>
@@ -7880,7 +7880,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H259" t="n">
         <v>2350</v>
@@ -7938,7 +7938,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H261" t="n">
         <v>2105</v>
@@ -7967,7 +7967,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H262" t="n">
         <v>500</v>
@@ -8141,7 +8141,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H268" t="n">
         <v>1450</v>
@@ -8170,7 +8170,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G269" t="n">
-        <v>5.50356960296631</v>
+        <v>5.50356912612915</v>
       </c>
       <c r="H269" t="n">
         <v>22096</v>
@@ -8286,7 +8286,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H273" t="n">
         <v>13409</v>
@@ -8402,7 +8402,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H277" t="n">
         <v>4450</v>
@@ -8431,7 +8431,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H278" t="n">
         <v>3400</v>
@@ -8489,7 +8489,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H280" t="n">
         <v>5210</v>
@@ -8518,7 +8518,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H281" t="n">
         <v>7624</v>
@@ -8547,7 +8547,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H282" t="n">
         <v>6500</v>
@@ -8576,7 +8576,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G283" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H283" t="n">
         <v>4800</v>
@@ -8605,7 +8605,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H284" t="n">
         <v>6060</v>
@@ -8692,7 +8692,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H287" t="n">
         <v>1750</v>
@@ -8750,7 +8750,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>5.50356960296631</v>
+        <v>5.50356912612915</v>
       </c>
       <c r="H289" t="n">
         <v>10165</v>
@@ -8779,7 +8779,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G290" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H290" t="n">
         <v>16096</v>
@@ -8837,7 +8837,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H292" t="n">
         <v>31220</v>
@@ -8924,7 +8924,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H295" t="n">
         <v>22500</v>
@@ -8953,7 +8953,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H296" t="n">
         <v>24602</v>
@@ -8982,7 +8982,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H297" t="n">
         <v>7700</v>
@@ -9011,7 +9011,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H298" t="n">
         <v>17311</v>
@@ -9069,7 +9069,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H300" t="n">
         <v>4728</v>
@@ -9098,7 +9098,7 @@
         <v>6.5</v>
       </c>
       <c r="G301" t="n">
-        <v>5.40380716323853</v>
+        <v>5.40380668640137</v>
       </c>
       <c r="H301" t="n">
         <v>21147</v>
@@ -9156,7 +9156,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067060470581</v>
       </c>
       <c r="H303" t="n">
         <v>4716</v>
@@ -9185,7 +9185,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067060470581</v>
       </c>
       <c r="H304" t="n">
         <v>1563</v>
@@ -9330,7 +9330,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067060470581</v>
       </c>
       <c r="H309" t="n">
         <v>3800</v>
@@ -9417,7 +9417,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765354156494</v>
       </c>
       <c r="H312" t="n">
         <v>4873</v>
@@ -9504,7 +9504,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H315" t="n">
         <v>3276</v>
@@ -9533,7 +9533,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H316" t="n">
         <v>29455</v>
@@ -9678,7 +9678,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067060470581</v>
       </c>
       <c r="H321" t="n">
         <v>5361</v>
@@ -9765,7 +9765,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G324" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H324" t="n">
         <v>4701</v>
@@ -9910,7 +9910,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H329" t="n">
         <v>24800</v>
@@ -9939,7 +9939,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067060470581</v>
       </c>
       <c r="H330" t="n">
         <v>5585</v>
@@ -9968,7 +9968,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>5.33729839324951</v>
+        <v>5.33729887008667</v>
       </c>
       <c r="H331" t="n">
         <v>11425</v>
@@ -10026,7 +10026,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G333" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H333" t="n">
         <v>1126</v>
@@ -10055,7 +10055,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G334" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H334" t="n">
         <v>10830</v>
@@ -10084,7 +10084,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G335" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H335" t="n">
         <v>11568</v>
@@ -10113,7 +10113,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G336" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428228378296</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G338" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H338" t="n">
         <v>2453</v>
@@ -10258,7 +10258,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H341" t="n">
         <v>13173</v>
@@ -10461,7 +10461,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H348" t="n">
         <v>3489</v>
@@ -10606,7 +10606,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G353" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H353" t="n">
         <v>6420</v>
@@ -10635,7 +10635,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H354" t="n">
         <v>7088</v>
@@ -10664,7 +10664,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H355" t="n">
         <v>1170</v>
@@ -10693,7 +10693,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H356" t="n">
         <v>2400</v>
@@ -10722,7 +10722,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H358" t="n">
         <v>4600</v>
@@ -10809,7 +10809,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765354156494</v>
       </c>
       <c r="H360" t="n">
         <v>1600</v>
@@ -10954,7 +10954,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G365" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H365" t="n">
         <v>1500</v>
@@ -10983,7 +10983,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102766036987</v>
       </c>
       <c r="H366" t="n">
         <v>710</v>
@@ -11012,7 +11012,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H367" t="n">
         <v>112</v>
@@ -11041,7 +11041,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G368" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067060470581</v>
       </c>
       <c r="H373" t="n">
         <v>4742</v>
@@ -11244,7 +11244,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G375" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H375" t="n">
         <v>2615</v>
@@ -11331,7 +11331,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102766036987</v>
       </c>
       <c r="H378" t="n">
         <v>112</v>
@@ -11360,7 +11360,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102766036987</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102766036987</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H383" t="n">
         <v>5263</v>
@@ -11505,7 +11505,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G391" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H391" t="n">
         <v>6720</v>
@@ -11737,7 +11737,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G394" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765354156494</v>
       </c>
       <c r="H394" t="n">
         <v>1700</v>
@@ -11824,7 +11824,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G395" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765354156494</v>
       </c>
       <c r="H395" t="n">
         <v>1098</v>
@@ -11853,7 +11853,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G396" t="n">
-        <v>5.1876540184021</v>
+        <v>5.18765354156494</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97150278091431</v>
+        <v>4.97150230407715</v>
       </c>
       <c r="H399" t="n">
         <v>5742</v>
@@ -12056,7 +12056,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>4.83848524093628</v>
+        <v>4.8384861946106</v>
       </c>
       <c r="H403" t="n">
         <v>339</v>
@@ -12085,7 +12085,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>4.88836717605591</v>
+        <v>4.88836669921875</v>
       </c>
       <c r="H404" t="n">
         <v>32</v>
@@ -12114,7 +12114,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G405" t="n">
-        <v>4.83848524093628</v>
+        <v>4.8384861946106</v>
       </c>
       <c r="H405" t="n">
         <v>5440</v>
@@ -12172,7 +12172,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594425201416</v>
       </c>
       <c r="H407" t="n">
         <v>9154</v>
@@ -12230,7 +12230,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G409" t="n">
-        <v>4.68884086608887</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H409" t="n">
         <v>700</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>4.80523204803467</v>
+        <v>4.80523109436035</v>
       </c>
       <c r="H412" t="n">
         <v>200</v>
@@ -12375,7 +12375,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G414" t="n">
-        <v>4.5890793800354</v>
+        <v>4.58907890319824</v>
       </c>
       <c r="H414" t="n">
         <v>4253</v>
@@ -12404,7 +12404,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594425201416</v>
       </c>
       <c r="H415" t="n">
         <v>970</v>
@@ -12578,7 +12578,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H421" t="n">
         <v>1908</v>
@@ -12636,7 +12636,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H423" t="n">
         <v>3457</v>
@@ -12665,7 +12665,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G424" t="n">
-        <v>4.80523204803467</v>
+        <v>4.80523109436035</v>
       </c>
       <c r="H424" t="n">
         <v>3714</v>
@@ -12752,7 +12752,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>4.55582523345947</v>
+        <v>4.55582475662231</v>
       </c>
       <c r="H427" t="n">
         <v>10094</v>
@@ -12810,7 +12810,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G429" t="n">
-        <v>4.68884086608887</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H429" t="n">
         <v>3246</v>
@@ -12839,7 +12839,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594425201416</v>
       </c>
       <c r="H430" t="n">
         <v>7925</v>
@@ -12868,7 +12868,7 @@
         <v>5.5</v>
       </c>
       <c r="G431" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H431" t="n">
         <v>2128</v>
@@ -12897,7 +12897,7 @@
         <v>5.5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>5.5</v>
       </c>
       <c r="G433" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H433" t="n">
         <v>2400</v>
@@ -12955,7 +12955,7 @@
         <v>5.5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>4.68884086608887</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H435" t="n">
         <v>2711</v>
@@ -13042,7 +13042,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H437" t="n">
         <v>6066</v>
@@ -13071,7 +13071,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H438" t="n">
         <v>1719</v>
@@ -13100,7 +13100,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G439" t="n">
-        <v>4.75534963607788</v>
+        <v>4.75535011291504</v>
       </c>
       <c r="H439" t="n">
         <v>4000</v>
@@ -13187,7 +13187,7 @@
         <v>5.5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H442" t="n">
         <v>700</v>
@@ -13245,7 +13245,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H444" t="n">
         <v>3000</v>
@@ -13303,7 +13303,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13332,7 +13332,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H447" t="n">
         <v>1000</v>
@@ -13361,7 +13361,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G463" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H463" t="n">
         <v>5</v>
@@ -13854,7 +13854,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H465" t="n">
         <v>205</v>
@@ -14057,7 +14057,7 @@
         <v>6</v>
       </c>
       <c r="G472" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H472" t="n">
         <v>2091</v>
@@ -14086,7 +14086,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H473" t="n">
         <v>9179</v>
@@ -14115,7 +14115,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G474" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H474" t="n">
         <v>1050</v>
@@ -14144,7 +14144,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G475" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H475" t="n">
         <v>1701</v>
@@ -14347,7 +14347,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>4.79028415679932</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H482" t="n">
         <v>1405</v>
@@ -14376,7 +14376,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>4.79028415679932</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G486" t="n">
-        <v>4.61981248855591</v>
+        <v>4.61981201171875</v>
       </c>
       <c r="H486" t="n">
         <v>4252</v>
@@ -14782,7 +14782,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G497" t="n">
-        <v>4.31296062469482</v>
+        <v>4.31296110153198</v>
       </c>
       <c r="H497" t="n">
         <v>5800</v>
@@ -14956,7 +14956,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G503" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H503" t="n">
         <v>5895</v>
@@ -15043,7 +15043,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G506" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H506" t="n">
         <v>55</v>
@@ -15072,7 +15072,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H507" t="n">
         <v>3700</v>
@@ -15101,7 +15101,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H511" t="n">
         <v>2505</v>
@@ -15275,7 +15275,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G514" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H514" t="n">
         <v>1247</v>
@@ -15304,7 +15304,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G515" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H515" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15362,7 +15362,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>4.79028415679932</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>4.79028415679932</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G521" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H521" t="n">
         <v>341</v>
@@ -15507,7 +15507,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G522" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H522" t="n">
         <v>769</v>
@@ -15536,7 +15536,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G523" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H523" t="n">
         <v>1285</v>
@@ -15623,7 +15623,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H526" t="n">
         <v>1325</v>
@@ -15652,7 +15652,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H527" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H528" t="n">
         <v>700</v>
@@ -15710,7 +15710,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008909225464</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H530" t="n">
         <v>1270</v>
@@ -15768,7 +15768,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H531" t="n">
         <v>1390</v>
@@ -15826,7 +15826,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.97780513763428</v>
+        <v>4.97780466079712</v>
       </c>
       <c r="H533" t="n">
         <v>524</v>
@@ -15884,7 +15884,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.79028415679932</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H535" t="n">
         <v>2280</v>
@@ -15913,7 +15913,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>4.79028415679932</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H536" t="n">
         <v>2123</v>
@@ -16145,7 +16145,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>4.87552165985107</v>
+        <v>4.87552118301392</v>
       </c>
       <c r="H544" t="n">
         <v>421</v>
@@ -16174,7 +16174,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H545" t="n">
         <v>2895</v>
@@ -16812,7 +16812,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G567" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H567" t="n">
         <v>2942</v>
@@ -16841,7 +16841,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G568" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H568" t="n">
         <v>360</v>
@@ -16870,7 +16870,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G569" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G570" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G571" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H571" t="n">
         <v>2010</v>
@@ -16957,7 +16957,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G572" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H572" t="n">
         <v>1210</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.80733251571655</v>
+        <v>4.80733203887939</v>
       </c>
       <c r="H580" t="n">
         <v>3158</v>
@@ -18088,7 +18088,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>4.79028415679932</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H611" t="n">
         <v>510</v>
@@ -18175,7 +18175,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H614" t="n">
         <v>186</v>
@@ -18204,7 +18204,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G616" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -18262,7 +18262,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G617" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G621" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H621" t="n">
         <v>200</v>
@@ -18407,7 +18407,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H622" t="n">
         <v>0</v>
@@ -18436,7 +18436,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G624" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18494,7 +18494,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>4.80733251571655</v>
+        <v>4.80733203887939</v>
       </c>
       <c r="H625" t="n">
         <v>1866</v>
@@ -18755,7 +18755,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H634" t="n">
         <v>10</v>
@@ -18813,7 +18813,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G636" t="n">
-        <v>4.79028415679932</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H636" t="n">
         <v>1898</v>
@@ -18842,7 +18842,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G637" t="n">
-        <v>5.01189994812012</v>
+        <v>5.01189947128296</v>
       </c>
       <c r="H637" t="n">
         <v>67041</v>
@@ -18871,7 +18871,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G638" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H638" t="n">
         <v>3800</v>
@@ -18900,7 +18900,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H639" t="n">
         <v>800</v>
@@ -18929,7 +18929,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G640" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H640" t="n">
         <v>6100</v>
@@ -18958,7 +18958,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>5.01189994812012</v>
+        <v>5.01189947128296</v>
       </c>
       <c r="H641" t="n">
         <v>3920</v>
@@ -19161,7 +19161,7 @@
         <v>6</v>
       </c>
       <c r="G648" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H648" t="n">
         <v>1200</v>
@@ -19190,7 +19190,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G649" t="n">
-        <v>5.21646642684937</v>
+        <v>5.21646690368652</v>
       </c>
       <c r="H649" t="n">
         <v>560</v>
@@ -19219,7 +19219,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G650" t="n">
-        <v>5.21646642684937</v>
+        <v>5.21646690368652</v>
       </c>
       <c r="H650" t="n">
         <v>4700</v>
@@ -19335,7 +19335,7 @@
         <v>6</v>
       </c>
       <c r="G654" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H654" t="n">
         <v>3833</v>
@@ -19393,7 +19393,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G656" t="n">
-        <v>5.21646642684937</v>
+        <v>5.21646690368652</v>
       </c>
       <c r="H656" t="n">
         <v>815</v>
@@ -19422,7 +19422,7 @@
         <v>6</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H657" t="n">
         <v>512</v>
@@ -19451,7 +19451,7 @@
         <v>6</v>
       </c>
       <c r="G658" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H658" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H659" t="n">
         <v>618</v>
@@ -19509,7 +19509,7 @@
         <v>6</v>
       </c>
       <c r="G660" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H660" t="n">
         <v>110</v>
@@ -19538,7 +19538,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H661" t="n">
         <v>160</v>
@@ -19596,7 +19596,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008909225464</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H663" t="n">
         <v>300</v>
@@ -19770,7 +19770,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G669" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H669" t="n">
         <v>100</v>
@@ -19799,7 +19799,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G670" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H670" t="n">
         <v>0</v>
@@ -19828,7 +19828,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G671" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H671" t="n">
         <v>2756</v>
@@ -19857,7 +19857,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G672" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H672" t="n">
         <v>1371</v>
@@ -19886,7 +19886,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G673" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>6</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H674" t="n">
         <v>1922</v>
@@ -19944,7 +19944,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G675" t="n">
-        <v>5.0459942817688</v>
+        <v>5.04599380493164</v>
       </c>
       <c r="H675" t="n">
         <v>2151</v>
@@ -19973,7 +19973,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H676" t="n">
         <v>3802</v>
@@ -20002,7 +20002,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H677" t="n">
         <v>1377</v>
@@ -20031,7 +20031,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>6</v>
       </c>
       <c r="G679" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H679" t="n">
         <v>4219</v>
@@ -20089,7 +20089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H680" t="n">
         <v>893</v>
@@ -20118,7 +20118,7 @@
         <v>6</v>
       </c>
       <c r="G681" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H681" t="n">
         <v>1250</v>
@@ -20147,7 +20147,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H682" t="n">
         <v>6283</v>
@@ -20176,7 +20176,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G683" t="n">
-        <v>4.9437108039856</v>
+        <v>4.94371032714844</v>
       </c>
       <c r="H683" t="n">
         <v>617</v>
@@ -20205,7 +20205,7 @@
         <v>6</v>
       </c>
       <c r="G684" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H684" t="n">
         <v>3929</v>
@@ -20292,7 +20292,7 @@
         <v>6</v>
       </c>
       <c r="G687" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H687" t="n">
         <v>3300</v>
@@ -20350,7 +20350,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H689" t="n">
         <v>820</v>
@@ -20379,7 +20379,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H690" t="n">
         <v>700</v>
@@ -20408,7 +20408,7 @@
         <v>6</v>
       </c>
       <c r="G691" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H691" t="n">
         <v>3324</v>
@@ -20437,7 +20437,7 @@
         <v>6</v>
       </c>
       <c r="G692" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H692" t="n">
         <v>3119</v>
@@ -20466,7 +20466,7 @@
         <v>6</v>
       </c>
       <c r="G693" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H693" t="n">
         <v>2354</v>
@@ -20553,7 +20553,7 @@
         <v>6</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H696" t="n">
         <v>10</v>
@@ -20669,7 +20669,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H700" t="n">
         <v>807</v>
@@ -20785,7 +20785,7 @@
         <v>6</v>
       </c>
       <c r="G704" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H704" t="n">
         <v>400</v>
@@ -20872,7 +20872,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G707" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H707" t="n">
         <v>1585</v>
@@ -20901,7 +20901,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G708" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H708" t="n">
         <v>8078</v>
@@ -20930,7 +20930,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H709" t="n">
         <v>1010</v>
@@ -20959,7 +20959,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -21017,7 +21017,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H712" t="n">
         <v>7386</v>
@@ -21104,7 +21104,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G715" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H715" t="n">
         <v>3214</v>
@@ -21133,7 +21133,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H716" t="n">
         <v>1000</v>
@@ -21162,7 +21162,7 @@
         <v>5.75</v>
       </c>
       <c r="G717" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H717" t="n">
         <v>1661</v>
@@ -21191,7 +21191,7 @@
         <v>5.75</v>
       </c>
       <c r="G718" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H718" t="n">
         <v>2500</v>
@@ -21220,7 +21220,7 @@
         <v>5.75</v>
       </c>
       <c r="G719" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>5.75</v>
       </c>
       <c r="G720" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21278,7 +21278,7 @@
         <v>5.75</v>
       </c>
       <c r="G721" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G724" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H724" t="n">
         <v>500</v>
@@ -21394,7 +21394,7 @@
         <v>5.75</v>
       </c>
       <c r="G725" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H725" t="n">
         <v>1926</v>
@@ -21423,7 +21423,7 @@
         <v>5.75</v>
       </c>
       <c r="G726" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H726" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>5.75</v>
       </c>
       <c r="G727" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H727" t="n">
         <v>6821</v>
@@ -21568,7 +21568,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H731" t="n">
         <v>350</v>
@@ -22699,7 +22699,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G770" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H770" t="n">
         <v>3256</v>
@@ -23366,7 +23366,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G793" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H793" t="n">
         <v>1992</v>
@@ -23395,7 +23395,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H794" t="n">
         <v>1641</v>
@@ -23424,7 +23424,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>4.98192024230957</v>
+        <v>4.98191976547241</v>
       </c>
       <c r="H795" t="n">
         <v>144</v>
@@ -23801,7 +23801,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>4.39114332199097</v>
+        <v>4.39114379882812</v>
       </c>
       <c r="H808" t="n">
         <v>7831</v>
@@ -23830,7 +23830,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G809" t="n">
-        <v>4.39114332199097</v>
+        <v>4.39114379882812</v>
       </c>
       <c r="H809" t="n">
         <v>322</v>
@@ -24004,7 +24004,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H815" t="n">
         <v>1188</v>
@@ -24033,7 +24033,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H816" t="n">
         <v>10</v>
@@ -24062,7 +24062,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H817" t="n">
         <v>365</v>
@@ -24091,7 +24091,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H818" t="n">
         <v>700</v>
@@ -24120,7 +24120,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H819" t="n">
         <v>166</v>
@@ -24149,7 +24149,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24207,7 +24207,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G822" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H822" t="n">
         <v>340</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H827" t="n">
         <v>2876</v>
@@ -24526,7 +24526,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H833" t="n">
         <v>1050</v>
@@ -24555,7 +24555,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G835" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H835" t="n">
         <v>1</v>
@@ -24613,7 +24613,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H836" t="n">
         <v>1974</v>
@@ -24787,7 +24787,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H842" t="n">
         <v>2500</v>
@@ -24816,7 +24816,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H843" t="n">
         <v>1253</v>
@@ -24932,7 +24932,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G847" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H847" t="n">
         <v>3500</v>
@@ -24961,7 +24961,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G848" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H848" t="n">
         <v>1250</v>
@@ -24990,7 +24990,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G849" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -25019,7 +25019,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -25048,7 +25048,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.09134674072266</v>
+        <v>4.0913462638855</v>
       </c>
       <c r="H851" t="n">
         <v>2200</v>
@@ -25077,7 +25077,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.00317049026489</v>
+        <v>4.00317096710205</v>
       </c>
       <c r="H852" t="n">
         <v>21572</v>
@@ -25135,7 +25135,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G854" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H854" t="n">
         <v>56826</v>
@@ -25164,7 +25164,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>4.00317049026489</v>
+        <v>4.00317096710205</v>
       </c>
       <c r="H855" t="n">
         <v>5901</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H856" t="n">
         <v>3097</v>
@@ -25309,7 +25309,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G860" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H860" t="n">
         <v>5097</v>
@@ -25338,7 +25338,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G861" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H861" t="n">
         <v>1733</v>
@@ -25367,7 +25367,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H862" t="n">
         <v>1450</v>
@@ -25396,7 +25396,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H863" t="n">
         <v>3550</v>
@@ -25425,7 +25425,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H864" t="n">
         <v>6616</v>
@@ -25483,7 +25483,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H866" t="n">
         <v>20519</v>
@@ -25541,7 +25541,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G868" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H868" t="n">
         <v>15412</v>
@@ -25570,7 +25570,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H869" t="n">
         <v>3776</v>
@@ -25599,7 +25599,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H870" t="n">
         <v>4073</v>
@@ -25686,7 +25686,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H873" t="n">
         <v>5847</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H875" t="n">
         <v>3194</v>
@@ -25802,7 +25802,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G877" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H877" t="n">
         <v>13736</v>
@@ -25947,7 +25947,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H882" t="n">
         <v>15378</v>
@@ -26005,7 +26005,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>3.72100877761841</v>
+        <v>3.72100901603699</v>
       </c>
       <c r="H884" t="n">
         <v>9694</v>
@@ -26034,7 +26034,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>3.68573880195618</v>
+        <v>3.68573904037476</v>
       </c>
       <c r="H885" t="n">
         <v>8364</v>
@@ -26063,7 +26063,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G886" t="n">
-        <v>3.73864412307739</v>
+        <v>3.73864436149597</v>
       </c>
       <c r="H886" t="n">
         <v>2531</v>
@@ -26121,7 +26121,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H888" t="n">
         <v>8519</v>
@@ -26150,7 +26150,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H889" t="n">
         <v>14342</v>
@@ -26179,7 +26179,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H890" t="n">
         <v>20433</v>
@@ -26208,7 +26208,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H891" t="n">
         <v>58437</v>
@@ -26266,7 +26266,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G893" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H893" t="n">
         <v>22381</v>
@@ -26353,7 +26353,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H896" t="n">
         <v>7640</v>
@@ -26527,7 +26527,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73864412307739</v>
+        <v>3.73864436149597</v>
       </c>
       <c r="H902" t="n">
         <v>44451</v>
@@ -26556,7 +26556,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H903" t="n">
         <v>25646</v>
@@ -26672,7 +26672,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H907" t="n">
         <v>7190</v>
@@ -26788,7 +26788,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H911" t="n">
         <v>85</v>
@@ -26846,7 +26846,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H913" t="n">
         <v>1250</v>
@@ -26875,7 +26875,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H914" t="n">
         <v>1050</v>
@@ -26933,7 +26933,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H916" t="n">
         <v>35</v>
@@ -27020,7 +27020,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G919" t="n">
-        <v>3.82682013511658</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H919" t="n">
         <v>1905</v>
@@ -27049,7 +27049,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H920" t="n">
         <v>8574</v>
@@ -27136,7 +27136,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H923" t="n">
         <v>10338</v>
@@ -27165,7 +27165,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G924" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H924" t="n">
         <v>2250</v>
@@ -27194,7 +27194,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H925" t="n">
         <v>2087</v>
@@ -27223,7 +27223,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H927" t="n">
         <v>1386</v>
@@ -27281,7 +27281,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H930" t="n">
         <v>125</v>
@@ -27397,7 +27397,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H932" t="n">
         <v>468</v>
@@ -27426,7 +27426,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H933" t="n">
         <v>7761</v>
@@ -27484,7 +27484,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>4.07371091842651</v>
+        <v>4.07371139526367</v>
       </c>
       <c r="H935" t="n">
         <v>2555</v>
@@ -27542,7 +27542,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G937" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H937" t="n">
         <v>8262</v>
@@ -27658,7 +27658,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H941" t="n">
         <v>430</v>
@@ -27745,7 +27745,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G944" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H944" t="n">
         <v>8544</v>
@@ -27774,7 +27774,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H945" t="n">
         <v>3230</v>
@@ -27890,7 +27890,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G949" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H949" t="n">
         <v>1750</v>
@@ -28064,7 +28064,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G955" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H955" t="n">
         <v>4302</v>
@@ -28093,7 +28093,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>4.33823823928833</v>
+        <v>4.33823776245117</v>
       </c>
       <c r="H956" t="n">
         <v>800</v>
@@ -46253,6 +46253,35 @@
         <v>5717</v>
       </c>
       <c r="I1582" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1583" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1583" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="D1583" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="E1583" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F1583" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="G1583" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="H1583" t="n">
+        <v>2679</v>
+      </c>
+      <c r="I1583" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H2" t="n">
         <v>425</v>
@@ -456,7 +456,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H3" t="n">
         <v>650</v>
@@ -485,7 +485,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H5" t="n">
         <v>1105</v>
@@ -572,7 +572,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H7" t="n">
         <v>5900</v>
@@ -601,7 +601,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H8" t="n">
         <v>1000</v>
@@ -659,7 +659,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G10" t="n">
-        <v>4.19595146179199</v>
+        <v>4.19595193862915</v>
       </c>
       <c r="H10" t="n">
         <v>1712</v>
@@ -688,7 +688,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H11" t="n">
         <v>6680</v>
@@ -717,7 +717,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.08210897445679</v>
+        <v>4.08210802078247</v>
       </c>
       <c r="H18" t="n">
         <v>970</v>
@@ -920,7 +920,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968893051147</v>
       </c>
       <c r="H19" t="n">
         <v>3229</v>
@@ -978,7 +978,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.27726936340332</v>
+        <v>4.27726888656616</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H22" t="n">
         <v>3365</v>
@@ -1036,7 +1036,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>4.27726936340332</v>
+        <v>4.27726888656616</v>
       </c>
       <c r="H23" t="n">
         <v>3200</v>
@@ -1065,7 +1065,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>4.26100540161133</v>
+        <v>4.26100492477417</v>
       </c>
       <c r="H24" t="n">
         <v>2429</v>
@@ -1094,7 +1094,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>4.26100540161133</v>
+        <v>4.26100492477417</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H28" t="n">
         <v>350</v>
@@ -1210,7 +1210,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H29" t="n">
         <v>1969</v>
@@ -1239,7 +1239,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H30" t="n">
         <v>4377</v>
@@ -1355,7 +1355,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H34" t="n">
         <v>3736</v>
@@ -1413,7 +1413,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G36" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H36" t="n">
         <v>550</v>
@@ -1442,7 +1442,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079202651978</v>
       </c>
       <c r="H37" t="n">
         <v>1422</v>
@@ -1471,7 +1471,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G38" t="n">
-        <v>4.08210897445679</v>
+        <v>4.08210802078247</v>
       </c>
       <c r="H38" t="n">
         <v>950</v>
@@ -1500,7 +1500,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H39" t="n">
         <v>300</v>
@@ -1587,7 +1587,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221590042114</v>
       </c>
       <c r="H42" t="n">
         <v>450</v>
@@ -1616,7 +1616,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G43" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221590042114</v>
       </c>
       <c r="H43" t="n">
         <v>450</v>
@@ -1703,7 +1703,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968893051147</v>
       </c>
       <c r="H46" t="n">
         <v>980</v>
@@ -1848,7 +1848,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200133323669</v>
+        <v>3.95200085639954</v>
       </c>
       <c r="H51" t="n">
         <v>4885</v>
@@ -1877,7 +1877,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H52" t="n">
         <v>1056</v>
@@ -1906,7 +1906,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H53" t="n">
         <v>504</v>
@@ -1935,7 +1935,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.9438693523407</v>
+        <v>3.94386911392212</v>
       </c>
       <c r="H54" t="n">
         <v>2108</v>
@@ -2022,7 +2022,7 @@
         <v>4.75</v>
       </c>
       <c r="G57" t="n">
-        <v>3.86255311965942</v>
+        <v>3.86255216598511</v>
       </c>
       <c r="H57" t="n">
         <v>4200</v>
@@ -2051,7 +2051,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442066192627</v>
+        <v>3.85442018508911</v>
       </c>
       <c r="H58" t="n">
         <v>450</v>
@@ -2080,7 +2080,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.88694858551025</v>
+        <v>3.88694834709167</v>
       </c>
       <c r="H59" t="n">
         <v>1153</v>
@@ -2225,7 +2225,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>3.63486504554749</v>
+        <v>3.63486528396606</v>
       </c>
       <c r="H64" t="n">
         <v>2884</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991946220398</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H65" t="n">
         <v>4762</v>
@@ -2283,7 +2283,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>3.71618247032166</v>
+        <v>3.71618270874023</v>
       </c>
       <c r="H66" t="n">
         <v>23931</v>
@@ -2312,7 +2312,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.67552328109741</v>
+        <v>3.67552375793457</v>
       </c>
       <c r="H67" t="n">
         <v>5250</v>
@@ -2341,7 +2341,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.64299750328064</v>
+        <v>3.64299654960632</v>
       </c>
       <c r="H68" t="n">
         <v>7900</v>
@@ -2370,7 +2370,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926051139832</v>
+        <v>3.65926027297974</v>
       </c>
       <c r="H69" t="n">
         <v>14000</v>
@@ -2399,7 +2399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991946220398</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H70" t="n">
         <v>12720</v>
@@ -2428,7 +2428,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926051139832</v>
+        <v>3.65926027297974</v>
       </c>
       <c r="H71" t="n">
         <v>11150</v>
@@ -2457,7 +2457,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>3.67552328109741</v>
+        <v>3.67552375793457</v>
       </c>
       <c r="H72" t="n">
         <v>6400</v>
@@ -2486,7 +2486,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.69178676605225</v>
+        <v>3.6917872428894</v>
       </c>
       <c r="H73" t="n">
         <v>281949</v>
@@ -2544,7 +2544,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991946220398</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H75" t="n">
         <v>12819</v>
@@ -2573,7 +2573,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>3.67552328109741</v>
+        <v>3.67552375793457</v>
       </c>
       <c r="H76" t="n">
         <v>24183</v>
@@ -2602,7 +2602,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079202651978</v>
       </c>
       <c r="H77" t="n">
         <v>35243</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079202651978</v>
       </c>
       <c r="H78" t="n">
         <v>15007</v>
@@ -2660,7 +2660,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H79" t="n">
         <v>61552</v>
@@ -2718,7 +2718,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G81" t="n">
-        <v>4.19595146179199</v>
+        <v>4.19595193862915</v>
       </c>
       <c r="H81" t="n">
         <v>4817</v>
@@ -2776,7 +2776,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G83" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H83" t="n">
         <v>11228</v>
@@ -2805,7 +2805,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968893051147</v>
       </c>
       <c r="H84" t="n">
         <v>8061</v>
@@ -2863,7 +2863,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -2950,7 +2950,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H89" t="n">
         <v>8400</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079202651978</v>
       </c>
       <c r="H91" t="n">
         <v>30633</v>
@@ -3066,7 +3066,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G93" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221590042114</v>
       </c>
       <c r="H93" t="n">
         <v>37142</v>
@@ -3095,7 +3095,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737676620483</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H94" t="n">
         <v>35821</v>
@@ -3124,7 +3124,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.42363929748535</v>
+        <v>4.42363882064819</v>
       </c>
       <c r="H95" t="n">
         <v>35724</v>
@@ -3153,7 +3153,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.45616579055786</v>
+        <v>4.45616626739502</v>
       </c>
       <c r="H96" t="n">
         <v>5000</v>
@@ -3182,7 +3182,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.42363929748535</v>
+        <v>4.42363882064819</v>
       </c>
       <c r="H97" t="n">
         <v>12350</v>
@@ -3327,7 +3327,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.32605838775635</v>
+        <v>4.32605886459351</v>
       </c>
       <c r="H102" t="n">
         <v>20579</v>
@@ -3356,7 +3356,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869228363037</v>
+        <v>4.48869276046753</v>
       </c>
       <c r="H103" t="n">
         <v>18889</v>
@@ -3385,7 +3385,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869228363037</v>
+        <v>4.48869276046753</v>
       </c>
       <c r="H104" t="n">
         <v>6100</v>
@@ -3414,7 +3414,7 @@
         <v>5.5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.4724292755127</v>
+        <v>4.47242975234985</v>
       </c>
       <c r="H105" t="n">
         <v>895</v>
@@ -3443,7 +3443,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H106" t="n">
         <v>11075</v>
@@ -3472,7 +3472,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H107" t="n">
         <v>9254</v>
@@ -3530,7 +3530,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.55374574661255</v>
+        <v>4.55374670028687</v>
       </c>
       <c r="H109" t="n">
         <v>6650</v>
@@ -3559,7 +3559,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>4.43990230560303</v>
+        <v>4.43990278244019</v>
       </c>
       <c r="H110" t="n">
         <v>13298</v>
@@ -3617,7 +3617,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G112" t="n">
-        <v>4.32605838775635</v>
+        <v>4.32605886459351</v>
       </c>
       <c r="H112" t="n">
         <v>8648</v>
@@ -3762,7 +3762,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H117" t="n">
         <v>20886</v>
@@ -3791,7 +3791,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H118" t="n">
         <v>47283</v>
@@ -3849,7 +3849,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737676620483</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H120" t="n">
         <v>50907</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H121" t="n">
         <v>5333</v>
@@ -3907,7 +3907,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>4.34232234954834</v>
+        <v>4.3423228263855</v>
       </c>
       <c r="H122" t="n">
         <v>510822</v>
@@ -3936,7 +3936,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H123" t="n">
         <v>30275</v>
@@ -3994,7 +3994,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H125" t="n">
         <v>59141</v>
@@ -4023,7 +4023,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.55374574661255</v>
+        <v>4.55374670028687</v>
       </c>
       <c r="H126" t="n">
         <v>89802</v>
@@ -4052,7 +4052,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H127" t="n">
         <v>19970</v>
@@ -4081,7 +4081,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H128" t="n">
         <v>22395</v>
@@ -4110,7 +4110,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H129" t="n">
         <v>7536</v>
@@ -4168,7 +4168,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H131" t="n">
         <v>37064</v>
@@ -4197,7 +4197,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>4.76517009735107</v>
+        <v>4.76517057418823</v>
       </c>
       <c r="H132" t="n">
         <v>17792</v>
@@ -4255,7 +4255,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>4.91154098510742</v>
+        <v>4.91154050827026</v>
       </c>
       <c r="H134" t="n">
         <v>14070</v>
@@ -4284,7 +4284,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>5.07417392730713</v>
+        <v>5.07417440414429</v>
       </c>
       <c r="H135" t="n">
         <v>34938</v>
@@ -4342,7 +4342,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H137" t="n">
         <v>12072</v>
@@ -4429,7 +4429,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>5.07417392730713</v>
+        <v>5.07417440414429</v>
       </c>
       <c r="H140" t="n">
         <v>18825</v>
@@ -4458,7 +4458,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H141" t="n">
         <v>13207</v>
@@ -4516,7 +4516,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043836593628</v>
+        <v>5.09043788909912</v>
       </c>
       <c r="H143" t="n">
         <v>11836</v>
@@ -4545,7 +4545,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H144" t="n">
         <v>4290</v>
@@ -4574,7 +4574,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H145" t="n">
         <v>16119</v>
@@ -4603,7 +4603,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H146" t="n">
         <v>2211</v>
@@ -4632,7 +4632,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H147" t="n">
         <v>10023</v>
@@ -4661,7 +4661,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164695739746</v>
+        <v>5.04164743423462</v>
       </c>
       <c r="H148" t="n">
         <v>9600</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>4.8790135383606</v>
+        <v>4.87901449203491</v>
       </c>
       <c r="H149" t="n">
         <v>16280</v>
@@ -4748,7 +4748,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H151" t="n">
         <v>10138</v>
@@ -4777,7 +4777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G152" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H152" t="n">
         <v>7104</v>
@@ -4806,7 +4806,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H153" t="n">
         <v>5444</v>
@@ -4835,7 +4835,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>5.07417392730713</v>
+        <v>5.07417440414429</v>
       </c>
       <c r="H154" t="n">
         <v>9966</v>
@@ -4864,7 +4864,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538394927979</v>
       </c>
       <c r="H155" t="n">
         <v>13422</v>
@@ -4893,7 +4893,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>5.10670137405396</v>
+        <v>5.10670185089111</v>
       </c>
       <c r="H156" t="n">
         <v>11754</v>
@@ -4922,7 +4922,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H157" t="n">
         <v>4698</v>
@@ -4951,7 +4951,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H158" t="n">
         <v>9550</v>
@@ -4980,7 +4980,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043836593628</v>
+        <v>5.09043788909912</v>
       </c>
       <c r="H159" t="n">
         <v>11350</v>
@@ -5038,7 +5038,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164695739746</v>
+        <v>5.04164743423462</v>
       </c>
       <c r="H161" t="n">
         <v>3098</v>
@@ -5067,7 +5067,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G162" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H162" t="n">
         <v>7250</v>
@@ -5096,7 +5096,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G163" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H163" t="n">
         <v>7961</v>
@@ -5125,7 +5125,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>4.94406700134277</v>
+        <v>4.94406652450562</v>
       </c>
       <c r="H164" t="n">
         <v>28419</v>
@@ -5154,7 +5154,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G165" t="n">
-        <v>4.9278039932251</v>
+        <v>4.92780351638794</v>
       </c>
       <c r="H165" t="n">
         <v>10999</v>
@@ -5183,7 +5183,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H166" t="n">
         <v>16468</v>
@@ -5212,7 +5212,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G167" t="n">
-        <v>4.89527702331543</v>
+        <v>4.89527797698975</v>
       </c>
       <c r="H167" t="n">
         <v>20850</v>
@@ -5241,7 +5241,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G168" t="n">
-        <v>4.9278039932251</v>
+        <v>4.92780351638794</v>
       </c>
       <c r="H168" t="n">
         <v>6210</v>
@@ -5270,7 +5270,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.94406700134277</v>
+        <v>4.94406652450562</v>
       </c>
       <c r="H169" t="n">
         <v>2656</v>
@@ -5299,7 +5299,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.89527702331543</v>
+        <v>4.89527797698975</v>
       </c>
       <c r="H170" t="n">
         <v>15167</v>
@@ -5328,7 +5328,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>4.91154098510742</v>
+        <v>4.91154050827026</v>
       </c>
       <c r="H171" t="n">
         <v>16947</v>
@@ -5357,7 +5357,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H172" t="n">
         <v>2308</v>
@@ -5386,7 +5386,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.96033096313477</v>
+        <v>4.96033048629761</v>
       </c>
       <c r="H173" t="n">
         <v>5030</v>
@@ -5415,7 +5415,7 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>4.8790135383606</v>
+        <v>4.87901449203491</v>
       </c>
       <c r="H174" t="n">
         <v>7490</v>
@@ -5473,7 +5473,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H176" t="n">
         <v>18455</v>
@@ -5502,7 +5502,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>5.25307178497314</v>
+        <v>5.25307130813599</v>
       </c>
       <c r="H177" t="n">
         <v>49926</v>
@@ -5676,7 +5676,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>5.38317823410034</v>
+        <v>5.3831787109375</v>
       </c>
       <c r="H183" t="n">
         <v>5662</v>
@@ -5705,7 +5705,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.36691474914551</v>
+        <v>5.36691522598267</v>
       </c>
       <c r="H184" t="n">
         <v>16090</v>
@@ -5734,7 +5734,7 @@
         <v>6.5</v>
       </c>
       <c r="G185" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H185" t="n">
         <v>14887</v>
@@ -5763,7 +5763,7 @@
         <v>6.5</v>
       </c>
       <c r="G186" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H186" t="n">
         <v>11690</v>
@@ -5792,7 +5792,7 @@
         <v>6.5</v>
       </c>
       <c r="G187" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>6.5</v>
       </c>
       <c r="G188" t="n">
-        <v>5.28559875488281</v>
+        <v>5.28559827804565</v>
       </c>
       <c r="H188" t="n">
         <v>10480</v>
@@ -5850,7 +5850,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922739028931</v>
+        <v>5.13922786712646</v>
       </c>
       <c r="H189" t="n">
         <v>10921</v>
@@ -5879,7 +5879,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538394927979</v>
       </c>
       <c r="H190" t="n">
         <v>5989</v>
@@ -5908,7 +5908,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G191" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H191" t="n">
         <v>110919</v>
@@ -5937,7 +5937,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G192" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H192" t="n">
         <v>2290</v>
@@ -5966,7 +5966,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H193" t="n">
         <v>4766</v>
@@ -5995,7 +5995,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G194" t="n">
-        <v>5.20428228378296</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H194" t="n">
         <v>2077</v>
@@ -6053,7 +6053,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>5.18765354156494</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H196" t="n">
         <v>5900</v>
@@ -6198,7 +6198,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G201" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H201" t="n">
         <v>8833</v>
@@ -6256,7 +6256,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067060470581</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H203" t="n">
         <v>5722</v>
@@ -6314,7 +6314,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G205" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H205" t="n">
         <v>1300</v>
@@ -6343,7 +6343,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H206" t="n">
         <v>4898</v>
@@ -6372,7 +6372,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067060470581</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H207" t="n">
         <v>5465</v>
@@ -6517,7 +6517,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368766784668</v>
+        <v>5.45368814468384</v>
       </c>
       <c r="H212" t="n">
         <v>6658</v>
@@ -6604,7 +6604,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H215" t="n">
         <v>22458</v>
@@ -6633,7 +6633,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368766784668</v>
+        <v>5.45368814468384</v>
       </c>
       <c r="H216" t="n">
         <v>10530</v>
@@ -6662,7 +6662,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G217" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H217" t="n">
         <v>7967</v>
@@ -6691,7 +6691,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H218" t="n">
         <v>6727</v>
@@ -6749,7 +6749,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H220" t="n">
         <v>4090</v>
@@ -6836,7 +6836,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H223" t="n">
         <v>3507</v>
@@ -6894,7 +6894,7 @@
         <v>7</v>
       </c>
       <c r="G225" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H225" t="n">
         <v>7539</v>
@@ -6952,7 +6952,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H227" t="n">
         <v>38319</v>
@@ -7010,7 +7010,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G229" t="n">
-        <v>5.96912813186646</v>
+        <v>5.9691276550293</v>
       </c>
       <c r="H229" t="n">
         <v>37060</v>
@@ -7039,7 +7039,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>5.93587350845337</v>
+        <v>5.93587398529053</v>
       </c>
       <c r="H230" t="n">
         <v>14060</v>
@@ -7068,7 +7068,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G231" t="n">
-        <v>5.80285739898682</v>
+        <v>5.80285692214966</v>
       </c>
       <c r="H231" t="n">
         <v>11590</v>
@@ -7097,7 +7097,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H232" t="n">
         <v>6952</v>
@@ -7126,7 +7126,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H233" t="n">
         <v>4553</v>
@@ -7155,7 +7155,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>5.85273790359497</v>
+        <v>5.85273838043213</v>
       </c>
       <c r="H234" t="n">
         <v>12940</v>
@@ -7184,7 +7184,7 @@
         <v>7</v>
       </c>
       <c r="G235" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H235" t="n">
         <v>7545</v>
@@ -7213,7 +7213,7 @@
         <v>7</v>
       </c>
       <c r="G236" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H236" t="n">
         <v>2000</v>
@@ -7300,7 +7300,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>5.80285739898682</v>
+        <v>5.80285692214966</v>
       </c>
       <c r="H239" t="n">
         <v>8443</v>
@@ -7329,7 +7329,7 @@
         <v>7</v>
       </c>
       <c r="G240" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H240" t="n">
         <v>3750</v>
@@ -7358,7 +7358,7 @@
         <v>7</v>
       </c>
       <c r="G241" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H241" t="n">
         <v>4000</v>
@@ -7387,7 +7387,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G242" t="n">
-        <v>5.71972227096558</v>
+        <v>5.71972179412842</v>
       </c>
       <c r="H242" t="n">
         <v>6410</v>
@@ -7416,7 +7416,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G243" t="n">
-        <v>5.76960229873657</v>
+        <v>5.76960277557373</v>
       </c>
       <c r="H243" t="n">
         <v>1500</v>
@@ -7474,7 +7474,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G245" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H245" t="n">
         <v>4200</v>
@@ -7503,7 +7503,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G246" t="n">
-        <v>5.71972227096558</v>
+        <v>5.71972179412842</v>
       </c>
       <c r="H246" t="n">
         <v>2137</v>
@@ -7532,7 +7532,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G247" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H247" t="n">
         <v>5180</v>
@@ -7561,7 +7561,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G248" t="n">
-        <v>5.71972227096558</v>
+        <v>5.71972179412842</v>
       </c>
       <c r="H248" t="n">
         <v>2125</v>
@@ -7590,7 +7590,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H249" t="n">
         <v>6312</v>
@@ -7619,7 +7619,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G250" t="n">
-        <v>5.58670473098755</v>
+        <v>5.58670425415039</v>
       </c>
       <c r="H250" t="n">
         <v>875</v>
@@ -7648,7 +7648,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H251" t="n">
         <v>1386</v>
@@ -7677,7 +7677,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G252" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H252" t="n">
         <v>8006</v>
@@ -7706,7 +7706,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H253" t="n">
         <v>472</v>
@@ -7735,7 +7735,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G254" t="n">
-        <v>5.58670473098755</v>
+        <v>5.58670425415039</v>
       </c>
       <c r="H254" t="n">
         <v>2610</v>
@@ -7764,7 +7764,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G255" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H255" t="n">
         <v>1900</v>
@@ -7793,7 +7793,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H257" t="n">
         <v>3560</v>
@@ -7851,7 +7851,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G258" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H258" t="n">
         <v>4652</v>
@@ -7880,7 +7880,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H259" t="n">
         <v>2350</v>
@@ -7909,7 +7909,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H260" t="n">
         <v>1200</v>
@@ -7938,7 +7938,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H261" t="n">
         <v>2105</v>
@@ -7996,7 +7996,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H263" t="n">
         <v>8019</v>
@@ -8054,7 +8054,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G265" t="n">
-        <v>5.61995887756348</v>
+        <v>5.61995935440063</v>
       </c>
       <c r="H265" t="n">
         <v>1620</v>
@@ -8083,7 +8083,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H266" t="n">
         <v>9438</v>
@@ -8141,7 +8141,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H268" t="n">
         <v>1450</v>
@@ -8199,7 +8199,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H270" t="n">
         <v>5650</v>
@@ -8228,7 +8228,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G271" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H271" t="n">
         <v>23690</v>
@@ -8286,7 +8286,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H273" t="n">
         <v>13409</v>
@@ -8315,7 +8315,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H274" t="n">
         <v>4619</v>
@@ -8344,7 +8344,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H275" t="n">
         <v>428</v>
@@ -8373,7 +8373,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H276" t="n">
         <v>7400</v>
@@ -8518,7 +8518,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H281" t="n">
         <v>7624</v>
@@ -8576,7 +8576,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G283" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H283" t="n">
         <v>4800</v>
@@ -8634,7 +8634,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H285" t="n">
         <v>15427</v>
@@ -8663,7 +8663,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H286" t="n">
         <v>32500</v>
@@ -8692,7 +8692,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H287" t="n">
         <v>1750</v>
@@ -8721,7 +8721,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H288" t="n">
         <v>1973</v>
@@ -8779,7 +8779,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G290" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H290" t="n">
         <v>16096</v>
@@ -8808,7 +8808,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H291" t="n">
         <v>4539</v>
@@ -8837,7 +8837,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H292" t="n">
         <v>31220</v>
@@ -8866,7 +8866,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H293" t="n">
         <v>14001</v>
@@ -8924,7 +8924,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H295" t="n">
         <v>22500</v>
@@ -8953,7 +8953,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H296" t="n">
         <v>24602</v>
@@ -8982,7 +8982,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H297" t="n">
         <v>7700</v>
@@ -9011,7 +9011,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H298" t="n">
         <v>17311</v>
@@ -9040,7 +9040,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>5.43706035614014</v>
+        <v>5.43706083297729</v>
       </c>
       <c r="H299" t="n">
         <v>4580</v>
@@ -9069,7 +9069,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H300" t="n">
         <v>4728</v>
@@ -9156,7 +9156,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067060470581</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H303" t="n">
         <v>4716</v>
@@ -9185,7 +9185,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067060470581</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H304" t="n">
         <v>1563</v>
@@ -9330,7 +9330,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067060470581</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H309" t="n">
         <v>3800</v>
@@ -9388,7 +9388,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H311" t="n">
         <v>15780</v>
@@ -9417,7 +9417,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>5.18765354156494</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H312" t="n">
         <v>4873</v>
@@ -9562,7 +9562,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>5.12114572525024</v>
+        <v>5.1211462020874</v>
       </c>
       <c r="H317" t="n">
         <v>4420</v>
@@ -9678,7 +9678,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067060470581</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H321" t="n">
         <v>5361</v>
@@ -9707,7 +9707,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H322" t="n">
         <v>6754</v>
@@ -9736,7 +9736,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G323" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H323" t="n">
         <v>11714</v>
@@ -9765,7 +9765,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G324" t="n">
-        <v>5.20428228378296</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H324" t="n">
         <v>4701</v>
@@ -9794,7 +9794,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G325" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H325" t="n">
         <v>3556</v>
@@ -9823,7 +9823,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H326" t="n">
         <v>4390</v>
@@ -9939,7 +9939,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067060470581</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H330" t="n">
         <v>5585</v>
@@ -9968,7 +9968,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>5.33729887008667</v>
+        <v>5.33729839324951</v>
       </c>
       <c r="H331" t="n">
         <v>11425</v>
@@ -9997,7 +9997,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G332" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H332" t="n">
         <v>8128</v>
@@ -10055,7 +10055,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G334" t="n">
-        <v>5.20428228378296</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H334" t="n">
         <v>10830</v>
@@ -10084,7 +10084,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G335" t="n">
-        <v>5.20428228378296</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H335" t="n">
         <v>11568</v>
@@ -10113,7 +10113,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G336" t="n">
-        <v>5.20428228378296</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G337" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H337" t="n">
         <v>15623</v>
@@ -10171,7 +10171,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G338" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H338" t="n">
         <v>2453</v>
@@ -10200,7 +10200,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G339" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H339" t="n">
         <v>2836</v>
@@ -10229,7 +10229,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G340" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H340" t="n">
         <v>2000</v>
@@ -10287,7 +10287,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H342" t="n">
         <v>2043</v>
@@ -10345,7 +10345,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H344" t="n">
         <v>13660</v>
@@ -10432,7 +10432,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G347" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H347" t="n">
         <v>5755</v>
@@ -10606,7 +10606,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G353" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H353" t="n">
         <v>6420</v>
@@ -10635,7 +10635,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H354" t="n">
         <v>7088</v>
@@ -10693,7 +10693,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H356" t="n">
         <v>2400</v>
@@ -10722,7 +10722,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H358" t="n">
         <v>4600</v>
@@ -10809,7 +10809,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>5.18765354156494</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H360" t="n">
         <v>1600</v>
@@ -10838,7 +10838,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G361" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H361" t="n">
         <v>1507</v>
@@ -10867,7 +10867,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G362" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H362" t="n">
         <v>1294</v>
@@ -10896,7 +10896,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.28741693496704</v>
+        <v>5.2874174118042</v>
       </c>
       <c r="H363" t="n">
         <v>4848</v>
@@ -10983,7 +10983,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102766036987</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H366" t="n">
         <v>710</v>
@@ -11012,7 +11012,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H367" t="n">
         <v>112</v>
@@ -11041,7 +11041,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G368" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067060470581</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H373" t="n">
         <v>4742</v>
@@ -11331,7 +11331,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102766036987</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H378" t="n">
         <v>112</v>
@@ -11360,7 +11360,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102766036987</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102766036987</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G381" t="n">
-        <v>5.12114572525024</v>
+        <v>5.1211462020874</v>
       </c>
       <c r="H381" t="n">
         <v>1071</v>
@@ -11563,7 +11563,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G386" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H386" t="n">
         <v>400</v>
@@ -11592,7 +11592,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G387" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11679,7 +11679,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G390" t="n">
-        <v>5.22090864181519</v>
+        <v>5.22090911865234</v>
       </c>
       <c r="H390" t="n">
         <v>1000</v>
@@ -11795,7 +11795,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G394" t="n">
-        <v>5.18765354156494</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H394" t="n">
         <v>1700</v>
@@ -11824,7 +11824,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G395" t="n">
-        <v>5.18765354156494</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H395" t="n">
         <v>1098</v>
@@ -11853,7 +11853,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G396" t="n">
-        <v>5.18765354156494</v>
+        <v>5.18765449523926</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -12027,7 +12027,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>4.90499401092529</v>
+        <v>4.90499448776245</v>
       </c>
       <c r="H402" t="n">
         <v>2893</v>
@@ -12056,7 +12056,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>4.8384861946106</v>
+        <v>4.83848571777344</v>
       </c>
       <c r="H403" t="n">
         <v>339</v>
@@ -12085,7 +12085,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>4.88836669921875</v>
+        <v>4.88836717605591</v>
       </c>
       <c r="H404" t="n">
         <v>32</v>
@@ -12114,7 +12114,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G405" t="n">
-        <v>4.8384861946106</v>
+        <v>4.83848571777344</v>
       </c>
       <c r="H405" t="n">
         <v>5440</v>
@@ -12172,7 +12172,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>4.50594425201416</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H407" t="n">
         <v>9154</v>
@@ -12201,7 +12201,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>4.48931646347046</v>
+        <v>4.4893159866333</v>
       </c>
       <c r="H408" t="n">
         <v>6788</v>
@@ -12230,7 +12230,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G409" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884181976318</v>
       </c>
       <c r="H409" t="n">
         <v>700</v>
@@ -12259,7 +12259,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G410" t="n">
-        <v>4.78860425949097</v>
+        <v>4.78860473632812</v>
       </c>
       <c r="H410" t="n">
         <v>300</v>
@@ -12288,7 +12288,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G411" t="n">
-        <v>4.70546865463257</v>
+        <v>4.70546817779541</v>
       </c>
       <c r="H411" t="n">
         <v>826</v>
@@ -12346,7 +12346,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H413" t="n">
         <v>6760</v>
@@ -12404,7 +12404,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>4.50594425201416</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H415" t="n">
         <v>970</v>
@@ -12433,7 +12433,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>4.43943500518799</v>
+        <v>4.43943548202515</v>
       </c>
       <c r="H416" t="n">
         <v>3039</v>
@@ -12462,7 +12462,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>4.48931646347046</v>
+        <v>4.4893159866333</v>
       </c>
       <c r="H417" t="n">
         <v>4244</v>
@@ -12520,7 +12520,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>4.35629892349243</v>
+        <v>4.35629940032959</v>
       </c>
       <c r="H419" t="n">
         <v>5206</v>
@@ -12607,7 +12607,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H422" t="n">
         <v>7657</v>
@@ -12752,7 +12752,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>4.55582475662231</v>
+        <v>4.55582523345947</v>
       </c>
       <c r="H427" t="n">
         <v>10094</v>
@@ -12810,7 +12810,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G429" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884181976318</v>
       </c>
       <c r="H429" t="n">
         <v>3246</v>
@@ -12839,7 +12839,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>4.50594425201416</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H430" t="n">
         <v>7925</v>
@@ -12984,7 +12984,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884181976318</v>
       </c>
       <c r="H435" t="n">
         <v>2711</v>
@@ -13013,7 +13013,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>4.78860425949097</v>
+        <v>4.78860473632812</v>
       </c>
       <c r="H436" t="n">
         <v>500</v>
@@ -13100,7 +13100,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G439" t="n">
-        <v>4.75535011291504</v>
+        <v>4.75534963607788</v>
       </c>
       <c r="H439" t="n">
         <v>4000</v>
@@ -13129,7 +13129,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G440" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H440" t="n">
         <v>700</v>
@@ -13158,7 +13158,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H441" t="n">
         <v>4384</v>
@@ -13216,7 +13216,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H443" t="n">
         <v>3174</v>
@@ -13274,7 +13274,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H445" t="n">
         <v>1010</v>
@@ -13419,7 +13419,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H450" t="n">
         <v>1700</v>
@@ -13448,7 +13448,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H451" t="n">
         <v>1487</v>
@@ -13477,7 +13477,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H452" t="n">
         <v>500</v>
@@ -13506,7 +13506,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H454" t="n">
         <v>4800</v>
@@ -13564,7 +13564,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H455" t="n">
         <v>5500</v>
@@ -13593,7 +13593,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G463" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H463" t="n">
         <v>5</v>
@@ -13854,7 +13854,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H465" t="n">
         <v>205</v>
@@ -13912,7 +13912,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H467" t="n">
         <v>1464</v>
@@ -13941,7 +13941,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H468" t="n">
         <v>810</v>
@@ -13970,7 +13970,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H469" t="n">
         <v>646</v>
@@ -13999,7 +13999,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H470" t="n">
         <v>1000</v>
@@ -14028,7 +14028,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -14057,7 +14057,7 @@
         <v>6</v>
       </c>
       <c r="G472" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H472" t="n">
         <v>2091</v>
@@ -14086,7 +14086,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H473" t="n">
         <v>9179</v>
@@ -14202,7 +14202,7 @@
         <v>5.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H477" t="n">
         <v>350</v>
@@ -14260,7 +14260,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G479" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H479" t="n">
         <v>5905</v>
@@ -14289,7 +14289,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H480" t="n">
         <v>20980</v>
@@ -14318,7 +14318,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H481" t="n">
         <v>500</v>
@@ -14347,7 +14347,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H482" t="n">
         <v>1405</v>
@@ -14376,7 +14376,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H487" t="n">
         <v>3597</v>
@@ -14695,7 +14695,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H494" t="n">
         <v>3377</v>
@@ -14724,7 +14724,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G495" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H496" t="n">
         <v>11723</v>
@@ -14898,7 +14898,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G501" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H501" t="n">
         <v>705</v>
@@ -14927,7 +14927,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G502" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H507" t="n">
         <v>3700</v>
@@ -15101,7 +15101,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H511" t="n">
         <v>2505</v>
@@ -15217,7 +15217,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H512" t="n">
         <v>2050</v>
@@ -15362,7 +15362,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G521" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H521" t="n">
         <v>341</v>
@@ -15565,7 +15565,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G524" t="n">
-        <v>4.99485206604004</v>
+        <v>4.9948525428772</v>
       </c>
       <c r="H524" t="n">
         <v>1780</v>
@@ -15594,7 +15594,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H525" t="n">
         <v>235</v>
@@ -15681,7 +15681,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H528" t="n">
         <v>700</v>
@@ -15710,7 +15710,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008813858032</v>
       </c>
       <c r="H530" t="n">
         <v>1270</v>
@@ -15855,7 +15855,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90961599349976</v>
+        <v>4.90961647033691</v>
       </c>
       <c r="H534" t="n">
         <v>2167</v>
@@ -15884,7 +15884,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H535" t="n">
         <v>2280</v>
@@ -15913,7 +15913,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H536" t="n">
         <v>2123</v>
@@ -15942,7 +15942,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H537" t="n">
         <v>1000</v>
@@ -15971,7 +15971,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H538" t="n">
         <v>1776</v>
@@ -16029,7 +16029,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H540" t="n">
         <v>350</v>
@@ -16058,7 +16058,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H542" t="n">
         <v>2760</v>
@@ -16116,7 +16116,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G543" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>4.87552118301392</v>
+        <v>4.87552070617676</v>
       </c>
       <c r="H544" t="n">
         <v>421</v>
@@ -16174,7 +16174,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H545" t="n">
         <v>2895</v>
@@ -16232,7 +16232,7 @@
         <v>5.5</v>
       </c>
       <c r="G547" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H547" t="n">
         <v>2535</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.48343467712402</v>
+        <v>4.48343420028687</v>
       </c>
       <c r="H549" t="n">
         <v>1022</v>
@@ -16348,7 +16348,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>4.48343467712402</v>
+        <v>4.48343420028687</v>
       </c>
       <c r="H551" t="n">
         <v>1200</v>
@@ -16406,7 +16406,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>4.36410284042358</v>
+        <v>4.36410236358643</v>
       </c>
       <c r="H553" t="n">
         <v>4928</v>
@@ -16435,7 +16435,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G554" t="n">
-        <v>4.44933891296387</v>
+        <v>4.44933938980103</v>
       </c>
       <c r="H554" t="n">
         <v>608</v>
@@ -16580,7 +16580,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G559" t="n">
-        <v>4.53457546234131</v>
+        <v>4.53457593917847</v>
       </c>
       <c r="H559" t="n">
         <v>750</v>
@@ -16609,7 +16609,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H560" t="n">
         <v>2687</v>
@@ -16638,7 +16638,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H561" t="n">
         <v>460</v>
@@ -16667,7 +16667,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G563" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H563" t="n">
         <v>2000</v>
@@ -17044,7 +17044,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H575" t="n">
         <v>20</v>
@@ -17073,7 +17073,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.80733203887939</v>
+        <v>4.80733251571655</v>
       </c>
       <c r="H580" t="n">
         <v>3158</v>
@@ -17334,7 +17334,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H585" t="n">
         <v>360</v>
@@ -17624,7 +17624,7 @@
         <v>5.5</v>
       </c>
       <c r="G595" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H595" t="n">
         <v>6710</v>
@@ -17682,7 +17682,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H597" t="n">
         <v>607</v>
@@ -17711,7 +17711,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G598" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H598" t="n">
         <v>65</v>
@@ -18059,7 +18059,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H610" t="n">
         <v>1351</v>
@@ -18088,7 +18088,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H611" t="n">
         <v>510</v>
@@ -18117,7 +18117,7 @@
         <v>5.5</v>
       </c>
       <c r="G612" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H612" t="n">
         <v>34</v>
@@ -18146,7 +18146,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H613" t="n">
         <v>186</v>
@@ -18320,7 +18320,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H619" t="n">
         <v>675</v>
@@ -18494,7 +18494,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>4.80733203887939</v>
+        <v>4.80733251571655</v>
       </c>
       <c r="H625" t="n">
         <v>1866</v>
@@ -18523,7 +18523,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H626" t="n">
         <v>110</v>
@@ -18552,7 +18552,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H627" t="n">
         <v>10</v>
@@ -18581,7 +18581,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H628" t="n">
         <v>400</v>
@@ -18610,7 +18610,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H629" t="n">
         <v>110</v>
@@ -18697,7 +18697,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H632" t="n">
         <v>872</v>
@@ -18726,7 +18726,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H633" t="n">
         <v>1703</v>
@@ -18755,7 +18755,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H634" t="n">
         <v>10</v>
@@ -18813,7 +18813,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G636" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H636" t="n">
         <v>1898</v>
@@ -18842,7 +18842,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G637" t="n">
-        <v>5.01189947128296</v>
+        <v>5.01189994812012</v>
       </c>
       <c r="H637" t="n">
         <v>67041</v>
@@ -18871,7 +18871,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G638" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H638" t="n">
         <v>3800</v>
@@ -18958,7 +18958,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>5.01189947128296</v>
+        <v>5.01189994812012</v>
       </c>
       <c r="H641" t="n">
         <v>3920</v>
@@ -18987,7 +18987,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H642" t="n">
         <v>5765</v>
@@ -19016,7 +19016,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>5.25056076049805</v>
+        <v>5.25056171417236</v>
       </c>
       <c r="H643" t="n">
         <v>4245</v>
@@ -19045,7 +19045,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G644" t="n">
-        <v>5.35284519195557</v>
+        <v>5.35284566879272</v>
       </c>
       <c r="H644" t="n">
         <v>15820</v>
@@ -19103,7 +19103,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H646" t="n">
         <v>12764</v>
@@ -19132,7 +19132,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G647" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H647" t="n">
         <v>1345</v>
@@ -19161,7 +19161,7 @@
         <v>6</v>
       </c>
       <c r="G648" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H648" t="n">
         <v>1200</v>
@@ -19248,7 +19248,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H651" t="n">
         <v>2400</v>
@@ -19335,7 +19335,7 @@
         <v>6</v>
       </c>
       <c r="G654" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H654" t="n">
         <v>3833</v>
@@ -19422,7 +19422,7 @@
         <v>6</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H657" t="n">
         <v>512</v>
@@ -19451,7 +19451,7 @@
         <v>6</v>
       </c>
       <c r="G658" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H658" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H659" t="n">
         <v>618</v>
@@ -19509,7 +19509,7 @@
         <v>6</v>
       </c>
       <c r="G660" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H660" t="n">
         <v>110</v>
@@ -19538,7 +19538,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H661" t="n">
         <v>160</v>
@@ -19596,7 +19596,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008813858032</v>
       </c>
       <c r="H663" t="n">
         <v>300</v>
@@ -19857,7 +19857,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G672" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H672" t="n">
         <v>1371</v>
@@ -19886,7 +19886,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G673" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>6</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H674" t="n">
         <v>1922</v>
@@ -19973,7 +19973,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H676" t="n">
         <v>3802</v>
@@ -20002,7 +20002,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H677" t="n">
         <v>1377</v>
@@ -20031,7 +20031,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>6</v>
       </c>
       <c r="G679" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H679" t="n">
         <v>4219</v>
@@ -20089,7 +20089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H680" t="n">
         <v>893</v>
@@ -20118,7 +20118,7 @@
         <v>6</v>
       </c>
       <c r="G681" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H681" t="n">
         <v>1250</v>
@@ -20147,7 +20147,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H682" t="n">
         <v>6283</v>
@@ -20205,7 +20205,7 @@
         <v>6</v>
       </c>
       <c r="G684" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H684" t="n">
         <v>3929</v>
@@ -20292,7 +20292,7 @@
         <v>6</v>
       </c>
       <c r="G687" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H687" t="n">
         <v>3300</v>
@@ -20350,7 +20350,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H689" t="n">
         <v>820</v>
@@ -20379,7 +20379,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H690" t="n">
         <v>700</v>
@@ -20408,7 +20408,7 @@
         <v>6</v>
       </c>
       <c r="G691" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H691" t="n">
         <v>3324</v>
@@ -20437,7 +20437,7 @@
         <v>6</v>
       </c>
       <c r="G692" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H692" t="n">
         <v>3119</v>
@@ -20466,7 +20466,7 @@
         <v>6</v>
       </c>
       <c r="G693" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H693" t="n">
         <v>2354</v>
@@ -20553,7 +20553,7 @@
         <v>6</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H696" t="n">
         <v>10</v>
@@ -20669,7 +20669,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H700" t="n">
         <v>807</v>
@@ -20785,7 +20785,7 @@
         <v>6</v>
       </c>
       <c r="G704" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H704" t="n">
         <v>400</v>
@@ -21162,7 +21162,7 @@
         <v>5.75</v>
       </c>
       <c r="G717" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H717" t="n">
         <v>1661</v>
@@ -21191,7 +21191,7 @@
         <v>5.75</v>
       </c>
       <c r="G718" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H718" t="n">
         <v>2500</v>
@@ -21220,7 +21220,7 @@
         <v>5.75</v>
       </c>
       <c r="G719" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>5.75</v>
       </c>
       <c r="G720" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21278,7 +21278,7 @@
         <v>5.75</v>
       </c>
       <c r="G721" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21394,7 +21394,7 @@
         <v>5.75</v>
       </c>
       <c r="G725" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H725" t="n">
         <v>1926</v>
@@ -21423,7 +21423,7 @@
         <v>5.75</v>
       </c>
       <c r="G726" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H726" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>5.75</v>
       </c>
       <c r="G727" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H727" t="n">
         <v>6821</v>
@@ -21481,7 +21481,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G728" t="n">
-        <v>4.93783187866211</v>
+        <v>4.93783235549927</v>
       </c>
       <c r="H728" t="n">
         <v>2930</v>
@@ -21510,7 +21510,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.93783187866211</v>
+        <v>4.93783235549927</v>
       </c>
       <c r="H729" t="n">
         <v>6873</v>
@@ -21568,7 +21568,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.89374494552612</v>
+        <v>4.89374446868896</v>
       </c>
       <c r="H731" t="n">
         <v>350</v>
@@ -21858,7 +21858,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G741" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H741" t="n">
         <v>966</v>
@@ -21887,7 +21887,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H742" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H752" t="n">
         <v>233</v>
@@ -22206,7 +22206,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H753" t="n">
         <v>2500</v>
@@ -22235,7 +22235,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H754" t="n">
         <v>4845</v>
@@ -22264,7 +22264,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G755" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H755" t="n">
         <v>5770</v>
@@ -22583,7 +22583,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G766" t="n">
-        <v>4.45286703109741</v>
+        <v>4.45286655426025</v>
       </c>
       <c r="H766" t="n">
         <v>6689</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H769" t="n">
         <v>2000</v>
@@ -22699,7 +22699,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G770" t="n">
-        <v>4.89374494552612</v>
+        <v>4.89374446868896</v>
       </c>
       <c r="H770" t="n">
         <v>3256</v>
@@ -23395,7 +23395,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>4.89374494552612</v>
+        <v>4.89374446868896</v>
       </c>
       <c r="H794" t="n">
         <v>1641</v>
@@ -23946,7 +23946,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H813" t="n">
         <v>1618</v>
@@ -23975,7 +23975,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24004,7 +24004,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H815" t="n">
         <v>1188</v>
@@ -24033,7 +24033,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H816" t="n">
         <v>10</v>
@@ -24062,7 +24062,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H817" t="n">
         <v>365</v>
@@ -24091,7 +24091,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H818" t="n">
         <v>700</v>
@@ -24207,7 +24207,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G822" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H822" t="n">
         <v>340</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H827" t="n">
         <v>2876</v>
@@ -24497,7 +24497,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G832" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H832" t="n">
         <v>207</v>
@@ -24526,7 +24526,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H833" t="n">
         <v>1050</v>
@@ -24555,7 +24555,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G835" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H835" t="n">
         <v>1</v>
@@ -24642,7 +24642,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H837" t="n">
         <v>1803</v>
@@ -24729,7 +24729,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H840" t="n">
         <v>609</v>
@@ -24758,7 +24758,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G841" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H841" t="n">
         <v>4500</v>
@@ -24787,7 +24787,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H842" t="n">
         <v>2500</v>
@@ -24816,7 +24816,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H843" t="n">
         <v>1253</v>
@@ -24874,7 +24874,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G845" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H845" t="n">
         <v>796</v>
@@ -25048,7 +25048,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.0913462638855</v>
+        <v>4.09134674072266</v>
       </c>
       <c r="H851" t="n">
         <v>2200</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H856" t="n">
         <v>3097</v>
@@ -25280,7 +25280,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G859" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H859" t="n">
         <v>6840</v>
@@ -25338,7 +25338,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G861" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H861" t="n">
         <v>1733</v>
@@ -25367,7 +25367,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H862" t="n">
         <v>1450</v>
@@ -25396,7 +25396,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H863" t="n">
         <v>3550</v>
@@ -25425,7 +25425,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H864" t="n">
         <v>6616</v>
@@ -25483,7 +25483,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H866" t="n">
         <v>20519</v>
@@ -25541,7 +25541,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G868" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H868" t="n">
         <v>15412</v>
@@ -25570,7 +25570,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H869" t="n">
         <v>3776</v>
@@ -25599,7 +25599,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H870" t="n">
         <v>4073</v>
@@ -25686,7 +25686,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H873" t="n">
         <v>5847</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H875" t="n">
         <v>3194</v>
@@ -25802,7 +25802,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G877" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H877" t="n">
         <v>13736</v>
@@ -25947,7 +25947,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H882" t="n">
         <v>15378</v>
@@ -25976,7 +25976,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G883" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H883" t="n">
         <v>18373</v>
@@ -26034,7 +26034,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>3.68573904037476</v>
+        <v>3.6857385635376</v>
       </c>
       <c r="H885" t="n">
         <v>8364</v>
@@ -26063,7 +26063,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G886" t="n">
-        <v>3.73864436149597</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H886" t="n">
         <v>2531</v>
@@ -26092,7 +26092,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H887" t="n">
         <v>5091</v>
@@ -26121,7 +26121,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H888" t="n">
         <v>8519</v>
@@ -26150,7 +26150,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H889" t="n">
         <v>14342</v>
@@ -26179,7 +26179,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H890" t="n">
         <v>20433</v>
@@ -26208,7 +26208,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H891" t="n">
         <v>58437</v>
@@ -26266,7 +26266,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G893" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H893" t="n">
         <v>22381</v>
@@ -26353,7 +26353,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H896" t="n">
         <v>7640</v>
@@ -26440,7 +26440,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G899" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H899" t="n">
         <v>25714</v>
@@ -26498,7 +26498,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G901" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H901" t="n">
         <v>17900</v>
@@ -26527,7 +26527,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73864436149597</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H902" t="n">
         <v>44451</v>
@@ -26556,7 +26556,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H903" t="n">
         <v>25646</v>
@@ -26585,7 +26585,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G904" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H904" t="n">
         <v>39491</v>
@@ -26672,7 +26672,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H907" t="n">
         <v>7190</v>
@@ -26730,7 +26730,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H909" t="n">
         <v>700</v>
@@ -26788,7 +26788,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H911" t="n">
         <v>85</v>
@@ -26846,7 +26846,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H913" t="n">
         <v>1250</v>
@@ -26875,7 +26875,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H914" t="n">
         <v>1050</v>
@@ -26933,7 +26933,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H916" t="n">
         <v>35</v>
@@ -27020,7 +27020,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G919" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H919" t="n">
         <v>1905</v>
@@ -27049,7 +27049,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H920" t="n">
         <v>8574</v>
@@ -27136,7 +27136,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H923" t="n">
         <v>10338</v>
@@ -27194,7 +27194,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H925" t="n">
         <v>2087</v>
@@ -27223,7 +27223,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H927" t="n">
         <v>1386</v>
@@ -27281,7 +27281,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H930" t="n">
         <v>125</v>
@@ -27397,7 +27397,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H932" t="n">
         <v>468</v>
@@ -27455,7 +27455,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G934" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H934" t="n">
         <v>5727</v>
@@ -27571,7 +27571,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G938" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H938" t="n">
         <v>10491</v>
@@ -27629,7 +27629,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G940" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H940" t="n">
         <v>194</v>
@@ -27716,7 +27716,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G943" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H943" t="n">
         <v>1635</v>
@@ -27745,7 +27745,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G944" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H944" t="n">
         <v>8544</v>
@@ -28093,7 +28093,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>4.33823776245117</v>
+        <v>4.33823823928833</v>
       </c>
       <c r="H956" t="n">
         <v>800</v>
@@ -28238,7 +28238,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>4.45286703109741</v>
+        <v>4.45286655426025</v>
       </c>
       <c r="H961" t="n">
         <v>1299</v>
@@ -46282,6 +46282,35 @@
         <v>2679</v>
       </c>
       <c r="I1583" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1584" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1584" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="D1584" t="n">
+        <v>6.19999980926514</v>
+      </c>
+      <c r="E1584" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="F1584" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G1584" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="H1584" t="n">
+        <v>26723</v>
+      </c>
+      <c r="I1584" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H2" t="n">
         <v>425</v>
@@ -456,7 +456,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H3" t="n">
         <v>650</v>
@@ -485,7 +485,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H5" t="n">
         <v>1105</v>
@@ -572,7 +572,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H7" t="n">
         <v>5900</v>
@@ -601,7 +601,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H8" t="n">
         <v>1000</v>
@@ -659,7 +659,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G10" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H10" t="n">
         <v>1712</v>
@@ -688,7 +688,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H11" t="n">
         <v>6680</v>
@@ -717,7 +717,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.08210802078247</v>
+        <v>4.08210849761963</v>
       </c>
       <c r="H18" t="n">
         <v>970</v>
@@ -978,7 +978,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.27726888656616</v>
+        <v>4.27726936340332</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H22" t="n">
         <v>3365</v>
@@ -1036,7 +1036,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>4.27726888656616</v>
+        <v>4.27726936340332</v>
       </c>
       <c r="H23" t="n">
         <v>3200</v>
@@ -1181,7 +1181,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H28" t="n">
         <v>350</v>
@@ -1210,7 +1210,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H29" t="n">
         <v>1969</v>
@@ -1442,7 +1442,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>4.00079202651978</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H37" t="n">
         <v>1422</v>
@@ -1471,7 +1471,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G38" t="n">
-        <v>4.08210802078247</v>
+        <v>4.08210849761963</v>
       </c>
       <c r="H38" t="n">
         <v>950</v>
@@ -1500,7 +1500,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H39" t="n">
         <v>300</v>
@@ -1587,7 +1587,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.21221590042114</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H42" t="n">
         <v>450</v>
@@ -1616,7 +1616,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G43" t="n">
-        <v>4.21221590042114</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H43" t="n">
         <v>450</v>
@@ -1645,7 +1645,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G44" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H44" t="n">
         <v>3940</v>
@@ -1674,7 +1674,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G45" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G49" t="n">
-        <v>4.0577130317688</v>
+        <v>4.05771207809448</v>
       </c>
       <c r="H49" t="n">
         <v>5985</v>
@@ -1848,7 +1848,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200085639954</v>
+        <v>3.95200204849243</v>
       </c>
       <c r="H51" t="n">
         <v>4885</v>
@@ -1964,7 +1964,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321111679077</v>
+        <v>3.90321087837219</v>
       </c>
       <c r="H55" t="n">
         <v>1248</v>
@@ -1993,7 +1993,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321111679077</v>
+        <v>3.90321087837219</v>
       </c>
       <c r="H56" t="n">
         <v>400</v>
@@ -2022,7 +2022,7 @@
         <v>4.75</v>
       </c>
       <c r="G57" t="n">
-        <v>3.86255216598511</v>
+        <v>3.86255264282227</v>
       </c>
       <c r="H57" t="n">
         <v>4200</v>
@@ -2051,7 +2051,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442018508911</v>
+        <v>3.85442137718201</v>
       </c>
       <c r="H58" t="n">
         <v>450</v>
@@ -2080,7 +2080,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.88694834709167</v>
+        <v>3.8869481086731</v>
       </c>
       <c r="H59" t="n">
         <v>1153</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991850852966</v>
       </c>
       <c r="H65" t="n">
         <v>4762</v>
@@ -2283,7 +2283,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>3.71618270874023</v>
+        <v>3.71618247032166</v>
       </c>
       <c r="H66" t="n">
         <v>23931</v>
@@ -2312,7 +2312,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.67552375793457</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H67" t="n">
         <v>5250</v>
@@ -2341,7 +2341,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.64299654960632</v>
+        <v>3.6429967880249</v>
       </c>
       <c r="H68" t="n">
         <v>7900</v>
@@ -2370,7 +2370,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926027297974</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H69" t="n">
         <v>14000</v>
@@ -2399,7 +2399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991850852966</v>
       </c>
       <c r="H70" t="n">
         <v>12720</v>
@@ -2428,7 +2428,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926027297974</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H71" t="n">
         <v>11150</v>
@@ -2457,7 +2457,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>3.67552375793457</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H72" t="n">
         <v>6400</v>
@@ -2515,7 +2515,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.77310395240784</v>
+        <v>3.7731032371521</v>
       </c>
       <c r="H74" t="n">
         <v>7850</v>
@@ -2544,7 +2544,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991850852966</v>
       </c>
       <c r="H75" t="n">
         <v>12819</v>
@@ -2573,7 +2573,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>3.67552375793457</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H76" t="n">
         <v>24183</v>
@@ -2602,7 +2602,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.00079202651978</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H77" t="n">
         <v>35243</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>4.00079202651978</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H78" t="n">
         <v>15007</v>
@@ -2718,7 +2718,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G81" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H81" t="n">
         <v>4817</v>
@@ -2776,7 +2776,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G83" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H83" t="n">
         <v>11228</v>
@@ -2863,7 +2863,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -2950,7 +2950,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H89" t="n">
         <v>8400</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>4.00079202651978</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H91" t="n">
         <v>30633</v>
@@ -3066,7 +3066,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G93" t="n">
-        <v>4.21221590042114</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H93" t="n">
         <v>37142</v>
@@ -3124,7 +3124,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G95" t="n">
-        <v>4.42363882064819</v>
+        <v>4.42363929748535</v>
       </c>
       <c r="H95" t="n">
         <v>35724</v>
@@ -3153,7 +3153,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.45616626739502</v>
+        <v>4.45616579055786</v>
       </c>
       <c r="H96" t="n">
         <v>5000</v>
@@ -3182,7 +3182,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G97" t="n">
-        <v>4.42363882064819</v>
+        <v>4.42363929748535</v>
       </c>
       <c r="H97" t="n">
         <v>12350</v>
@@ -3327,7 +3327,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.32605886459351</v>
+        <v>4.32605934143066</v>
       </c>
       <c r="H102" t="n">
         <v>20579</v>
@@ -3443,7 +3443,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495624542236</v>
+        <v>4.50495672225952</v>
       </c>
       <c r="H106" t="n">
         <v>11075</v>
@@ -3472,7 +3472,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495624542236</v>
+        <v>4.50495672225952</v>
       </c>
       <c r="H107" t="n">
         <v>9254</v>
@@ -3501,7 +3501,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>4.5212197303772</v>
+        <v>4.52121925354004</v>
       </c>
       <c r="H108" t="n">
         <v>11295</v>
@@ -3530,7 +3530,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.55374670028687</v>
+        <v>4.55374622344971</v>
       </c>
       <c r="H109" t="n">
         <v>6650</v>
@@ -3588,7 +3588,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H111" t="n">
         <v>9209</v>
@@ -3617,7 +3617,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G112" t="n">
-        <v>4.32605886459351</v>
+        <v>4.32605934143066</v>
       </c>
       <c r="H112" t="n">
         <v>8648</v>
@@ -3675,7 +3675,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G114" t="n">
-        <v>4.35858583450317</v>
+        <v>4.35858631134033</v>
       </c>
       <c r="H114" t="n">
         <v>39778</v>
@@ -3704,7 +3704,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G115" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H115" t="n">
         <v>9983</v>
@@ -3733,7 +3733,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H116" t="n">
         <v>12350</v>
@@ -3762,7 +3762,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H117" t="n">
         <v>20886</v>
@@ -3791,7 +3791,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H118" t="n">
         <v>47283</v>
@@ -3820,7 +3820,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G119" t="n">
-        <v>4.35858583450317</v>
+        <v>4.35858631134033</v>
       </c>
       <c r="H119" t="n">
         <v>76765</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H121" t="n">
         <v>5333</v>
@@ -3907,7 +3907,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>4.3423228263855</v>
+        <v>4.34232234954834</v>
       </c>
       <c r="H122" t="n">
         <v>510822</v>
@@ -3936,7 +3936,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.30979537963867</v>
+        <v>4.30979585647583</v>
       </c>
       <c r="H123" t="n">
         <v>30275</v>
@@ -3994,7 +3994,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H125" t="n">
         <v>59141</v>
@@ -4023,7 +4023,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.55374670028687</v>
+        <v>4.55374622344971</v>
       </c>
       <c r="H126" t="n">
         <v>89802</v>
@@ -4052,7 +4052,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H127" t="n">
         <v>19970</v>
@@ -4081,7 +4081,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H128" t="n">
         <v>22395</v>
@@ -4110,7 +4110,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H129" t="n">
         <v>7536</v>
@@ -4139,7 +4139,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G130" t="n">
-        <v>4.61879920959473</v>
+        <v>4.61879968643188</v>
       </c>
       <c r="H130" t="n">
         <v>12487</v>
@@ -4168,7 +4168,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H131" t="n">
         <v>37064</v>
@@ -4226,7 +4226,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>4.86275100708008</v>
+        <v>4.86275005340576</v>
       </c>
       <c r="H133" t="n">
         <v>5321</v>
@@ -4313,7 +4313,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791091918945</v>
+        <v>5.05791044235229</v>
       </c>
       <c r="H136" t="n">
         <v>24382</v>
@@ -4371,7 +4371,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>5.1554913520813</v>
+        <v>5.15549087524414</v>
       </c>
       <c r="H138" t="n">
         <v>14771</v>
@@ -4400,7 +4400,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>5.1554913520813</v>
+        <v>5.15549087524414</v>
       </c>
       <c r="H139" t="n">
         <v>5761</v>
@@ -4458,7 +4458,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H141" t="n">
         <v>13207</v>
@@ -4487,7 +4487,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801832199097</v>
+        <v>5.18801736831665</v>
       </c>
       <c r="H142" t="n">
         <v>16197</v>
@@ -4545,7 +4545,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H144" t="n">
         <v>4290</v>
@@ -4574,7 +4574,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H145" t="n">
         <v>16119</v>
@@ -4603,7 +4603,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H146" t="n">
         <v>2211</v>
@@ -4632,7 +4632,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H147" t="n">
         <v>10023</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>4.87901449203491</v>
+        <v>4.87901401519775</v>
       </c>
       <c r="H149" t="n">
         <v>16280</v>
@@ -4719,7 +4719,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791091918945</v>
+        <v>5.05791044235229</v>
       </c>
       <c r="H150" t="n">
         <v>6072</v>
@@ -4748,7 +4748,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H151" t="n">
         <v>10138</v>
@@ -4777,7 +4777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G152" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H152" t="n">
         <v>7104</v>
@@ -4806,7 +4806,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H153" t="n">
         <v>5444</v>
@@ -4893,7 +4893,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>5.10670185089111</v>
+        <v>5.10670137405396</v>
       </c>
       <c r="H156" t="n">
         <v>11754</v>
@@ -4922,7 +4922,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H157" t="n">
         <v>4698</v>
@@ -4951,7 +4951,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H158" t="n">
         <v>9550</v>
@@ -5067,7 +5067,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G162" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H162" t="n">
         <v>7250</v>
@@ -5096,7 +5096,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G163" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H163" t="n">
         <v>7961</v>
@@ -5125,7 +5125,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>4.94406652450562</v>
+        <v>4.94406747817993</v>
       </c>
       <c r="H164" t="n">
         <v>28419</v>
@@ -5183,7 +5183,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>4.99285745620728</v>
+        <v>4.99285697937012</v>
       </c>
       <c r="H166" t="n">
         <v>16468</v>
@@ -5212,7 +5212,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G167" t="n">
-        <v>4.89527797698975</v>
+        <v>4.89527702331543</v>
       </c>
       <c r="H167" t="n">
         <v>20850</v>
@@ -5270,7 +5270,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.94406652450562</v>
+        <v>4.94406747817993</v>
       </c>
       <c r="H169" t="n">
         <v>2656</v>
@@ -5299,7 +5299,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.89527797698975</v>
+        <v>4.89527702331543</v>
       </c>
       <c r="H170" t="n">
         <v>15167</v>
@@ -5357,7 +5357,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H172" t="n">
         <v>2308</v>
@@ -5415,7 +5415,7 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>4.87901449203491</v>
+        <v>4.87901401519775</v>
       </c>
       <c r="H174" t="n">
         <v>7490</v>
@@ -5473,7 +5473,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H176" t="n">
         <v>18455</v>
@@ -5531,7 +5531,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G178" t="n">
-        <v>5.23680830001831</v>
+        <v>5.23680877685547</v>
       </c>
       <c r="H178" t="n">
         <v>49204</v>
@@ -5676,7 +5676,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>5.3831787109375</v>
+        <v>5.38317823410034</v>
       </c>
       <c r="H183" t="n">
         <v>5662</v>
@@ -5850,7 +5850,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922786712646</v>
+        <v>5.13922834396362</v>
       </c>
       <c r="H189" t="n">
         <v>10921</v>
@@ -5908,7 +5908,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G191" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H191" t="n">
         <v>110919</v>
@@ -5937,7 +5937,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G192" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H192" t="n">
         <v>2290</v>
@@ -5995,7 +5995,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G194" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H194" t="n">
         <v>2077</v>
@@ -6024,7 +6024,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>5.00475692749023</v>
+        <v>5.00475597381592</v>
       </c>
       <c r="H195" t="n">
         <v>15185</v>
@@ -6140,7 +6140,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H199" t="n">
         <v>6894</v>
@@ -6169,7 +6169,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H200" t="n">
         <v>28649</v>
@@ -6227,7 +6227,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H202" t="n">
         <v>680</v>
@@ -6256,7 +6256,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H203" t="n">
         <v>5722</v>
@@ -6285,7 +6285,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H204" t="n">
         <v>3896</v>
@@ -6372,7 +6372,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H207" t="n">
         <v>5465</v>
@@ -6401,7 +6401,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H208" t="n">
         <v>3971</v>
@@ -6430,7 +6430,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H209" t="n">
         <v>6644</v>
@@ -6720,7 +6720,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333108901978</v>
       </c>
       <c r="H219" t="n">
         <v>20185</v>
@@ -6749,7 +6749,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H220" t="n">
         <v>4090</v>
@@ -6807,7 +6807,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G222" t="n">
-        <v>5.78623008728027</v>
+        <v>5.78622961044312</v>
       </c>
       <c r="H222" t="n">
         <v>8191</v>
@@ -6894,7 +6894,7 @@
         <v>7</v>
       </c>
       <c r="G225" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H225" t="n">
         <v>7539</v>
@@ -6923,7 +6923,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>5.78623008728027</v>
+        <v>5.78622961044312</v>
       </c>
       <c r="H226" t="n">
         <v>20880</v>
@@ -7039,7 +7039,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>5.93587398529053</v>
+        <v>5.93587350845337</v>
       </c>
       <c r="H230" t="n">
         <v>14060</v>
@@ -7184,7 +7184,7 @@
         <v>7</v>
       </c>
       <c r="G235" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H235" t="n">
         <v>7545</v>
@@ -7213,7 +7213,7 @@
         <v>7</v>
       </c>
       <c r="G236" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H236" t="n">
         <v>2000</v>
@@ -7242,7 +7242,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>5.78623008728027</v>
+        <v>5.78622961044312</v>
       </c>
       <c r="H237" t="n">
         <v>8720</v>
@@ -7329,7 +7329,7 @@
         <v>7</v>
       </c>
       <c r="G240" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H240" t="n">
         <v>3750</v>
@@ -7358,7 +7358,7 @@
         <v>7</v>
       </c>
       <c r="G241" t="n">
-        <v>5.8194842338562</v>
+        <v>5.81948375701904</v>
       </c>
       <c r="H241" t="n">
         <v>4000</v>
@@ -7474,7 +7474,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G245" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H245" t="n">
         <v>4200</v>
@@ -7532,7 +7532,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G247" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H247" t="n">
         <v>5180</v>
@@ -7590,7 +7590,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H249" t="n">
         <v>6312</v>
@@ -7619,7 +7619,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G250" t="n">
-        <v>5.58670425415039</v>
+        <v>5.58670473098755</v>
       </c>
       <c r="H250" t="n">
         <v>875</v>
@@ -7735,7 +7735,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G254" t="n">
-        <v>5.58670425415039</v>
+        <v>5.58670473098755</v>
       </c>
       <c r="H254" t="n">
         <v>2610</v>
@@ -7764,7 +7764,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G255" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H255" t="n">
         <v>1900</v>
@@ -7793,7 +7793,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H257" t="n">
         <v>3560</v>
@@ -7851,7 +7851,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G258" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H258" t="n">
         <v>4652</v>
@@ -7880,7 +7880,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H259" t="n">
         <v>2350</v>
@@ -7909,7 +7909,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H260" t="n">
         <v>1200</v>
@@ -7938,7 +7938,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H261" t="n">
         <v>2105</v>
@@ -7996,7 +7996,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H263" t="n">
         <v>8019</v>
@@ -8025,7 +8025,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333108901978</v>
       </c>
       <c r="H264" t="n">
         <v>1211</v>
@@ -8054,7 +8054,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G265" t="n">
-        <v>5.61995935440063</v>
+        <v>5.61995887756348</v>
       </c>
       <c r="H265" t="n">
         <v>1620</v>
@@ -8083,7 +8083,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H266" t="n">
         <v>9438</v>
@@ -8112,7 +8112,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G267" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333108901978</v>
       </c>
       <c r="H267" t="n">
         <v>175</v>
@@ -8199,7 +8199,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H270" t="n">
         <v>5650</v>
@@ -8228,7 +8228,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G271" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H271" t="n">
         <v>23690</v>
@@ -8257,7 +8257,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G272" t="n">
-        <v>5.52019596099854</v>
+        <v>5.52019643783569</v>
       </c>
       <c r="H272" t="n">
         <v>2848</v>
@@ -8286,7 +8286,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H273" t="n">
         <v>13409</v>
@@ -8315,7 +8315,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H274" t="n">
         <v>4619</v>
@@ -8344,7 +8344,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H275" t="n">
         <v>428</v>
@@ -8373,7 +8373,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H276" t="n">
         <v>7400</v>
@@ -8518,7 +8518,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H281" t="n">
         <v>7624</v>
@@ -8576,7 +8576,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G283" t="n">
-        <v>5.68646764755249</v>
+        <v>5.68646717071533</v>
       </c>
       <c r="H283" t="n">
         <v>4800</v>
@@ -8634,7 +8634,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H285" t="n">
         <v>15427</v>
@@ -8663,7 +8663,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.65321350097656</v>
+        <v>5.6532130241394</v>
       </c>
       <c r="H286" t="n">
         <v>32500</v>
@@ -8692,7 +8692,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658571243286</v>
       </c>
       <c r="H287" t="n">
         <v>1750</v>
@@ -8721,7 +8721,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H288" t="n">
         <v>1973</v>
@@ -8808,7 +8808,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H291" t="n">
         <v>4539</v>
@@ -8866,7 +8866,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H293" t="n">
         <v>14001</v>
@@ -8895,7 +8895,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G294" t="n">
-        <v>5.60333156585693</v>
+        <v>5.60333108901978</v>
       </c>
       <c r="H294" t="n">
         <v>31744</v>
@@ -9040,7 +9040,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>5.43706083297729</v>
+        <v>5.43706035614014</v>
       </c>
       <c r="H299" t="n">
         <v>4580</v>
@@ -9156,7 +9156,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H303" t="n">
         <v>4716</v>
@@ -9185,7 +9185,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H304" t="n">
         <v>1563</v>
@@ -9301,7 +9301,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H308" t="n">
         <v>7755</v>
@@ -9330,7 +9330,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H309" t="n">
         <v>3800</v>
@@ -9359,7 +9359,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H310" t="n">
         <v>27369</v>
@@ -9504,7 +9504,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H315" t="n">
         <v>3276</v>
@@ -9562,7 +9562,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>5.1211462020874</v>
+        <v>5.12114572525024</v>
       </c>
       <c r="H317" t="n">
         <v>4420</v>
@@ -9620,7 +9620,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G319" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H319" t="n">
         <v>1750</v>
@@ -9678,7 +9678,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H321" t="n">
         <v>5361</v>
@@ -9765,7 +9765,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G324" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H324" t="n">
         <v>4701</v>
@@ -9852,7 +9852,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G327" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H327" t="n">
         <v>10600</v>
@@ -9881,7 +9881,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H328" t="n">
         <v>6860</v>
@@ -9910,7 +9910,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H329" t="n">
         <v>24800</v>
@@ -9939,7 +9939,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H330" t="n">
         <v>5585</v>
@@ -10026,7 +10026,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G333" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H333" t="n">
         <v>1126</v>
@@ -10055,7 +10055,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G334" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H334" t="n">
         <v>10830</v>
@@ -10084,7 +10084,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G335" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H335" t="n">
         <v>11568</v>
@@ -10113,7 +10113,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G336" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10258,7 +10258,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H341" t="n">
         <v>13173</v>
@@ -10374,7 +10374,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H345" t="n">
         <v>8254</v>
@@ -10403,7 +10403,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H348" t="n">
         <v>3489</v>
@@ -10490,7 +10490,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G349" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H349" t="n">
         <v>8775</v>
@@ -10635,7 +10635,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H354" t="n">
         <v>7088</v>
@@ -10693,7 +10693,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H356" t="n">
         <v>2400</v>
@@ -10722,7 +10722,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463743209839</v>
       </c>
       <c r="H358" t="n">
         <v>4600</v>
@@ -10780,7 +10780,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>5.07126474380493</v>
+        <v>5.07126426696777</v>
       </c>
       <c r="H359" t="n">
         <v>3000</v>
@@ -10925,7 +10925,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G364" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H364" t="n">
         <v>2203</v>
@@ -10954,7 +10954,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G365" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H365" t="n">
         <v>1500</v>
@@ -10983,7 +10983,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H366" t="n">
         <v>710</v>
@@ -11186,7 +11186,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H373" t="n">
         <v>4742</v>
@@ -11244,7 +11244,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G375" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H375" t="n">
         <v>2615</v>
@@ -11331,7 +11331,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H378" t="n">
         <v>112</v>
@@ -11360,7 +11360,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G381" t="n">
-        <v>5.1211462020874</v>
+        <v>5.12114572525024</v>
       </c>
       <c r="H381" t="n">
         <v>1071</v>
@@ -11476,7 +11476,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H383" t="n">
         <v>5263</v>
@@ -11505,7 +11505,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97150230407715</v>
+        <v>4.97150182723999</v>
       </c>
       <c r="H399" t="n">
         <v>5742</v>
@@ -11998,7 +11998,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G401" t="n">
-        <v>4.92162084579468</v>
+        <v>4.92162132263184</v>
       </c>
       <c r="H401" t="n">
         <v>1890</v>
@@ -12027,7 +12027,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>4.90499448776245</v>
+        <v>4.90499401092529</v>
       </c>
       <c r="H402" t="n">
         <v>2893</v>
@@ -12143,7 +12143,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>4.67221450805664</v>
+        <v>4.67221403121948</v>
       </c>
       <c r="H406" t="n">
         <v>19716</v>
@@ -12230,7 +12230,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G409" t="n">
-        <v>4.68884181976318</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H409" t="n">
         <v>700</v>
@@ -12259,7 +12259,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G410" t="n">
-        <v>4.78860473632812</v>
+        <v>4.78860425949097</v>
       </c>
       <c r="H410" t="n">
         <v>300</v>
@@ -12288,7 +12288,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G411" t="n">
-        <v>4.70546817779541</v>
+        <v>4.70546865463257</v>
       </c>
       <c r="H411" t="n">
         <v>826</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>4.80523109436035</v>
+        <v>4.80523157119751</v>
       </c>
       <c r="H412" t="n">
         <v>200</v>
@@ -12346,7 +12346,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.65558767318726</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H413" t="n">
         <v>6760</v>
@@ -12433,7 +12433,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>4.43943548202515</v>
+        <v>4.43943500518799</v>
       </c>
       <c r="H416" t="n">
         <v>3039</v>
@@ -12491,7 +12491,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>4.47268962860107</v>
+        <v>4.47268915176392</v>
       </c>
       <c r="H418" t="n">
         <v>25169</v>
@@ -12578,7 +12578,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H421" t="n">
         <v>1908</v>
@@ -12607,7 +12607,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>4.65558767318726</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H422" t="n">
         <v>7657</v>
@@ -12636,7 +12636,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H423" t="n">
         <v>3457</v>
@@ -12665,7 +12665,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G424" t="n">
-        <v>4.80523109436035</v>
+        <v>4.80523157119751</v>
       </c>
       <c r="H424" t="n">
         <v>3714</v>
@@ -12694,7 +12694,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>4.67221450805664</v>
+        <v>4.67221403121948</v>
       </c>
       <c r="H425" t="n">
         <v>5049</v>
@@ -12723,7 +12723,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>4.60570573806763</v>
+        <v>4.60570621490479</v>
       </c>
       <c r="H426" t="n">
         <v>6617</v>
@@ -12752,7 +12752,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>4.55582523345947</v>
+        <v>4.55582475662231</v>
       </c>
       <c r="H427" t="n">
         <v>10094</v>
@@ -12781,7 +12781,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>4.52257013320923</v>
+        <v>4.52257061004639</v>
       </c>
       <c r="H428" t="n">
         <v>8580</v>
@@ -12810,7 +12810,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G429" t="n">
-        <v>4.68884181976318</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H429" t="n">
         <v>3246</v>
@@ -12984,7 +12984,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>4.68884181976318</v>
+        <v>4.68884134292603</v>
       </c>
       <c r="H435" t="n">
         <v>2711</v>
@@ -13013,7 +13013,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>4.78860473632812</v>
+        <v>4.78860425949097</v>
       </c>
       <c r="H436" t="n">
         <v>500</v>
@@ -13042,7 +13042,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H437" t="n">
         <v>6066</v>
@@ -13071,7 +13071,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H438" t="n">
         <v>1719</v>
@@ -13100,7 +13100,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G439" t="n">
-        <v>4.75534963607788</v>
+        <v>4.75535011291504</v>
       </c>
       <c r="H439" t="n">
         <v>4000</v>
@@ -13129,7 +13129,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G440" t="n">
-        <v>4.65558767318726</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H440" t="n">
         <v>700</v>
@@ -13158,7 +13158,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.65558767318726</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H441" t="n">
         <v>4384</v>
@@ -13216,7 +13216,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>4.65558767318726</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H443" t="n">
         <v>3174</v>
@@ -13245,7 +13245,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H444" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.65558767318726</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H445" t="n">
         <v>1010</v>
@@ -13303,7 +13303,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13332,7 +13332,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H447" t="n">
         <v>1000</v>
@@ -13361,7 +13361,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504903793335</v>
       </c>
       <c r="H452" t="n">
         <v>500</v>
@@ -13506,7 +13506,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504903793335</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H454" t="n">
         <v>4800</v>
@@ -13680,7 +13680,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H459" t="n">
         <v>510</v>
@@ -13709,7 +13709,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G460" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G461" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H461" t="n">
         <v>686</v>
@@ -13767,7 +13767,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G462" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G475" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H475" t="n">
         <v>1701</v>
@@ -14318,7 +14318,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504903793335</v>
       </c>
       <c r="H481" t="n">
         <v>500</v>
@@ -14347,7 +14347,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H482" t="n">
         <v>1405</v>
@@ -14376,7 +14376,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G484" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H484" t="n">
         <v>3400</v>
@@ -14434,7 +14434,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -14811,7 +14811,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G498" t="n">
-        <v>4.41524505615234</v>
+        <v>4.41524457931519</v>
       </c>
       <c r="H498" t="n">
         <v>3223</v>
@@ -14840,7 +14840,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G499" t="n">
-        <v>4.41524505615234</v>
+        <v>4.41524457931519</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G500" t="n">
-        <v>4.41524505615234</v>
+        <v>4.41524457931519</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G503" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H503" t="n">
         <v>5895</v>
@@ -15043,7 +15043,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G506" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H506" t="n">
         <v>55</v>
@@ -15072,7 +15072,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H507" t="n">
         <v>3700</v>
@@ -15101,7 +15101,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H511" t="n">
         <v>2505</v>
@@ -15275,7 +15275,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G514" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H514" t="n">
         <v>1247</v>
@@ -15304,7 +15304,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G515" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H515" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15362,7 +15362,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.89256858825684</v>
+        <v>4.89256906509399</v>
       </c>
       <c r="H519" t="n">
         <v>320</v>
@@ -15449,7 +15449,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.89256858825684</v>
+        <v>4.89256906509399</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15681,7 +15681,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H528" t="n">
         <v>700</v>
@@ -15710,7 +15710,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008813858032</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H530" t="n">
         <v>1270</v>
@@ -15797,7 +15797,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G532" t="n">
-        <v>4.92666292190552</v>
+        <v>4.92666339874268</v>
       </c>
       <c r="H532" t="n">
         <v>374</v>
@@ -15855,7 +15855,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90961647033691</v>
+        <v>4.90961599349976</v>
       </c>
       <c r="H534" t="n">
         <v>2167</v>
@@ -15884,7 +15884,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H535" t="n">
         <v>2280</v>
@@ -15913,7 +15913,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H536" t="n">
         <v>2123</v>
@@ -15942,7 +15942,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H537" t="n">
         <v>1000</v>
@@ -16029,7 +16029,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H540" t="n">
         <v>350</v>
@@ -16058,7 +16058,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H542" t="n">
         <v>2760</v>
@@ -16116,7 +16116,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G543" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>4.87552070617676</v>
+        <v>4.87552118301392</v>
       </c>
       <c r="H544" t="n">
         <v>421</v>
@@ -16174,7 +16174,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H545" t="n">
         <v>2895</v>
@@ -16203,7 +16203,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H546" t="n">
         <v>2567</v>
@@ -16406,7 +16406,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>4.36410236358643</v>
+        <v>4.36410284042358</v>
       </c>
       <c r="H553" t="n">
         <v>4928</v>
@@ -16435,7 +16435,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G554" t="n">
-        <v>4.44933938980103</v>
+        <v>4.44933891296387</v>
       </c>
       <c r="H554" t="n">
         <v>608</v>
@@ -16812,7 +16812,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G567" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H567" t="n">
         <v>2942</v>
@@ -16841,7 +16841,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G568" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H568" t="n">
         <v>360</v>
@@ -16870,7 +16870,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G569" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G570" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G571" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H571" t="n">
         <v>2010</v>
@@ -16957,7 +16957,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G572" t="n">
-        <v>4.50048112869263</v>
+        <v>4.50048160552979</v>
       </c>
       <c r="H572" t="n">
         <v>1210</v>
@@ -17160,7 +17160,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H579" t="n">
         <v>4350</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.80733251571655</v>
+        <v>4.80733203887939</v>
       </c>
       <c r="H580" t="n">
         <v>3158</v>
@@ -17218,7 +17218,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H581" t="n">
         <v>1495</v>
@@ -17247,7 +17247,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G582" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H582" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H583" t="n">
         <v>1150</v>
@@ -17392,7 +17392,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H587" t="n">
         <v>1750</v>
@@ -17450,7 +17450,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H589" t="n">
         <v>710</v>
@@ -17479,7 +17479,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H590" t="n">
         <v>900</v>
@@ -17508,7 +17508,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H591" t="n">
         <v>2311</v>
@@ -17537,7 +17537,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H592" t="n">
         <v>901</v>
@@ -17566,7 +17566,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H593" t="n">
         <v>2905</v>
@@ -17595,7 +17595,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17653,7 +17653,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>4.67095422744751</v>
+        <v>4.67095375061035</v>
       </c>
       <c r="H596" t="n">
         <v>128</v>
@@ -17682,7 +17682,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H597" t="n">
         <v>607</v>
@@ -17711,7 +17711,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G598" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H598" t="n">
         <v>65</v>
@@ -17769,7 +17769,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G600" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H600" t="n">
         <v>2186</v>
@@ -17798,7 +17798,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.85847330093384</v>
+        <v>4.858473777771</v>
       </c>
       <c r="H603" t="n">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H610" t="n">
         <v>1351</v>
@@ -18088,7 +18088,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H611" t="n">
         <v>510</v>
@@ -18175,7 +18175,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H614" t="n">
         <v>186</v>
@@ -18204,7 +18204,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G616" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -18262,7 +18262,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G617" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G621" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H621" t="n">
         <v>200</v>
@@ -18407,7 +18407,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H622" t="n">
         <v>0</v>
@@ -18436,7 +18436,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G624" t="n">
-        <v>4.73914289474487</v>
+        <v>4.73914337158203</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18494,7 +18494,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>4.80733251571655</v>
+        <v>4.80733203887939</v>
       </c>
       <c r="H625" t="n">
         <v>1866</v>
@@ -18697,7 +18697,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H632" t="n">
         <v>872</v>
@@ -18726,7 +18726,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504903793335</v>
       </c>
       <c r="H633" t="n">
         <v>1703</v>
@@ -18755,7 +18755,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H634" t="n">
         <v>10</v>
@@ -18813,7 +18813,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G636" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H636" t="n">
         <v>1898</v>
@@ -18842,7 +18842,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G637" t="n">
-        <v>5.01189994812012</v>
+        <v>5.01189947128296</v>
       </c>
       <c r="H637" t="n">
         <v>67041</v>
@@ -18871,7 +18871,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G638" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H638" t="n">
         <v>3800</v>
@@ -18958,7 +18958,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>5.01189994812012</v>
+        <v>5.01189947128296</v>
       </c>
       <c r="H641" t="n">
         <v>3920</v>
@@ -19016,7 +19016,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>5.25056171417236</v>
+        <v>5.25056076049805</v>
       </c>
       <c r="H643" t="n">
         <v>4245</v>
@@ -19045,7 +19045,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G644" t="n">
-        <v>5.35284566879272</v>
+        <v>5.35284519195557</v>
       </c>
       <c r="H644" t="n">
         <v>15820</v>
@@ -19074,7 +19074,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G645" t="n">
-        <v>5.30170297622681</v>
+        <v>5.30170345306396</v>
       </c>
       <c r="H645" t="n">
         <v>2953</v>
@@ -19277,7 +19277,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>5.13123083114624</v>
+        <v>5.13123035430908</v>
       </c>
       <c r="H652" t="n">
         <v>317</v>
@@ -19364,7 +19364,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>5.18237161636353</v>
+        <v>5.18237209320068</v>
       </c>
       <c r="H655" t="n">
         <v>1585</v>
@@ -19567,7 +19567,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G662" t="n">
-        <v>5.18237161636353</v>
+        <v>5.18237209320068</v>
       </c>
       <c r="H662" t="n">
         <v>4300</v>
@@ -19596,7 +19596,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008813858032</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H663" t="n">
         <v>300</v>
@@ -19625,7 +19625,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>5.13123083114624</v>
+        <v>5.13123035430908</v>
       </c>
       <c r="H664" t="n">
         <v>5303</v>
@@ -19654,7 +19654,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>5.18237161636353</v>
+        <v>5.18237209320068</v>
       </c>
       <c r="H665" t="n">
         <v>3800</v>
@@ -19683,7 +19683,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>5.18237161636353</v>
+        <v>5.18237209320068</v>
       </c>
       <c r="H666" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G672" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H672" t="n">
         <v>1371</v>
@@ -19886,7 +19886,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G673" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19973,7 +19973,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H676" t="n">
         <v>3802</v>
@@ -20002,7 +20002,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H677" t="n">
         <v>1377</v>
@@ -20031,7 +20031,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20089,7 +20089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H680" t="n">
         <v>893</v>
@@ -20147,7 +20147,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H682" t="n">
         <v>6283</v>
@@ -20234,7 +20234,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G685" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H685" t="n">
         <v>298</v>
@@ -20263,7 +20263,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H686" t="n">
         <v>1900</v>
@@ -20321,7 +20321,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H688" t="n">
         <v>3796</v>
@@ -20350,7 +20350,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H689" t="n">
         <v>820</v>
@@ -20379,7 +20379,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H690" t="n">
         <v>700</v>
@@ -20495,7 +20495,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H694" t="n">
         <v>2751</v>
@@ -20524,7 +20524,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G695" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H695" t="n">
         <v>331</v>
@@ -20640,7 +20640,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G699" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H699" t="n">
         <v>380</v>
@@ -20669,7 +20669,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H700" t="n">
         <v>807</v>
@@ -20698,7 +20698,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H701" t="n">
         <v>150</v>
@@ -20727,7 +20727,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -20756,7 +20756,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.07156467437744</v>
+        <v>5.0715651512146</v>
       </c>
       <c r="H703" t="n">
         <v>200</v>
@@ -20872,7 +20872,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G707" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H707" t="n">
         <v>1585</v>
@@ -20901,7 +20901,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G708" t="n">
-        <v>5.20235919952393</v>
+        <v>5.20235872268677</v>
       </c>
       <c r="H708" t="n">
         <v>8078</v>
@@ -20930,7 +20930,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>5.20235919952393</v>
+        <v>5.20235872268677</v>
       </c>
       <c r="H709" t="n">
         <v>1010</v>
@@ -20959,7 +20959,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.20235919952393</v>
+        <v>5.20235872268677</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -21017,7 +21017,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>5.20235919952393</v>
+        <v>5.20235872268677</v>
       </c>
       <c r="H712" t="n">
         <v>7386</v>
@@ -21104,7 +21104,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G715" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H715" t="n">
         <v>3214</v>
@@ -21133,7 +21133,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H716" t="n">
         <v>1000</v>
@@ -21365,7 +21365,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G724" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H724" t="n">
         <v>500</v>
@@ -21481,7 +21481,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G728" t="n">
-        <v>4.93783235549927</v>
+        <v>4.93783187866211</v>
       </c>
       <c r="H728" t="n">
         <v>2930</v>
@@ -21510,7 +21510,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.93783235549927</v>
+        <v>4.93783187866211</v>
       </c>
       <c r="H729" t="n">
         <v>6873</v>
@@ -21858,7 +21858,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G741" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H741" t="n">
         <v>966</v>
@@ -21887,7 +21887,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H742" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H752" t="n">
         <v>233</v>
@@ -22206,7 +22206,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H753" t="n">
         <v>2500</v>
@@ -22235,7 +22235,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H754" t="n">
         <v>4845</v>
@@ -22264,7 +22264,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G755" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H755" t="n">
         <v>5770</v>
@@ -22583,7 +22583,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G766" t="n">
-        <v>4.45286655426025</v>
+        <v>4.45286703109741</v>
       </c>
       <c r="H766" t="n">
         <v>6689</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H769" t="n">
         <v>2000</v>
@@ -23366,7 +23366,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G793" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418390274048</v>
       </c>
       <c r="H793" t="n">
         <v>1992</v>
@@ -23424,7 +23424,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>4.98191976547241</v>
+        <v>4.98192024230957</v>
       </c>
       <c r="H795" t="n">
         <v>144</v>
@@ -23801,7 +23801,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>4.39114379882812</v>
+        <v>4.39114332199097</v>
       </c>
       <c r="H808" t="n">
         <v>7831</v>
@@ -23830,7 +23830,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G809" t="n">
-        <v>4.39114379882812</v>
+        <v>4.39114332199097</v>
       </c>
       <c r="H809" t="n">
         <v>322</v>
@@ -23946,7 +23946,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H813" t="n">
         <v>1618</v>
@@ -23975,7 +23975,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24120,7 +24120,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H819" t="n">
         <v>166</v>
@@ -24149,7 +24149,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24497,7 +24497,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G832" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H832" t="n">
         <v>207</v>
@@ -24613,7 +24613,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H836" t="n">
         <v>1974</v>
@@ -24642,7 +24642,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12661695480347</v>
+        <v>4.12661647796631</v>
       </c>
       <c r="H837" t="n">
         <v>1803</v>
@@ -24729,7 +24729,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>4.12661695480347</v>
+        <v>4.12661647796631</v>
       </c>
       <c r="H840" t="n">
         <v>609</v>
@@ -24758,7 +24758,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G841" t="n">
-        <v>4.12661695480347</v>
+        <v>4.12661647796631</v>
       </c>
       <c r="H841" t="n">
         <v>4500</v>
@@ -24874,7 +24874,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H845" t="n">
         <v>796</v>
@@ -24932,7 +24932,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G847" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H847" t="n">
         <v>3500</v>
@@ -24961,7 +24961,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G848" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H848" t="n">
         <v>1250</v>
@@ -24990,7 +24990,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G849" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -25019,7 +25019,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>4.16188669204712</v>
+        <v>4.16188716888428</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -25077,7 +25077,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.00317096710205</v>
+        <v>4.00317049026489</v>
       </c>
       <c r="H852" t="n">
         <v>21572</v>
@@ -25135,7 +25135,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G854" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H854" t="n">
         <v>56826</v>
@@ -25164,7 +25164,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>4.00317096710205</v>
+        <v>4.00317049026489</v>
       </c>
       <c r="H855" t="n">
         <v>5901</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H856" t="n">
         <v>3097</v>
@@ -25280,7 +25280,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G859" t="n">
-        <v>4.12661695480347</v>
+        <v>4.12661647796631</v>
       </c>
       <c r="H859" t="n">
         <v>6840</v>
@@ -25309,7 +25309,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G860" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H860" t="n">
         <v>5097</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H875" t="n">
         <v>3194</v>
@@ -25947,7 +25947,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86209034919739</v>
+        <v>3.86208987236023</v>
       </c>
       <c r="H882" t="n">
         <v>15378</v>
@@ -25976,7 +25976,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G883" t="n">
-        <v>3.80918455123901</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H883" t="n">
         <v>18373</v>
@@ -26005,7 +26005,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>3.72100901603699</v>
+        <v>3.72100877761841</v>
       </c>
       <c r="H884" t="n">
         <v>9694</v>
@@ -26034,7 +26034,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>3.6857385635376</v>
+        <v>3.68573880195618</v>
       </c>
       <c r="H885" t="n">
         <v>8364</v>
@@ -26092,7 +26092,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>3.80918455123901</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H887" t="n">
         <v>5091</v>
@@ -26150,7 +26150,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H889" t="n">
         <v>14342</v>
@@ -26179,7 +26179,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H890" t="n">
         <v>20433</v>
@@ -26353,7 +26353,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>3.82681965827942</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H896" t="n">
         <v>7640</v>
@@ -26440,7 +26440,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G899" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H899" t="n">
         <v>25714</v>
@@ -26498,7 +26498,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G901" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H901" t="n">
         <v>17900</v>
@@ -26556,7 +26556,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>3.82681965827942</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H903" t="n">
         <v>25646</v>
@@ -26585,7 +26585,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G904" t="n">
-        <v>3.80918455123901</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H904" t="n">
         <v>39491</v>
@@ -26672,7 +26672,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86209034919739</v>
+        <v>3.86208987236023</v>
       </c>
       <c r="H907" t="n">
         <v>7190</v>
@@ -26730,7 +26730,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H909" t="n">
         <v>700</v>
@@ -26788,7 +26788,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>3.82681965827942</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H911" t="n">
         <v>85</v>
@@ -26875,7 +26875,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86209034919739</v>
+        <v>3.86208987236023</v>
       </c>
       <c r="H914" t="n">
         <v>1050</v>
@@ -27020,7 +27020,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G919" t="n">
-        <v>3.82681965827942</v>
+        <v>3.82682013511658</v>
       </c>
       <c r="H919" t="n">
         <v>1905</v>
@@ -27049,7 +27049,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H920" t="n">
         <v>8574</v>
@@ -27165,7 +27165,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G924" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H924" t="n">
         <v>2250</v>
@@ -27339,7 +27339,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H930" t="n">
         <v>125</v>
@@ -27397,7 +27397,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026588439941</v>
       </c>
       <c r="H932" t="n">
         <v>468</v>
@@ -27426,7 +27426,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>4.05607604980469</v>
+        <v>4.05607652664185</v>
       </c>
       <c r="H933" t="n">
         <v>7761</v>
@@ -27455,7 +27455,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G934" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H934" t="n">
         <v>5727</v>
@@ -27484,7 +27484,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>4.07371139526367</v>
+        <v>4.07371091842651</v>
       </c>
       <c r="H935" t="n">
         <v>2555</v>
@@ -27542,7 +27542,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G937" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H937" t="n">
         <v>8262</v>
@@ -27571,7 +27571,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G938" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H938" t="n">
         <v>10491</v>
@@ -27629,7 +27629,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G940" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H940" t="n">
         <v>194</v>
@@ -27658,7 +27658,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H941" t="n">
         <v>430</v>
@@ -27716,7 +27716,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G943" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H943" t="n">
         <v>1635</v>
@@ -27774,7 +27774,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H945" t="n">
         <v>3230</v>
@@ -27890,7 +27890,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G949" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H949" t="n">
         <v>1750</v>
@@ -28064,7 +28064,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G955" t="n">
-        <v>4.30296802520752</v>
+        <v>4.30296850204468</v>
       </c>
       <c r="H955" t="n">
         <v>4302</v>
@@ -28238,7 +28238,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>4.45286655426025</v>
+        <v>4.45286703109741</v>
       </c>
       <c r="H961" t="n">
         <v>1299</v>
@@ -46311,6 +46311,35 @@
         <v>26723</v>
       </c>
       <c r="I1584" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1585" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1585" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="D1585" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="E1585" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F1585" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G1585" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="H1585" t="n">
+        <v>1517</v>
+      </c>
+      <c r="I1585" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H2" t="n">
         <v>425</v>
@@ -456,7 +456,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H3" t="n">
         <v>650</v>
@@ -485,7 +485,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H5" t="n">
         <v>1105</v>
@@ -543,7 +543,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.22847843170166</v>
+        <v>4.2284779548645</v>
       </c>
       <c r="H6" t="n">
         <v>18626</v>
@@ -630,7 +630,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G9" t="n">
-        <v>4.16342496871948</v>
+        <v>4.16342449188232</v>
       </c>
       <c r="H9" t="n">
         <v>5755</v>
@@ -688,7 +688,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H11" t="n">
         <v>6680</v>
@@ -717,7 +717,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.17968893051147</v>
+        <v>4.17968845367432</v>
       </c>
       <c r="H19" t="n">
         <v>3229</v>
@@ -1065,7 +1065,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>4.26100492477417</v>
+        <v>4.26100444793701</v>
       </c>
       <c r="H24" t="n">
         <v>2429</v>
@@ -1094,7 +1094,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>4.26100492477417</v>
+        <v>4.26100444793701</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.22847843170166</v>
+        <v>4.2284779548645</v>
       </c>
       <c r="H26" t="n">
         <v>1926</v>
@@ -1152,7 +1152,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G27" t="n">
-        <v>4.22847843170166</v>
+        <v>4.2284779548645</v>
       </c>
       <c r="H27" t="n">
         <v>651</v>
@@ -1210,7 +1210,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H29" t="n">
         <v>1969</v>
@@ -1268,7 +1268,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H31" t="n">
         <v>6330</v>
@@ -1297,7 +1297,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H32" t="n">
         <v>1096</v>
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H35" t="n">
         <v>500</v>
@@ -1500,7 +1500,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H39" t="n">
         <v>300</v>
@@ -1529,7 +1529,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>4.22847843170166</v>
+        <v>4.2284779548645</v>
       </c>
       <c r="H40" t="n">
         <v>1276</v>
@@ -1558,7 +1558,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G41" t="n">
-        <v>4.22847843170166</v>
+        <v>4.2284779548645</v>
       </c>
       <c r="H41" t="n">
         <v>470</v>
@@ -1645,7 +1645,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G44" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H44" t="n">
         <v>3940</v>
@@ -1674,7 +1674,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G45" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>4.17968893051147</v>
+        <v>4.17968845367432</v>
       </c>
       <c r="H46" t="n">
         <v>980</v>
@@ -1732,7 +1732,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G47" t="n">
-        <v>4.16342496871948</v>
+        <v>4.16342449188232</v>
       </c>
       <c r="H47" t="n">
         <v>1066</v>
@@ -1761,7 +1761,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>4.16342496871948</v>
+        <v>4.16342449188232</v>
       </c>
       <c r="H48" t="n">
         <v>400</v>
@@ -1790,7 +1790,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G49" t="n">
-        <v>4.05771207809448</v>
+        <v>4.0577130317688</v>
       </c>
       <c r="H49" t="n">
         <v>5985</v>
@@ -1848,7 +1848,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200204849243</v>
+        <v>3.95200085639954</v>
       </c>
       <c r="H51" t="n">
         <v>4885</v>
@@ -1877,7 +1877,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639632225037</v>
+        <v>3.97639679908752</v>
       </c>
       <c r="H52" t="n">
         <v>1056</v>
@@ -1906,7 +1906,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639632225037</v>
+        <v>3.97639679908752</v>
       </c>
       <c r="H53" t="n">
         <v>504</v>
@@ -1935,7 +1935,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94386911392212</v>
+        <v>3.9438693523407</v>
       </c>
       <c r="H54" t="n">
         <v>2108</v>
@@ -1964,7 +1964,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321087837219</v>
+        <v>3.90321135520935</v>
       </c>
       <c r="H55" t="n">
         <v>1248</v>
@@ -1993,7 +1993,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321087837219</v>
+        <v>3.90321135520935</v>
       </c>
       <c r="H56" t="n">
         <v>400</v>
@@ -2022,7 +2022,7 @@
         <v>4.75</v>
       </c>
       <c r="G57" t="n">
-        <v>3.86255264282227</v>
+        <v>3.86255240440369</v>
       </c>
       <c r="H57" t="n">
         <v>4200</v>
@@ -2051,7 +2051,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442137718201</v>
+        <v>3.85442042350769</v>
       </c>
       <c r="H58" t="n">
         <v>450</v>
@@ -2080,7 +2080,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.8869481086731</v>
+        <v>3.88694763183594</v>
       </c>
       <c r="H59" t="n">
         <v>1153</v>
@@ -2138,7 +2138,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057674407959</v>
+        <v>3.74057698249817</v>
       </c>
       <c r="H61" t="n">
         <v>2000</v>
@@ -2167,7 +2167,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057674407959</v>
+        <v>3.74057698249817</v>
       </c>
       <c r="H62" t="n">
         <v>1245</v>
@@ -2225,7 +2225,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G64" t="n">
-        <v>3.63486528396606</v>
+        <v>3.63486504554749</v>
       </c>
       <c r="H64" t="n">
         <v>2884</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991850852966</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H65" t="n">
         <v>4762</v>
@@ -2312,7 +2312,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552351951599</v>
       </c>
       <c r="H67" t="n">
         <v>5250</v>
@@ -2370,7 +2370,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926051139832</v>
+        <v>3.65926003456116</v>
       </c>
       <c r="H69" t="n">
         <v>14000</v>
@@ -2399,7 +2399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991850852966</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H70" t="n">
         <v>12720</v>
@@ -2428,7 +2428,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926051139832</v>
+        <v>3.65926003456116</v>
       </c>
       <c r="H71" t="n">
         <v>11150</v>
@@ -2457,7 +2457,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552351951599</v>
       </c>
       <c r="H72" t="n">
         <v>6400</v>
@@ -2515,7 +2515,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.7731032371521</v>
+        <v>3.77310347557068</v>
       </c>
       <c r="H74" t="n">
         <v>7850</v>
@@ -2544,7 +2544,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991850852966</v>
+        <v>3.69991898536682</v>
       </c>
       <c r="H75" t="n">
         <v>12819</v>
@@ -2573,7 +2573,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552351951599</v>
       </c>
       <c r="H76" t="n">
         <v>24183</v>
@@ -2689,7 +2689,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16342496871948</v>
+        <v>4.16342449188232</v>
       </c>
       <c r="H80" t="n">
         <v>8198</v>
@@ -2776,7 +2776,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G83" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H83" t="n">
         <v>11228</v>
@@ -2805,7 +2805,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>4.17968893051147</v>
+        <v>4.17968845367432</v>
       </c>
       <c r="H84" t="n">
         <v>8061</v>
@@ -2921,7 +2921,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G88" t="n">
-        <v>4.22847843170166</v>
+        <v>4.2284779548645</v>
       </c>
       <c r="H88" t="n">
         <v>4736</v>
@@ -2950,7 +2950,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H89" t="n">
         <v>8400</v>
@@ -2979,7 +2979,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H90" t="n">
         <v>11784</v>
@@ -3037,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H92" t="n">
         <v>124660</v>
@@ -3095,7 +3095,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H94" t="n">
         <v>35821</v>
@@ -3153,7 +3153,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.45616579055786</v>
+        <v>4.4561653137207</v>
       </c>
       <c r="H96" t="n">
         <v>5000</v>
@@ -3327,7 +3327,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.32605934143066</v>
+        <v>4.32605838775635</v>
       </c>
       <c r="H102" t="n">
         <v>20579</v>
@@ -3356,7 +3356,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869276046753</v>
+        <v>4.48869228363037</v>
       </c>
       <c r="H103" t="n">
         <v>18889</v>
@@ -3385,7 +3385,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869276046753</v>
+        <v>4.48869228363037</v>
       </c>
       <c r="H104" t="n">
         <v>6100</v>
@@ -3443,7 +3443,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495672225952</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H106" t="n">
         <v>11075</v>
@@ -3472,7 +3472,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495672225952</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H107" t="n">
         <v>9254</v>
@@ -3530,7 +3530,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.55374622344971</v>
+        <v>4.55374574661255</v>
       </c>
       <c r="H109" t="n">
         <v>6650</v>
@@ -3559,7 +3559,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>4.43990278244019</v>
+        <v>4.43990325927734</v>
       </c>
       <c r="H110" t="n">
         <v>13298</v>
@@ -3588,7 +3588,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H111" t="n">
         <v>9209</v>
@@ -3617,7 +3617,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G112" t="n">
-        <v>4.32605934143066</v>
+        <v>4.32605838775635</v>
       </c>
       <c r="H112" t="n">
         <v>8648</v>
@@ -3646,7 +3646,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>4.22847843170166</v>
+        <v>4.2284779548645</v>
       </c>
       <c r="H113" t="n">
         <v>32551</v>
@@ -3675,7 +3675,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G114" t="n">
-        <v>4.35858631134033</v>
+        <v>4.35858535766602</v>
       </c>
       <c r="H114" t="n">
         <v>39778</v>
@@ -3704,7 +3704,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G115" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H115" t="n">
         <v>9983</v>
@@ -3733,7 +3733,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.293532371521</v>
+        <v>4.29353189468384</v>
       </c>
       <c r="H116" t="n">
         <v>12350</v>
@@ -3820,7 +3820,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G119" t="n">
-        <v>4.35858631134033</v>
+        <v>4.35858535766602</v>
       </c>
       <c r="H119" t="n">
         <v>76765</v>
@@ -3849,7 +3849,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H120" t="n">
         <v>50907</v>
@@ -3907,7 +3907,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>4.34232234954834</v>
+        <v>4.3423228263855</v>
       </c>
       <c r="H122" t="n">
         <v>510822</v>
@@ -3994,7 +3994,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H125" t="n">
         <v>59141</v>
@@ -4023,7 +4023,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.55374622344971</v>
+        <v>4.55374574661255</v>
       </c>
       <c r="H126" t="n">
         <v>89802</v>
@@ -4052,7 +4052,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H127" t="n">
         <v>19970</v>
@@ -4081,7 +4081,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H128" t="n">
         <v>22395</v>
@@ -4110,7 +4110,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H129" t="n">
         <v>7536</v>
@@ -4168,7 +4168,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.63506317138672</v>
+        <v>4.6350622177124</v>
       </c>
       <c r="H131" t="n">
         <v>37064</v>
@@ -4226,7 +4226,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>4.86275005340576</v>
+        <v>4.86275053024292</v>
       </c>
       <c r="H133" t="n">
         <v>5321</v>
@@ -4284,7 +4284,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>5.07417440414429</v>
+        <v>5.07417392730713</v>
       </c>
       <c r="H135" t="n">
         <v>34938</v>
@@ -4313,7 +4313,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791044235229</v>
+        <v>5.05791139602661</v>
       </c>
       <c r="H136" t="n">
         <v>24382</v>
@@ -4342,7 +4342,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H137" t="n">
         <v>12072</v>
@@ -4371,7 +4371,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>5.15549087524414</v>
+        <v>5.1554913520813</v>
       </c>
       <c r="H138" t="n">
         <v>14771</v>
@@ -4400,7 +4400,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>5.15549087524414</v>
+        <v>5.1554913520813</v>
       </c>
       <c r="H139" t="n">
         <v>5761</v>
@@ -4429,7 +4429,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G140" t="n">
-        <v>5.07417440414429</v>
+        <v>5.07417392730713</v>
       </c>
       <c r="H140" t="n">
         <v>18825</v>
@@ -4458,7 +4458,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H141" t="n">
         <v>13207</v>
@@ -4487,7 +4487,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801736831665</v>
+        <v>5.18801832199097</v>
       </c>
       <c r="H142" t="n">
         <v>16197</v>
@@ -4516,7 +4516,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H143" t="n">
         <v>11836</v>
@@ -4545,7 +4545,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H144" t="n">
         <v>4290</v>
@@ -4603,7 +4603,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G146" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H146" t="n">
         <v>2211</v>
@@ -4632,7 +4632,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H147" t="n">
         <v>10023</v>
@@ -4661,7 +4661,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164743423462</v>
+        <v>5.04164695739746</v>
       </c>
       <c r="H148" t="n">
         <v>9600</v>
@@ -4719,7 +4719,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791044235229</v>
+        <v>5.05791139602661</v>
       </c>
       <c r="H150" t="n">
         <v>6072</v>
@@ -4748,7 +4748,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H151" t="n">
         <v>10138</v>
@@ -4777,7 +4777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G152" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H152" t="n">
         <v>7104</v>
@@ -4806,7 +4806,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H153" t="n">
         <v>5444</v>
@@ -4835,7 +4835,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G154" t="n">
-        <v>5.07417440414429</v>
+        <v>5.07417392730713</v>
       </c>
       <c r="H154" t="n">
         <v>9966</v>
@@ -4864,7 +4864,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538394927979</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H155" t="n">
         <v>13422</v>
@@ -4922,7 +4922,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H157" t="n">
         <v>4698</v>
@@ -4980,7 +4980,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H159" t="n">
         <v>11350</v>
@@ -5038,7 +5038,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164743423462</v>
+        <v>5.04164695739746</v>
       </c>
       <c r="H161" t="n">
         <v>3098</v>
@@ -5067,7 +5067,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G162" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H162" t="n">
         <v>7250</v>
@@ -5096,7 +5096,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G163" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H163" t="n">
         <v>7961</v>
@@ -5154,7 +5154,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G165" t="n">
-        <v>4.92780351638794</v>
+        <v>4.9278039932251</v>
       </c>
       <c r="H165" t="n">
         <v>10999</v>
@@ -5183,7 +5183,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G166" t="n">
-        <v>4.99285697937012</v>
+        <v>4.99285745620728</v>
       </c>
       <c r="H166" t="n">
         <v>16468</v>
@@ -5212,7 +5212,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G167" t="n">
-        <v>4.89527702331543</v>
+        <v>4.89527750015259</v>
       </c>
       <c r="H167" t="n">
         <v>20850</v>
@@ -5241,7 +5241,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G168" t="n">
-        <v>4.92780351638794</v>
+        <v>4.9278039932251</v>
       </c>
       <c r="H168" t="n">
         <v>6210</v>
@@ -5299,7 +5299,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.89527702331543</v>
+        <v>4.89527750015259</v>
       </c>
       <c r="H170" t="n">
         <v>15167</v>
@@ -5386,7 +5386,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.96033048629761</v>
+        <v>4.96033096313477</v>
       </c>
       <c r="H173" t="n">
         <v>5030</v>
@@ -5502,7 +5502,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>5.25307130813599</v>
+        <v>5.2530722618103</v>
       </c>
       <c r="H177" t="n">
         <v>49926</v>
@@ -5531,7 +5531,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G178" t="n">
-        <v>5.23680877685547</v>
+        <v>5.23680782318115</v>
       </c>
       <c r="H178" t="n">
         <v>49204</v>
@@ -5560,7 +5560,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065221786499</v>
       </c>
       <c r="H179" t="n">
         <v>12820</v>
@@ -5589,7 +5589,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065221786499</v>
       </c>
       <c r="H180" t="n">
         <v>11620</v>
@@ -5618,7 +5618,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065221786499</v>
       </c>
       <c r="H181" t="n">
         <v>5800</v>
@@ -5647,7 +5647,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>5.35065174102783</v>
+        <v>5.35065221786499</v>
       </c>
       <c r="H182" t="n">
         <v>7541</v>
@@ -5676,7 +5676,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>5.38317823410034</v>
+        <v>5.3831787109375</v>
       </c>
       <c r="H183" t="n">
         <v>5662</v>
@@ -5734,7 +5734,7 @@
         <v>6.5</v>
       </c>
       <c r="G185" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H185" t="n">
         <v>14887</v>
@@ -5763,7 +5763,7 @@
         <v>6.5</v>
       </c>
       <c r="G186" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H186" t="n">
         <v>11690</v>
@@ -5792,7 +5792,7 @@
         <v>6.5</v>
       </c>
       <c r="G187" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>6.5</v>
       </c>
       <c r="G188" t="n">
-        <v>5.28559827804565</v>
+        <v>5.28559875488281</v>
       </c>
       <c r="H188" t="n">
         <v>10480</v>
@@ -5850,7 +5850,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922834396362</v>
+        <v>5.13922739028931</v>
       </c>
       <c r="H189" t="n">
         <v>10921</v>
@@ -5879,7 +5879,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538394927979</v>
+        <v>5.02538442611694</v>
       </c>
       <c r="H190" t="n">
         <v>5989</v>
@@ -5966,7 +5966,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H193" t="n">
         <v>4766</v>
@@ -5995,7 +5995,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G194" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H194" t="n">
         <v>2077</v>
@@ -6024,7 +6024,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>5.00475597381592</v>
+        <v>5.00475692749023</v>
       </c>
       <c r="H195" t="n">
         <v>15185</v>
@@ -6053,7 +6053,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H196" t="n">
         <v>5900</v>
@@ -6140,7 +6140,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H199" t="n">
         <v>6894</v>
@@ -6169,7 +6169,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H200" t="n">
         <v>28649</v>
@@ -6227,7 +6227,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H202" t="n">
         <v>680</v>
@@ -6256,7 +6256,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H203" t="n">
         <v>5722</v>
@@ -6285,7 +6285,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H204" t="n">
         <v>3896</v>
@@ -6372,7 +6372,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H207" t="n">
         <v>5465</v>
@@ -6401,7 +6401,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>5.35392570495605</v>
+        <v>5.35392475128174</v>
       </c>
       <c r="H208" t="n">
         <v>3971</v>
@@ -6430,7 +6430,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.35392570495605</v>
+        <v>5.35392475128174</v>
       </c>
       <c r="H209" t="n">
         <v>6644</v>
@@ -6517,7 +6517,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368766784668</v>
       </c>
       <c r="H212" t="n">
         <v>6658</v>
@@ -6604,7 +6604,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H215" t="n">
         <v>22458</v>
@@ -6633,7 +6633,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368814468384</v>
+        <v>5.45368766784668</v>
       </c>
       <c r="H216" t="n">
         <v>10530</v>
@@ -6662,7 +6662,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G217" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H217" t="n">
         <v>7967</v>
@@ -6691,7 +6691,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H218" t="n">
         <v>6727</v>
@@ -6720,7 +6720,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>5.60333108901978</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H219" t="n">
         <v>20185</v>
@@ -6749,7 +6749,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H220" t="n">
         <v>4090</v>
@@ -6807,7 +6807,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G222" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H222" t="n">
         <v>8191</v>
@@ -6836,7 +6836,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66984033584595</v>
+        <v>5.66984081268311</v>
       </c>
       <c r="H223" t="n">
         <v>3507</v>
@@ -6923,7 +6923,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H226" t="n">
         <v>20880</v>
@@ -6952,7 +6952,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>5.9026198387146</v>
+        <v>5.90261936187744</v>
       </c>
       <c r="H227" t="n">
         <v>38319</v>
@@ -7010,7 +7010,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G229" t="n">
-        <v>5.9691276550293</v>
+        <v>5.96912813186646</v>
       </c>
       <c r="H229" t="n">
         <v>37060</v>
@@ -7068,7 +7068,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G231" t="n">
-        <v>5.80285692214966</v>
+        <v>5.80285739898682</v>
       </c>
       <c r="H231" t="n">
         <v>11590</v>
@@ -7097,7 +7097,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>5.9026198387146</v>
+        <v>5.90261936187744</v>
       </c>
       <c r="H232" t="n">
         <v>6952</v>
@@ -7126,7 +7126,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>5.9026198387146</v>
+        <v>5.90261936187744</v>
       </c>
       <c r="H233" t="n">
         <v>4553</v>
@@ -7155,7 +7155,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>5.85273838043213</v>
+        <v>5.85273790359497</v>
       </c>
       <c r="H234" t="n">
         <v>12940</v>
@@ -7242,7 +7242,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H237" t="n">
         <v>8720</v>
@@ -7271,7 +7271,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>5.83611106872559</v>
+        <v>5.83611154556274</v>
       </c>
       <c r="H238" t="n">
         <v>2340</v>
@@ -7300,7 +7300,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>5.80285692214966</v>
+        <v>5.80285739898682</v>
       </c>
       <c r="H239" t="n">
         <v>8443</v>
@@ -7416,7 +7416,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G243" t="n">
-        <v>5.76960277557373</v>
+        <v>5.76960325241089</v>
       </c>
       <c r="H243" t="n">
         <v>1500</v>
@@ -7445,7 +7445,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G244" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H244" t="n">
         <v>4011</v>
@@ -7474,7 +7474,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G245" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H245" t="n">
         <v>4200</v>
@@ -7532,7 +7532,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G247" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H247" t="n">
         <v>5180</v>
@@ -7648,7 +7648,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66984033584595</v>
+        <v>5.66984081268311</v>
       </c>
       <c r="H251" t="n">
         <v>1386</v>
@@ -7677,7 +7677,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G252" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H252" t="n">
         <v>8006</v>
@@ -7706,7 +7706,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H253" t="n">
         <v>472</v>
@@ -7764,7 +7764,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G255" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H255" t="n">
         <v>1900</v>
@@ -7793,7 +7793,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G258" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H258" t="n">
         <v>4652</v>
@@ -7880,7 +7880,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G259" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H259" t="n">
         <v>2350</v>
@@ -7938,7 +7938,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H261" t="n">
         <v>2105</v>
@@ -7967,7 +7967,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H262" t="n">
         <v>500</v>
@@ -8025,7 +8025,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>5.60333108901978</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H264" t="n">
         <v>1211</v>
@@ -8054,7 +8054,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G265" t="n">
-        <v>5.61995887756348</v>
+        <v>5.61995935440063</v>
       </c>
       <c r="H265" t="n">
         <v>1620</v>
@@ -8112,7 +8112,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G267" t="n">
-        <v>5.60333108901978</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H267" t="n">
         <v>175</v>
@@ -8141,7 +8141,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H268" t="n">
         <v>1450</v>
@@ -8199,7 +8199,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H270" t="n">
         <v>5650</v>
@@ -8286,7 +8286,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H273" t="n">
         <v>13409</v>
@@ -8315,7 +8315,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H274" t="n">
         <v>4619</v>
@@ -8518,7 +8518,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G281" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H281" t="n">
         <v>7624</v>
@@ -8576,7 +8576,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G283" t="n">
-        <v>5.68646717071533</v>
+        <v>5.68646764755249</v>
       </c>
       <c r="H283" t="n">
         <v>4800</v>
@@ -8605,7 +8605,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H284" t="n">
         <v>6060</v>
@@ -8692,7 +8692,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>5.63658571243286</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H287" t="n">
         <v>1750</v>
@@ -8721,7 +8721,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H288" t="n">
         <v>1973</v>
@@ -8779,7 +8779,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G290" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H290" t="n">
         <v>16096</v>
@@ -8808,7 +8808,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H291" t="n">
         <v>4539</v>
@@ -8837,7 +8837,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H292" t="n">
         <v>31220</v>
@@ -8895,7 +8895,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G294" t="n">
-        <v>5.60333108901978</v>
+        <v>5.60333204269409</v>
       </c>
       <c r="H294" t="n">
         <v>31744</v>
@@ -8924,7 +8924,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H295" t="n">
         <v>22500</v>
@@ -8953,7 +8953,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>5.53682327270508</v>
+        <v>5.53682374954224</v>
       </c>
       <c r="H296" t="n">
         <v>24602</v>
@@ -8982,7 +8982,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H297" t="n">
         <v>7700</v>
@@ -9011,7 +9011,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H298" t="n">
         <v>17311</v>
@@ -9069,7 +9069,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>5.48694229125977</v>
+        <v>5.48694181442261</v>
       </c>
       <c r="H300" t="n">
         <v>4728</v>
@@ -9156,7 +9156,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H303" t="n">
         <v>4716</v>
@@ -9185,7 +9185,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H304" t="n">
         <v>1563</v>
@@ -9301,7 +9301,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>5.35392570495605</v>
+        <v>5.35392475128174</v>
       </c>
       <c r="H308" t="n">
         <v>7755</v>
@@ -9330,7 +9330,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H309" t="n">
         <v>3800</v>
@@ -9359,7 +9359,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H310" t="n">
         <v>27369</v>
@@ -9417,7 +9417,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G312" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H312" t="n">
         <v>4873</v>
@@ -9504,7 +9504,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H315" t="n">
         <v>3276</v>
@@ -9620,7 +9620,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G319" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H319" t="n">
         <v>1750</v>
@@ -9678,7 +9678,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H321" t="n">
         <v>5361</v>
@@ -9765,7 +9765,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G324" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H324" t="n">
         <v>4701</v>
@@ -9852,7 +9852,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G327" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H327" t="n">
         <v>10600</v>
@@ -9881,7 +9881,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H328" t="n">
         <v>6860</v>
@@ -9910,7 +9910,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H329" t="n">
         <v>24800</v>
@@ -9939,7 +9939,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H330" t="n">
         <v>5585</v>
@@ -10026,7 +10026,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G333" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H333" t="n">
         <v>1126</v>
@@ -10055,7 +10055,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G334" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H334" t="n">
         <v>10830</v>
@@ -10084,7 +10084,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G335" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H335" t="n">
         <v>11568</v>
@@ -10113,7 +10113,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G336" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10171,7 +10171,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G338" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777351379395</v>
       </c>
       <c r="H338" t="n">
         <v>2453</v>
@@ -10258,7 +10258,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H341" t="n">
         <v>13173</v>
@@ -10374,7 +10374,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H345" t="n">
         <v>8254</v>
@@ -10403,7 +10403,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10461,7 +10461,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H348" t="n">
         <v>3489</v>
@@ -10490,7 +10490,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G349" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H349" t="n">
         <v>8775</v>
@@ -10606,7 +10606,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G353" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777351379395</v>
       </c>
       <c r="H353" t="n">
         <v>6420</v>
@@ -10635,7 +10635,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H354" t="n">
         <v>7088</v>
@@ -10693,7 +10693,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H356" t="n">
         <v>2400</v>
@@ -10722,7 +10722,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463743209839</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H358" t="n">
         <v>4600</v>
@@ -10780,7 +10780,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>5.07126426696777</v>
+        <v>5.07126522064209</v>
       </c>
       <c r="H359" t="n">
         <v>3000</v>
@@ -10809,7 +10809,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G360" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H360" t="n">
         <v>1600</v>
@@ -10925,7 +10925,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G364" t="n">
-        <v>5.2707896232605</v>
+        <v>5.27079010009766</v>
       </c>
       <c r="H364" t="n">
         <v>2203</v>
@@ -10954,7 +10954,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G365" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H365" t="n">
         <v>1500</v>
@@ -10983,7 +10983,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102766036987</v>
       </c>
       <c r="H366" t="n">
         <v>710</v>
@@ -11012,7 +11012,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777351379395</v>
       </c>
       <c r="H367" t="n">
         <v>112</v>
@@ -11041,7 +11041,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G368" t="n">
-        <v>5.13777256011963</v>
+        <v>5.13777351379395</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H373" t="n">
         <v>4742</v>
@@ -11244,7 +11244,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G375" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H375" t="n">
         <v>2615</v>
@@ -11331,7 +11331,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102766036987</v>
       </c>
       <c r="H378" t="n">
         <v>112</v>
@@ -11360,7 +11360,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102766036987</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102670669556</v>
+        <v>5.17102766036987</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H383" t="n">
         <v>5263</v>
@@ -11505,7 +11505,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404376983643</v>
+        <v>5.30404472351074</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11795,7 +11795,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G394" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H394" t="n">
         <v>1700</v>
@@ -11824,7 +11824,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G395" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H395" t="n">
         <v>1098</v>
@@ -11853,7 +11853,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G396" t="n">
-        <v>5.18765449523926</v>
+        <v>5.1876540184021</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11940,7 +11940,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97150182723999</v>
+        <v>4.97150230407715</v>
       </c>
       <c r="H399" t="n">
         <v>5742</v>
@@ -11969,7 +11969,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>4.82185840606689</v>
+        <v>4.82185792922974</v>
       </c>
       <c r="H400" t="n">
         <v>7273</v>
@@ -11998,7 +11998,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G401" t="n">
-        <v>4.92162132263184</v>
+        <v>4.92162084579468</v>
       </c>
       <c r="H401" t="n">
         <v>1890</v>
@@ -12085,7 +12085,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>4.88836717605591</v>
+        <v>4.88836669921875</v>
       </c>
       <c r="H404" t="n">
         <v>32</v>
@@ -12143,7 +12143,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>4.67221403121948</v>
+        <v>4.6722149848938</v>
       </c>
       <c r="H406" t="n">
         <v>19716</v>
@@ -12172,7 +12172,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H407" t="n">
         <v>9154</v>
@@ -12201,7 +12201,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>4.4893159866333</v>
+        <v>4.48931646347046</v>
       </c>
       <c r="H408" t="n">
         <v>6788</v>
@@ -12346,7 +12346,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H413" t="n">
         <v>6760</v>
@@ -12404,7 +12404,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H415" t="n">
         <v>970</v>
@@ -12462,7 +12462,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>4.4893159866333</v>
+        <v>4.48931646347046</v>
       </c>
       <c r="H417" t="n">
         <v>4244</v>
@@ -12491,7 +12491,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>4.47268915176392</v>
+        <v>4.47268962860107</v>
       </c>
       <c r="H418" t="n">
         <v>25169</v>
@@ -12520,7 +12520,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>4.35629940032959</v>
+        <v>4.35629844665527</v>
       </c>
       <c r="H419" t="n">
         <v>5206</v>
@@ -12549,7 +12549,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G420" t="n">
-        <v>4.45606231689453</v>
+        <v>4.45606184005737</v>
       </c>
       <c r="H420" t="n">
         <v>5661</v>
@@ -12578,7 +12578,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H421" t="n">
         <v>1908</v>
@@ -12607,7 +12607,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H422" t="n">
         <v>7657</v>
@@ -12636,7 +12636,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H423" t="n">
         <v>3457</v>
@@ -12694,7 +12694,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>4.67221403121948</v>
+        <v>4.6722149848938</v>
       </c>
       <c r="H425" t="n">
         <v>5049</v>
@@ -12839,7 +12839,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H430" t="n">
         <v>7925</v>
@@ -13042,7 +13042,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H437" t="n">
         <v>6066</v>
@@ -13071,7 +13071,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H438" t="n">
         <v>1719</v>
@@ -13100,7 +13100,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G439" t="n">
-        <v>4.75535011291504</v>
+        <v>4.75534963607788</v>
       </c>
       <c r="H439" t="n">
         <v>4000</v>
@@ -13129,7 +13129,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G440" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H440" t="n">
         <v>700</v>
@@ -13158,7 +13158,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H441" t="n">
         <v>4384</v>
@@ -13216,7 +13216,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H443" t="n">
         <v>3174</v>
@@ -13245,7 +13245,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H444" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558671951294</v>
       </c>
       <c r="H445" t="n">
         <v>1010</v>
@@ -13303,7 +13303,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13332,7 +13332,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H447" t="n">
         <v>1000</v>
@@ -13361,7 +13361,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H450" t="n">
         <v>1700</v>
@@ -13477,7 +13477,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504903793335</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H452" t="n">
         <v>500</v>
@@ -13506,7 +13506,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504903793335</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13564,7 +13564,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H455" t="n">
         <v>5500</v>
@@ -13593,7 +13593,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G463" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H463" t="n">
         <v>5</v>
@@ -13854,7 +13854,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H465" t="n">
         <v>205</v>
@@ -13912,7 +13912,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H467" t="n">
         <v>1464</v>
@@ -13941,7 +13941,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H468" t="n">
         <v>810</v>
@@ -13970,7 +13970,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H469" t="n">
         <v>646</v>
@@ -13999,7 +13999,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H470" t="n">
         <v>1000</v>
@@ -14028,7 +14028,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -14057,7 +14057,7 @@
         <v>6</v>
       </c>
       <c r="G472" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H472" t="n">
         <v>2091</v>
@@ -14086,7 +14086,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H473" t="n">
         <v>9179</v>
@@ -14144,7 +14144,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G475" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H475" t="n">
         <v>1701</v>
@@ -14202,7 +14202,7 @@
         <v>5.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H477" t="n">
         <v>350</v>
@@ -14318,7 +14318,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504903793335</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H481" t="n">
         <v>500</v>
@@ -14550,7 +14550,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G489" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H489" t="n">
         <v>3700</v>
@@ -14608,7 +14608,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G491" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H491" t="n">
         <v>500</v>
@@ -14637,7 +14637,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G492" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H492" t="n">
         <v>23909</v>
@@ -14666,7 +14666,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G493" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H493" t="n">
         <v>26022</v>
@@ -14811,7 +14811,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G498" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H498" t="n">
         <v>3223</v>
@@ -14840,7 +14840,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G499" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G500" t="n">
-        <v>4.41524457931519</v>
+        <v>4.41524505615234</v>
       </c>
       <c r="H500" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G506" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H506" t="n">
         <v>55</v>
@@ -15217,7 +15217,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H512" t="n">
         <v>2050</v>
@@ -15275,7 +15275,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G514" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H514" t="n">
         <v>1247</v>
@@ -15304,7 +15304,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G515" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H515" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G516" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H516" t="n">
         <v>0</v>
@@ -15420,7 +15420,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G519" t="n">
-        <v>4.89256906509399</v>
+        <v>4.89256858825684</v>
       </c>
       <c r="H519" t="n">
         <v>320</v>
@@ -15449,7 +15449,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G520" t="n">
-        <v>4.89256906509399</v>
+        <v>4.89256858825684</v>
       </c>
       <c r="H520" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G521" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H521" t="n">
         <v>341</v>
@@ -15565,7 +15565,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G524" t="n">
-        <v>4.9948525428772</v>
+        <v>4.99485206604004</v>
       </c>
       <c r="H524" t="n">
         <v>1780</v>
@@ -15594,7 +15594,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H525" t="n">
         <v>235</v>
@@ -15681,7 +15681,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H528" t="n">
         <v>700</v>
@@ -15710,7 +15710,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008813858032</v>
       </c>
       <c r="H530" t="n">
         <v>1270</v>
@@ -15971,7 +15971,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H538" t="n">
         <v>1776</v>
@@ -16232,7 +16232,7 @@
         <v>5.5</v>
       </c>
       <c r="G547" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H547" t="n">
         <v>2535</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.48343420028687</v>
+        <v>4.48343467712402</v>
       </c>
       <c r="H549" t="n">
         <v>1022</v>
@@ -16319,7 +16319,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>4.55162334442139</v>
+        <v>4.55162286758423</v>
       </c>
       <c r="H550" t="n">
         <v>360</v>
@@ -16348,7 +16348,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>4.48343420028687</v>
+        <v>4.48343467712402</v>
       </c>
       <c r="H551" t="n">
         <v>1200</v>
@@ -16377,7 +16377,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.55162334442139</v>
+        <v>4.55162286758423</v>
       </c>
       <c r="H552" t="n">
         <v>450</v>
@@ -16435,7 +16435,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G554" t="n">
-        <v>4.44933891296387</v>
+        <v>4.44933938980103</v>
       </c>
       <c r="H554" t="n">
         <v>608</v>
@@ -16464,7 +16464,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H555" t="n">
         <v>855</v>
@@ -16493,7 +16493,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -16522,7 +16522,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H557" t="n">
         <v>622</v>
@@ -16551,7 +16551,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G558" t="n">
-        <v>4.51752853393555</v>
+        <v>4.51752901077271</v>
       </c>
       <c r="H558" t="n">
         <v>3300</v>
@@ -17044,7 +17044,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H575" t="n">
         <v>20</v>
@@ -17073,7 +17073,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17334,7 +17334,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H585" t="n">
         <v>360</v>
@@ -17624,7 +17624,7 @@
         <v>5.5</v>
       </c>
       <c r="G595" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H595" t="n">
         <v>6710</v>
@@ -18117,7 +18117,7 @@
         <v>5.5</v>
       </c>
       <c r="G612" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H612" t="n">
         <v>34</v>
@@ -18146,7 +18146,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H613" t="n">
         <v>186</v>
@@ -18175,7 +18175,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G614" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H614" t="n">
         <v>186</v>
@@ -18204,7 +18204,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G615" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H615" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G616" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H616" t="n">
         <v>0</v>
@@ -18262,7 +18262,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G617" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18291,7 +18291,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G618" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H618" t="n">
         <v>0</v>
@@ -18320,7 +18320,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H619" t="n">
         <v>675</v>
@@ -18378,7 +18378,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G621" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H621" t="n">
         <v>200</v>
@@ -18407,7 +18407,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G622" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H622" t="n">
         <v>0</v>
@@ -18436,7 +18436,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H623" t="n">
         <v>0</v>
@@ -18465,7 +18465,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G624" t="n">
-        <v>4.73914337158203</v>
+        <v>4.73914289474487</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18523,7 +18523,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H626" t="n">
         <v>110</v>
@@ -18552,7 +18552,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H627" t="n">
         <v>10</v>
@@ -18581,7 +18581,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H628" t="n">
         <v>400</v>
@@ -18610,7 +18610,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H629" t="n">
         <v>110</v>
@@ -18726,7 +18726,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504903793335</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H633" t="n">
         <v>1703</v>
@@ -18842,7 +18842,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G637" t="n">
-        <v>5.01189947128296</v>
+        <v>5.0118989944458</v>
       </c>
       <c r="H637" t="n">
         <v>67041</v>
@@ -18871,7 +18871,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G638" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H638" t="n">
         <v>3800</v>
@@ -18958,7 +18958,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>5.01189947128296</v>
+        <v>5.0118989944458</v>
       </c>
       <c r="H641" t="n">
         <v>3920</v>
@@ -18987,7 +18987,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H642" t="n">
         <v>5765</v>
@@ -19016,7 +19016,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>5.25056076049805</v>
+        <v>5.25056123733521</v>
       </c>
       <c r="H643" t="n">
         <v>4245</v>
@@ -19045,7 +19045,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G644" t="n">
-        <v>5.35284519195557</v>
+        <v>5.35284566879272</v>
       </c>
       <c r="H644" t="n">
         <v>15820</v>
@@ -19161,7 +19161,7 @@
         <v>6</v>
       </c>
       <c r="G648" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H648" t="n">
         <v>1200</v>
@@ -19335,7 +19335,7 @@
         <v>6</v>
       </c>
       <c r="G654" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H654" t="n">
         <v>3833</v>
@@ -19364,7 +19364,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G655" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H655" t="n">
         <v>1585</v>
@@ -19422,7 +19422,7 @@
         <v>6</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H657" t="n">
         <v>512</v>
@@ -19451,7 +19451,7 @@
         <v>6</v>
       </c>
       <c r="G658" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H658" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H659" t="n">
         <v>618</v>
@@ -19509,7 +19509,7 @@
         <v>6</v>
       </c>
       <c r="G660" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H660" t="n">
         <v>110</v>
@@ -19538,7 +19538,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H661" t="n">
         <v>160</v>
@@ -19567,7 +19567,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G662" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H662" t="n">
         <v>4300</v>
@@ -19596,7 +19596,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008813858032</v>
       </c>
       <c r="H663" t="n">
         <v>300</v>
@@ -19654,7 +19654,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G665" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H665" t="n">
         <v>3800</v>
@@ -19683,7 +19683,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>5.18237209320068</v>
+        <v>5.18237161636353</v>
       </c>
       <c r="H666" t="n">
         <v>0</v>
@@ -19857,7 +19857,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G672" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H672" t="n">
         <v>1371</v>
@@ -19886,7 +19886,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G673" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>6</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H674" t="n">
         <v>1922</v>
@@ -19973,7 +19973,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H676" t="n">
         <v>3802</v>
@@ -20002,7 +20002,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H677" t="n">
         <v>1377</v>
@@ -20031,7 +20031,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>6</v>
       </c>
       <c r="G679" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H679" t="n">
         <v>4219</v>
@@ -20089,7 +20089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H680" t="n">
         <v>893</v>
@@ -20118,7 +20118,7 @@
         <v>6</v>
       </c>
       <c r="G681" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H681" t="n">
         <v>1250</v>
@@ -20147,7 +20147,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H682" t="n">
         <v>6283</v>
@@ -20205,7 +20205,7 @@
         <v>6</v>
       </c>
       <c r="G684" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H684" t="n">
         <v>3929</v>
@@ -20234,7 +20234,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G685" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H685" t="n">
         <v>298</v>
@@ -20263,7 +20263,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G686" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H686" t="n">
         <v>1900</v>
@@ -20292,7 +20292,7 @@
         <v>6</v>
       </c>
       <c r="G687" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H687" t="n">
         <v>3300</v>
@@ -20321,7 +20321,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G688" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H688" t="n">
         <v>3796</v>
@@ -20350,7 +20350,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H689" t="n">
         <v>820</v>
@@ -20379,7 +20379,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H690" t="n">
         <v>700</v>
@@ -20408,7 +20408,7 @@
         <v>6</v>
       </c>
       <c r="G691" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H691" t="n">
         <v>3324</v>
@@ -20437,7 +20437,7 @@
         <v>6</v>
       </c>
       <c r="G692" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H692" t="n">
         <v>3119</v>
@@ -20466,7 +20466,7 @@
         <v>6</v>
       </c>
       <c r="G693" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H693" t="n">
         <v>2354</v>
@@ -20495,7 +20495,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G694" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H694" t="n">
         <v>2751</v>
@@ -20524,7 +20524,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G695" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H695" t="n">
         <v>331</v>
@@ -20553,7 +20553,7 @@
         <v>6</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H696" t="n">
         <v>10</v>
@@ -20640,7 +20640,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G699" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H699" t="n">
         <v>380</v>
@@ -20669,7 +20669,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894639968872</v>
       </c>
       <c r="H700" t="n">
         <v>807</v>
@@ -20698,7 +20698,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G701" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H701" t="n">
         <v>150</v>
@@ -20727,7 +20727,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G702" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H702" t="n">
         <v>0</v>
@@ -20756,7 +20756,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>5.0715651512146</v>
+        <v>5.07156467437744</v>
       </c>
       <c r="H703" t="n">
         <v>200</v>
@@ -20785,7 +20785,7 @@
         <v>6</v>
       </c>
       <c r="G704" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H704" t="n">
         <v>400</v>
@@ -20843,7 +20843,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>5.24644660949707</v>
+        <v>5.24644613265991</v>
       </c>
       <c r="H706" t="n">
         <v>100</v>
@@ -20872,7 +20872,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G707" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H707" t="n">
         <v>1585</v>
@@ -20988,7 +20988,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G711" t="n">
-        <v>5.24644660949707</v>
+        <v>5.24644613265991</v>
       </c>
       <c r="H711" t="n">
         <v>1834</v>
@@ -21046,7 +21046,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G713" t="n">
-        <v>5.24644660949707</v>
+        <v>5.24644613265991</v>
       </c>
       <c r="H713" t="n">
         <v>4193</v>
@@ -21075,7 +21075,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G714" t="n">
-        <v>5.24644660949707</v>
+        <v>5.24644613265991</v>
       </c>
       <c r="H714" t="n">
         <v>0</v>
@@ -21104,7 +21104,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G715" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H715" t="n">
         <v>3214</v>
@@ -21133,7 +21133,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G716" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H716" t="n">
         <v>1000</v>
@@ -21307,7 +21307,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G722" t="n">
-        <v>5.02600717544556</v>
+        <v>5.02600765228271</v>
       </c>
       <c r="H722" t="n">
         <v>2000</v>
@@ -21336,7 +21336,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G723" t="n">
-        <v>5.02600717544556</v>
+        <v>5.02600765228271</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G724" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H724" t="n">
         <v>500</v>
@@ -21539,7 +21539,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G730" t="n">
-        <v>5.02600717544556</v>
+        <v>5.02600765228271</v>
       </c>
       <c r="H730" t="n">
         <v>5500</v>
@@ -21684,7 +21684,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G735" t="n">
-        <v>4.67330551147461</v>
+        <v>4.67330598831177</v>
       </c>
       <c r="H735" t="n">
         <v>2823</v>
@@ -21858,7 +21858,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G741" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H741" t="n">
         <v>966</v>
@@ -21887,7 +21887,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H742" t="n">
         <v>0</v>
@@ -22061,7 +22061,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>4.67330551147461</v>
+        <v>4.67330598831177</v>
       </c>
       <c r="H748" t="n">
         <v>10155</v>
@@ -22177,7 +22177,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H752" t="n">
         <v>233</v>
@@ -22206,7 +22206,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H753" t="n">
         <v>2500</v>
@@ -22235,7 +22235,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H754" t="n">
         <v>4845</v>
@@ -22264,7 +22264,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G755" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H755" t="n">
         <v>5770</v>
@@ -22438,7 +22438,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G761" t="n">
-        <v>4.67330551147461</v>
+        <v>4.67330598831177</v>
       </c>
       <c r="H761" t="n">
         <v>3633</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H769" t="n">
         <v>2000</v>
@@ -22844,7 +22844,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>4.67330551147461</v>
+        <v>4.67330598831177</v>
       </c>
       <c r="H775" t="n">
         <v>2709</v>
@@ -22873,7 +22873,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G776" t="n">
-        <v>4.67330551147461</v>
+        <v>4.67330598831177</v>
       </c>
       <c r="H776" t="n">
         <v>0</v>
@@ -23018,7 +23018,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G781" t="n">
-        <v>4.67330551147461</v>
+        <v>4.67330598831177</v>
       </c>
       <c r="H781" t="n">
         <v>505</v>
@@ -23047,7 +23047,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>4.67330551147461</v>
+        <v>4.67330598831177</v>
       </c>
       <c r="H782" t="n">
         <v>0</v>
@@ -23076,7 +23076,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G783" t="n">
-        <v>4.67330551147461</v>
+        <v>4.67330598831177</v>
       </c>
       <c r="H783" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G785" t="n">
-        <v>4.67330551147461</v>
+        <v>4.67330598831177</v>
       </c>
       <c r="H785" t="n">
         <v>170</v>
@@ -23163,7 +23163,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G786" t="n">
-        <v>4.67330551147461</v>
+        <v>4.67330598831177</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23366,7 +23366,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G793" t="n">
-        <v>5.11418390274048</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H793" t="n">
         <v>1992</v>
@@ -23540,7 +23540,7 @@
         <v>5.25</v>
       </c>
       <c r="G799" t="n">
-        <v>4.62921762466431</v>
+        <v>4.62921810150146</v>
       </c>
       <c r="H799" t="n">
         <v>495</v>
@@ -23772,7 +23772,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.3206033706665</v>
+        <v>4.32060289382935</v>
       </c>
       <c r="H807" t="n">
         <v>9722</v>
@@ -23917,7 +23917,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.37350845336914</v>
+        <v>4.37350797653198</v>
       </c>
       <c r="H812" t="n">
         <v>1000</v>
@@ -24004,7 +24004,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H815" t="n">
         <v>1188</v>
@@ -24033,7 +24033,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H816" t="n">
         <v>10</v>
@@ -24091,7 +24091,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H818" t="n">
         <v>700</v>
@@ -24120,7 +24120,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H819" t="n">
         <v>166</v>
@@ -24149,7 +24149,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>4.02080631256104</v>
+        <v>4.02080583572388</v>
       </c>
       <c r="H823" t="n">
         <v>4500</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H827" t="n">
         <v>2876</v>
@@ -24381,7 +24381,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G828" t="n">
-        <v>3.87972545623779</v>
+        <v>3.87972497940063</v>
       </c>
       <c r="H828" t="n">
         <v>1550</v>
@@ -24410,7 +24410,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>4.02080631256104</v>
+        <v>4.02080583572388</v>
       </c>
       <c r="H829" t="n">
         <v>1007</v>
@@ -24497,7 +24497,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G832" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H832" t="n">
         <v>207</v>
@@ -24526,7 +24526,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H833" t="n">
         <v>1050</v>
@@ -24555,7 +24555,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G835" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H835" t="n">
         <v>1</v>
@@ -24613,7 +24613,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G836" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H836" t="n">
         <v>1974</v>
@@ -24787,7 +24787,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H842" t="n">
         <v>2500</v>
@@ -24816,7 +24816,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H843" t="n">
         <v>1253</v>
@@ -24903,7 +24903,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G846" t="n">
-        <v>4.25006294250488</v>
+        <v>4.25006246566772</v>
       </c>
       <c r="H846" t="n">
         <v>3297</v>
@@ -24932,7 +24932,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G847" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H847" t="n">
         <v>3500</v>
@@ -24961,7 +24961,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G848" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H848" t="n">
         <v>1250</v>
@@ -24990,7 +24990,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G849" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -25019,7 +25019,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G850" t="n">
-        <v>4.16188716888428</v>
+        <v>4.16188669204712</v>
       </c>
       <c r="H850" t="n">
         <v>0</v>
@@ -25048,7 +25048,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.09134674072266</v>
+        <v>4.0913462638855</v>
       </c>
       <c r="H851" t="n">
         <v>2200</v>
@@ -25077,7 +25077,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G852" t="n">
-        <v>4.00317049026489</v>
+        <v>4.00317096710205</v>
       </c>
       <c r="H852" t="n">
         <v>21572</v>
@@ -25135,7 +25135,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G854" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H854" t="n">
         <v>56826</v>
@@ -25164,7 +25164,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>4.00317049026489</v>
+        <v>4.00317096710205</v>
       </c>
       <c r="H855" t="n">
         <v>5901</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H856" t="n">
         <v>3097</v>
@@ -25222,7 +25222,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>4.02080631256104</v>
+        <v>4.02080583572388</v>
       </c>
       <c r="H857" t="n">
         <v>1400</v>
@@ -25309,7 +25309,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G860" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H860" t="n">
         <v>5097</v>
@@ -25483,7 +25483,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H866" t="n">
         <v>20519</v>
@@ -25512,7 +25512,7 @@
         <v>4.5</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96790099143982</v>
+        <v>3.96790075302124</v>
       </c>
       <c r="H867" t="n">
         <v>14414</v>
@@ -25541,7 +25541,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G868" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499519348145</v>
       </c>
       <c r="H868" t="n">
         <v>15412</v>
@@ -25570,7 +25570,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H869" t="n">
         <v>3776</v>
@@ -25599,7 +25599,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H870" t="n">
         <v>4073</v>
@@ -25657,7 +25657,7 @@
         <v>4.5</v>
       </c>
       <c r="G872" t="n">
-        <v>3.96790099143982</v>
+        <v>3.96790075302124</v>
       </c>
       <c r="H872" t="n">
         <v>2450</v>
@@ -25686,7 +25686,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H873" t="n">
         <v>5847</v>
@@ -25715,7 +25715,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.96790099143982</v>
+        <v>3.96790075302124</v>
       </c>
       <c r="H874" t="n">
         <v>3098</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H875" t="n">
         <v>3194</v>
@@ -25773,7 +25773,7 @@
         <v>4.5</v>
       </c>
       <c r="G876" t="n">
-        <v>3.96790099143982</v>
+        <v>3.96790075302124</v>
       </c>
       <c r="H876" t="n">
         <v>2457</v>
@@ -25802,7 +25802,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G877" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499519348145</v>
       </c>
       <c r="H877" t="n">
         <v>13736</v>
@@ -25831,7 +25831,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G878" t="n">
-        <v>3.84445524215698</v>
+        <v>3.8444550037384</v>
       </c>
       <c r="H878" t="n">
         <v>20986</v>
@@ -25860,7 +25860,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G879" t="n">
-        <v>3.84445524215698</v>
+        <v>3.8444550037384</v>
       </c>
       <c r="H879" t="n">
         <v>21055</v>
@@ -25889,7 +25889,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G880" t="n">
-        <v>3.84445524215698</v>
+        <v>3.8444550037384</v>
       </c>
       <c r="H880" t="n">
         <v>26401</v>
@@ -25918,7 +25918,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>3.8973605632782</v>
+        <v>3.89736032485962</v>
       </c>
       <c r="H881" t="n">
         <v>30875</v>
@@ -25947,7 +25947,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H882" t="n">
         <v>15378</v>
@@ -25976,7 +25976,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G883" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918478965759</v>
       </c>
       <c r="H883" t="n">
         <v>18373</v>
@@ -26005,7 +26005,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G884" t="n">
-        <v>3.72100877761841</v>
+        <v>3.72100901603699</v>
       </c>
       <c r="H884" t="n">
         <v>9694</v>
@@ -26034,7 +26034,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>3.68573880195618</v>
+        <v>3.68573904037476</v>
       </c>
       <c r="H885" t="n">
         <v>8364</v>
@@ -26063,7 +26063,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G886" t="n">
-        <v>3.73864412307739</v>
+        <v>3.73864388465881</v>
       </c>
       <c r="H886" t="n">
         <v>2531</v>
@@ -26092,7 +26092,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918478965759</v>
       </c>
       <c r="H887" t="n">
         <v>5091</v>
@@ -26121,7 +26121,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H888" t="n">
         <v>8519</v>
@@ -26150,7 +26150,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H889" t="n">
         <v>14342</v>
@@ -26179,7 +26179,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H890" t="n">
         <v>20433</v>
@@ -26208,7 +26208,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H891" t="n">
         <v>58437</v>
@@ -26237,7 +26237,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>3.8973605632782</v>
+        <v>3.89736032485962</v>
       </c>
       <c r="H892" t="n">
         <v>25887</v>
@@ -26266,7 +26266,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G893" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499519348145</v>
       </c>
       <c r="H893" t="n">
         <v>22381</v>
@@ -26295,7 +26295,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G894" t="n">
-        <v>3.87972545623779</v>
+        <v>3.87972497940063</v>
       </c>
       <c r="H894" t="n">
         <v>30205</v>
@@ -26324,7 +26324,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G895" t="n">
-        <v>3.84445524215698</v>
+        <v>3.8444550037384</v>
       </c>
       <c r="H895" t="n">
         <v>16801</v>
@@ -26382,7 +26382,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G897" t="n">
-        <v>3.84445524215698</v>
+        <v>3.8444550037384</v>
       </c>
       <c r="H897" t="n">
         <v>4097</v>
@@ -26469,7 +26469,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>3.79154968261719</v>
+        <v>3.79154992103577</v>
       </c>
       <c r="H900" t="n">
         <v>21083</v>
@@ -26527,7 +26527,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73864412307739</v>
+        <v>3.73864388465881</v>
       </c>
       <c r="H902" t="n">
         <v>44451</v>
@@ -26585,7 +26585,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G904" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918478965759</v>
       </c>
       <c r="H904" t="n">
         <v>39491</v>
@@ -26614,7 +26614,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G905" t="n">
-        <v>3.79154968261719</v>
+        <v>3.79154992103577</v>
       </c>
       <c r="H905" t="n">
         <v>14849</v>
@@ -26643,7 +26643,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G906" t="n">
-        <v>3.79154968261719</v>
+        <v>3.79154992103577</v>
       </c>
       <c r="H906" t="n">
         <v>5341</v>
@@ -26672,7 +26672,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H907" t="n">
         <v>7190</v>
@@ -26701,7 +26701,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G908" t="n">
-        <v>3.79154968261719</v>
+        <v>3.79154992103577</v>
       </c>
       <c r="H908" t="n">
         <v>400</v>
@@ -26759,7 +26759,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G910" t="n">
-        <v>3.79154968261719</v>
+        <v>3.79154992103577</v>
       </c>
       <c r="H910" t="n">
         <v>15870</v>
@@ -26817,7 +26817,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G912" t="n">
-        <v>3.87972545623779</v>
+        <v>3.87972497940063</v>
       </c>
       <c r="H912" t="n">
         <v>800</v>
@@ -26846,7 +26846,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499519348145</v>
       </c>
       <c r="H913" t="n">
         <v>1250</v>
@@ -26875,7 +26875,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86208987236023</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H914" t="n">
         <v>1050</v>
@@ -26904,7 +26904,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G915" t="n">
-        <v>3.8973605632782</v>
+        <v>3.89736032485962</v>
       </c>
       <c r="H915" t="n">
         <v>2945</v>
@@ -26933,7 +26933,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H916" t="n">
         <v>35</v>
@@ -26962,7 +26962,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G917" t="n">
-        <v>3.87972545623779</v>
+        <v>3.87972497940063</v>
       </c>
       <c r="H917" t="n">
         <v>1200</v>
@@ -26991,7 +26991,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>3.87972545623779</v>
+        <v>3.87972497940063</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27049,7 +27049,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H920" t="n">
         <v>8574</v>
@@ -27078,7 +27078,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G921" t="n">
-        <v>3.84445524215698</v>
+        <v>3.8444550037384</v>
       </c>
       <c r="H921" t="n">
         <v>1920</v>
@@ -27107,7 +27107,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G922" t="n">
-        <v>3.84445524215698</v>
+        <v>3.8444550037384</v>
       </c>
       <c r="H922" t="n">
         <v>9837</v>
@@ -27136,7 +27136,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499519348145</v>
       </c>
       <c r="H923" t="n">
         <v>10338</v>
@@ -27165,7 +27165,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G924" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H924" t="n">
         <v>2250</v>
@@ -27194,7 +27194,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H925" t="n">
         <v>2087</v>
@@ -27223,7 +27223,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H927" t="n">
         <v>1386</v>
@@ -27281,7 +27281,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G929" t="n">
-        <v>3.87972545623779</v>
+        <v>3.87972497940063</v>
       </c>
       <c r="H929" t="n">
         <v>1000</v>
@@ -27339,7 +27339,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H930" t="n">
         <v>125</v>
@@ -27368,7 +27368,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>3.87972545623779</v>
+        <v>3.87972497940063</v>
       </c>
       <c r="H931" t="n">
         <v>700</v>
@@ -27397,7 +27397,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026588439941</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H932" t="n">
         <v>468</v>
@@ -27426,7 +27426,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G933" t="n">
-        <v>4.05607652664185</v>
+        <v>4.05607604980469</v>
       </c>
       <c r="H933" t="n">
         <v>7761</v>
@@ -27484,7 +27484,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G935" t="n">
-        <v>4.07371091842651</v>
+        <v>4.07371139526367</v>
       </c>
       <c r="H935" t="n">
         <v>2555</v>
@@ -27513,7 +27513,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G936" t="n">
-        <v>4.25006294250488</v>
+        <v>4.25006246566772</v>
       </c>
       <c r="H936" t="n">
         <v>38360</v>
@@ -27542,7 +27542,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G937" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H937" t="n">
         <v>8262</v>
@@ -27571,7 +27571,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G938" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H938" t="n">
         <v>10491</v>
@@ -27600,7 +27600,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G939" t="n">
-        <v>4.37350845336914</v>
+        <v>4.37350797653198</v>
       </c>
       <c r="H939" t="n">
         <v>12401</v>
@@ -27629,7 +27629,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G940" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H940" t="n">
         <v>194</v>
@@ -27658,7 +27658,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H941" t="n">
         <v>430</v>
@@ -27687,7 +27687,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>4.37350845336914</v>
+        <v>4.37350797653198</v>
       </c>
       <c r="H942" t="n">
         <v>250</v>
@@ -27716,7 +27716,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G943" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H943" t="n">
         <v>1635</v>
@@ -27745,7 +27745,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G944" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H944" t="n">
         <v>8544</v>
@@ -27774,7 +27774,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H945" t="n">
         <v>3230</v>
@@ -27803,7 +27803,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>4.37350845336914</v>
+        <v>4.37350797653198</v>
       </c>
       <c r="H946" t="n">
         <v>28</v>
@@ -27832,7 +27832,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G947" t="n">
-        <v>4.37350845336914</v>
+        <v>4.37350797653198</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>4.3206033706665</v>
+        <v>4.32060289382935</v>
       </c>
       <c r="H948" t="n">
         <v>1000</v>
@@ -27890,7 +27890,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G949" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H949" t="n">
         <v>1750</v>
@@ -27919,7 +27919,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G950" t="n">
-        <v>4.3206033706665</v>
+        <v>4.32060289382935</v>
       </c>
       <c r="H950" t="n">
         <v>1675</v>
@@ -27948,7 +27948,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G951" t="n">
-        <v>4.3206033706665</v>
+        <v>4.32060289382935</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -27977,7 +27977,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>4.3206033706665</v>
+        <v>4.32060289382935</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -28006,7 +28006,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G953" t="n">
-        <v>4.3206033706665</v>
+        <v>4.32060289382935</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -28035,7 +28035,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G954" t="n">
-        <v>4.3206033706665</v>
+        <v>4.32060289382935</v>
       </c>
       <c r="H954" t="n">
         <v>0</v>
@@ -28064,7 +28064,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G955" t="n">
-        <v>4.30296850204468</v>
+        <v>4.30296754837036</v>
       </c>
       <c r="H955" t="n">
         <v>4302</v>
@@ -28093,7 +28093,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>4.33823823928833</v>
+        <v>4.33823776245117</v>
       </c>
       <c r="H956" t="n">
         <v>800</v>
@@ -28122,7 +28122,7 @@
         <v>5</v>
       </c>
       <c r="G957" t="n">
-        <v>4.40877819061279</v>
+        <v>4.40877866744995</v>
       </c>
       <c r="H957" t="n">
         <v>2700</v>
@@ -28412,7 +28412,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G967" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H967" t="n">
         <v>1977</v>
@@ -29282,7 +29282,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>4.45847797393799</v>
+        <v>4.45847749710083</v>
       </c>
       <c r="H997" t="n">
         <v>700</v>
@@ -29543,7 +29543,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.31169652938843</v>
+        <v>4.31169605255127</v>
       </c>
       <c r="H1006" t="n">
         <v>2585</v>
@@ -29572,7 +29572,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.31169652938843</v>
+        <v>4.31169605255127</v>
       </c>
       <c r="H1007" t="n">
         <v>2103</v>
@@ -29601,7 +29601,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H1008" t="n">
         <v>1200</v>
@@ -29630,7 +29630,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H1009" t="n">
         <v>600</v>
@@ -29659,7 +29659,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H1011" t="n">
         <v>300</v>
@@ -30790,7 +30790,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.0364818572998</v>
+        <v>4.03648138046265</v>
       </c>
       <c r="H1049" t="n">
         <v>2020</v>
@@ -30819,7 +30819,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.0364818572998</v>
+        <v>4.03648138046265</v>
       </c>
       <c r="H1050" t="n">
         <v>1250</v>
@@ -31080,7 +31080,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.9630913734436</v>
+        <v>3.96309113502502</v>
       </c>
       <c r="H1059" t="n">
         <v>4001</v>
@@ -31109,7 +31109,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.88970065116882</v>
+        <v>3.88970017433167</v>
       </c>
       <c r="H1060" t="n">
         <v>14640</v>
@@ -31196,7 +31196,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.9630913734436</v>
+        <v>3.96309113502502</v>
       </c>
       <c r="H1063" t="n">
         <v>6269</v>
@@ -31370,7 +31370,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.88970065116882</v>
+        <v>3.88970017433167</v>
       </c>
       <c r="H1069" t="n">
         <v>861</v>
@@ -32008,7 +32008,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1091" t="n">
-        <v>4.0364818572998</v>
+        <v>4.03648138046265</v>
       </c>
       <c r="H1091" t="n">
         <v>7006</v>
@@ -32037,7 +32037,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.0364818572998</v>
+        <v>4.03648138046265</v>
       </c>
       <c r="H1092" t="n">
         <v>10055</v>
@@ -32124,7 +32124,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.9630913734436</v>
+        <v>3.96309113502502</v>
       </c>
       <c r="H1095" t="n">
         <v>1998</v>
@@ -32153,7 +32153,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.9630913734436</v>
+        <v>3.96309113502502</v>
       </c>
       <c r="H1096" t="n">
         <v>0</v>
@@ -33226,7 +33226,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1133" t="n">
-        <v>4.38508749008179</v>
+        <v>4.38508701324463</v>
       </c>
       <c r="H1133" t="n">
         <v>1360</v>
@@ -33255,7 +33255,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.31169652938843</v>
+        <v>4.31169605255127</v>
       </c>
       <c r="H1134" t="n">
         <v>2035</v>
@@ -33516,7 +33516,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.31169652938843</v>
+        <v>4.31169605255127</v>
       </c>
       <c r="H1143" t="n">
         <v>500</v>
@@ -33661,7 +33661,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.45847797393799</v>
+        <v>4.45847749710083</v>
       </c>
       <c r="H1148" t="n">
         <v>12871</v>
@@ -46340,6 +46340,35 @@
         <v>1517</v>
       </c>
       <c r="I1585" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1586" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1586" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="D1586" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="E1586" t="n">
+        <v>6.05000019073486</v>
+      </c>
+      <c r="F1586" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="G1586" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="H1586" t="n">
+        <v>20294</v>
+      </c>
+      <c r="I1586" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H2" t="n">
         <v>425</v>
@@ -456,7 +456,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H3" t="n">
         <v>650</v>
@@ -485,7 +485,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H5" t="n">
         <v>1105</v>
@@ -543,7 +543,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H6" t="n">
         <v>18626</v>
@@ -572,7 +572,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H7" t="n">
         <v>5900</v>
@@ -601,7 +601,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H8" t="n">
         <v>1000</v>
@@ -630,7 +630,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G9" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H9" t="n">
         <v>5755</v>
@@ -659,7 +659,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G10" t="n">
-        <v>4.19595146179199</v>
+        <v>4.19595193862915</v>
       </c>
       <c r="H10" t="n">
         <v>1712</v>
@@ -688,7 +688,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H11" t="n">
         <v>6680</v>
@@ -717,7 +717,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>4.04958152770996</v>
+        <v>4.04958200454712</v>
       </c>
       <c r="H14" t="n">
         <v>810</v>
@@ -804,7 +804,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G15" t="n">
-        <v>4.11463499069214</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H15" t="n">
         <v>1464</v>
@@ -833,7 +833,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>4.11463499069214</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>4.11463499069214</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.08210849761963</v>
+        <v>4.08210802078247</v>
       </c>
       <c r="H18" t="n">
         <v>970</v>
@@ -978,7 +978,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.27726936340332</v>
+        <v>4.27726888656616</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H22" t="n">
         <v>3365</v>
@@ -1036,7 +1036,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>4.27726936340332</v>
+        <v>4.27726888656616</v>
       </c>
       <c r="H23" t="n">
         <v>3200</v>
@@ -1065,7 +1065,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G24" t="n">
-        <v>4.26100444793701</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H24" t="n">
         <v>2429</v>
@@ -1094,7 +1094,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G25" t="n">
-        <v>4.26100444793701</v>
+        <v>4.26100540161133</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H26" t="n">
         <v>1926</v>
@@ -1152,7 +1152,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G27" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H27" t="n">
         <v>651</v>
@@ -1181,7 +1181,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H28" t="n">
         <v>350</v>
@@ -1210,7 +1210,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H29" t="n">
         <v>1969</v>
@@ -1239,7 +1239,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H30" t="n">
         <v>4377</v>
@@ -1268,7 +1268,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H31" t="n">
         <v>6330</v>
@@ -1297,7 +1297,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H32" t="n">
         <v>1096</v>
@@ -1326,7 +1326,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.11463499069214</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H33" t="n">
         <v>2550</v>
@@ -1355,7 +1355,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H34" t="n">
         <v>3736</v>
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H35" t="n">
         <v>500</v>
@@ -1413,7 +1413,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G36" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H36" t="n">
         <v>550</v>
@@ -1442,7 +1442,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079202651978</v>
       </c>
       <c r="H37" t="n">
         <v>1422</v>
@@ -1471,7 +1471,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G38" t="n">
-        <v>4.08210849761963</v>
+        <v>4.08210802078247</v>
       </c>
       <c r="H38" t="n">
         <v>950</v>
@@ -1500,7 +1500,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H39" t="n">
         <v>300</v>
@@ -1529,7 +1529,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H40" t="n">
         <v>1276</v>
@@ -1558,7 +1558,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G41" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H41" t="n">
         <v>470</v>
@@ -1732,7 +1732,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G47" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H47" t="n">
         <v>1066</v>
@@ -1761,7 +1761,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G48" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H48" t="n">
         <v>400</v>
@@ -1790,7 +1790,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G49" t="n">
-        <v>4.0577130317688</v>
+        <v>4.05771255493164</v>
       </c>
       <c r="H49" t="n">
         <v>5985</v>
@@ -1819,7 +1819,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.98452830314636</v>
+        <v>3.98452806472778</v>
       </c>
       <c r="H50" t="n">
         <v>6262</v>
@@ -1848,7 +1848,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200085639954</v>
+        <v>3.95200133323669</v>
       </c>
       <c r="H51" t="n">
         <v>4885</v>
@@ -1877,7 +1877,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639679908752</v>
+        <v>3.97639608383179</v>
       </c>
       <c r="H52" t="n">
         <v>1056</v>
@@ -1906,7 +1906,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639679908752</v>
+        <v>3.97639608383179</v>
       </c>
       <c r="H53" t="n">
         <v>504</v>
@@ -1935,7 +1935,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.9438693523407</v>
+        <v>3.94386982917786</v>
       </c>
       <c r="H54" t="n">
         <v>2108</v>
@@ -2022,7 +2022,7 @@
         <v>4.75</v>
       </c>
       <c r="G57" t="n">
-        <v>3.86255240440369</v>
+        <v>3.86255264282227</v>
       </c>
       <c r="H57" t="n">
         <v>4200</v>
@@ -2080,7 +2080,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.88694763183594</v>
+        <v>3.88694787025452</v>
       </c>
       <c r="H59" t="n">
         <v>1153</v>
@@ -2138,7 +2138,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057698249817</v>
+        <v>3.74057674407959</v>
       </c>
       <c r="H61" t="n">
         <v>2000</v>
@@ -2167,7 +2167,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057698249817</v>
+        <v>3.74057674407959</v>
       </c>
       <c r="H62" t="n">
         <v>1245</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991850852966</v>
       </c>
       <c r="H65" t="n">
         <v>4762</v>
@@ -2283,7 +2283,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G66" t="n">
-        <v>3.71618247032166</v>
+        <v>3.71618270874023</v>
       </c>
       <c r="H66" t="n">
         <v>23931</v>
@@ -2312,7 +2312,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.67552351951599</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H67" t="n">
         <v>5250</v>
@@ -2370,7 +2370,7 @@
         <v>4.5</v>
       </c>
       <c r="G69" t="n">
-        <v>3.65926003456116</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H69" t="n">
         <v>14000</v>
@@ -2399,7 +2399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991850852966</v>
       </c>
       <c r="H70" t="n">
         <v>12720</v>
@@ -2428,7 +2428,7 @@
         <v>4.5</v>
       </c>
       <c r="G71" t="n">
-        <v>3.65926003456116</v>
+        <v>3.65926051139832</v>
       </c>
       <c r="H71" t="n">
         <v>11150</v>
@@ -2457,7 +2457,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>3.67552351951599</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H72" t="n">
         <v>6400</v>
@@ -2515,7 +2515,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.77310347557068</v>
+        <v>3.77310395240784</v>
       </c>
       <c r="H74" t="n">
         <v>7850</v>
@@ -2544,7 +2544,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991898536682</v>
+        <v>3.69991850852966</v>
       </c>
       <c r="H75" t="n">
         <v>12819</v>
@@ -2573,7 +2573,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>3.67552351951599</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H76" t="n">
         <v>24183</v>
@@ -2602,7 +2602,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079202651978</v>
       </c>
       <c r="H77" t="n">
         <v>35243</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079202651978</v>
       </c>
       <c r="H78" t="n">
         <v>15007</v>
@@ -2660,7 +2660,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>4.09837198257446</v>
+        <v>4.0983715057373</v>
       </c>
       <c r="H79" t="n">
         <v>61552</v>
@@ -2689,7 +2689,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G80" t="n">
-        <v>4.16342449188232</v>
+        <v>4.16342496871948</v>
       </c>
       <c r="H80" t="n">
         <v>8198</v>
@@ -2718,7 +2718,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G81" t="n">
-        <v>4.19595146179199</v>
+        <v>4.19595193862915</v>
       </c>
       <c r="H81" t="n">
         <v>4817</v>
@@ -2747,7 +2747,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>4.11463499069214</v>
+        <v>4.1146354675293</v>
       </c>
       <c r="H82" t="n">
         <v>8365</v>
@@ -2776,7 +2776,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G83" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H83" t="n">
         <v>11228</v>
@@ -2863,7 +2863,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -2921,7 +2921,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G88" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H88" t="n">
         <v>4736</v>
@@ -2950,7 +2950,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H89" t="n">
         <v>8400</v>
@@ -2979,7 +2979,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H90" t="n">
         <v>11784</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>4.00079154968262</v>
+        <v>4.00079202651978</v>
       </c>
       <c r="H91" t="n">
         <v>30633</v>
@@ -3037,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H92" t="n">
         <v>124660</v>
@@ -3095,7 +3095,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737628936768</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H94" t="n">
         <v>35821</v>
@@ -3153,7 +3153,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G96" t="n">
-        <v>4.4561653137207</v>
+        <v>4.45616579055786</v>
       </c>
       <c r="H96" t="n">
         <v>5000</v>
@@ -3327,7 +3327,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.32605838775635</v>
+        <v>4.32605981826782</v>
       </c>
       <c r="H102" t="n">
         <v>20579</v>
@@ -3356,7 +3356,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869228363037</v>
+        <v>4.48869276046753</v>
       </c>
       <c r="H103" t="n">
         <v>18889</v>
@@ -3385,7 +3385,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869228363037</v>
+        <v>4.48869276046753</v>
       </c>
       <c r="H104" t="n">
         <v>6100</v>
@@ -3443,7 +3443,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495624542236</v>
+        <v>4.50495576858521</v>
       </c>
       <c r="H106" t="n">
         <v>11075</v>
@@ -3472,7 +3472,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495624542236</v>
+        <v>4.50495576858521</v>
       </c>
       <c r="H107" t="n">
         <v>9254</v>
@@ -3530,7 +3530,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.55374574661255</v>
+        <v>4.55374622344971</v>
       </c>
       <c r="H109" t="n">
         <v>6650</v>
@@ -3559,7 +3559,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G110" t="n">
-        <v>4.43990325927734</v>
+        <v>4.43990278244019</v>
       </c>
       <c r="H110" t="n">
         <v>13298</v>
@@ -3617,7 +3617,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G112" t="n">
-        <v>4.32605838775635</v>
+        <v>4.32605981826782</v>
       </c>
       <c r="H112" t="n">
         <v>8648</v>
@@ -3646,7 +3646,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>4.2284779548645</v>
+        <v>4.22847843170166</v>
       </c>
       <c r="H113" t="n">
         <v>32551</v>
@@ -3675,7 +3675,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G114" t="n">
-        <v>4.35858535766602</v>
+        <v>4.35858583450317</v>
       </c>
       <c r="H114" t="n">
         <v>39778</v>
@@ -3762,7 +3762,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H117" t="n">
         <v>20886</v>
@@ -3791,7 +3791,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H118" t="n">
         <v>47283</v>
@@ -3820,7 +3820,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G119" t="n">
-        <v>4.35858535766602</v>
+        <v>4.35858583450317</v>
       </c>
       <c r="H119" t="n">
         <v>76765</v>
@@ -3849,7 +3849,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737628936768</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H120" t="n">
         <v>50907</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H121" t="n">
         <v>5333</v>
@@ -3907,7 +3907,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G122" t="n">
-        <v>4.3423228263855</v>
+        <v>4.34232234954834</v>
       </c>
       <c r="H122" t="n">
         <v>510822</v>
@@ -3936,7 +3936,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.30979585647583</v>
+        <v>4.30979490280151</v>
       </c>
       <c r="H123" t="n">
         <v>30275</v>
@@ -3994,7 +3994,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H125" t="n">
         <v>59141</v>
@@ -4023,7 +4023,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.55374574661255</v>
+        <v>4.55374622344971</v>
       </c>
       <c r="H126" t="n">
         <v>89802</v>
@@ -4052,7 +4052,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H127" t="n">
         <v>19970</v>
@@ -4081,7 +4081,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H128" t="n">
         <v>22395</v>
@@ -4110,7 +4110,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H129" t="n">
         <v>7536</v>
@@ -4168,7 +4168,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.6350622177124</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H131" t="n">
         <v>37064</v>
@@ -4226,7 +4226,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>4.86275053024292</v>
+        <v>4.86275005340576</v>
       </c>
       <c r="H133" t="n">
         <v>5321</v>
@@ -4313,7 +4313,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791139602661</v>
+        <v>5.05791091918945</v>
       </c>
       <c r="H136" t="n">
         <v>24382</v>
@@ -4342,7 +4342,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H137" t="n">
         <v>12072</v>
@@ -4516,7 +4516,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043836593628</v>
+        <v>5.09043788909912</v>
       </c>
       <c r="H143" t="n">
         <v>11836</v>
@@ -4574,7 +4574,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H145" t="n">
         <v>16119</v>
@@ -4661,7 +4661,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164695739746</v>
+        <v>5.04164791107178</v>
       </c>
       <c r="H148" t="n">
         <v>9600</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>4.87901401519775</v>
+        <v>4.8790135383606</v>
       </c>
       <c r="H149" t="n">
         <v>16280</v>
@@ -4719,7 +4719,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791139602661</v>
+        <v>5.05791091918945</v>
       </c>
       <c r="H150" t="n">
         <v>6072</v>
@@ -4864,7 +4864,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G155" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538394927979</v>
       </c>
       <c r="H155" t="n">
         <v>13422</v>
@@ -4951,7 +4951,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H158" t="n">
         <v>9550</v>
@@ -4980,7 +4980,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043836593628</v>
+        <v>5.09043788909912</v>
       </c>
       <c r="H159" t="n">
         <v>11350</v>
@@ -5009,7 +5009,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>4.97659397125244</v>
+        <v>4.97659349441528</v>
       </c>
       <c r="H160" t="n">
         <v>12705</v>
@@ -5038,7 +5038,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164695739746</v>
+        <v>5.04164791107178</v>
       </c>
       <c r="H161" t="n">
         <v>3098</v>
@@ -5125,7 +5125,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>4.94406747817993</v>
+        <v>4.94406652450562</v>
       </c>
       <c r="H164" t="n">
         <v>28419</v>
@@ -5212,7 +5212,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G167" t="n">
-        <v>4.89527750015259</v>
+        <v>4.89527702331543</v>
       </c>
       <c r="H167" t="n">
         <v>20850</v>
@@ -5270,7 +5270,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.94406747817993</v>
+        <v>4.94406652450562</v>
       </c>
       <c r="H169" t="n">
         <v>2656</v>
@@ -5299,7 +5299,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.89527750015259</v>
+        <v>4.89527702331543</v>
       </c>
       <c r="H170" t="n">
         <v>15167</v>
@@ -5357,7 +5357,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H172" t="n">
         <v>2308</v>
@@ -5386,7 +5386,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G173" t="n">
-        <v>4.96033096313477</v>
+        <v>4.96033048629761</v>
       </c>
       <c r="H173" t="n">
         <v>5030</v>
@@ -5415,7 +5415,7 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>4.87901401519775</v>
+        <v>4.8790135383606</v>
       </c>
       <c r="H174" t="n">
         <v>7490</v>
@@ -5444,7 +5444,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G175" t="n">
-        <v>4.83022356033325</v>
+        <v>4.83022403717041</v>
       </c>
       <c r="H175" t="n">
         <v>11057</v>
@@ -5473,7 +5473,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H176" t="n">
         <v>18455</v>
@@ -5502,7 +5502,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>5.2530722618103</v>
+        <v>5.25307178497314</v>
       </c>
       <c r="H177" t="n">
         <v>49926</v>
@@ -5531,7 +5531,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G178" t="n">
-        <v>5.23680782318115</v>
+        <v>5.23680877685547</v>
       </c>
       <c r="H178" t="n">
         <v>49204</v>
@@ -5850,7 +5850,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922739028931</v>
+        <v>5.13922834396362</v>
       </c>
       <c r="H189" t="n">
         <v>10921</v>
@@ -5879,7 +5879,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G190" t="n">
-        <v>5.02538442611694</v>
+        <v>5.02538394927979</v>
       </c>
       <c r="H190" t="n">
         <v>5989</v>
@@ -5908,7 +5908,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G191" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H191" t="n">
         <v>110919</v>
@@ -5937,7 +5937,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G192" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H192" t="n">
         <v>2290</v>
@@ -5966,7 +5966,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>5.20428133010864</v>
+        <v>5.2042818069458</v>
       </c>
       <c r="H193" t="n">
         <v>4766</v>
@@ -6024,7 +6024,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>5.00475692749023</v>
+        <v>5.00475597381592</v>
       </c>
       <c r="H195" t="n">
         <v>15185</v>
@@ -6140,7 +6140,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H199" t="n">
         <v>6894</v>
@@ -6169,7 +6169,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H200" t="n">
         <v>28649</v>
@@ -6198,7 +6198,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G201" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H201" t="n">
         <v>8833</v>
@@ -6227,7 +6227,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H202" t="n">
         <v>680</v>
@@ -6256,7 +6256,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H203" t="n">
         <v>5722</v>
@@ -6285,7 +6285,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H204" t="n">
         <v>3896</v>
@@ -6314,7 +6314,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G205" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H205" t="n">
         <v>1300</v>
@@ -6343,7 +6343,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H206" t="n">
         <v>4898</v>
@@ -6372,7 +6372,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H207" t="n">
         <v>5465</v>
@@ -6401,7 +6401,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>5.35392475128174</v>
+        <v>5.35392618179321</v>
       </c>
       <c r="H208" t="n">
         <v>3971</v>
@@ -6430,7 +6430,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.35392475128174</v>
+        <v>5.35392618179321</v>
       </c>
       <c r="H209" t="n">
         <v>6644</v>
@@ -6459,7 +6459,7 @@
         <v>6.5</v>
       </c>
       <c r="G210" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H210" t="n">
         <v>8091</v>
@@ -6488,7 +6488,7 @@
         <v>6.5</v>
       </c>
       <c r="G211" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H211" t="n">
         <v>5361</v>
@@ -6517,7 +6517,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368766784668</v>
+        <v>5.45368814468384</v>
       </c>
       <c r="H212" t="n">
         <v>6658</v>
@@ -6575,7 +6575,7 @@
         <v>6.5</v>
       </c>
       <c r="G214" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H214" t="n">
         <v>24252</v>
@@ -6604,7 +6604,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G215" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H215" t="n">
         <v>22458</v>
@@ -6633,7 +6633,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368766784668</v>
+        <v>5.45368814468384</v>
       </c>
       <c r="H216" t="n">
         <v>10530</v>
@@ -6662,7 +6662,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G217" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H217" t="n">
         <v>7967</v>
@@ -6691,7 +6691,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G218" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H218" t="n">
         <v>6727</v>
@@ -6749,7 +6749,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H220" t="n">
         <v>4090</v>
@@ -6778,7 +6778,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H221" t="n">
         <v>22001</v>
@@ -6807,7 +6807,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G222" t="n">
-        <v>5.78623008728027</v>
+        <v>5.78622961044312</v>
       </c>
       <c r="H222" t="n">
         <v>8191</v>
@@ -6836,7 +6836,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66983985900879</v>
       </c>
       <c r="H223" t="n">
         <v>3507</v>
@@ -6894,7 +6894,7 @@
         <v>7</v>
       </c>
       <c r="G225" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H225" t="n">
         <v>7539</v>
@@ -6923,7 +6923,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>5.78623008728027</v>
+        <v>5.78622961044312</v>
       </c>
       <c r="H226" t="n">
         <v>20880</v>
@@ -6981,7 +6981,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G228" t="n">
-        <v>5.88599252700806</v>
+        <v>5.8859920501709</v>
       </c>
       <c r="H228" t="n">
         <v>21811</v>
@@ -7039,7 +7039,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>5.93587350845337</v>
+        <v>5.93587446212769</v>
       </c>
       <c r="H230" t="n">
         <v>14060</v>
@@ -7155,7 +7155,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G234" t="n">
-        <v>5.85273790359497</v>
+        <v>5.85273838043213</v>
       </c>
       <c r="H234" t="n">
         <v>12940</v>
@@ -7184,7 +7184,7 @@
         <v>7</v>
       </c>
       <c r="G235" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H235" t="n">
         <v>7545</v>
@@ -7213,7 +7213,7 @@
         <v>7</v>
       </c>
       <c r="G236" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H236" t="n">
         <v>2000</v>
@@ -7242,7 +7242,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>5.78623008728027</v>
+        <v>5.78622961044312</v>
       </c>
       <c r="H237" t="n">
         <v>8720</v>
@@ -7271,7 +7271,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G238" t="n">
-        <v>5.83611154556274</v>
+        <v>5.83611106872559</v>
       </c>
       <c r="H238" t="n">
         <v>2340</v>
@@ -7329,7 +7329,7 @@
         <v>7</v>
       </c>
       <c r="G240" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H240" t="n">
         <v>3750</v>
@@ -7358,7 +7358,7 @@
         <v>7</v>
       </c>
       <c r="G241" t="n">
-        <v>5.81948375701904</v>
+        <v>5.8194842338562</v>
       </c>
       <c r="H241" t="n">
         <v>4000</v>
@@ -7416,7 +7416,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G243" t="n">
-        <v>5.76960325241089</v>
+        <v>5.76960277557373</v>
       </c>
       <c r="H243" t="n">
         <v>1500</v>
@@ -7445,7 +7445,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G244" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H244" t="n">
         <v>4011</v>
@@ -7619,7 +7619,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G250" t="n">
-        <v>5.58670473098755</v>
+        <v>5.58670425415039</v>
       </c>
       <c r="H250" t="n">
         <v>875</v>
@@ -7648,7 +7648,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66983985900879</v>
       </c>
       <c r="H251" t="n">
         <v>1386</v>
@@ -7677,7 +7677,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G252" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H252" t="n">
         <v>8006</v>
@@ -7706,7 +7706,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G253" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H253" t="n">
         <v>472</v>
@@ -7735,7 +7735,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G254" t="n">
-        <v>5.58670473098755</v>
+        <v>5.58670425415039</v>
       </c>
       <c r="H254" t="n">
         <v>2610</v>
@@ -7764,7 +7764,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G255" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H255" t="n">
         <v>1900</v>
@@ -7793,7 +7793,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H261" t="n">
         <v>2105</v>
@@ -7967,7 +7967,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H262" t="n">
         <v>500</v>
@@ -8054,7 +8054,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G265" t="n">
-        <v>5.61995935440063</v>
+        <v>5.61995887756348</v>
       </c>
       <c r="H265" t="n">
         <v>1620</v>
@@ -8083,7 +8083,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H266" t="n">
         <v>9438</v>
@@ -8141,7 +8141,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H268" t="n">
         <v>1450</v>
@@ -8170,7 +8170,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G269" t="n">
-        <v>5.50356912612915</v>
+        <v>5.50356960296631</v>
       </c>
       <c r="H269" t="n">
         <v>22096</v>
@@ -8228,7 +8228,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G271" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H271" t="n">
         <v>23690</v>
@@ -8286,7 +8286,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H273" t="n">
         <v>13409</v>
@@ -8402,7 +8402,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H277" t="n">
         <v>4450</v>
@@ -8431,7 +8431,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H278" t="n">
         <v>3400</v>
@@ -8489,7 +8489,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H280" t="n">
         <v>5210</v>
@@ -8547,7 +8547,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>5.7363486289978</v>
+        <v>5.73634815216064</v>
       </c>
       <c r="H282" t="n">
         <v>6500</v>
@@ -8605,7 +8605,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H284" t="n">
         <v>6060</v>
@@ -8692,7 +8692,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H287" t="n">
         <v>1750</v>
@@ -8750,7 +8750,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>5.50356912612915</v>
+        <v>5.50356960296631</v>
       </c>
       <c r="H289" t="n">
         <v>10165</v>
@@ -8779,7 +8779,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G290" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H290" t="n">
         <v>16096</v>
@@ -8837,7 +8837,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G292" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H292" t="n">
         <v>31220</v>
@@ -8866,7 +8866,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H293" t="n">
         <v>14001</v>
@@ -8924,7 +8924,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H295" t="n">
         <v>22500</v>
@@ -8953,7 +8953,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G296" t="n">
-        <v>5.53682374954224</v>
+        <v>5.53682327270508</v>
       </c>
       <c r="H296" t="n">
         <v>24602</v>
@@ -8982,7 +8982,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H297" t="n">
         <v>7700</v>
@@ -9011,7 +9011,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G298" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H298" t="n">
         <v>17311</v>
@@ -9040,7 +9040,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>5.43706035614014</v>
+        <v>5.43706083297729</v>
       </c>
       <c r="H299" t="n">
         <v>4580</v>
@@ -9069,7 +9069,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>5.48694181442261</v>
+        <v>5.48694229125977</v>
       </c>
       <c r="H300" t="n">
         <v>4728</v>
@@ -9098,7 +9098,7 @@
         <v>6.5</v>
       </c>
       <c r="G301" t="n">
-        <v>5.40380668640137</v>
+        <v>5.40380716323853</v>
       </c>
       <c r="H301" t="n">
         <v>21147</v>
@@ -9156,7 +9156,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H303" t="n">
         <v>4716</v>
@@ -9185,7 +9185,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H304" t="n">
         <v>1563</v>
@@ -9301,7 +9301,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>5.35392475128174</v>
+        <v>5.35392618179321</v>
       </c>
       <c r="H308" t="n">
         <v>7755</v>
@@ -9330,7 +9330,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H309" t="n">
         <v>3800</v>
@@ -9504,7 +9504,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H315" t="n">
         <v>3276</v>
@@ -9533,7 +9533,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H316" t="n">
         <v>29455</v>
@@ -9562,7 +9562,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>5.12114572525024</v>
+        <v>5.1211462020874</v>
       </c>
       <c r="H317" t="n">
         <v>4420</v>
@@ -9678,7 +9678,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H321" t="n">
         <v>5361</v>
@@ -9707,7 +9707,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H322" t="n">
         <v>6754</v>
@@ -9823,7 +9823,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H326" t="n">
         <v>4390</v>
@@ -9910,7 +9910,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H329" t="n">
         <v>24800</v>
@@ -9939,7 +9939,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H330" t="n">
         <v>5585</v>
@@ -10026,7 +10026,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G333" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H333" t="n">
         <v>1126</v>
@@ -10142,7 +10142,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G337" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H337" t="n">
         <v>15623</v>
@@ -10171,7 +10171,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G338" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H338" t="n">
         <v>2453</v>
@@ -10258,7 +10258,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H341" t="n">
         <v>13173</v>
@@ -10287,7 +10287,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H342" t="n">
         <v>2043</v>
@@ -10345,7 +10345,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H344" t="n">
         <v>13660</v>
@@ -10432,7 +10432,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G347" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H347" t="n">
         <v>5755</v>
@@ -10461,7 +10461,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H348" t="n">
         <v>3489</v>
@@ -10606,7 +10606,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G353" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H353" t="n">
         <v>6420</v>
@@ -10635,7 +10635,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H354" t="n">
         <v>7088</v>
@@ -10664,7 +10664,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H355" t="n">
         <v>1170</v>
@@ -10693,7 +10693,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H356" t="n">
         <v>2400</v>
@@ -10722,7 +10722,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H358" t="n">
         <v>4600</v>
@@ -10780,7 +10780,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>5.07126522064209</v>
+        <v>5.07126474380493</v>
       </c>
       <c r="H359" t="n">
         <v>3000</v>
@@ -10896,7 +10896,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.2874174118042</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H363" t="n">
         <v>4848</v>
@@ -10954,7 +10954,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G365" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H365" t="n">
         <v>1500</v>
@@ -10983,7 +10983,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102766036987</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H366" t="n">
         <v>710</v>
@@ -11012,7 +11012,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H367" t="n">
         <v>112</v>
@@ -11041,7 +11041,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G368" t="n">
-        <v>5.13777351379395</v>
+        <v>5.13777303695679</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H373" t="n">
         <v>4742</v>
@@ -11244,7 +11244,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G375" t="n">
-        <v>5.25416278839111</v>
+        <v>5.25416326522827</v>
       </c>
       <c r="H375" t="n">
         <v>2615</v>
@@ -11331,7 +11331,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102766036987</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H378" t="n">
         <v>112</v>
@@ -11360,7 +11360,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102766036987</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102766036987</v>
+        <v>5.17102718353271</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G381" t="n">
-        <v>5.12114572525024</v>
+        <v>5.1211462020874</v>
       </c>
       <c r="H381" t="n">
         <v>1071</v>
@@ -11476,7 +11476,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H383" t="n">
         <v>5263</v>
@@ -11505,7 +11505,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404472351074</v>
+        <v>5.30404424667358</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G391" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H391" t="n">
         <v>6720</v>
@@ -11737,7 +11737,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.15439987182617</v>
+        <v>5.15440034866333</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G397" t="n">
-        <v>5.08789205551147</v>
+        <v>5.08789110183716</v>
       </c>
       <c r="H397" t="n">
         <v>1898</v>
@@ -11911,7 +11911,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G398" t="n">
-        <v>5.08789205551147</v>
+        <v>5.08789110183716</v>
       </c>
       <c r="H398" t="n">
         <v>2425</v>
@@ -11940,7 +11940,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97150230407715</v>
+        <v>4.97150182723999</v>
       </c>
       <c r="H399" t="n">
         <v>5742</v>
@@ -11969,7 +11969,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>4.82185792922974</v>
+        <v>4.82185888290405</v>
       </c>
       <c r="H400" t="n">
         <v>7273</v>
@@ -11998,7 +11998,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G401" t="n">
-        <v>4.92162084579468</v>
+        <v>4.92162132263184</v>
       </c>
       <c r="H401" t="n">
         <v>1890</v>
@@ -12056,7 +12056,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>4.83848571777344</v>
+        <v>4.83848524093628</v>
       </c>
       <c r="H403" t="n">
         <v>339</v>
@@ -12085,7 +12085,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G404" t="n">
-        <v>4.88836669921875</v>
+        <v>4.88836717605591</v>
       </c>
       <c r="H404" t="n">
         <v>32</v>
@@ -12114,7 +12114,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G405" t="n">
-        <v>4.83848571777344</v>
+        <v>4.83848524093628</v>
       </c>
       <c r="H405" t="n">
         <v>5440</v>
@@ -12143,7 +12143,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G406" t="n">
-        <v>4.6722149848938</v>
+        <v>4.67221450805664</v>
       </c>
       <c r="H406" t="n">
         <v>19716</v>
@@ -12172,7 +12172,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H407" t="n">
         <v>9154</v>
@@ -12259,7 +12259,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G410" t="n">
-        <v>4.78860425949097</v>
+        <v>4.78860473632812</v>
       </c>
       <c r="H410" t="n">
         <v>300</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>4.80523157119751</v>
+        <v>4.80523109436035</v>
       </c>
       <c r="H412" t="n">
         <v>200</v>
@@ -12346,7 +12346,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H413" t="n">
         <v>6760</v>
@@ -12404,7 +12404,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H415" t="n">
         <v>970</v>
@@ -12491,7 +12491,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>4.47268962860107</v>
+        <v>4.47268915176392</v>
       </c>
       <c r="H418" t="n">
         <v>25169</v>
@@ -12520,7 +12520,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>4.35629844665527</v>
+        <v>4.35629940032959</v>
       </c>
       <c r="H419" t="n">
         <v>5206</v>
@@ -12549,7 +12549,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G420" t="n">
-        <v>4.45606184005737</v>
+        <v>4.45606231689453</v>
       </c>
       <c r="H420" t="n">
         <v>5661</v>
@@ -12578,7 +12578,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H421" t="n">
         <v>1908</v>
@@ -12607,7 +12607,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H422" t="n">
         <v>7657</v>
@@ -12636,7 +12636,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H423" t="n">
         <v>3457</v>
@@ -12665,7 +12665,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G424" t="n">
-        <v>4.80523157119751</v>
+        <v>4.80523109436035</v>
       </c>
       <c r="H424" t="n">
         <v>3714</v>
@@ -12694,7 +12694,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G425" t="n">
-        <v>4.6722149848938</v>
+        <v>4.67221450805664</v>
       </c>
       <c r="H425" t="n">
         <v>5049</v>
@@ -12723,7 +12723,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G426" t="n">
-        <v>4.60570621490479</v>
+        <v>4.60570573806763</v>
       </c>
       <c r="H426" t="n">
         <v>6617</v>
@@ -12839,7 +12839,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H430" t="n">
         <v>7925</v>
@@ -13013,7 +13013,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>4.78860425949097</v>
+        <v>4.78860473632812</v>
       </c>
       <c r="H436" t="n">
         <v>500</v>
@@ -13042,7 +13042,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H437" t="n">
         <v>6066</v>
@@ -13071,7 +13071,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H438" t="n">
         <v>1719</v>
@@ -13129,7 +13129,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G440" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H440" t="n">
         <v>700</v>
@@ -13158,7 +13158,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H441" t="n">
         <v>4384</v>
@@ -13216,7 +13216,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H443" t="n">
         <v>3174</v>
@@ -13245,7 +13245,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H444" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.65558671951294</v>
+        <v>4.6555871963501</v>
       </c>
       <c r="H445" t="n">
         <v>1010</v>
@@ -13303,7 +13303,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13332,7 +13332,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H447" t="n">
         <v>1000</v>
@@ -13361,7 +13361,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>4.73872232437134</v>
+        <v>4.7387228012085</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13419,7 +13419,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H450" t="n">
         <v>1700</v>
@@ -13477,7 +13477,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H452" t="n">
         <v>500</v>
@@ -13506,7 +13506,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H454" t="n">
         <v>4800</v>
@@ -13564,7 +13564,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H455" t="n">
         <v>5500</v>
@@ -13593,7 +13593,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13680,7 +13680,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G459" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H459" t="n">
         <v>510</v>
@@ -13709,7 +13709,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G460" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H460" t="n">
         <v>0</v>
@@ -13738,7 +13738,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G461" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H461" t="n">
         <v>686</v>
@@ -13767,7 +13767,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G462" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G463" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H463" t="n">
         <v>5</v>
@@ -13854,7 +13854,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H465" t="n">
         <v>205</v>
@@ -13912,7 +13912,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H467" t="n">
         <v>1464</v>
@@ -13941,7 +13941,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H468" t="n">
         <v>810</v>
@@ -13970,7 +13970,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H469" t="n">
         <v>646</v>
@@ -13999,7 +13999,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H470" t="n">
         <v>1000</v>
@@ -14028,7 +14028,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -14057,7 +14057,7 @@
         <v>6</v>
       </c>
       <c r="G472" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H472" t="n">
         <v>2091</v>
@@ -14086,7 +14086,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H473" t="n">
         <v>9179</v>
@@ -14202,7 +14202,7 @@
         <v>5.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H477" t="n">
         <v>350</v>
@@ -14318,7 +14318,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H481" t="n">
         <v>500</v>
@@ -14347,7 +14347,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H482" t="n">
         <v>1405</v>
@@ -14376,7 +14376,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14405,7 +14405,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G484" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H484" t="n">
         <v>3400</v>
@@ -14434,7 +14434,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H485" t="n">
         <v>0</v>
@@ -14550,7 +14550,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G489" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H489" t="n">
         <v>3700</v>
@@ -14608,7 +14608,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G491" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H491" t="n">
         <v>500</v>
@@ -14637,7 +14637,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G492" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H492" t="n">
         <v>23909</v>
@@ -14666,7 +14666,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G493" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H493" t="n">
         <v>26022</v>
@@ -14956,7 +14956,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G503" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H503" t="n">
         <v>5895</v>
@@ -15072,7 +15072,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H507" t="n">
         <v>3700</v>
@@ -15101,7 +15101,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H511" t="n">
         <v>2505</v>
@@ -15217,7 +15217,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H512" t="n">
         <v>2050</v>
@@ -15362,7 +15362,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G521" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H521" t="n">
         <v>341</v>
@@ -15565,7 +15565,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G524" t="n">
-        <v>4.99485206604004</v>
+        <v>4.9948525428772</v>
       </c>
       <c r="H524" t="n">
         <v>1780</v>
@@ -15594,7 +15594,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H525" t="n">
         <v>235</v>
@@ -15681,7 +15681,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H528" t="n">
         <v>700</v>
@@ -15710,7 +15710,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15797,7 +15797,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G532" t="n">
-        <v>4.92666339874268</v>
+        <v>4.92666292190552</v>
       </c>
       <c r="H532" t="n">
         <v>374</v>
@@ -15855,7 +15855,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90961599349976</v>
+        <v>4.90961647033691</v>
       </c>
       <c r="H534" t="n">
         <v>2167</v>
@@ -15884,7 +15884,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H535" t="n">
         <v>2280</v>
@@ -15913,7 +15913,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H536" t="n">
         <v>2123</v>
@@ -15942,7 +15942,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H537" t="n">
         <v>1000</v>
@@ -15971,7 +15971,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H538" t="n">
         <v>1776</v>
@@ -16029,7 +16029,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H540" t="n">
         <v>350</v>
@@ -16058,7 +16058,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H542" t="n">
         <v>2760</v>
@@ -16116,7 +16116,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G543" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>4.87552118301392</v>
+        <v>4.87552070617676</v>
       </c>
       <c r="H544" t="n">
         <v>421</v>
@@ -16174,7 +16174,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H545" t="n">
         <v>2895</v>
@@ -16203,7 +16203,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G546" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H546" t="n">
         <v>2567</v>
@@ -16232,7 +16232,7 @@
         <v>5.5</v>
       </c>
       <c r="G547" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H547" t="n">
         <v>2535</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.48343467712402</v>
+        <v>4.48343420028687</v>
       </c>
       <c r="H549" t="n">
         <v>1022</v>
@@ -16319,7 +16319,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G550" t="n">
-        <v>4.55162286758423</v>
+        <v>4.55162334442139</v>
       </c>
       <c r="H550" t="n">
         <v>360</v>
@@ -16348,7 +16348,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>4.48343467712402</v>
+        <v>4.48343420028687</v>
       </c>
       <c r="H551" t="n">
         <v>1200</v>
@@ -16377,7 +16377,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>4.55162286758423</v>
+        <v>4.55162334442139</v>
       </c>
       <c r="H552" t="n">
         <v>450</v>
@@ -16406,7 +16406,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>4.36410284042358</v>
+        <v>4.36410236358643</v>
       </c>
       <c r="H553" t="n">
         <v>4928</v>
@@ -16464,7 +16464,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G555" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H555" t="n">
         <v>855</v>
@@ -16493,7 +16493,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G556" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H556" t="n">
         <v>0</v>
@@ -16522,7 +16522,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G557" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H557" t="n">
         <v>622</v>
@@ -16551,7 +16551,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G558" t="n">
-        <v>4.51752901077271</v>
+        <v>4.51752853393555</v>
       </c>
       <c r="H558" t="n">
         <v>3300</v>
@@ -16812,7 +16812,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G567" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H567" t="n">
         <v>2942</v>
@@ -16841,7 +16841,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G568" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H568" t="n">
         <v>360</v>
@@ -16870,7 +16870,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G569" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H569" t="n">
         <v>0</v>
@@ -16899,7 +16899,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G570" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H570" t="n">
         <v>0</v>
@@ -16928,7 +16928,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G571" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H571" t="n">
         <v>2010</v>
@@ -16957,7 +16957,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G572" t="n">
-        <v>4.50048160552979</v>
+        <v>4.50048112869263</v>
       </c>
       <c r="H572" t="n">
         <v>1210</v>
@@ -17044,7 +17044,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H575" t="n">
         <v>20</v>
@@ -17073,7 +17073,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17160,7 +17160,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G579" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H579" t="n">
         <v>4350</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.80733203887939</v>
+        <v>4.80733251571655</v>
       </c>
       <c r="H580" t="n">
         <v>3158</v>
@@ -17218,7 +17218,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G581" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H581" t="n">
         <v>1495</v>
@@ -17247,7 +17247,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G582" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H582" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G583" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H583" t="n">
         <v>1150</v>
@@ -17334,7 +17334,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H585" t="n">
         <v>360</v>
@@ -17392,7 +17392,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G587" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H587" t="n">
         <v>1750</v>
@@ -17450,7 +17450,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G589" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H589" t="n">
         <v>710</v>
@@ -17479,7 +17479,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G590" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H590" t="n">
         <v>900</v>
@@ -17508,7 +17508,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G591" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H591" t="n">
         <v>2311</v>
@@ -17537,7 +17537,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G592" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H592" t="n">
         <v>901</v>
@@ -17566,7 +17566,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G593" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H593" t="n">
         <v>2905</v>
@@ -17595,7 +17595,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G594" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H594" t="n">
         <v>0</v>
@@ -17624,7 +17624,7 @@
         <v>5.5</v>
       </c>
       <c r="G595" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H595" t="n">
         <v>6710</v>
@@ -17653,7 +17653,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G596" t="n">
-        <v>4.67095375061035</v>
+        <v>4.67095422744751</v>
       </c>
       <c r="H596" t="n">
         <v>128</v>
@@ -17682,7 +17682,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H597" t="n">
         <v>607</v>
@@ -17711,7 +17711,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G598" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H598" t="n">
         <v>65</v>
@@ -17769,7 +17769,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G600" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H600" t="n">
         <v>2186</v>
@@ -17798,7 +17798,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G601" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H601" t="n">
         <v>0</v>
@@ -17827,7 +17827,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G602" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H602" t="n">
         <v>0</v>
@@ -17856,7 +17856,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G603" t="n">
-        <v>4.858473777771</v>
+        <v>4.85847330093384</v>
       </c>
       <c r="H603" t="n">
         <v>0</v>
@@ -18059,7 +18059,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H610" t="n">
         <v>1351</v>
@@ -18088,7 +18088,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H611" t="n">
         <v>510</v>
@@ -18117,7 +18117,7 @@
         <v>5.5</v>
       </c>
       <c r="G612" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H612" t="n">
         <v>34</v>
@@ -18146,7 +18146,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H613" t="n">
         <v>186</v>
@@ -18320,7 +18320,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H619" t="n">
         <v>675</v>
@@ -18494,7 +18494,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>4.80733203887939</v>
+        <v>4.80733251571655</v>
       </c>
       <c r="H625" t="n">
         <v>1866</v>
@@ -18523,7 +18523,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H626" t="n">
         <v>110</v>
@@ -18552,7 +18552,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H627" t="n">
         <v>10</v>
@@ -18581,7 +18581,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H628" t="n">
         <v>400</v>
@@ -18610,7 +18610,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H629" t="n">
         <v>110</v>
@@ -18697,7 +18697,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H632" t="n">
         <v>872</v>
@@ -18726,7 +18726,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H633" t="n">
         <v>1703</v>
@@ -18755,7 +18755,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H634" t="n">
         <v>10</v>
@@ -18813,7 +18813,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G636" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H636" t="n">
         <v>1898</v>
@@ -18842,7 +18842,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G637" t="n">
-        <v>5.0118989944458</v>
+        <v>5.01189994812012</v>
       </c>
       <c r="H637" t="n">
         <v>67041</v>
@@ -18871,7 +18871,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G638" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H638" t="n">
         <v>3800</v>
@@ -18958,7 +18958,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>5.0118989944458</v>
+        <v>5.01189994812012</v>
       </c>
       <c r="H641" t="n">
         <v>3920</v>
@@ -18987,7 +18987,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H642" t="n">
         <v>5765</v>
@@ -19016,7 +19016,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>5.25056123733521</v>
+        <v>5.25056171417236</v>
       </c>
       <c r="H643" t="n">
         <v>4245</v>
@@ -19074,7 +19074,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G645" t="n">
-        <v>5.30170345306396</v>
+        <v>5.30170297622681</v>
       </c>
       <c r="H645" t="n">
         <v>2953</v>
@@ -19161,7 +19161,7 @@
         <v>6</v>
       </c>
       <c r="G648" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H648" t="n">
         <v>1200</v>
@@ -19277,7 +19277,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>5.13123035430908</v>
+        <v>5.13123083114624</v>
       </c>
       <c r="H652" t="n">
         <v>317</v>
@@ -19335,7 +19335,7 @@
         <v>6</v>
       </c>
       <c r="G654" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H654" t="n">
         <v>3833</v>
@@ -19422,7 +19422,7 @@
         <v>6</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H657" t="n">
         <v>512</v>
@@ -19451,7 +19451,7 @@
         <v>6</v>
       </c>
       <c r="G658" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H658" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H659" t="n">
         <v>618</v>
@@ -19509,7 +19509,7 @@
         <v>6</v>
       </c>
       <c r="G660" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H660" t="n">
         <v>110</v>
@@ -19538,7 +19538,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H661" t="n">
         <v>160</v>
@@ -19625,7 +19625,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G664" t="n">
-        <v>5.13123035430908</v>
+        <v>5.13123083114624</v>
       </c>
       <c r="H664" t="n">
         <v>5303</v>
@@ -19857,7 +19857,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G672" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H672" t="n">
         <v>1371</v>
@@ -19886,7 +19886,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G673" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>6</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H674" t="n">
         <v>1922</v>
@@ -19973,7 +19973,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H676" t="n">
         <v>3802</v>
@@ -20002,7 +20002,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H677" t="n">
         <v>1377</v>
@@ -20031,7 +20031,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>6</v>
       </c>
       <c r="G679" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H679" t="n">
         <v>4219</v>
@@ -20089,7 +20089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H680" t="n">
         <v>893</v>
@@ -20118,7 +20118,7 @@
         <v>6</v>
       </c>
       <c r="G681" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H681" t="n">
         <v>1250</v>
@@ -20147,7 +20147,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H682" t="n">
         <v>6283</v>
@@ -20205,7 +20205,7 @@
         <v>6</v>
       </c>
       <c r="G684" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H684" t="n">
         <v>3929</v>
@@ -20292,7 +20292,7 @@
         <v>6</v>
       </c>
       <c r="G687" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H687" t="n">
         <v>3300</v>
@@ -20350,7 +20350,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H689" t="n">
         <v>820</v>
@@ -20379,7 +20379,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H690" t="n">
         <v>700</v>
@@ -20408,7 +20408,7 @@
         <v>6</v>
       </c>
       <c r="G691" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H691" t="n">
         <v>3324</v>
@@ -20437,7 +20437,7 @@
         <v>6</v>
       </c>
       <c r="G692" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H692" t="n">
         <v>3119</v>
@@ -20466,7 +20466,7 @@
         <v>6</v>
       </c>
       <c r="G693" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H693" t="n">
         <v>2354</v>
@@ -20553,7 +20553,7 @@
         <v>6</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H696" t="n">
         <v>10</v>
@@ -20669,7 +20669,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>5.02894639968872</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H700" t="n">
         <v>807</v>
@@ -20785,7 +20785,7 @@
         <v>6</v>
       </c>
       <c r="G704" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H704" t="n">
         <v>400</v>
@@ -20843,7 +20843,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>5.24644613265991</v>
+        <v>5.24644660949707</v>
       </c>
       <c r="H706" t="n">
         <v>100</v>
@@ -20901,7 +20901,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G708" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H708" t="n">
         <v>8078</v>
@@ -20930,7 +20930,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G709" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H709" t="n">
         <v>1010</v>
@@ -20959,7 +20959,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G710" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H710" t="n">
         <v>0</v>
@@ -20988,7 +20988,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G711" t="n">
-        <v>5.24644613265991</v>
+        <v>5.24644660949707</v>
       </c>
       <c r="H711" t="n">
         <v>1834</v>
@@ -21017,7 +21017,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G712" t="n">
-        <v>5.20235872268677</v>
+        <v>5.20235919952393</v>
       </c>
       <c r="H712" t="n">
         <v>7386</v>
@@ -21046,7 +21046,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G713" t="n">
-        <v>5.24644613265991</v>
+        <v>5.24644660949707</v>
       </c>
       <c r="H713" t="n">
         <v>4193</v>
@@ -21075,7 +21075,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G714" t="n">
-        <v>5.24644613265991</v>
+        <v>5.24644660949707</v>
       </c>
       <c r="H714" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G722" t="n">
-        <v>5.02600765228271</v>
+        <v>5.02600717544556</v>
       </c>
       <c r="H722" t="n">
         <v>2000</v>
@@ -21336,7 +21336,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G723" t="n">
-        <v>5.02600765228271</v>
+        <v>5.02600717544556</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21481,7 +21481,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G728" t="n">
-        <v>4.93783187866211</v>
+        <v>4.93783235549927</v>
       </c>
       <c r="H728" t="n">
         <v>2930</v>
@@ -21510,7 +21510,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.93783187866211</v>
+        <v>4.93783235549927</v>
       </c>
       <c r="H729" t="n">
         <v>6873</v>
@@ -21539,7 +21539,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G730" t="n">
-        <v>5.02600765228271</v>
+        <v>5.02600717544556</v>
       </c>
       <c r="H730" t="n">
         <v>5500</v>
@@ -21684,7 +21684,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G735" t="n">
-        <v>4.67330598831177</v>
+        <v>4.67330551147461</v>
       </c>
       <c r="H735" t="n">
         <v>2823</v>
@@ -22061,7 +22061,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G748" t="n">
-        <v>4.67330598831177</v>
+        <v>4.67330551147461</v>
       </c>
       <c r="H748" t="n">
         <v>10155</v>
@@ -22438,7 +22438,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G761" t="n">
-        <v>4.67330598831177</v>
+        <v>4.67330551147461</v>
       </c>
       <c r="H761" t="n">
         <v>3633</v>
@@ -22583,7 +22583,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G766" t="n">
-        <v>4.45286703109741</v>
+        <v>4.45286655426025</v>
       </c>
       <c r="H766" t="n">
         <v>6689</v>
@@ -22844,7 +22844,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G775" t="n">
-        <v>4.67330598831177</v>
+        <v>4.67330551147461</v>
       </c>
       <c r="H775" t="n">
         <v>2709</v>
@@ -22873,7 +22873,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G776" t="n">
-        <v>4.67330598831177</v>
+        <v>4.67330551147461</v>
       </c>
       <c r="H776" t="n">
         <v>0</v>
@@ -23018,7 +23018,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G781" t="n">
-        <v>4.67330598831177</v>
+        <v>4.67330551147461</v>
       </c>
       <c r="H781" t="n">
         <v>505</v>
@@ -23047,7 +23047,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G782" t="n">
-        <v>4.67330598831177</v>
+        <v>4.67330551147461</v>
       </c>
       <c r="H782" t="n">
         <v>0</v>
@@ -23076,7 +23076,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G783" t="n">
-        <v>4.67330598831177</v>
+        <v>4.67330551147461</v>
       </c>
       <c r="H783" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G785" t="n">
-        <v>4.67330598831177</v>
+        <v>4.67330551147461</v>
       </c>
       <c r="H785" t="n">
         <v>170</v>
@@ -23163,7 +23163,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G786" t="n">
-        <v>4.67330598831177</v>
+        <v>4.67330551147461</v>
       </c>
       <c r="H786" t="n">
         <v>0</v>
@@ -23424,7 +23424,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G795" t="n">
-        <v>4.98192024230957</v>
+        <v>4.98191976547241</v>
       </c>
       <c r="H795" t="n">
         <v>144</v>
@@ -23540,7 +23540,7 @@
         <v>5.25</v>
       </c>
       <c r="G799" t="n">
-        <v>4.62921810150146</v>
+        <v>4.62921762466431</v>
       </c>
       <c r="H799" t="n">
         <v>495</v>
@@ -23772,7 +23772,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G807" t="n">
-        <v>4.32060289382935</v>
+        <v>4.3206033706665</v>
       </c>
       <c r="H807" t="n">
         <v>9722</v>
@@ -23801,7 +23801,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>4.39114332199097</v>
+        <v>4.39114379882812</v>
       </c>
       <c r="H808" t="n">
         <v>7831</v>
@@ -23830,7 +23830,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G809" t="n">
-        <v>4.39114332199097</v>
+        <v>4.39114379882812</v>
       </c>
       <c r="H809" t="n">
         <v>322</v>
@@ -23917,7 +23917,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G812" t="n">
-        <v>4.37350797653198</v>
+        <v>4.37350845336914</v>
       </c>
       <c r="H812" t="n">
         <v>1000</v>
@@ -23946,7 +23946,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H813" t="n">
         <v>1618</v>
@@ -23975,7 +23975,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24004,7 +24004,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H815" t="n">
         <v>1188</v>
@@ -24033,7 +24033,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H816" t="n">
         <v>10</v>
@@ -24091,7 +24091,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H818" t="n">
         <v>700</v>
@@ -24120,7 +24120,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H819" t="n">
         <v>166</v>
@@ -24149,7 +24149,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G820" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H820" t="n">
         <v>0</v>
@@ -24236,7 +24236,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>4.02080583572388</v>
+        <v>4.02080631256104</v>
       </c>
       <c r="H823" t="n">
         <v>4500</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H827" t="n">
         <v>2876</v>
@@ -24381,7 +24381,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G828" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H828" t="n">
         <v>1550</v>
@@ -24410,7 +24410,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G829" t="n">
-        <v>4.02080583572388</v>
+        <v>4.02080631256104</v>
       </c>
       <c r="H829" t="n">
         <v>1007</v>
@@ -24526,7 +24526,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H833" t="n">
         <v>1050</v>
@@ -24555,7 +24555,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G835" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H835" t="n">
         <v>1</v>
@@ -24642,7 +24642,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H837" t="n">
         <v>1803</v>
@@ -24729,7 +24729,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H840" t="n">
         <v>609</v>
@@ -24758,7 +24758,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G841" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H841" t="n">
         <v>4500</v>
@@ -24787,7 +24787,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H842" t="n">
         <v>2500</v>
@@ -24816,7 +24816,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H843" t="n">
         <v>1253</v>
@@ -24874,7 +24874,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G845" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H845" t="n">
         <v>796</v>
@@ -24903,7 +24903,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G846" t="n">
-        <v>4.25006246566772</v>
+        <v>4.25006294250488</v>
       </c>
       <c r="H846" t="n">
         <v>3297</v>
@@ -25048,7 +25048,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.0913462638855</v>
+        <v>4.09134674072266</v>
       </c>
       <c r="H851" t="n">
         <v>2200</v>
@@ -25222,7 +25222,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G857" t="n">
-        <v>4.02080583572388</v>
+        <v>4.02080631256104</v>
       </c>
       <c r="H857" t="n">
         <v>1400</v>
@@ -25280,7 +25280,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G859" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H859" t="n">
         <v>6840</v>
@@ -25483,7 +25483,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H866" t="n">
         <v>20519</v>
@@ -25512,7 +25512,7 @@
         <v>4.5</v>
       </c>
       <c r="G867" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H867" t="n">
         <v>14414</v>
@@ -25541,7 +25541,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G868" t="n">
-        <v>3.91499519348145</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H868" t="n">
         <v>15412</v>
@@ -25570,7 +25570,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H869" t="n">
         <v>3776</v>
@@ -25599,7 +25599,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H870" t="n">
         <v>4073</v>
@@ -25657,7 +25657,7 @@
         <v>4.5</v>
       </c>
       <c r="G872" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H872" t="n">
         <v>2450</v>
@@ -25686,7 +25686,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H873" t="n">
         <v>5847</v>
@@ -25715,7 +25715,7 @@
         <v>4.5</v>
       </c>
       <c r="G874" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H874" t="n">
         <v>3098</v>
@@ -25773,7 +25773,7 @@
         <v>4.5</v>
       </c>
       <c r="G876" t="n">
-        <v>3.96790075302124</v>
+        <v>3.96790099143982</v>
       </c>
       <c r="H876" t="n">
         <v>2457</v>
@@ -25802,7 +25802,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G877" t="n">
-        <v>3.91499519348145</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H877" t="n">
         <v>13736</v>
@@ -25831,7 +25831,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G878" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H878" t="n">
         <v>20986</v>
@@ -25860,7 +25860,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G879" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H879" t="n">
         <v>21055</v>
@@ -25889,7 +25889,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G880" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H880" t="n">
         <v>26401</v>
@@ -25918,7 +25918,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>3.89736032485962</v>
+        <v>3.8973605632782</v>
       </c>
       <c r="H881" t="n">
         <v>30875</v>
@@ -25947,7 +25947,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H882" t="n">
         <v>15378</v>
@@ -25976,7 +25976,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G883" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H883" t="n">
         <v>18373</v>
@@ -26034,7 +26034,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>3.68573904037476</v>
+        <v>3.6857385635376</v>
       </c>
       <c r="H885" t="n">
         <v>8364</v>
@@ -26063,7 +26063,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G886" t="n">
-        <v>3.73864388465881</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H886" t="n">
         <v>2531</v>
@@ -26092,7 +26092,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H887" t="n">
         <v>5091</v>
@@ -26121,7 +26121,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H888" t="n">
         <v>8519</v>
@@ -26208,7 +26208,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H891" t="n">
         <v>58437</v>
@@ -26237,7 +26237,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G892" t="n">
-        <v>3.89736032485962</v>
+        <v>3.8973605632782</v>
       </c>
       <c r="H892" t="n">
         <v>25887</v>
@@ -26266,7 +26266,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G893" t="n">
-        <v>3.91499519348145</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H893" t="n">
         <v>22381</v>
@@ -26295,7 +26295,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G894" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H894" t="n">
         <v>30205</v>
@@ -26324,7 +26324,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G895" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H895" t="n">
         <v>16801</v>
@@ -26353,7 +26353,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>3.82682013511658</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H896" t="n">
         <v>7640</v>
@@ -26382,7 +26382,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G897" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H897" t="n">
         <v>4097</v>
@@ -26440,7 +26440,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G899" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H899" t="n">
         <v>25714</v>
@@ -26469,7 +26469,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G900" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H900" t="n">
         <v>21083</v>
@@ -26498,7 +26498,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G901" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H901" t="n">
         <v>17900</v>
@@ -26527,7 +26527,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73864388465881</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H902" t="n">
         <v>44451</v>
@@ -26556,7 +26556,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>3.82682013511658</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H903" t="n">
         <v>25646</v>
@@ -26585,7 +26585,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G904" t="n">
-        <v>3.80918478965759</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H904" t="n">
         <v>39491</v>
@@ -26614,7 +26614,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G905" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H905" t="n">
         <v>14849</v>
@@ -26643,7 +26643,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G906" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H906" t="n">
         <v>5341</v>
@@ -26672,7 +26672,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H907" t="n">
         <v>7190</v>
@@ -26701,7 +26701,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G908" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H908" t="n">
         <v>400</v>
@@ -26730,7 +26730,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H909" t="n">
         <v>700</v>
@@ -26759,7 +26759,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G910" t="n">
-        <v>3.79154992103577</v>
+        <v>3.79154968261719</v>
       </c>
       <c r="H910" t="n">
         <v>15870</v>
@@ -26788,7 +26788,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>3.82682013511658</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H911" t="n">
         <v>85</v>
@@ -26817,7 +26817,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G912" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H912" t="n">
         <v>800</v>
@@ -26846,7 +26846,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>3.91499519348145</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H913" t="n">
         <v>1250</v>
@@ -26875,7 +26875,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H914" t="n">
         <v>1050</v>
@@ -26904,7 +26904,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G915" t="n">
-        <v>3.89736032485962</v>
+        <v>3.8973605632782</v>
       </c>
       <c r="H915" t="n">
         <v>2945</v>
@@ -26933,7 +26933,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H916" t="n">
         <v>35</v>
@@ -26962,7 +26962,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G917" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H917" t="n">
         <v>1200</v>
@@ -26991,7 +26991,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G918" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H918" t="n">
         <v>0</v>
@@ -27020,7 +27020,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G919" t="n">
-        <v>3.82682013511658</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H919" t="n">
         <v>1905</v>
@@ -27078,7 +27078,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G921" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H921" t="n">
         <v>1920</v>
@@ -27107,7 +27107,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G922" t="n">
-        <v>3.8444550037384</v>
+        <v>3.84445524215698</v>
       </c>
       <c r="H922" t="n">
         <v>9837</v>
@@ -27136,7 +27136,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.91499519348145</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H923" t="n">
         <v>10338</v>
@@ -27194,7 +27194,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H925" t="n">
         <v>2087</v>
@@ -27223,7 +27223,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H927" t="n">
         <v>1386</v>
@@ -27281,7 +27281,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -27310,7 +27310,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G929" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H929" t="n">
         <v>1000</v>
@@ -27368,7 +27368,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>3.87972497940063</v>
+        <v>3.87972545623779</v>
       </c>
       <c r="H931" t="n">
         <v>700</v>
@@ -27455,7 +27455,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G934" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H934" t="n">
         <v>5727</v>
@@ -27513,7 +27513,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G936" t="n">
-        <v>4.25006246566772</v>
+        <v>4.25006294250488</v>
       </c>
       <c r="H936" t="n">
         <v>38360</v>
@@ -27542,7 +27542,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G937" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H937" t="n">
         <v>8262</v>
@@ -27600,7 +27600,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G939" t="n">
-        <v>4.37350797653198</v>
+        <v>4.37350845336914</v>
       </c>
       <c r="H939" t="n">
         <v>12401</v>
@@ -27658,7 +27658,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G941" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H941" t="n">
         <v>430</v>
@@ -27687,7 +27687,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>4.37350797653198</v>
+        <v>4.37350845336914</v>
       </c>
       <c r="H942" t="n">
         <v>250</v>
@@ -27745,7 +27745,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G944" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H944" t="n">
         <v>8544</v>
@@ -27774,7 +27774,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G945" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H945" t="n">
         <v>3230</v>
@@ -27803,7 +27803,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>4.37350797653198</v>
+        <v>4.37350845336914</v>
       </c>
       <c r="H946" t="n">
         <v>28</v>
@@ -27832,7 +27832,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G947" t="n">
-        <v>4.37350797653198</v>
+        <v>4.37350845336914</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G948" t="n">
-        <v>4.32060289382935</v>
+        <v>4.3206033706665</v>
       </c>
       <c r="H948" t="n">
         <v>1000</v>
@@ -27890,7 +27890,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G949" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H949" t="n">
         <v>1750</v>
@@ -27919,7 +27919,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G950" t="n">
-        <v>4.32060289382935</v>
+        <v>4.3206033706665</v>
       </c>
       <c r="H950" t="n">
         <v>1675</v>
@@ -27948,7 +27948,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G951" t="n">
-        <v>4.32060289382935</v>
+        <v>4.3206033706665</v>
       </c>
       <c r="H951" t="n">
         <v>0</v>
@@ -27977,7 +27977,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G952" t="n">
-        <v>4.32060289382935</v>
+        <v>4.3206033706665</v>
       </c>
       <c r="H952" t="n">
         <v>0</v>
@@ -28006,7 +28006,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G953" t="n">
-        <v>4.32060289382935</v>
+        <v>4.3206033706665</v>
       </c>
       <c r="H953" t="n">
         <v>0</v>
@@ -28035,7 +28035,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G954" t="n">
-        <v>4.32060289382935</v>
+        <v>4.3206033706665</v>
       </c>
       <c r="H954" t="n">
         <v>0</v>
@@ -28064,7 +28064,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G955" t="n">
-        <v>4.30296754837036</v>
+        <v>4.30296802520752</v>
       </c>
       <c r="H955" t="n">
         <v>4302</v>
@@ -28093,7 +28093,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>4.33823776245117</v>
+        <v>4.33823823928833</v>
       </c>
       <c r="H956" t="n">
         <v>800</v>
@@ -28122,7 +28122,7 @@
         <v>5</v>
       </c>
       <c r="G957" t="n">
-        <v>4.40877866744995</v>
+        <v>4.40877819061279</v>
       </c>
       <c r="H957" t="n">
         <v>2700</v>
@@ -28238,7 +28238,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>4.45286703109741</v>
+        <v>4.45286655426025</v>
       </c>
       <c r="H961" t="n">
         <v>1299</v>
@@ -28412,7 +28412,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G967" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H967" t="n">
         <v>1977</v>
@@ -29282,7 +29282,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G997" t="n">
-        <v>4.45847749710083</v>
+        <v>4.45847797393799</v>
       </c>
       <c r="H997" t="n">
         <v>700</v>
@@ -29543,7 +29543,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1006" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1006" t="n">
         <v>2585</v>
@@ -29572,7 +29572,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1007" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1007" t="n">
         <v>2103</v>
@@ -29601,7 +29601,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1008" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1008" t="n">
         <v>1200</v>
@@ -29630,7 +29630,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1009" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1009" t="n">
         <v>600</v>
@@ -29659,7 +29659,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1010" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1010" t="n">
         <v>0</v>
@@ -29688,7 +29688,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1011" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1011" t="n">
         <v>300</v>
@@ -30790,7 +30790,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1049" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1049" t="n">
         <v>2020</v>
@@ -30819,7 +30819,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1050" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1050" t="n">
         <v>1250</v>
@@ -31080,7 +31080,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1059" t="n">
         <v>4001</v>
@@ -31109,7 +31109,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.88970017433167</v>
+        <v>3.88970065116882</v>
       </c>
       <c r="H1060" t="n">
         <v>14640</v>
@@ -31196,7 +31196,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1063" t="n">
         <v>6269</v>
@@ -31370,7 +31370,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.88970017433167</v>
+        <v>3.88970065116882</v>
       </c>
       <c r="H1069" t="n">
         <v>861</v>
@@ -32008,7 +32008,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1091" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1091" t="n">
         <v>7006</v>
@@ -32037,7 +32037,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G1092" t="n">
-        <v>4.03648138046265</v>
+        <v>4.0364818572998</v>
       </c>
       <c r="H1092" t="n">
         <v>10055</v>
@@ -32124,7 +32124,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1095" t="n">
         <v>1998</v>
@@ -32153,7 +32153,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.96309113502502</v>
+        <v>3.9630913734436</v>
       </c>
       <c r="H1096" t="n">
         <v>0</v>
@@ -33226,7 +33226,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1133" t="n">
-        <v>4.38508701324463</v>
+        <v>4.38508749008179</v>
       </c>
       <c r="H1133" t="n">
         <v>1360</v>
@@ -33255,7 +33255,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1134" t="n">
         <v>2035</v>
@@ -33516,7 +33516,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.31169605255127</v>
+        <v>4.31169652938843</v>
       </c>
       <c r="H1143" t="n">
         <v>500</v>
@@ -33661,7 +33661,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.45847749710083</v>
+        <v>4.45847797393799</v>
       </c>
       <c r="H1148" t="n">
         <v>12871</v>
@@ -46369,6 +46369,35 @@
         <v>20294</v>
       </c>
       <c r="I1586" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1587" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1587" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="D1587" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="G1587" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="H1587" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I1587" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H2" t="n">
         <v>425</v>
@@ -456,7 +456,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H3" t="n">
         <v>650</v>
@@ -485,7 +485,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H5" t="n">
         <v>1105</v>
@@ -572,7 +572,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H7" t="n">
         <v>5900</v>
@@ -601,7 +601,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G8" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H8" t="n">
         <v>1000</v>
@@ -688,7 +688,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H11" t="n">
         <v>6680</v>
@@ -717,7 +717,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>4.04958200454712</v>
+        <v>4.04958152770996</v>
       </c>
       <c r="H14" t="n">
         <v>810</v>
@@ -804,7 +804,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H15" t="n">
         <v>1464</v>
@@ -833,7 +833,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.08210802078247</v>
+        <v>4.08210849761963</v>
       </c>
       <c r="H18" t="n">
         <v>970</v>
@@ -920,7 +920,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G19" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H19" t="n">
         <v>3229</v>
@@ -978,7 +978,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.27726888656616</v>
+        <v>4.27726936340332</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1007,7 +1007,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G22" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H22" t="n">
         <v>3365</v>
@@ -1036,7 +1036,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>4.27726888656616</v>
+        <v>4.27726936340332</v>
       </c>
       <c r="H23" t="n">
         <v>3200</v>
@@ -1181,7 +1181,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H28" t="n">
         <v>350</v>
@@ -1210,7 +1210,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H29" t="n">
         <v>1969</v>
@@ -1239,7 +1239,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G30" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H30" t="n">
         <v>4377</v>
@@ -1268,7 +1268,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H31" t="n">
         <v>6330</v>
@@ -1297,7 +1297,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H32" t="n">
         <v>1096</v>
@@ -1326,7 +1326,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G33" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H33" t="n">
         <v>2550</v>
@@ -1355,7 +1355,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G34" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H34" t="n">
         <v>3736</v>
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H35" t="n">
         <v>500</v>
@@ -1413,7 +1413,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G36" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H36" t="n">
         <v>550</v>
@@ -1442,7 +1442,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>4.00079202651978</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H37" t="n">
         <v>1422</v>
@@ -1471,7 +1471,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G38" t="n">
-        <v>4.08210802078247</v>
+        <v>4.08210849761963</v>
       </c>
       <c r="H38" t="n">
         <v>950</v>
@@ -1500,7 +1500,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H39" t="n">
         <v>300</v>
@@ -1587,7 +1587,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H42" t="n">
         <v>450</v>
@@ -1616,7 +1616,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G43" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H43" t="n">
         <v>450</v>
@@ -1645,7 +1645,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G44" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H44" t="n">
         <v>3940</v>
@@ -1674,7 +1674,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G45" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G46" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H46" t="n">
         <v>980</v>
@@ -1819,7 +1819,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G50" t="n">
-        <v>3.98452806472778</v>
+        <v>3.98452830314636</v>
       </c>
       <c r="H50" t="n">
         <v>6262</v>
@@ -1877,7 +1877,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639608383179</v>
+        <v>3.97639584541321</v>
       </c>
       <c r="H52" t="n">
         <v>1056</v>
@@ -1906,7 +1906,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639608383179</v>
+        <v>3.97639584541321</v>
       </c>
       <c r="H53" t="n">
         <v>504</v>
@@ -1935,7 +1935,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.94386982917786</v>
+        <v>3.9438693523407</v>
       </c>
       <c r="H54" t="n">
         <v>2108</v>
@@ -1964,7 +1964,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321135520935</v>
+        <v>3.90321063995361</v>
       </c>
       <c r="H55" t="n">
         <v>1248</v>
@@ -1993,7 +1993,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321135520935</v>
+        <v>3.90321063995361</v>
       </c>
       <c r="H56" t="n">
         <v>400</v>
@@ -2022,7 +2022,7 @@
         <v>4.75</v>
       </c>
       <c r="G57" t="n">
-        <v>3.86255264282227</v>
+        <v>3.86255311965942</v>
       </c>
       <c r="H57" t="n">
         <v>4200</v>
@@ -2051,7 +2051,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442042350769</v>
+        <v>3.85442113876343</v>
       </c>
       <c r="H58" t="n">
         <v>450</v>
@@ -2080,7 +2080,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.88694787025452</v>
+        <v>3.8869481086731</v>
       </c>
       <c r="H59" t="n">
         <v>1153</v>
@@ -2109,7 +2109,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.82189416885376</v>
+        <v>3.82189393043518</v>
       </c>
       <c r="H60" t="n">
         <v>400</v>
@@ -2138,7 +2138,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057674407959</v>
+        <v>3.74057698249817</v>
       </c>
       <c r="H61" t="n">
         <v>2000</v>
@@ -2167,7 +2167,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057674407959</v>
+        <v>3.74057698249817</v>
       </c>
       <c r="H62" t="n">
         <v>1245</v>
@@ -2196,7 +2196,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>3.82189416885376</v>
+        <v>3.82189393043518</v>
       </c>
       <c r="H63" t="n">
         <v>1994</v>
@@ -2254,7 +2254,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G65" t="n">
-        <v>3.69991850852966</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H65" t="n">
         <v>4762</v>
@@ -2312,7 +2312,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552423477173</v>
       </c>
       <c r="H67" t="n">
         <v>5250</v>
@@ -2341,7 +2341,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.6429967880249</v>
+        <v>3.64299726486206</v>
       </c>
       <c r="H68" t="n">
         <v>7900</v>
@@ -2399,7 +2399,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G70" t="n">
-        <v>3.69991850852966</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H70" t="n">
         <v>12720</v>
@@ -2457,7 +2457,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552423477173</v>
       </c>
       <c r="H72" t="n">
         <v>6400</v>
@@ -2544,7 +2544,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G75" t="n">
-        <v>3.69991850852966</v>
+        <v>3.69991874694824</v>
       </c>
       <c r="H75" t="n">
         <v>12819</v>
@@ -2573,7 +2573,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>3.67552399635315</v>
+        <v>3.67552423477173</v>
       </c>
       <c r="H76" t="n">
         <v>24183</v>
@@ -2602,7 +2602,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.00079202651978</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H77" t="n">
         <v>35243</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>4.00079202651978</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H78" t="n">
         <v>15007</v>
@@ -2660,7 +2660,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>4.0983715057373</v>
+        <v>4.09837198257446</v>
       </c>
       <c r="H79" t="n">
         <v>61552</v>
@@ -2747,7 +2747,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G82" t="n">
-        <v>4.1146354675293</v>
+        <v>4.11463499069214</v>
       </c>
       <c r="H82" t="n">
         <v>8365</v>
@@ -2776,7 +2776,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G83" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H83" t="n">
         <v>11228</v>
@@ -2805,7 +2805,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G84" t="n">
-        <v>4.17968845367432</v>
+        <v>4.17968797683716</v>
       </c>
       <c r="H84" t="n">
         <v>8061</v>
@@ -2863,7 +2863,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G86" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H86" t="n">
         <v>3000</v>
@@ -2950,7 +2950,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.14716196060181</v>
+        <v>4.14716148376465</v>
       </c>
       <c r="H89" t="n">
         <v>8400</v>
@@ -2979,7 +2979,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H90" t="n">
         <v>11784</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>4.00079202651978</v>
+        <v>4.00079107284546</v>
       </c>
       <c r="H91" t="n">
         <v>30633</v>
@@ -3037,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584453582764</v>
+        <v>4.06584501266479</v>
       </c>
       <c r="H92" t="n">
         <v>124660</v>
@@ -3066,7 +3066,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G93" t="n">
-        <v>4.21221542358398</v>
+        <v>4.21221494674683</v>
       </c>
       <c r="H93" t="n">
         <v>37142</v>
@@ -3095,7 +3095,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H94" t="n">
         <v>35821</v>
@@ -3327,7 +3327,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.32605981826782</v>
+        <v>4.32605886459351</v>
       </c>
       <c r="H102" t="n">
         <v>20579</v>
@@ -3356,7 +3356,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869276046753</v>
+        <v>4.48869228363037</v>
       </c>
       <c r="H103" t="n">
         <v>18889</v>
@@ -3385,7 +3385,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869276046753</v>
+        <v>4.48869228363037</v>
       </c>
       <c r="H104" t="n">
         <v>6100</v>
@@ -3414,7 +3414,7 @@
         <v>5.5</v>
       </c>
       <c r="G105" t="n">
-        <v>4.47242975234985</v>
+        <v>4.4724292755127</v>
       </c>
       <c r="H105" t="n">
         <v>895</v>
@@ -3501,7 +3501,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>4.52121925354004</v>
+        <v>4.5212197303772</v>
       </c>
       <c r="H108" t="n">
         <v>11295</v>
@@ -3588,7 +3588,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G111" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H111" t="n">
         <v>9209</v>
@@ -3617,7 +3617,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G112" t="n">
-        <v>4.32605981826782</v>
+        <v>4.32605886459351</v>
       </c>
       <c r="H112" t="n">
         <v>8648</v>
@@ -3704,7 +3704,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G115" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H115" t="n">
         <v>9983</v>
@@ -3733,7 +3733,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G116" t="n">
-        <v>4.29353189468384</v>
+        <v>4.293532371521</v>
       </c>
       <c r="H116" t="n">
         <v>12350</v>
@@ -3762,7 +3762,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H117" t="n">
         <v>20886</v>
@@ -3791,7 +3791,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G118" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H118" t="n">
         <v>47283</v>
@@ -3849,7 +3849,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737581253052</v>
+        <v>4.40737628936768</v>
       </c>
       <c r="H120" t="n">
         <v>50907</v>
@@ -3878,7 +3878,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G121" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H121" t="n">
         <v>5333</v>
@@ -3936,7 +3936,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G123" t="n">
-        <v>4.30979490280151</v>
+        <v>4.30979537963867</v>
       </c>
       <c r="H123" t="n">
         <v>30275</v>
@@ -3994,7 +3994,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.63506317138672</v>
+        <v>4.63506269454956</v>
       </c>
       <c r="H125" t="n">
         <v>59141</v>
@@ -4052,7 +4052,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.63506317138672</v>
+        <v>4.63506269454956</v>
       </c>
       <c r="H127" t="n">
         <v>19970</v>
@@ -4081,7 +4081,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.63506317138672</v>
+        <v>4.63506269454956</v>
       </c>
       <c r="H128" t="n">
         <v>22395</v>
@@ -4110,7 +4110,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.63506317138672</v>
+        <v>4.63506269454956</v>
       </c>
       <c r="H129" t="n">
         <v>7536</v>
@@ -4168,7 +4168,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.63506317138672</v>
+        <v>4.63506269454956</v>
       </c>
       <c r="H131" t="n">
         <v>37064</v>
@@ -4197,7 +4197,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>4.76517057418823</v>
+        <v>4.76517009735107</v>
       </c>
       <c r="H132" t="n">
         <v>17792</v>
@@ -4226,7 +4226,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>4.86275005340576</v>
+        <v>4.86275100708008</v>
       </c>
       <c r="H133" t="n">
         <v>5321</v>
@@ -4313,7 +4313,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791091918945</v>
+        <v>5.05791139602661</v>
       </c>
       <c r="H136" t="n">
         <v>24382</v>
@@ -4371,7 +4371,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>5.1554913520813</v>
+        <v>5.15549087524414</v>
       </c>
       <c r="H138" t="n">
         <v>14771</v>
@@ -4400,7 +4400,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>5.1554913520813</v>
+        <v>5.15549087524414</v>
       </c>
       <c r="H139" t="n">
         <v>5761</v>
@@ -4458,7 +4458,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H141" t="n">
         <v>13207</v>
@@ -4487,7 +4487,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G142" t="n">
-        <v>5.18801832199097</v>
+        <v>5.18801784515381</v>
       </c>
       <c r="H142" t="n">
         <v>16197</v>
@@ -4516,7 +4516,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G143" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H143" t="n">
         <v>11836</v>
@@ -4545,7 +4545,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H144" t="n">
         <v>4290</v>
@@ -4574,7 +4574,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H145" t="n">
         <v>16119</v>
@@ -4632,7 +4632,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H147" t="n">
         <v>10023</v>
@@ -4661,7 +4661,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164791107178</v>
+        <v>5.04164743423462</v>
       </c>
       <c r="H148" t="n">
         <v>9600</v>
@@ -4690,7 +4690,7 @@
         <v>6</v>
       </c>
       <c r="G149" t="n">
-        <v>4.8790135383606</v>
+        <v>4.87901401519775</v>
       </c>
       <c r="H149" t="n">
         <v>16280</v>
@@ -4719,7 +4719,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791091918945</v>
+        <v>5.05791139602661</v>
       </c>
       <c r="H150" t="n">
         <v>6072</v>
@@ -4748,7 +4748,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H151" t="n">
         <v>10138</v>
@@ -4777,7 +4777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G152" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H152" t="n">
         <v>7104</v>
@@ -4806,7 +4806,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H153" t="n">
         <v>5444</v>
@@ -4893,7 +4893,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>5.10670137405396</v>
+        <v>5.1067008972168</v>
       </c>
       <c r="H156" t="n">
         <v>11754</v>
@@ -4922,7 +4922,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>5.12296485900879</v>
+        <v>5.12296438217163</v>
       </c>
       <c r="H157" t="n">
         <v>4698</v>
@@ -4951,7 +4951,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H158" t="n">
         <v>9550</v>
@@ -4980,7 +4980,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G159" t="n">
-        <v>5.09043788909912</v>
+        <v>5.09043836593628</v>
       </c>
       <c r="H159" t="n">
         <v>11350</v>
@@ -5009,7 +5009,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G160" t="n">
-        <v>4.97659349441528</v>
+        <v>4.97659397125244</v>
       </c>
       <c r="H160" t="n">
         <v>12705</v>
@@ -5038,7 +5038,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164791107178</v>
+        <v>5.04164743423462</v>
       </c>
       <c r="H161" t="n">
         <v>3098</v>
@@ -5125,7 +5125,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>4.94406652450562</v>
+        <v>4.94406747817993</v>
       </c>
       <c r="H164" t="n">
         <v>28419</v>
@@ -5154,7 +5154,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G165" t="n">
-        <v>4.9278039932251</v>
+        <v>4.92780351638794</v>
       </c>
       <c r="H165" t="n">
         <v>10999</v>
@@ -5241,7 +5241,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G168" t="n">
-        <v>4.9278039932251</v>
+        <v>4.92780351638794</v>
       </c>
       <c r="H168" t="n">
         <v>6210</v>
@@ -5270,7 +5270,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.94406652450562</v>
+        <v>4.94406747817993</v>
       </c>
       <c r="H169" t="n">
         <v>2656</v>
@@ -5357,7 +5357,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H172" t="n">
         <v>2308</v>
@@ -5415,7 +5415,7 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
-        <v>4.8790135383606</v>
+        <v>4.87901401519775</v>
       </c>
       <c r="H174" t="n">
         <v>7490</v>
@@ -5473,7 +5473,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H176" t="n">
         <v>18455</v>
@@ -5502,7 +5502,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G177" t="n">
-        <v>5.25307178497314</v>
+        <v>5.25307130813599</v>
       </c>
       <c r="H177" t="n">
         <v>49926</v>
@@ -5531,7 +5531,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G178" t="n">
-        <v>5.23680877685547</v>
+        <v>5.23680830001831</v>
       </c>
       <c r="H178" t="n">
         <v>49204</v>
@@ -5560,7 +5560,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G179" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H179" t="n">
         <v>12820</v>
@@ -5589,7 +5589,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G180" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H180" t="n">
         <v>11620</v>
@@ -5618,7 +5618,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G181" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H181" t="n">
         <v>5800</v>
@@ -5647,7 +5647,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G182" t="n">
-        <v>5.35065221786499</v>
+        <v>5.35065174102783</v>
       </c>
       <c r="H182" t="n">
         <v>7541</v>
@@ -5676,7 +5676,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>5.3831787109375</v>
+        <v>5.38317823410034</v>
       </c>
       <c r="H183" t="n">
         <v>5662</v>
@@ -5705,7 +5705,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.36691522598267</v>
+        <v>5.36691570281982</v>
       </c>
       <c r="H184" t="n">
         <v>16090</v>
@@ -5908,7 +5908,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G191" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H191" t="n">
         <v>110919</v>
@@ -5937,7 +5937,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G192" t="n">
-        <v>5.00912094116211</v>
+        <v>5.00912046432495</v>
       </c>
       <c r="H192" t="n">
         <v>2290</v>
@@ -6024,7 +6024,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>5.00475597381592</v>
+        <v>5.00475645065308</v>
       </c>
       <c r="H195" t="n">
         <v>15185</v>
@@ -6198,7 +6198,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G201" t="n">
-        <v>5.28741693496704</v>
+        <v>5.28741645812988</v>
       </c>
       <c r="H201" t="n">
         <v>8833</v>
@@ -6256,7 +6256,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H203" t="n">
         <v>5722</v>
@@ -6314,7 +6314,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G205" t="n">
-        <v>5.28741693496704</v>
+        <v>5.28741645812988</v>
       </c>
       <c r="H205" t="n">
         <v>1300</v>
@@ -6343,7 +6343,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>5.28741693496704</v>
+        <v>5.28741645812988</v>
       </c>
       <c r="H206" t="n">
         <v>4898</v>
@@ -6372,7 +6372,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H207" t="n">
         <v>5465</v>
@@ -6401,7 +6401,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>5.35392618179321</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H208" t="n">
         <v>3971</v>
@@ -6430,7 +6430,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.35392618179321</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H209" t="n">
         <v>6644</v>
@@ -6720,7 +6720,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G219" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H219" t="n">
         <v>20185</v>
@@ -6749,7 +6749,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H220" t="n">
         <v>4090</v>
@@ -6807,7 +6807,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G222" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H222" t="n">
         <v>8191</v>
@@ -6836,7 +6836,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66983985900879</v>
+        <v>5.66984081268311</v>
       </c>
       <c r="H223" t="n">
         <v>3507</v>
@@ -6865,7 +6865,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>5.75297594070435</v>
+        <v>5.7529764175415</v>
       </c>
       <c r="H224" t="n">
         <v>500</v>
@@ -6923,7 +6923,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H226" t="n">
         <v>20880</v>
@@ -6981,7 +6981,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G228" t="n">
-        <v>5.8859920501709</v>
+        <v>5.88599252700806</v>
       </c>
       <c r="H228" t="n">
         <v>21811</v>
@@ -7039,7 +7039,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G230" t="n">
-        <v>5.93587446212769</v>
+        <v>5.93587398529053</v>
       </c>
       <c r="H230" t="n">
         <v>14060</v>
@@ -7068,7 +7068,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G231" t="n">
-        <v>5.80285739898682</v>
+        <v>5.80285692214966</v>
       </c>
       <c r="H231" t="n">
         <v>11590</v>
@@ -7242,7 +7242,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>5.78622961044312</v>
+        <v>5.78623008728027</v>
       </c>
       <c r="H237" t="n">
         <v>8720</v>
@@ -7300,7 +7300,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G239" t="n">
-        <v>5.80285739898682</v>
+        <v>5.80285692214966</v>
       </c>
       <c r="H239" t="n">
         <v>8443</v>
@@ -7416,7 +7416,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G243" t="n">
-        <v>5.76960277557373</v>
+        <v>5.76960229873657</v>
       </c>
       <c r="H243" t="n">
         <v>1500</v>
@@ -7445,7 +7445,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G244" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H244" t="n">
         <v>4011</v>
@@ -7590,7 +7590,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321254730225</v>
       </c>
       <c r="H249" t="n">
         <v>6312</v>
@@ -7619,7 +7619,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G250" t="n">
-        <v>5.58670425415039</v>
+        <v>5.58670473098755</v>
       </c>
       <c r="H250" t="n">
         <v>875</v>
@@ -7648,7 +7648,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66983985900879</v>
+        <v>5.66984081268311</v>
       </c>
       <c r="H251" t="n">
         <v>1386</v>
@@ -7735,7 +7735,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G254" t="n">
-        <v>5.58670425415039</v>
+        <v>5.58670473098755</v>
       </c>
       <c r="H254" t="n">
         <v>2610</v>
@@ -7764,7 +7764,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G255" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H255" t="n">
         <v>1900</v>
@@ -7793,7 +7793,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321254730225</v>
       </c>
       <c r="H257" t="n">
         <v>3560</v>
@@ -7909,7 +7909,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321254730225</v>
       </c>
       <c r="H260" t="n">
         <v>1200</v>
@@ -7938,7 +7938,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H261" t="n">
         <v>2105</v>
@@ -7967,7 +7967,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H262" t="n">
         <v>500</v>
@@ -7996,7 +7996,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321254730225</v>
       </c>
       <c r="H263" t="n">
         <v>8019</v>
@@ -8025,7 +8025,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G264" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H264" t="n">
         <v>1211</v>
@@ -8083,7 +8083,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H266" t="n">
         <v>9438</v>
@@ -8112,7 +8112,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G267" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H267" t="n">
         <v>175</v>
@@ -8170,7 +8170,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G269" t="n">
-        <v>5.50356960296631</v>
+        <v>5.50356912612915</v>
       </c>
       <c r="H269" t="n">
         <v>22096</v>
@@ -8199,7 +8199,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H270" t="n">
         <v>5650</v>
@@ -8228,7 +8228,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G271" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H271" t="n">
         <v>23690</v>
@@ -8286,7 +8286,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H273" t="n">
         <v>13409</v>
@@ -8315,7 +8315,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H274" t="n">
         <v>4619</v>
@@ -8344,7 +8344,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321254730225</v>
       </c>
       <c r="H275" t="n">
         <v>428</v>
@@ -8373,7 +8373,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321254730225</v>
       </c>
       <c r="H276" t="n">
         <v>7400</v>
@@ -8460,7 +8460,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>5.75297594070435</v>
+        <v>5.7529764175415</v>
       </c>
       <c r="H279" t="n">
         <v>13700</v>
@@ -8605,7 +8605,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>5.70309448242188</v>
+        <v>5.70309495925903</v>
       </c>
       <c r="H284" t="n">
         <v>6060</v>
@@ -8634,7 +8634,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321254730225</v>
       </c>
       <c r="H285" t="n">
         <v>15427</v>
@@ -8663,7 +8663,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.6532130241394</v>
+        <v>5.65321254730225</v>
       </c>
       <c r="H286" t="n">
         <v>32500</v>
@@ -8692,7 +8692,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>5.63658618927002</v>
+        <v>5.63658666610718</v>
       </c>
       <c r="H287" t="n">
         <v>1750</v>
@@ -8721,7 +8721,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H288" t="n">
         <v>1973</v>
@@ -8750,7 +8750,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>5.50356960296631</v>
+        <v>5.50356912612915</v>
       </c>
       <c r="H289" t="n">
         <v>10165</v>
@@ -8808,7 +8808,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>5.57007789611816</v>
+        <v>5.57007741928101</v>
       </c>
       <c r="H291" t="n">
         <v>4539</v>
@@ -8866,7 +8866,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>5.55345010757446</v>
+        <v>5.55345058441162</v>
       </c>
       <c r="H293" t="n">
         <v>14001</v>
@@ -8895,7 +8895,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G294" t="n">
-        <v>5.60333204269409</v>
+        <v>5.60333156585693</v>
       </c>
       <c r="H294" t="n">
         <v>31744</v>
@@ -9040,7 +9040,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>5.43706083297729</v>
+        <v>5.43706035614014</v>
       </c>
       <c r="H299" t="n">
         <v>4580</v>
@@ -9156,7 +9156,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H303" t="n">
         <v>4716</v>
@@ -9185,7 +9185,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H304" t="n">
         <v>1563</v>
@@ -9301,7 +9301,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>5.35392618179321</v>
+        <v>5.3539252281189</v>
       </c>
       <c r="H308" t="n">
         <v>7755</v>
@@ -9330,7 +9330,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H309" t="n">
         <v>3800</v>
@@ -9562,7 +9562,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>5.1211462020874</v>
+        <v>5.12114572525024</v>
       </c>
       <c r="H317" t="n">
         <v>4420</v>
@@ -9678,7 +9678,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H321" t="n">
         <v>5361</v>
@@ -9707,7 +9707,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>5.28741693496704</v>
+        <v>5.28741645812988</v>
       </c>
       <c r="H322" t="n">
         <v>6754</v>
@@ -9823,7 +9823,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.28741693496704</v>
+        <v>5.28741645812988</v>
       </c>
       <c r="H326" t="n">
         <v>4390</v>
@@ -9939,7 +9939,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H330" t="n">
         <v>5585</v>
@@ -9968,7 +9968,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G331" t="n">
-        <v>5.33729839324951</v>
+        <v>5.33729887008667</v>
       </c>
       <c r="H331" t="n">
         <v>11425</v>
@@ -10142,7 +10142,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G337" t="n">
-        <v>5.28741693496704</v>
+        <v>5.28741645812988</v>
       </c>
       <c r="H337" t="n">
         <v>15623</v>
@@ -10171,7 +10171,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G338" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H338" t="n">
         <v>2453</v>
@@ -10287,7 +10287,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>5.28741693496704</v>
+        <v>5.28741645812988</v>
       </c>
       <c r="H342" t="n">
         <v>2043</v>
@@ -10345,7 +10345,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.28741693496704</v>
+        <v>5.28741645812988</v>
       </c>
       <c r="H344" t="n">
         <v>13660</v>
@@ -10432,7 +10432,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G347" t="n">
-        <v>5.28741693496704</v>
+        <v>5.28741645812988</v>
       </c>
       <c r="H347" t="n">
         <v>5755</v>
@@ -10606,7 +10606,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G353" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H353" t="n">
         <v>6420</v>
@@ -10635,7 +10635,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H354" t="n">
         <v>7088</v>
@@ -10693,7 +10693,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H356" t="n">
         <v>2400</v>
@@ -10722,7 +10722,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463695526123</v>
+        <v>5.05463790893555</v>
       </c>
       <c r="H358" t="n">
         <v>4600</v>
@@ -10896,7 +10896,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.28741693496704</v>
+        <v>5.28741645812988</v>
       </c>
       <c r="H363" t="n">
         <v>4848</v>
@@ -11012,7 +11012,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G367" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H367" t="n">
         <v>112</v>
@@ -11041,7 +11041,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G368" t="n">
-        <v>5.13777303695679</v>
+        <v>5.13777256011963</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067155838013</v>
+        <v>5.32067108154297</v>
       </c>
       <c r="H373" t="n">
         <v>4742</v>
@@ -11418,7 +11418,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G381" t="n">
-        <v>5.1211462020874</v>
+        <v>5.12114572525024</v>
       </c>
       <c r="H381" t="n">
         <v>1071</v>
@@ -11882,7 +11882,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G397" t="n">
-        <v>5.08789110183716</v>
+        <v>5.08789205551147</v>
       </c>
       <c r="H397" t="n">
         <v>1898</v>
@@ -11911,7 +11911,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G398" t="n">
-        <v>5.08789110183716</v>
+        <v>5.08789205551147</v>
       </c>
       <c r="H398" t="n">
         <v>2425</v>
@@ -11940,7 +11940,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97150182723999</v>
+        <v>4.97150278091431</v>
       </c>
       <c r="H399" t="n">
         <v>5742</v>
@@ -11969,7 +11969,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G400" t="n">
-        <v>4.82185888290405</v>
+        <v>4.82185840606689</v>
       </c>
       <c r="H400" t="n">
         <v>7273</v>
@@ -12056,7 +12056,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G403" t="n">
-        <v>4.83848524093628</v>
+        <v>4.83848571777344</v>
       </c>
       <c r="H403" t="n">
         <v>339</v>
@@ -12114,7 +12114,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G405" t="n">
-        <v>4.83848524093628</v>
+        <v>4.83848571777344</v>
       </c>
       <c r="H405" t="n">
         <v>5440</v>
@@ -12172,7 +12172,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H407" t="n">
         <v>9154</v>
@@ -12230,7 +12230,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G409" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884086608887</v>
       </c>
       <c r="H409" t="n">
         <v>700</v>
@@ -12259,7 +12259,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G410" t="n">
-        <v>4.78860473632812</v>
+        <v>4.78860425949097</v>
       </c>
       <c r="H410" t="n">
         <v>300</v>
@@ -12288,7 +12288,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G411" t="n">
-        <v>4.70546865463257</v>
+        <v>4.70546817779541</v>
       </c>
       <c r="H411" t="n">
         <v>826</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>4.80523109436035</v>
+        <v>4.80523157119751</v>
       </c>
       <c r="H412" t="n">
         <v>200</v>
@@ -12346,7 +12346,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G413" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H413" t="n">
         <v>6760</v>
@@ -12404,7 +12404,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H415" t="n">
         <v>970</v>
@@ -12491,7 +12491,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>4.47268915176392</v>
+        <v>4.47268962860107</v>
       </c>
       <c r="H418" t="n">
         <v>25169</v>
@@ -12607,7 +12607,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H422" t="n">
         <v>7657</v>
@@ -12665,7 +12665,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G424" t="n">
-        <v>4.80523109436035</v>
+        <v>4.80523157119751</v>
       </c>
       <c r="H424" t="n">
         <v>3714</v>
@@ -12752,7 +12752,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G427" t="n">
-        <v>4.55582475662231</v>
+        <v>4.55582523345947</v>
       </c>
       <c r="H427" t="n">
         <v>10094</v>
@@ -12781,7 +12781,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G428" t="n">
-        <v>4.52257061004639</v>
+        <v>4.52257013320923</v>
       </c>
       <c r="H428" t="n">
         <v>8580</v>
@@ -12810,7 +12810,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G429" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884086608887</v>
       </c>
       <c r="H429" t="n">
         <v>3246</v>
@@ -12839,7 +12839,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>4.50594329833984</v>
+        <v>4.505943775177</v>
       </c>
       <c r="H430" t="n">
         <v>7925</v>
@@ -12868,7 +12868,7 @@
         <v>5.5</v>
       </c>
       <c r="G431" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H431" t="n">
         <v>2128</v>
@@ -12897,7 +12897,7 @@
         <v>5.5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>5.5</v>
       </c>
       <c r="G433" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H433" t="n">
         <v>2400</v>
@@ -12955,7 +12955,7 @@
         <v>5.5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>4.68884134292603</v>
+        <v>4.68884086608887</v>
       </c>
       <c r="H435" t="n">
         <v>2711</v>
@@ -13013,7 +13013,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>4.78860473632812</v>
+        <v>4.78860425949097</v>
       </c>
       <c r="H436" t="n">
         <v>500</v>
@@ -13129,7 +13129,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G440" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H440" t="n">
         <v>700</v>
@@ -13158,7 +13158,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H441" t="n">
         <v>4384</v>
@@ -13187,7 +13187,7 @@
         <v>5.5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.57245206832886</v>
+        <v>4.5724515914917</v>
       </c>
       <c r="H442" t="n">
         <v>700</v>
@@ -13216,7 +13216,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G443" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H443" t="n">
         <v>3174</v>
@@ -13274,7 +13274,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G445" t="n">
-        <v>4.6555871963501</v>
+        <v>4.65558767318726</v>
       </c>
       <c r="H445" t="n">
         <v>1010</v>
@@ -13390,7 +13390,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G449" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H449" t="n">
         <v>3090</v>
@@ -13419,7 +13419,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H450" t="n">
         <v>1700</v>
@@ -13448,7 +13448,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H451" t="n">
         <v>1487</v>
@@ -13477,7 +13477,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H452" t="n">
         <v>500</v>
@@ -13506,7 +13506,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H454" t="n">
         <v>4800</v>
@@ -13564,7 +13564,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H455" t="n">
         <v>5500</v>
@@ -13593,7 +13593,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G463" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H463" t="n">
         <v>5</v>
@@ -13854,7 +13854,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H465" t="n">
         <v>205</v>
@@ -13912,7 +13912,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H467" t="n">
         <v>1464</v>
@@ -13941,7 +13941,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H468" t="n">
         <v>810</v>
@@ -13970,7 +13970,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H469" t="n">
         <v>646</v>
@@ -13999,7 +13999,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H470" t="n">
         <v>1000</v>
@@ -14028,7 +14028,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -14057,7 +14057,7 @@
         <v>6</v>
       </c>
       <c r="G472" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H472" t="n">
         <v>2091</v>
@@ -14086,7 +14086,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H473" t="n">
         <v>9179</v>
@@ -14202,7 +14202,7 @@
         <v>5.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H477" t="n">
         <v>350</v>
@@ -14260,7 +14260,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G479" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H479" t="n">
         <v>5905</v>
@@ -14289,7 +14289,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H480" t="n">
         <v>20980</v>
@@ -14318,7 +14318,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H481" t="n">
         <v>500</v>
@@ -14347,7 +14347,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H482" t="n">
         <v>1405</v>
@@ -14376,7 +14376,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H487" t="n">
         <v>3597</v>
@@ -14695,7 +14695,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H494" t="n">
         <v>3377</v>
@@ -14724,7 +14724,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G495" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H496" t="n">
         <v>11723</v>
@@ -14898,7 +14898,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G501" t="n">
-        <v>4.46638631820679</v>
+        <v>4.46638584136963</v>
       </c>
       <c r="H501" t="n">
         <v>705</v>
@@ -14927,7 +14927,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G502" t="n">
-        <v>4.46638631820679</v>
+        <v>4.46638584136963</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H507" t="n">
         <v>3700</v>
@@ -15101,7 +15101,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H511" t="n">
         <v>2505</v>
@@ -15217,7 +15217,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H512" t="n">
         <v>2050</v>
@@ -15362,7 +15362,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G521" t="n">
-        <v>4.96075773239136</v>
+        <v>4.96075820922852</v>
       </c>
       <c r="H521" t="n">
         <v>341</v>
@@ -15565,7 +15565,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G524" t="n">
-        <v>4.9948525428772</v>
+        <v>4.99485206604004</v>
       </c>
       <c r="H524" t="n">
         <v>1780</v>
@@ -15594,7 +15594,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H525" t="n">
         <v>235</v>
@@ -15681,7 +15681,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H528" t="n">
         <v>700</v>
@@ -15710,7 +15710,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008813858032</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H530" t="n">
         <v>1270</v>
@@ -15855,7 +15855,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90961647033691</v>
+        <v>4.90961599349976</v>
       </c>
       <c r="H534" t="n">
         <v>2167</v>
@@ -15884,7 +15884,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H535" t="n">
         <v>2280</v>
@@ -15913,7 +15913,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H536" t="n">
         <v>2123</v>
@@ -15942,7 +15942,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H537" t="n">
         <v>1000</v>
@@ -15971,7 +15971,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H538" t="n">
         <v>1776</v>
@@ -16029,7 +16029,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H540" t="n">
         <v>350</v>
@@ -16058,7 +16058,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H542" t="n">
         <v>2760</v>
@@ -16116,7 +16116,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G543" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>4.87552070617676</v>
+        <v>4.87552118301392</v>
       </c>
       <c r="H544" t="n">
         <v>421</v>
@@ -16174,7 +16174,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H545" t="n">
         <v>2895</v>
@@ -16232,7 +16232,7 @@
         <v>5.5</v>
       </c>
       <c r="G547" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H547" t="n">
         <v>2535</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.48343420028687</v>
+        <v>4.48343467712402</v>
       </c>
       <c r="H549" t="n">
         <v>1022</v>
@@ -16348,7 +16348,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>4.48343420028687</v>
+        <v>4.48343467712402</v>
       </c>
       <c r="H551" t="n">
         <v>1200</v>
@@ -16406,7 +16406,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>4.36410236358643</v>
+        <v>4.36410284042358</v>
       </c>
       <c r="H553" t="n">
         <v>4928</v>
@@ -16435,7 +16435,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G554" t="n">
-        <v>4.44933938980103</v>
+        <v>4.44933891296387</v>
       </c>
       <c r="H554" t="n">
         <v>608</v>
@@ -16580,7 +16580,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G559" t="n">
-        <v>4.53457593917847</v>
+        <v>4.53457546234131</v>
       </c>
       <c r="H559" t="n">
         <v>750</v>
@@ -16609,7 +16609,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H560" t="n">
         <v>2687</v>
@@ -16638,7 +16638,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H561" t="n">
         <v>460</v>
@@ -16667,7 +16667,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.60276460647583</v>
+        <v>4.60276508331299</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G563" t="n">
-        <v>4.46638631820679</v>
+        <v>4.46638584136963</v>
       </c>
       <c r="H563" t="n">
         <v>2000</v>
@@ -17044,7 +17044,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H575" t="n">
         <v>20</v>
@@ -17073,7 +17073,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.80733251571655</v>
+        <v>4.80733203887939</v>
       </c>
       <c r="H580" t="n">
         <v>3158</v>
@@ -17334,7 +17334,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H585" t="n">
         <v>360</v>
@@ -17624,7 +17624,7 @@
         <v>5.5</v>
       </c>
       <c r="G595" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H595" t="n">
         <v>6710</v>
@@ -17682,7 +17682,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H597" t="n">
         <v>607</v>
@@ -17711,7 +17711,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G598" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H598" t="n">
         <v>65</v>
@@ -18059,7 +18059,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H610" t="n">
         <v>1351</v>
@@ -18088,7 +18088,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H611" t="n">
         <v>510</v>
@@ -18117,7 +18117,7 @@
         <v>5.5</v>
       </c>
       <c r="G612" t="n">
-        <v>4.68800163269043</v>
+        <v>4.68800115585327</v>
       </c>
       <c r="H612" t="n">
         <v>34</v>
@@ -18146,7 +18146,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>4.75618982315063</v>
+        <v>4.75619029998779</v>
       </c>
       <c r="H613" t="n">
         <v>186</v>
@@ -18320,7 +18320,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H619" t="n">
         <v>675</v>
@@ -18494,7 +18494,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>4.80733251571655</v>
+        <v>4.80733203887939</v>
       </c>
       <c r="H625" t="n">
         <v>1866</v>
@@ -18523,7 +18523,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H626" t="n">
         <v>110</v>
@@ -18552,7 +18552,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H627" t="n">
         <v>10</v>
@@ -18581,7 +18581,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H628" t="n">
         <v>400</v>
@@ -18610,7 +18610,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437896728516</v>
+        <v>4.82437944412231</v>
       </c>
       <c r="H629" t="n">
         <v>110</v>
@@ -18697,7 +18697,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>4.77323770523071</v>
+        <v>4.77323722839355</v>
       </c>
       <c r="H632" t="n">
         <v>872</v>
@@ -18726,7 +18726,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504856109619</v>
+        <v>4.70504808425903</v>
       </c>
       <c r="H633" t="n">
         <v>1703</v>
@@ -18755,7 +18755,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>4.72209548950195</v>
+        <v>4.72209596633911</v>
       </c>
       <c r="H634" t="n">
         <v>10</v>
@@ -18813,7 +18813,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G636" t="n">
-        <v>4.79028511047363</v>
+        <v>4.79028463363647</v>
       </c>
       <c r="H636" t="n">
         <v>1898</v>
@@ -18842,7 +18842,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G637" t="n">
-        <v>5.01189994812012</v>
+        <v>5.01189947128296</v>
       </c>
       <c r="H637" t="n">
         <v>67041</v>
@@ -18871,7 +18871,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G638" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H638" t="n">
         <v>3800</v>
@@ -18958,7 +18958,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>5.01189994812012</v>
+        <v>5.01189947128296</v>
       </c>
       <c r="H641" t="n">
         <v>3920</v>
@@ -18987,7 +18987,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.0971360206604</v>
+        <v>5.09713554382324</v>
       </c>
       <c r="H642" t="n">
         <v>5765</v>
@@ -19016,7 +19016,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>5.25056171417236</v>
+        <v>5.25056076049805</v>
       </c>
       <c r="H643" t="n">
         <v>4245</v>
@@ -19045,7 +19045,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G644" t="n">
-        <v>5.35284566879272</v>
+        <v>5.35284519195557</v>
       </c>
       <c r="H644" t="n">
         <v>15820</v>
@@ -19103,7 +19103,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.1994194984436</v>
+        <v>5.19941997528076</v>
       </c>
       <c r="H646" t="n">
         <v>12764</v>
@@ -19132,7 +19132,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G647" t="n">
-        <v>5.1994194984436</v>
+        <v>5.19941997528076</v>
       </c>
       <c r="H647" t="n">
         <v>1345</v>
@@ -19161,7 +19161,7 @@
         <v>6</v>
       </c>
       <c r="G648" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H648" t="n">
         <v>1200</v>
@@ -19248,7 +19248,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>5.1994194984436</v>
+        <v>5.19941997528076</v>
       </c>
       <c r="H651" t="n">
         <v>2400</v>
@@ -19335,7 +19335,7 @@
         <v>6</v>
       </c>
       <c r="G654" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H654" t="n">
         <v>3833</v>
@@ -19422,7 +19422,7 @@
         <v>6</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H657" t="n">
         <v>512</v>
@@ -19451,7 +19451,7 @@
         <v>6</v>
       </c>
       <c r="G658" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H658" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H659" t="n">
         <v>618</v>
@@ -19509,7 +19509,7 @@
         <v>6</v>
       </c>
       <c r="G660" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H660" t="n">
         <v>110</v>
@@ -19538,7 +19538,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H661" t="n">
         <v>160</v>
@@ -19596,7 +19596,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008813858032</v>
+        <v>5.08008861541748</v>
       </c>
       <c r="H663" t="n">
         <v>300</v>
@@ -19857,7 +19857,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G672" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H672" t="n">
         <v>1371</v>
@@ -19886,7 +19886,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G673" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>6</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H674" t="n">
         <v>1922</v>
@@ -19973,7 +19973,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H676" t="n">
         <v>3802</v>
@@ -20002,7 +20002,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H677" t="n">
         <v>1377</v>
@@ -20031,7 +20031,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>6</v>
       </c>
       <c r="G679" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H679" t="n">
         <v>4219</v>
@@ -20089,7 +20089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H680" t="n">
         <v>893</v>
@@ -20118,7 +20118,7 @@
         <v>6</v>
       </c>
       <c r="G681" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H681" t="n">
         <v>1250</v>
@@ -20147,7 +20147,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H682" t="n">
         <v>6283</v>
@@ -20205,7 +20205,7 @@
         <v>6</v>
       </c>
       <c r="G684" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H684" t="n">
         <v>3929</v>
@@ -20292,7 +20292,7 @@
         <v>6</v>
       </c>
       <c r="G687" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H687" t="n">
         <v>3300</v>
@@ -20350,7 +20350,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H689" t="n">
         <v>820</v>
@@ -20379,7 +20379,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H690" t="n">
         <v>700</v>
@@ -20408,7 +20408,7 @@
         <v>6</v>
       </c>
       <c r="G691" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H691" t="n">
         <v>3324</v>
@@ -20437,7 +20437,7 @@
         <v>6</v>
       </c>
       <c r="G692" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H692" t="n">
         <v>3119</v>
@@ -20466,7 +20466,7 @@
         <v>6</v>
       </c>
       <c r="G693" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H693" t="n">
         <v>2354</v>
@@ -20553,7 +20553,7 @@
         <v>6</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H696" t="n">
         <v>10</v>
@@ -20669,7 +20669,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>5.02894735336304</v>
+        <v>5.02894687652588</v>
       </c>
       <c r="H700" t="n">
         <v>807</v>
@@ -20785,7 +20785,7 @@
         <v>6</v>
       </c>
       <c r="G704" t="n">
-        <v>5.11418342590332</v>
+        <v>5.11418294906616</v>
       </c>
       <c r="H704" t="n">
         <v>400</v>
@@ -21162,7 +21162,7 @@
         <v>5.75</v>
       </c>
       <c r="G717" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H717" t="n">
         <v>1661</v>
@@ -21191,7 +21191,7 @@
         <v>5.75</v>
       </c>
       <c r="G718" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H718" t="n">
         <v>2500</v>
@@ -21220,7 +21220,7 @@
         <v>5.75</v>
       </c>
       <c r="G719" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>5.75</v>
       </c>
       <c r="G720" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21278,7 +21278,7 @@
         <v>5.75</v>
       </c>
       <c r="G721" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21394,7 +21394,7 @@
         <v>5.75</v>
       </c>
       <c r="G725" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H725" t="n">
         <v>1926</v>
@@ -21423,7 +21423,7 @@
         <v>5.75</v>
       </c>
       <c r="G726" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H726" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>5.75</v>
       </c>
       <c r="G727" t="n">
-        <v>5.07009553909302</v>
+        <v>5.07009601593018</v>
       </c>
       <c r="H727" t="n">
         <v>6821</v>
@@ -21481,7 +21481,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G728" t="n">
-        <v>4.93783235549927</v>
+        <v>4.93783187866211</v>
       </c>
       <c r="H728" t="n">
         <v>2930</v>
@@ -21510,7 +21510,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.93783235549927</v>
+        <v>4.93783187866211</v>
       </c>
       <c r="H729" t="n">
         <v>6873</v>
@@ -21568,7 +21568,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H731" t="n">
         <v>350</v>
@@ -21858,7 +21858,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G741" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H741" t="n">
         <v>966</v>
@@ -21887,7 +21887,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H742" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H752" t="n">
         <v>233</v>
@@ -22206,7 +22206,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H753" t="n">
         <v>2500</v>
@@ -22235,7 +22235,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H754" t="n">
         <v>4845</v>
@@ -22264,7 +22264,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G755" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H755" t="n">
         <v>5770</v>
@@ -22583,7 +22583,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G766" t="n">
-        <v>4.45286655426025</v>
+        <v>4.45286703109741</v>
       </c>
       <c r="H766" t="n">
         <v>6689</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>4.76148080825806</v>
+        <v>4.76148128509521</v>
       </c>
       <c r="H769" t="n">
         <v>2000</v>
@@ -22699,7 +22699,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G770" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H770" t="n">
         <v>3256</v>
@@ -23395,7 +23395,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>4.89374446868896</v>
+        <v>4.89374494552612</v>
       </c>
       <c r="H794" t="n">
         <v>1641</v>
@@ -23946,7 +23946,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H813" t="n">
         <v>1618</v>
@@ -23975,7 +23975,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24004,7 +24004,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H815" t="n">
         <v>1188</v>
@@ -24033,7 +24033,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H816" t="n">
         <v>10</v>
@@ -24062,7 +24062,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H817" t="n">
         <v>365</v>
@@ -24091,7 +24091,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H818" t="n">
         <v>700</v>
@@ -24207,7 +24207,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G822" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H822" t="n">
         <v>340</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H827" t="n">
         <v>2876</v>
@@ -24497,7 +24497,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G832" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H832" t="n">
         <v>207</v>
@@ -24526,7 +24526,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H833" t="n">
         <v>1050</v>
@@ -24555,7 +24555,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G835" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H835" t="n">
         <v>1</v>
@@ -24642,7 +24642,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12661695480347</v>
+        <v>4.12661647796631</v>
       </c>
       <c r="H837" t="n">
         <v>1803</v>
@@ -24729,7 +24729,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>4.12661695480347</v>
+        <v>4.12661647796631</v>
       </c>
       <c r="H840" t="n">
         <v>609</v>
@@ -24758,7 +24758,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G841" t="n">
-        <v>4.12661695480347</v>
+        <v>4.12661647796631</v>
       </c>
       <c r="H841" t="n">
         <v>4500</v>
@@ -24787,7 +24787,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H842" t="n">
         <v>2500</v>
@@ -24816,7 +24816,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H843" t="n">
         <v>1253</v>
@@ -24874,7 +24874,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G845" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H845" t="n">
         <v>796</v>
@@ -25048,7 +25048,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.09134674072266</v>
+        <v>4.0913462638855</v>
       </c>
       <c r="H851" t="n">
         <v>2200</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H856" t="n">
         <v>3097</v>
@@ -25280,7 +25280,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G859" t="n">
-        <v>4.12661695480347</v>
+        <v>4.12661647796631</v>
       </c>
       <c r="H859" t="n">
         <v>6840</v>
@@ -25338,7 +25338,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G861" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H861" t="n">
         <v>1733</v>
@@ -25367,7 +25367,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H862" t="n">
         <v>1450</v>
@@ -25396,7 +25396,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H863" t="n">
         <v>3550</v>
@@ -25425,7 +25425,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.14425182342529</v>
+        <v>4.14425230026245</v>
       </c>
       <c r="H864" t="n">
         <v>6616</v>
@@ -25483,7 +25483,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H866" t="n">
         <v>20519</v>
@@ -25541,7 +25541,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G868" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H868" t="n">
         <v>15412</v>
@@ -25570,7 +25570,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H869" t="n">
         <v>3776</v>
@@ -25599,7 +25599,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H870" t="n">
         <v>4073</v>
@@ -25686,7 +25686,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H873" t="n">
         <v>5847</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H875" t="n">
         <v>3194</v>
@@ -25802,7 +25802,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G877" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H877" t="n">
         <v>13736</v>
@@ -25947,7 +25947,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86209034919739</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H882" t="n">
         <v>15378</v>
@@ -25976,7 +25976,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G883" t="n">
-        <v>3.80918455123901</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H883" t="n">
         <v>18373</v>
@@ -26034,7 +26034,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>3.6857385635376</v>
+        <v>3.68573904037476</v>
       </c>
       <c r="H885" t="n">
         <v>8364</v>
@@ -26063,7 +26063,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G886" t="n">
-        <v>3.73864412307739</v>
+        <v>3.73864436149597</v>
       </c>
       <c r="H886" t="n">
         <v>2531</v>
@@ -26092,7 +26092,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>3.80918455123901</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H887" t="n">
         <v>5091</v>
@@ -26121,7 +26121,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H888" t="n">
         <v>8519</v>
@@ -26150,7 +26150,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H889" t="n">
         <v>14342</v>
@@ -26179,7 +26179,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H890" t="n">
         <v>20433</v>
@@ -26208,7 +26208,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H891" t="n">
         <v>58437</v>
@@ -26266,7 +26266,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G893" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H893" t="n">
         <v>22381</v>
@@ -26353,7 +26353,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>3.82681965827942</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H896" t="n">
         <v>7640</v>
@@ -26440,7 +26440,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G899" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H899" t="n">
         <v>25714</v>
@@ -26498,7 +26498,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G901" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H901" t="n">
         <v>17900</v>
@@ -26527,7 +26527,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73864412307739</v>
+        <v>3.73864436149597</v>
       </c>
       <c r="H902" t="n">
         <v>44451</v>
@@ -26556,7 +26556,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>3.82681965827942</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H903" t="n">
         <v>25646</v>
@@ -26585,7 +26585,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G904" t="n">
-        <v>3.80918455123901</v>
+        <v>3.80918502807617</v>
       </c>
       <c r="H904" t="n">
         <v>39491</v>
@@ -26672,7 +26672,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86209034919739</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H907" t="n">
         <v>7190</v>
@@ -26730,7 +26730,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>3.77391481399536</v>
+        <v>3.77391457557678</v>
       </c>
       <c r="H909" t="n">
         <v>700</v>
@@ -26788,7 +26788,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>3.82681965827942</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H911" t="n">
         <v>85</v>
@@ -26846,7 +26846,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H913" t="n">
         <v>1250</v>
@@ -26875,7 +26875,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86209034919739</v>
+        <v>3.86209011077881</v>
       </c>
       <c r="H914" t="n">
         <v>1050</v>
@@ -26933,7 +26933,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H916" t="n">
         <v>35</v>
@@ -27020,7 +27020,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G919" t="n">
-        <v>3.82681965827942</v>
+        <v>3.826819896698</v>
       </c>
       <c r="H919" t="n">
         <v>1905</v>
@@ -27049,7 +27049,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H920" t="n">
         <v>8574</v>
@@ -27136,7 +27136,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.9149956703186</v>
+        <v>3.91499543190002</v>
       </c>
       <c r="H923" t="n">
         <v>10338</v>
@@ -27194,7 +27194,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H925" t="n">
         <v>2087</v>
@@ -27223,7 +27223,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93263030052185</v>
+        <v>3.93263053894043</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H927" t="n">
         <v>1386</v>
@@ -27281,7 +27281,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.98553609848022</v>
+        <v>3.98553562164307</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H930" t="n">
         <v>125</v>
@@ -27397,7 +27397,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026540756226</v>
+        <v>3.95026564598083</v>
       </c>
       <c r="H932" t="n">
         <v>468</v>
@@ -27455,7 +27455,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G934" t="n">
-        <v>4.17952156066895</v>
+        <v>4.1795220375061</v>
       </c>
       <c r="H934" t="n">
         <v>5727</v>
@@ -27571,7 +27571,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G938" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H938" t="n">
         <v>10491</v>
@@ -27629,7 +27629,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G940" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H940" t="n">
         <v>194</v>
@@ -27716,7 +27716,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G943" t="n">
-        <v>4.28533267974854</v>
+        <v>4.28533315658569</v>
       </c>
       <c r="H943" t="n">
         <v>1635</v>
@@ -27745,7 +27745,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G944" t="n">
-        <v>4.23242807388306</v>
+        <v>4.2324275970459</v>
       </c>
       <c r="H944" t="n">
         <v>8544</v>
@@ -28093,7 +28093,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>4.33823823928833</v>
+        <v>4.33823776245117</v>
       </c>
       <c r="H956" t="n">
         <v>800</v>
@@ -28238,7 +28238,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>4.45286655426025</v>
+        <v>4.45286703109741</v>
       </c>
       <c r="H961" t="n">
         <v>1299</v>
@@ -46398,6 +46398,35 @@
         <v>5500</v>
       </c>
       <c r="I1587" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1588" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1588" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="D1588" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="G1588" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="H1588" t="n">
+        <v>708</v>
+      </c>
+      <c r="I1588" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ICF.MI.xlsx
+++ b/data/ICF.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H2" t="n">
         <v>425</v>
@@ -456,7 +456,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H3" t="n">
         <v>650</v>
@@ -485,7 +485,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G4" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G5" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H5" t="n">
         <v>1105</v>
@@ -543,7 +543,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G6" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H6" t="n">
         <v>18626</v>
@@ -659,7 +659,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G10" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H10" t="n">
         <v>1712</v>
@@ -688,7 +688,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G11" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H11" t="n">
         <v>6680</v>
@@ -717,7 +717,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G13" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>4.08210849761963</v>
+        <v>4.08210802078247</v>
       </c>
       <c r="H18" t="n">
         <v>970</v>
@@ -949,7 +949,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G20" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H20" t="n">
         <v>3268</v>
@@ -978,7 +978,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G21" t="n">
-        <v>4.27726936340332</v>
+        <v>4.27726888656616</v>
       </c>
       <c r="H21" t="n">
         <v>800</v>
@@ -1036,7 +1036,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>4.27726936340332</v>
+        <v>4.27726888656616</v>
       </c>
       <c r="H23" t="n">
         <v>3200</v>
@@ -1123,7 +1123,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G26" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H26" t="n">
         <v>1926</v>
@@ -1152,7 +1152,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G27" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H27" t="n">
         <v>651</v>
@@ -1210,7 +1210,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H29" t="n">
         <v>1969</v>
@@ -1268,7 +1268,7 @@
         <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H31" t="n">
         <v>6330</v>
@@ -1297,7 +1297,7 @@
         <v>5</v>
       </c>
       <c r="G32" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H32" t="n">
         <v>1096</v>
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H35" t="n">
         <v>500</v>
@@ -1442,7 +1442,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H37" t="n">
         <v>1422</v>
@@ -1471,7 +1471,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G38" t="n">
-        <v>4.08210849761963</v>
+        <v>4.08210802078247</v>
       </c>
       <c r="H38" t="n">
         <v>950</v>
@@ -1500,7 +1500,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H39" t="n">
         <v>300</v>
@@ -1529,7 +1529,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G40" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H40" t="n">
         <v>1276</v>
@@ -1558,7 +1558,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G41" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H41" t="n">
         <v>470</v>
@@ -1587,7 +1587,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>4.21221494674683</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H42" t="n">
         <v>450</v>
@@ -1616,7 +1616,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G43" t="n">
-        <v>4.21221494674683</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H43" t="n">
         <v>450</v>
@@ -1848,7 +1848,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G51" t="n">
-        <v>3.95200133323669</v>
+        <v>3.95200109481812</v>
       </c>
       <c r="H51" t="n">
         <v>4885</v>
@@ -1877,7 +1877,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G52" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H52" t="n">
         <v>1056</v>
@@ -1906,7 +1906,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G53" t="n">
-        <v>3.97639584541321</v>
+        <v>3.97639632225037</v>
       </c>
       <c r="H53" t="n">
         <v>504</v>
@@ -1935,7 +1935,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G54" t="n">
-        <v>3.9438693523407</v>
+        <v>3.94386911392212</v>
       </c>
       <c r="H54" t="n">
         <v>2108</v>
@@ -1964,7 +1964,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G55" t="n">
-        <v>3.90321063995361</v>
+        <v>3.90321183204651</v>
       </c>
       <c r="H55" t="n">
         <v>1248</v>
@@ -1993,7 +1993,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G56" t="n">
-        <v>3.90321063995361</v>
+        <v>3.90321183204651</v>
       </c>
       <c r="H56" t="n">
         <v>400</v>
@@ -2022,7 +2022,7 @@
         <v>4.75</v>
       </c>
       <c r="G57" t="n">
-        <v>3.86255311965942</v>
+        <v>3.86255264282227</v>
       </c>
       <c r="H57" t="n">
         <v>4200</v>
@@ -2051,7 +2051,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G58" t="n">
-        <v>3.85442113876343</v>
+        <v>3.85442042350769</v>
       </c>
       <c r="H58" t="n">
         <v>450</v>
@@ -2080,7 +2080,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G59" t="n">
-        <v>3.8869481086731</v>
+        <v>3.88694834709167</v>
       </c>
       <c r="H59" t="n">
         <v>1153</v>
@@ -2109,7 +2109,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G60" t="n">
-        <v>3.82189393043518</v>
+        <v>3.8218936920166</v>
       </c>
       <c r="H60" t="n">
         <v>400</v>
@@ -2138,7 +2138,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G61" t="n">
-        <v>3.74057698249817</v>
+        <v>3.74057674407959</v>
       </c>
       <c r="H61" t="n">
         <v>2000</v>
@@ -2167,7 +2167,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G62" t="n">
-        <v>3.74057698249817</v>
+        <v>3.74057674407959</v>
       </c>
       <c r="H62" t="n">
         <v>1245</v>
@@ -2196,7 +2196,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G63" t="n">
-        <v>3.82189393043518</v>
+        <v>3.8218936920166</v>
       </c>
       <c r="H63" t="n">
         <v>1994</v>
@@ -2312,7 +2312,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G67" t="n">
-        <v>3.67552423477173</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H67" t="n">
         <v>5250</v>
@@ -2341,7 +2341,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>3.64299726486206</v>
+        <v>3.6429967880249</v>
       </c>
       <c r="H68" t="n">
         <v>7900</v>
@@ -2457,7 +2457,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G72" t="n">
-        <v>3.67552423477173</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H72" t="n">
         <v>6400</v>
@@ -2486,7 +2486,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G73" t="n">
-        <v>3.6917872428894</v>
+        <v>3.69178748130798</v>
       </c>
       <c r="H73" t="n">
         <v>281949</v>
@@ -2515,7 +2515,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G74" t="n">
-        <v>3.77310395240784</v>
+        <v>3.77310419082642</v>
       </c>
       <c r="H74" t="n">
         <v>7850</v>
@@ -2573,7 +2573,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G76" t="n">
-        <v>3.67552423477173</v>
+        <v>3.67552399635315</v>
       </c>
       <c r="H76" t="n">
         <v>24183</v>
@@ -2602,7 +2602,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G77" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H77" t="n">
         <v>35243</v>
@@ -2631,7 +2631,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G78" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H78" t="n">
         <v>15007</v>
@@ -2718,7 +2718,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G81" t="n">
-        <v>4.19595193862915</v>
+        <v>4.19595146179199</v>
       </c>
       <c r="H81" t="n">
         <v>4817</v>
@@ -2776,7 +2776,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G83" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H83" t="n">
         <v>11228</v>
@@ -2834,7 +2834,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G85" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H85" t="n">
         <v>4943</v>
@@ -2892,7 +2892,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G87" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H87" t="n">
         <v>1000</v>
@@ -2921,7 +2921,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G88" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H88" t="n">
         <v>4736</v>
@@ -2950,7 +2950,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G89" t="n">
-        <v>4.14716148376465</v>
+        <v>4.14716196060181</v>
       </c>
       <c r="H89" t="n">
         <v>8400</v>
@@ -2979,7 +2979,7 @@
         <v>5</v>
       </c>
       <c r="G90" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H90" t="n">
         <v>11784</v>
@@ -3008,7 +3008,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G91" t="n">
-        <v>4.00079107284546</v>
+        <v>4.00079154968262</v>
       </c>
       <c r="H91" t="n">
         <v>30633</v>
@@ -3037,7 +3037,7 @@
         <v>5</v>
       </c>
       <c r="G92" t="n">
-        <v>4.06584501266479</v>
+        <v>4.06584453582764</v>
       </c>
       <c r="H92" t="n">
         <v>124660</v>
@@ -3066,7 +3066,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G93" t="n">
-        <v>4.21221494674683</v>
+        <v>4.21221542358398</v>
       </c>
       <c r="H93" t="n">
         <v>37142</v>
@@ -3095,7 +3095,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G94" t="n">
-        <v>4.40737628936768</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H94" t="n">
         <v>35821</v>
@@ -3269,7 +3269,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G100" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H100" t="n">
         <v>13735</v>
@@ -3298,7 +3298,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G101" t="n">
-        <v>4.24474191665649</v>
+        <v>4.24474143981934</v>
       </c>
       <c r="H101" t="n">
         <v>17485</v>
@@ -3327,7 +3327,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G102" t="n">
-        <v>4.32605886459351</v>
+        <v>4.32605934143066</v>
       </c>
       <c r="H102" t="n">
         <v>20579</v>
@@ -3356,7 +3356,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G103" t="n">
-        <v>4.48869228363037</v>
+        <v>4.48869276046753</v>
       </c>
       <c r="H103" t="n">
         <v>18889</v>
@@ -3385,7 +3385,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G104" t="n">
-        <v>4.48869228363037</v>
+        <v>4.48869276046753</v>
       </c>
       <c r="H104" t="n">
         <v>6100</v>
@@ -3443,7 +3443,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G106" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H106" t="n">
         <v>11075</v>
@@ -3472,7 +3472,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>4.50495576858521</v>
+        <v>4.50495624542236</v>
       </c>
       <c r="H107" t="n">
         <v>9254</v>
@@ -3501,7 +3501,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G108" t="n">
-        <v>4.5212197303772</v>
+        <v>4.52121925354004</v>
       </c>
       <c r="H108" t="n">
         <v>11295</v>
@@ -3530,7 +3530,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>4.55374622344971</v>
+        <v>4.55374670028687</v>
       </c>
       <c r="H109" t="n">
         <v>6650</v>
@@ -3617,7 +3617,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G112" t="n">
-        <v>4.32605886459351</v>
+        <v>4.32605934143066</v>
       </c>
       <c r="H112" t="n">
         <v>8648</v>
@@ -3646,7 +3646,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G113" t="n">
-        <v>4.22847843170166</v>
+        <v>4.22847890853882</v>
       </c>
       <c r="H113" t="n">
         <v>32551</v>
@@ -3849,7 +3849,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G120" t="n">
-        <v>4.40737628936768</v>
+        <v>4.40737581253052</v>
       </c>
       <c r="H120" t="n">
         <v>50907</v>
@@ -3994,7 +3994,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H125" t="n">
         <v>59141</v>
@@ -4023,7 +4023,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>4.55374622344971</v>
+        <v>4.55374670028687</v>
       </c>
       <c r="H126" t="n">
         <v>89802</v>
@@ -4052,7 +4052,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G127" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H127" t="n">
         <v>19970</v>
@@ -4081,7 +4081,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G128" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H128" t="n">
         <v>22395</v>
@@ -4110,7 +4110,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G129" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H129" t="n">
         <v>7536</v>
@@ -4168,7 +4168,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G131" t="n">
-        <v>4.63506269454956</v>
+        <v>4.63506317138672</v>
       </c>
       <c r="H131" t="n">
         <v>37064</v>
@@ -4197,7 +4197,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G132" t="n">
-        <v>4.76517009735107</v>
+        <v>4.76517057418823</v>
       </c>
       <c r="H132" t="n">
         <v>17792</v>
@@ -4226,7 +4226,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G133" t="n">
-        <v>4.86275100708008</v>
+        <v>4.86275053024292</v>
       </c>
       <c r="H133" t="n">
         <v>5321</v>
@@ -4255,7 +4255,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>4.91154050827026</v>
+        <v>4.91154098510742</v>
       </c>
       <c r="H134" t="n">
         <v>14070</v>
@@ -4313,7 +4313,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G136" t="n">
-        <v>5.05791139602661</v>
+        <v>5.05791044235229</v>
       </c>
       <c r="H136" t="n">
         <v>24382</v>
@@ -4342,7 +4342,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428085327148</v>
       </c>
       <c r="H137" t="n">
         <v>12072</v>
@@ -4371,7 +4371,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G138" t="n">
-        <v>5.15549087524414</v>
+        <v>5.15549182891846</v>
       </c>
       <c r="H138" t="n">
         <v>14771</v>
@@ -4400,7 +4400,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G139" t="n">
-        <v>5.15549087524414</v>
+        <v>5.15549182891846</v>
       </c>
       <c r="H139" t="n">
         <v>5761</v>
@@ -4458,7 +4458,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H141" t="n">
         <v>13207</v>
@@ -4545,7 +4545,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G144" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H144" t="n">
         <v>4290</v>
@@ -4574,7 +4574,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G145" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H145" t="n">
         <v>16119</v>
@@ -4632,7 +4632,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G147" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H147" t="n">
         <v>10023</v>
@@ -4661,7 +4661,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G148" t="n">
-        <v>5.04164743423462</v>
+        <v>5.04164791107178</v>
       </c>
       <c r="H148" t="n">
         <v>9600</v>
@@ -4719,7 +4719,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G150" t="n">
-        <v>5.05791139602661</v>
+        <v>5.05791044235229</v>
       </c>
       <c r="H150" t="n">
         <v>6072</v>
@@ -4748,7 +4748,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G151" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H151" t="n">
         <v>10138</v>
@@ -4777,7 +4777,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G152" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H152" t="n">
         <v>7104</v>
@@ -4806,7 +4806,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G153" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H153" t="n">
         <v>5444</v>
@@ -4893,7 +4893,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G156" t="n">
-        <v>5.1067008972168</v>
+        <v>5.10670137405396</v>
       </c>
       <c r="H156" t="n">
         <v>11754</v>
@@ -4922,7 +4922,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G157" t="n">
-        <v>5.12296438217163</v>
+        <v>5.12296485900879</v>
       </c>
       <c r="H157" t="n">
         <v>4698</v>
@@ -4951,7 +4951,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G158" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H158" t="n">
         <v>9550</v>
@@ -5038,7 +5038,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>5.04164743423462</v>
+        <v>5.04164791107178</v>
       </c>
       <c r="H161" t="n">
         <v>3098</v>
@@ -5125,7 +5125,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G164" t="n">
-        <v>4.94406747817993</v>
+        <v>4.94406700134277</v>
       </c>
       <c r="H164" t="n">
         <v>28419</v>
@@ -5212,7 +5212,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G167" t="n">
-        <v>4.89527702331543</v>
+        <v>4.89527750015259</v>
       </c>
       <c r="H167" t="n">
         <v>20850</v>
@@ -5270,7 +5270,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>4.94406747817993</v>
+        <v>4.94406700134277</v>
       </c>
       <c r="H169" t="n">
         <v>2656</v>
@@ -5299,7 +5299,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G170" t="n">
-        <v>4.89527702331543</v>
+        <v>4.89527750015259</v>
       </c>
       <c r="H170" t="n">
         <v>15167</v>
@@ -5328,7 +5328,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>4.91154050827026</v>
+        <v>4.91154098510742</v>
       </c>
       <c r="H171" t="n">
         <v>16947</v>
@@ -5357,7 +5357,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H172" t="n">
         <v>2308</v>
@@ -5444,7 +5444,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G175" t="n">
-        <v>4.83022403717041</v>
+        <v>4.83022356033325</v>
       </c>
       <c r="H175" t="n">
         <v>11057</v>
@@ -5473,7 +5473,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G176" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H176" t="n">
         <v>18455</v>
@@ -5705,7 +5705,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G184" t="n">
-        <v>5.36691570281982</v>
+        <v>5.36691522598267</v>
       </c>
       <c r="H184" t="n">
         <v>16090</v>
@@ -5850,7 +5850,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G189" t="n">
-        <v>5.13922834396362</v>
+        <v>5.13922786712646</v>
       </c>
       <c r="H189" t="n">
         <v>10921</v>
@@ -5908,7 +5908,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G191" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H191" t="n">
         <v>110919</v>
@@ -5937,7 +5937,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G192" t="n">
-        <v>5.00912046432495</v>
+        <v>5.00912094116211</v>
       </c>
       <c r="H192" t="n">
         <v>2290</v>
@@ -5966,7 +5966,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G193" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428085327148</v>
       </c>
       <c r="H193" t="n">
         <v>4766</v>
@@ -5995,7 +5995,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G194" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H194" t="n">
         <v>2077</v>
@@ -6140,7 +6140,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G199" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H199" t="n">
         <v>6894</v>
@@ -6169,7 +6169,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G200" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H200" t="n">
         <v>28649</v>
@@ -6198,7 +6198,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G201" t="n">
-        <v>5.28741645812988</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H201" t="n">
         <v>8833</v>
@@ -6227,7 +6227,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G202" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H202" t="n">
         <v>680</v>
@@ -6256,7 +6256,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G203" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H203" t="n">
         <v>5722</v>
@@ -6285,7 +6285,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G204" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H204" t="n">
         <v>3896</v>
@@ -6314,7 +6314,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G205" t="n">
-        <v>5.28741645812988</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H205" t="n">
         <v>1300</v>
@@ -6343,7 +6343,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>5.28741645812988</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H206" t="n">
         <v>4898</v>
@@ -6372,7 +6372,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H207" t="n">
         <v>5465</v>
@@ -6401,7 +6401,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G208" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H208" t="n">
         <v>3971</v>
@@ -6430,7 +6430,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G209" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H209" t="n">
         <v>6644</v>
@@ -6517,7 +6517,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G212" t="n">
-        <v>5.45368814468384</v>
+        <v>5.453688621521</v>
       </c>
       <c r="H212" t="n">
         <v>6658</v>
@@ -6633,7 +6633,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G216" t="n">
-        <v>5.45368814468384</v>
+        <v>5.453688621521</v>
       </c>
       <c r="H216" t="n">
         <v>10530</v>
@@ -6749,7 +6749,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G220" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H220" t="n">
         <v>4090</v>
@@ -6778,7 +6778,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G221" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H221" t="n">
         <v>22001</v>
@@ -6836,7 +6836,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G223" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H223" t="n">
         <v>3507</v>
@@ -6865,7 +6865,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G224" t="n">
-        <v>5.7529764175415</v>
+        <v>5.75297594070435</v>
       </c>
       <c r="H224" t="n">
         <v>500</v>
@@ -6952,7 +6952,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G227" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H227" t="n">
         <v>38319</v>
@@ -7097,7 +7097,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G232" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H232" t="n">
         <v>6952</v>
@@ -7126,7 +7126,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G233" t="n">
-        <v>5.90261936187744</v>
+        <v>5.9026198387146</v>
       </c>
       <c r="H233" t="n">
         <v>4553</v>
@@ -7416,7 +7416,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G243" t="n">
-        <v>5.76960229873657</v>
+        <v>5.76960277557373</v>
       </c>
       <c r="H243" t="n">
         <v>1500</v>
@@ -7445,7 +7445,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G244" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H244" t="n">
         <v>4011</v>
@@ -7590,7 +7590,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G249" t="n">
-        <v>5.65321254730225</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H249" t="n">
         <v>6312</v>
@@ -7619,7 +7619,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G250" t="n">
-        <v>5.58670473098755</v>
+        <v>5.58670425415039</v>
       </c>
       <c r="H250" t="n">
         <v>875</v>
@@ -7648,7 +7648,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>5.66984081268311</v>
+        <v>5.66984033584595</v>
       </c>
       <c r="H251" t="n">
         <v>1386</v>
@@ -7735,7 +7735,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G254" t="n">
-        <v>5.58670473098755</v>
+        <v>5.58670425415039</v>
       </c>
       <c r="H254" t="n">
         <v>2610</v>
@@ -7764,7 +7764,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G255" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H255" t="n">
         <v>1900</v>
@@ -7793,7 +7793,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G256" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G257" t="n">
-        <v>5.65321254730225</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H257" t="n">
         <v>3560</v>
@@ -7909,7 +7909,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G260" t="n">
-        <v>5.65321254730225</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H260" t="n">
         <v>1200</v>
@@ -7938,7 +7938,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H261" t="n">
         <v>2105</v>
@@ -7967,7 +7967,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G262" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H262" t="n">
         <v>500</v>
@@ -7996,7 +7996,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G263" t="n">
-        <v>5.65321254730225</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H263" t="n">
         <v>8019</v>
@@ -8054,7 +8054,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G265" t="n">
-        <v>5.61995887756348</v>
+        <v>5.61995935440063</v>
       </c>
       <c r="H265" t="n">
         <v>1620</v>
@@ -8083,7 +8083,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G266" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H266" t="n">
         <v>9438</v>
@@ -8170,7 +8170,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G269" t="n">
-        <v>5.50356912612915</v>
+        <v>5.50356960296631</v>
       </c>
       <c r="H269" t="n">
         <v>22096</v>
@@ -8199,7 +8199,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H270" t="n">
         <v>5650</v>
@@ -8228,7 +8228,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G271" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H271" t="n">
         <v>23690</v>
@@ -8286,7 +8286,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G273" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H273" t="n">
         <v>13409</v>
@@ -8315,7 +8315,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H274" t="n">
         <v>4619</v>
@@ -8344,7 +8344,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>5.65321254730225</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H275" t="n">
         <v>428</v>
@@ -8373,7 +8373,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>5.65321254730225</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H276" t="n">
         <v>7400</v>
@@ -8402,7 +8402,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G277" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H277" t="n">
         <v>4450</v>
@@ -8431,7 +8431,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G278" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H278" t="n">
         <v>3400</v>
@@ -8460,7 +8460,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G279" t="n">
-        <v>5.7529764175415</v>
+        <v>5.75297594070435</v>
       </c>
       <c r="H279" t="n">
         <v>13700</v>
@@ -8489,7 +8489,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G280" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H280" t="n">
         <v>5210</v>
@@ -8547,7 +8547,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>5.73634815216064</v>
+        <v>5.7363486289978</v>
       </c>
       <c r="H282" t="n">
         <v>6500</v>
@@ -8605,7 +8605,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G284" t="n">
-        <v>5.70309495925903</v>
+        <v>5.70309448242188</v>
       </c>
       <c r="H284" t="n">
         <v>6060</v>
@@ -8634,7 +8634,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>5.65321254730225</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H285" t="n">
         <v>15427</v>
@@ -8663,7 +8663,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.65321254730225</v>
+        <v>5.65321350097656</v>
       </c>
       <c r="H286" t="n">
         <v>32500</v>
@@ -8692,7 +8692,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G287" t="n">
-        <v>5.63658666610718</v>
+        <v>5.63658618927002</v>
       </c>
       <c r="H287" t="n">
         <v>1750</v>
@@ -8721,7 +8721,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G288" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H288" t="n">
         <v>1973</v>
@@ -8750,7 +8750,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G289" t="n">
-        <v>5.50356912612915</v>
+        <v>5.50356960296631</v>
       </c>
       <c r="H289" t="n">
         <v>10165</v>
@@ -8808,7 +8808,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G291" t="n">
-        <v>5.57007741928101</v>
+        <v>5.57007789611816</v>
       </c>
       <c r="H291" t="n">
         <v>4539</v>
@@ -8866,7 +8866,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G293" t="n">
-        <v>5.55345058441162</v>
+        <v>5.55345010757446</v>
       </c>
       <c r="H293" t="n">
         <v>14001</v>
@@ -9040,7 +9040,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>5.43706035614014</v>
+        <v>5.43706130981445</v>
       </c>
       <c r="H299" t="n">
         <v>4580</v>
@@ -9156,7 +9156,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G303" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H303" t="n">
         <v>4716</v>
@@ -9185,7 +9185,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G304" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H304" t="n">
         <v>1563</v>
@@ -9301,7 +9301,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G308" t="n">
-        <v>5.3539252281189</v>
+        <v>5.35392570495605</v>
       </c>
       <c r="H308" t="n">
         <v>7755</v>
@@ -9330,7 +9330,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G309" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H309" t="n">
         <v>3800</v>
@@ -9359,7 +9359,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H310" t="n">
         <v>27369</v>
@@ -9504,7 +9504,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G315" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H315" t="n">
         <v>3276</v>
@@ -9533,7 +9533,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G316" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H316" t="n">
         <v>29455</v>
@@ -9562,7 +9562,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G317" t="n">
-        <v>5.12114572525024</v>
+        <v>5.1211462020874</v>
       </c>
       <c r="H317" t="n">
         <v>4420</v>
@@ -9620,7 +9620,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G319" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H319" t="n">
         <v>1750</v>
@@ -9678,7 +9678,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G321" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H321" t="n">
         <v>5361</v>
@@ -9707,7 +9707,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G322" t="n">
-        <v>5.28741645812988</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H322" t="n">
         <v>6754</v>
@@ -9765,7 +9765,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G324" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H324" t="n">
         <v>4701</v>
@@ -9823,7 +9823,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G326" t="n">
-        <v>5.28741645812988</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H326" t="n">
         <v>4390</v>
@@ -9852,7 +9852,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G327" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H327" t="n">
         <v>10600</v>
@@ -9881,7 +9881,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G328" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H328" t="n">
         <v>6860</v>
@@ -9910,7 +9910,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G329" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H329" t="n">
         <v>24800</v>
@@ -9939,7 +9939,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H330" t="n">
         <v>5585</v>
@@ -10026,7 +10026,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G333" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H333" t="n">
         <v>1126</v>
@@ -10055,7 +10055,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G334" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H334" t="n">
         <v>10830</v>
@@ -10084,7 +10084,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G335" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H335" t="n">
         <v>11568</v>
@@ -10113,7 +10113,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G336" t="n">
-        <v>5.2042818069458</v>
+        <v>5.20428133010864</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -10142,7 +10142,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G337" t="n">
-        <v>5.28741645812988</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H337" t="n">
         <v>15623</v>
@@ -10258,7 +10258,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G341" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H341" t="n">
         <v>13173</v>
@@ -10287,7 +10287,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G342" t="n">
-        <v>5.28741645812988</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H342" t="n">
         <v>2043</v>
@@ -10345,7 +10345,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G344" t="n">
-        <v>5.28741645812988</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H344" t="n">
         <v>13660</v>
@@ -10374,7 +10374,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H345" t="n">
         <v>8254</v>
@@ -10403,7 +10403,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G346" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -10432,7 +10432,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G347" t="n">
-        <v>5.28741645812988</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H347" t="n">
         <v>5755</v>
@@ -10461,7 +10461,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G348" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H348" t="n">
         <v>3489</v>
@@ -10490,7 +10490,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G349" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H349" t="n">
         <v>8775</v>
@@ -10635,7 +10635,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G354" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H354" t="n">
         <v>7088</v>
@@ -10664,7 +10664,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G355" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H355" t="n">
         <v>1170</v>
@@ -10693,7 +10693,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G356" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H356" t="n">
         <v>2400</v>
@@ -10722,7 +10722,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G358" t="n">
-        <v>5.05463790893555</v>
+        <v>5.05463695526123</v>
       </c>
       <c r="H358" t="n">
         <v>4600</v>
@@ -10780,7 +10780,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G359" t="n">
-        <v>5.07126474380493</v>
+        <v>5.07126426696777</v>
       </c>
       <c r="H359" t="n">
         <v>3000</v>
@@ -10896,7 +10896,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G363" t="n">
-        <v>5.28741645812988</v>
+        <v>5.28741693496704</v>
       </c>
       <c r="H363" t="n">
         <v>4848</v>
@@ -10925,7 +10925,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G364" t="n">
-        <v>5.27079010009766</v>
+        <v>5.2707896232605</v>
       </c>
       <c r="H364" t="n">
         <v>2203</v>
@@ -10954,7 +10954,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G365" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H365" t="n">
         <v>1500</v>
@@ -10983,7 +10983,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G366" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H366" t="n">
         <v>710</v>
@@ -11186,7 +11186,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G373" t="n">
-        <v>5.32067108154297</v>
+        <v>5.32067155838013</v>
       </c>
       <c r="H373" t="n">
         <v>4742</v>
@@ -11244,7 +11244,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G375" t="n">
-        <v>5.25416326522827</v>
+        <v>5.25416278839111</v>
       </c>
       <c r="H375" t="n">
         <v>2615</v>
@@ -11331,7 +11331,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G378" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H378" t="n">
         <v>112</v>
@@ -11360,7 +11360,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G379" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11389,7 +11389,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G380" t="n">
-        <v>5.17102718353271</v>
+        <v>5.17102670669556</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G381" t="n">
-        <v>5.12114572525024</v>
+        <v>5.1211462020874</v>
       </c>
       <c r="H381" t="n">
         <v>1071</v>
@@ -11476,7 +11476,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G383" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H383" t="n">
         <v>5263</v>
@@ -11505,7 +11505,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -11534,7 +11534,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>5.30404424667358</v>
+        <v>5.30404376983643</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -11708,7 +11708,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G391" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H391" t="n">
         <v>6720</v>
@@ -11737,7 +11737,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G392" t="n">
-        <v>5.15440034866333</v>
+        <v>5.15439987182617</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G397" t="n">
-        <v>5.08789205551147</v>
+        <v>5.08789157867432</v>
       </c>
       <c r="H397" t="n">
         <v>1898</v>
@@ -11911,7 +11911,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G398" t="n">
-        <v>5.08789205551147</v>
+        <v>5.08789157867432</v>
       </c>
       <c r="H398" t="n">
         <v>2425</v>
@@ -11940,7 +11940,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G399" t="n">
-        <v>4.97150278091431</v>
+        <v>4.97150182723999</v>
       </c>
       <c r="H399" t="n">
         <v>5742</v>
@@ -11998,7 +11998,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G401" t="n">
-        <v>4.92162132263184</v>
+        <v>4.92162084579468</v>
       </c>
       <c r="H401" t="n">
         <v>1890</v>
@@ -12027,7 +12027,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>4.90499401092529</v>
+        <v>4.90499448776245</v>
       </c>
       <c r="H402" t="n">
         <v>2893</v>
@@ -12172,7 +12172,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H407" t="n">
         <v>9154</v>
@@ -12201,7 +12201,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G408" t="n">
-        <v>4.48931646347046</v>
+        <v>4.4893159866333</v>
       </c>
       <c r="H408" t="n">
         <v>6788</v>
@@ -12230,7 +12230,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G409" t="n">
-        <v>4.68884086608887</v>
+        <v>4.68884181976318</v>
       </c>
       <c r="H409" t="n">
         <v>700</v>
@@ -12259,7 +12259,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G410" t="n">
-        <v>4.78860425949097</v>
+        <v>4.78860473632812</v>
       </c>
       <c r="H410" t="n">
         <v>300</v>
@@ -12317,7 +12317,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G412" t="n">
-        <v>4.80523157119751</v>
+        <v>4.80523109436035</v>
       </c>
       <c r="H412" t="n">
         <v>200</v>
@@ -12404,7 +12404,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H415" t="n">
         <v>970</v>
@@ -12433,7 +12433,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G416" t="n">
-        <v>4.43943500518799</v>
+        <v>4.43943548202515</v>
       </c>
       <c r="H416" t="n">
         <v>3039</v>
@@ -12462,7 +12462,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>4.48931646347046</v>
+        <v>4.4893159866333</v>
       </c>
       <c r="H417" t="n">
         <v>4244</v>
@@ -12491,7 +12491,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>4.47268962860107</v>
+        <v>4.47268915176392</v>
       </c>
       <c r="H418" t="n">
         <v>25169</v>
@@ -12520,7 +12520,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G419" t="n">
-        <v>4.35629940032959</v>
+        <v>4.35629987716675</v>
       </c>
       <c r="H419" t="n">
         <v>5206</v>
@@ -12578,7 +12578,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H421" t="n">
         <v>1908</v>
@@ -12636,7 +12636,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G423" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H423" t="n">
         <v>3457</v>
@@ -12665,7 +12665,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G424" t="n">
-        <v>4.80523157119751</v>
+        <v>4.80523109436035</v>
       </c>
       <c r="H424" t="n">
         <v>3714</v>
@@ -12810,7 +12810,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G429" t="n">
-        <v>4.68884086608887</v>
+        <v>4.68884181976318</v>
       </c>
       <c r="H429" t="n">
         <v>3246</v>
@@ -12839,7 +12839,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G430" t="n">
-        <v>4.505943775177</v>
+        <v>4.50594329833984</v>
       </c>
       <c r="H430" t="n">
         <v>7925</v>
@@ -12868,7 +12868,7 @@
         <v>5.5</v>
       </c>
       <c r="G431" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H431" t="n">
         <v>2128</v>
@@ -12897,7 +12897,7 @@
         <v>5.5</v>
       </c>
       <c r="G432" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>5.5</v>
       </c>
       <c r="G433" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H433" t="n">
         <v>2400</v>
@@ -12955,7 +12955,7 @@
         <v>5.5</v>
       </c>
       <c r="G434" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H434" t="n">
         <v>0</v>
@@ -12984,7 +12984,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>4.68884086608887</v>
+        <v>4.68884181976318</v>
       </c>
       <c r="H435" t="n">
         <v>2711</v>
@@ -13013,7 +13013,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G436" t="n">
-        <v>4.78860425949097</v>
+        <v>4.78860473632812</v>
       </c>
       <c r="H436" t="n">
         <v>500</v>
@@ -13042,7 +13042,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G437" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H437" t="n">
         <v>6066</v>
@@ -13071,7 +13071,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G438" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H438" t="n">
         <v>1719</v>
@@ -13187,7 +13187,7 @@
         <v>5.5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.5724515914917</v>
+        <v>4.57245206832886</v>
       </c>
       <c r="H442" t="n">
         <v>700</v>
@@ -13245,7 +13245,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G444" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H444" t="n">
         <v>3000</v>
@@ -13303,7 +13303,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G446" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H446" t="n">
         <v>3000</v>
@@ -13332,7 +13332,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G447" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H447" t="n">
         <v>1000</v>
@@ -13361,7 +13361,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G448" t="n">
-        <v>4.7387228012085</v>
+        <v>4.73872232437134</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G449" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H449" t="n">
         <v>3090</v>
@@ -13419,7 +13419,7 @@
         <v>5.5</v>
       </c>
       <c r="G450" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H450" t="n">
         <v>1700</v>
@@ -13448,7 +13448,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G451" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H451" t="n">
         <v>1487</v>
@@ -13477,7 +13477,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H452" t="n">
         <v>500</v>
@@ -13506,7 +13506,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G453" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H453" t="n">
         <v>0</v>
@@ -13535,7 +13535,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G454" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H454" t="n">
         <v>4800</v>
@@ -13564,7 +13564,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G455" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H455" t="n">
         <v>5500</v>
@@ -13593,7 +13593,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G456" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H456" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G463" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H463" t="n">
         <v>5</v>
@@ -13854,7 +13854,7 @@
         <v>6</v>
       </c>
       <c r="G465" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H465" t="n">
         <v>205</v>
@@ -13912,7 +13912,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G467" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H467" t="n">
         <v>1464</v>
@@ -13941,7 +13941,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G468" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H468" t="n">
         <v>810</v>
@@ -13970,7 +13970,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G469" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H469" t="n">
         <v>646</v>
@@ -13999,7 +13999,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G470" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H470" t="n">
         <v>1000</v>
@@ -14028,7 +14028,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H471" t="n">
         <v>0</v>
@@ -14057,7 +14057,7 @@
         <v>6</v>
       </c>
       <c r="G472" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H472" t="n">
         <v>2091</v>
@@ -14086,7 +14086,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G473" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H473" t="n">
         <v>9179</v>
@@ -14202,7 +14202,7 @@
         <v>5.5</v>
       </c>
       <c r="G477" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H477" t="n">
         <v>350</v>
@@ -14260,7 +14260,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G479" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H479" t="n">
         <v>5905</v>
@@ -14289,7 +14289,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H480" t="n">
         <v>20980</v>
@@ -14318,7 +14318,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G481" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H481" t="n">
         <v>500</v>
@@ -14347,7 +14347,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G482" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H482" t="n">
         <v>1405</v>
@@ -14376,7 +14376,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G483" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H483" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G487" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H487" t="n">
         <v>3597</v>
@@ -14695,7 +14695,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H494" t="n">
         <v>3377</v>
@@ -14724,7 +14724,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G495" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H495" t="n">
         <v>0</v>
@@ -14753,7 +14753,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H496" t="n">
         <v>11723</v>
@@ -14898,7 +14898,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G501" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H501" t="n">
         <v>705</v>
@@ -14927,7 +14927,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G502" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H502" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G507" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H507" t="n">
         <v>3700</v>
@@ -15101,7 +15101,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G508" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H508" t="n">
         <v>0</v>
@@ -15130,7 +15130,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G509" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H509" t="n">
         <v>0</v>
@@ -15159,7 +15159,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G510" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H510" t="n">
         <v>0</v>
@@ -15188,7 +15188,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G511" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H511" t="n">
         <v>2505</v>
@@ -15217,7 +15217,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G512" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H512" t="n">
         <v>2050</v>
@@ -15362,7 +15362,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G517" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15391,7 +15391,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G518" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H518" t="n">
         <v>0</v>
@@ -15478,7 +15478,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G521" t="n">
-        <v>4.96075820922852</v>
+        <v>4.96075773239136</v>
       </c>
       <c r="H521" t="n">
         <v>341</v>
@@ -15565,7 +15565,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G524" t="n">
-        <v>4.99485206604004</v>
+        <v>4.9948525428772</v>
       </c>
       <c r="H524" t="n">
         <v>1780</v>
@@ -15594,7 +15594,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G525" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H525" t="n">
         <v>235</v>
@@ -15681,7 +15681,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H528" t="n">
         <v>700</v>
@@ -15710,7 +15710,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H529" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G530" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008813858032</v>
       </c>
       <c r="H530" t="n">
         <v>1270</v>
@@ -15855,7 +15855,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G534" t="n">
-        <v>4.90961599349976</v>
+        <v>4.90961647033691</v>
       </c>
       <c r="H534" t="n">
         <v>2167</v>
@@ -15884,7 +15884,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H535" t="n">
         <v>2280</v>
@@ -15913,7 +15913,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G536" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H536" t="n">
         <v>2123</v>
@@ -15942,7 +15942,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G537" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H537" t="n">
         <v>1000</v>
@@ -15971,7 +15971,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H538" t="n">
         <v>1776</v>
@@ -16029,7 +16029,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G540" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H540" t="n">
         <v>350</v>
@@ -16058,7 +16058,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G541" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16087,7 +16087,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H542" t="n">
         <v>2760</v>
@@ -16116,7 +16116,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G543" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H543" t="n">
         <v>0</v>
@@ -16145,7 +16145,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G544" t="n">
-        <v>4.87552118301392</v>
+        <v>4.87552070617676</v>
       </c>
       <c r="H544" t="n">
         <v>421</v>
@@ -16174,7 +16174,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H545" t="n">
         <v>2895</v>
@@ -16232,7 +16232,7 @@
         <v>5.5</v>
       </c>
       <c r="G547" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H547" t="n">
         <v>2535</v>
@@ -16290,7 +16290,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G549" t="n">
-        <v>4.48343467712402</v>
+        <v>4.48343420028687</v>
       </c>
       <c r="H549" t="n">
         <v>1022</v>
@@ -16348,7 +16348,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G551" t="n">
-        <v>4.48343467712402</v>
+        <v>4.48343420028687</v>
       </c>
       <c r="H551" t="n">
         <v>1200</v>
@@ -16406,7 +16406,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G553" t="n">
-        <v>4.36410284042358</v>
+        <v>4.36410236358643</v>
       </c>
       <c r="H553" t="n">
         <v>4928</v>
@@ -16435,7 +16435,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G554" t="n">
-        <v>4.44933891296387</v>
+        <v>4.44933938980103</v>
       </c>
       <c r="H554" t="n">
         <v>608</v>
@@ -16580,7 +16580,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G559" t="n">
-        <v>4.53457546234131</v>
+        <v>4.53457593917847</v>
       </c>
       <c r="H559" t="n">
         <v>750</v>
@@ -16609,7 +16609,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H560" t="n">
         <v>2687</v>
@@ -16638,7 +16638,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G561" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H561" t="n">
         <v>460</v>
@@ -16667,7 +16667,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G562" t="n">
-        <v>4.60276508331299</v>
+        <v>4.60276460647583</v>
       </c>
       <c r="H562" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G563" t="n">
-        <v>4.46638584136963</v>
+        <v>4.46638631820679</v>
       </c>
       <c r="H563" t="n">
         <v>2000</v>
@@ -17044,7 +17044,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G575" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H575" t="n">
         <v>20</v>
@@ -17073,7 +17073,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G576" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H576" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G580" t="n">
-        <v>4.80733203887939</v>
+        <v>4.80733251571655</v>
       </c>
       <c r="H580" t="n">
         <v>3158</v>
@@ -17334,7 +17334,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G585" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H585" t="n">
         <v>360</v>
@@ -17624,7 +17624,7 @@
         <v>5.5</v>
       </c>
       <c r="G595" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H595" t="n">
         <v>6710</v>
@@ -17682,7 +17682,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H597" t="n">
         <v>607</v>
@@ -17711,7 +17711,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G598" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H598" t="n">
         <v>65</v>
@@ -18059,7 +18059,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H610" t="n">
         <v>1351</v>
@@ -18088,7 +18088,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G611" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H611" t="n">
         <v>510</v>
@@ -18117,7 +18117,7 @@
         <v>5.5</v>
       </c>
       <c r="G612" t="n">
-        <v>4.68800115585327</v>
+        <v>4.68800163269043</v>
       </c>
       <c r="H612" t="n">
         <v>34</v>
@@ -18146,7 +18146,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G613" t="n">
-        <v>4.75619029998779</v>
+        <v>4.75618982315063</v>
       </c>
       <c r="H613" t="n">
         <v>186</v>
@@ -18320,7 +18320,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G619" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H619" t="n">
         <v>675</v>
@@ -18494,7 +18494,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G625" t="n">
-        <v>4.80733203887939</v>
+        <v>4.80733251571655</v>
       </c>
       <c r="H625" t="n">
         <v>1866</v>
@@ -18523,7 +18523,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G626" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H626" t="n">
         <v>110</v>
@@ -18552,7 +18552,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G627" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H627" t="n">
         <v>10</v>
@@ -18581,7 +18581,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H628" t="n">
         <v>400</v>
@@ -18610,7 +18610,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>4.82437944412231</v>
+        <v>4.82437896728516</v>
       </c>
       <c r="H629" t="n">
         <v>110</v>
@@ -18697,7 +18697,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G632" t="n">
-        <v>4.77323722839355</v>
+        <v>4.77323770523071</v>
       </c>
       <c r="H632" t="n">
         <v>872</v>
@@ -18726,7 +18726,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G633" t="n">
-        <v>4.70504808425903</v>
+        <v>4.70504856109619</v>
       </c>
       <c r="H633" t="n">
         <v>1703</v>
@@ -18755,7 +18755,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G634" t="n">
-        <v>4.72209596633911</v>
+        <v>4.72209548950195</v>
       </c>
       <c r="H634" t="n">
         <v>10</v>
@@ -18813,7 +18813,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G636" t="n">
-        <v>4.79028463363647</v>
+        <v>4.79028511047363</v>
       </c>
       <c r="H636" t="n">
         <v>1898</v>
@@ -18842,7 +18842,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G637" t="n">
-        <v>5.01189947128296</v>
+        <v>5.01189994812012</v>
       </c>
       <c r="H637" t="n">
         <v>67041</v>
@@ -18871,7 +18871,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G638" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H638" t="n">
         <v>3800</v>
@@ -18958,7 +18958,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>5.01189947128296</v>
+        <v>5.01189994812012</v>
       </c>
       <c r="H641" t="n">
         <v>3920</v>
@@ -18987,7 +18987,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G642" t="n">
-        <v>5.09713554382324</v>
+        <v>5.0971360206604</v>
       </c>
       <c r="H642" t="n">
         <v>5765</v>
@@ -19016,7 +19016,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G643" t="n">
-        <v>5.25056076049805</v>
+        <v>5.25056171417236</v>
       </c>
       <c r="H643" t="n">
         <v>4245</v>
@@ -19045,7 +19045,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G644" t="n">
-        <v>5.35284519195557</v>
+        <v>5.35284566879272</v>
       </c>
       <c r="H644" t="n">
         <v>15820</v>
@@ -19103,7 +19103,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H646" t="n">
         <v>12764</v>
@@ -19132,7 +19132,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G647" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H647" t="n">
         <v>1345</v>
@@ -19161,7 +19161,7 @@
         <v>6</v>
       </c>
       <c r="G648" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H648" t="n">
         <v>1200</v>
@@ -19248,7 +19248,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G651" t="n">
-        <v>5.19941997528076</v>
+        <v>5.1994194984436</v>
       </c>
       <c r="H651" t="n">
         <v>2400</v>
@@ -19335,7 +19335,7 @@
         <v>6</v>
       </c>
       <c r="G654" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H654" t="n">
         <v>3833</v>
@@ -19422,7 +19422,7 @@
         <v>6</v>
       </c>
       <c r="G657" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H657" t="n">
         <v>512</v>
@@ -19451,7 +19451,7 @@
         <v>6</v>
       </c>
       <c r="G658" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H658" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>6</v>
       </c>
       <c r="G659" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H659" t="n">
         <v>618</v>
@@ -19509,7 +19509,7 @@
         <v>6</v>
       </c>
       <c r="G660" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H660" t="n">
         <v>110</v>
@@ -19538,7 +19538,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H661" t="n">
         <v>160</v>
@@ -19596,7 +19596,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G663" t="n">
-        <v>5.08008861541748</v>
+        <v>5.08008813858032</v>
       </c>
       <c r="H663" t="n">
         <v>300</v>
@@ -19857,7 +19857,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G672" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H672" t="n">
         <v>1371</v>
@@ -19886,7 +19886,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G673" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -19915,7 +19915,7 @@
         <v>6</v>
       </c>
       <c r="G674" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H674" t="n">
         <v>1922</v>
@@ -19973,7 +19973,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G676" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H676" t="n">
         <v>3802</v>
@@ -20002,7 +20002,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H677" t="n">
         <v>1377</v>
@@ -20031,7 +20031,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>6</v>
       </c>
       <c r="G679" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H679" t="n">
         <v>4219</v>
@@ -20089,7 +20089,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G680" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H680" t="n">
         <v>893</v>
@@ -20118,7 +20118,7 @@
         <v>6</v>
       </c>
       <c r="G681" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H681" t="n">
         <v>1250</v>
@@ -20147,7 +20147,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H682" t="n">
         <v>6283</v>
@@ -20205,7 +20205,7 @@
         <v>6</v>
       </c>
       <c r="G684" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H684" t="n">
         <v>3929</v>
@@ -20292,7 +20292,7 @@
         <v>6</v>
       </c>
       <c r="G687" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H687" t="n">
         <v>3300</v>
@@ -20350,7 +20350,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G689" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H689" t="n">
         <v>820</v>
@@ -20379,7 +20379,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G690" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H690" t="n">
         <v>700</v>
@@ -20408,7 +20408,7 @@
         <v>6</v>
       </c>
       <c r="G691" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H691" t="n">
         <v>3324</v>
@@ -20437,7 +20437,7 @@
         <v>6</v>
       </c>
       <c r="G692" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H692" t="n">
         <v>3119</v>
@@ -20466,7 +20466,7 @@
         <v>6</v>
       </c>
       <c r="G693" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H693" t="n">
         <v>2354</v>
@@ -20553,7 +20553,7 @@
         <v>6</v>
       </c>
       <c r="G696" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H696" t="n">
         <v>10</v>
@@ -20669,7 +20669,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G700" t="n">
-        <v>5.02894687652588</v>
+        <v>5.02894735336304</v>
       </c>
       <c r="H700" t="n">
         <v>807</v>
@@ -20785,7 +20785,7 @@
         <v>6</v>
       </c>
       <c r="G704" t="n">
-        <v>5.11418294906616</v>
+        <v>5.11418342590332</v>
       </c>
       <c r="H704" t="n">
         <v>400</v>
@@ -21162,7 +21162,7 @@
         <v>5.75</v>
       </c>
       <c r="G717" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H717" t="n">
         <v>1661</v>
@@ -21191,7 +21191,7 @@
         <v>5.75</v>
       </c>
       <c r="G718" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H718" t="n">
         <v>2500</v>
@@ -21220,7 +21220,7 @@
         <v>5.75</v>
       </c>
       <c r="G719" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>5.75</v>
       </c>
       <c r="G720" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H720" t="n">
         <v>0</v>
@@ -21278,7 +21278,7 @@
         <v>5.75</v>
       </c>
       <c r="G721" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21394,7 +21394,7 @@
         <v>5.75</v>
       </c>
       <c r="G725" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H725" t="n">
         <v>1926</v>
@@ -21423,7 +21423,7 @@
         <v>5.75</v>
       </c>
       <c r="G726" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H726" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>5.75</v>
       </c>
       <c r="G727" t="n">
-        <v>5.07009601593018</v>
+        <v>5.07009553909302</v>
       </c>
       <c r="H727" t="n">
         <v>6821</v>
@@ -21481,7 +21481,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G728" t="n">
-        <v>4.93783187866211</v>
+        <v>4.93783235549927</v>
       </c>
       <c r="H728" t="n">
         <v>2930</v>
@@ -21510,7 +21510,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G729" t="n">
-        <v>4.93783187866211</v>
+        <v>4.93783235549927</v>
       </c>
       <c r="H729" t="n">
         <v>6873</v>
@@ -21568,7 +21568,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G731" t="n">
-        <v>4.89374494552612</v>
+        <v>4.89374446868896</v>
       </c>
       <c r="H731" t="n">
         <v>350</v>
@@ -21858,7 +21858,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G741" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H741" t="n">
         <v>966</v>
@@ -21887,7 +21887,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G742" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H742" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G752" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H752" t="n">
         <v>233</v>
@@ -22206,7 +22206,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G753" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H753" t="n">
         <v>2500</v>
@@ -22235,7 +22235,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G754" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H754" t="n">
         <v>4845</v>
@@ -22264,7 +22264,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G755" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H755" t="n">
         <v>5770</v>
@@ -22583,7 +22583,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G766" t="n">
-        <v>4.45286703109741</v>
+        <v>4.45286655426025</v>
       </c>
       <c r="H766" t="n">
         <v>6689</v>
@@ -22670,7 +22670,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G769" t="n">
-        <v>4.76148128509521</v>
+        <v>4.76148080825806</v>
       </c>
       <c r="H769" t="n">
         <v>2000</v>
@@ -22699,7 +22699,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G770" t="n">
-        <v>4.89374494552612</v>
+        <v>4.89374446868896</v>
       </c>
       <c r="H770" t="n">
         <v>3256</v>
@@ -23395,7 +23395,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G794" t="n">
-        <v>4.89374494552612</v>
+        <v>4.89374446868896</v>
       </c>
       <c r="H794" t="n">
         <v>1641</v>
@@ -23946,7 +23946,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G813" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H813" t="n">
         <v>1618</v>
@@ -23975,7 +23975,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G814" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H814" t="n">
         <v>0</v>
@@ -24004,7 +24004,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G815" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H815" t="n">
         <v>1188</v>
@@ -24033,7 +24033,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G816" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H816" t="n">
         <v>10</v>
@@ -24062,7 +24062,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G817" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H817" t="n">
         <v>365</v>
@@ -24091,7 +24091,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G818" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H818" t="n">
         <v>700</v>
@@ -24207,7 +24207,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G822" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H822" t="n">
         <v>340</v>
@@ -24352,7 +24352,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H827" t="n">
         <v>2876</v>
@@ -24497,7 +24497,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G832" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H832" t="n">
         <v>207</v>
@@ -24526,7 +24526,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G833" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H833" t="n">
         <v>1050</v>
@@ -24555,7 +24555,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G834" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H834" t="n">
         <v>0</v>
@@ -24584,7 +24584,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G835" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H835" t="n">
         <v>1</v>
@@ -24642,7 +24642,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G837" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H837" t="n">
         <v>1803</v>
@@ -24729,7 +24729,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G840" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H840" t="n">
         <v>609</v>
@@ -24758,7 +24758,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G841" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H841" t="n">
         <v>4500</v>
@@ -24787,7 +24787,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G842" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H842" t="n">
         <v>2500</v>
@@ -24816,7 +24816,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G843" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H843" t="n">
         <v>1253</v>
@@ -24874,7 +24874,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G845" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H845" t="n">
         <v>796</v>
@@ -25048,7 +25048,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G851" t="n">
-        <v>4.0913462638855</v>
+        <v>4.09134674072266</v>
       </c>
       <c r="H851" t="n">
         <v>2200</v>
@@ -25193,7 +25193,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H856" t="n">
         <v>3097</v>
@@ -25280,7 +25280,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G859" t="n">
-        <v>4.12661647796631</v>
+        <v>4.12661695480347</v>
       </c>
       <c r="H859" t="n">
         <v>6840</v>
@@ -25338,7 +25338,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G861" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H861" t="n">
         <v>1733</v>
@@ -25367,7 +25367,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G862" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H862" t="n">
         <v>1450</v>
@@ -25396,7 +25396,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G863" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H863" t="n">
         <v>3550</v>
@@ -25425,7 +25425,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G864" t="n">
-        <v>4.14425230026245</v>
+        <v>4.14425182342529</v>
       </c>
       <c r="H864" t="n">
         <v>6616</v>
@@ -25483,7 +25483,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G866" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H866" t="n">
         <v>20519</v>
@@ -25541,7 +25541,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G868" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H868" t="n">
         <v>15412</v>
@@ -25570,7 +25570,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G869" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H869" t="n">
         <v>3776</v>
@@ -25599,7 +25599,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G870" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H870" t="n">
         <v>4073</v>
@@ -25686,7 +25686,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H873" t="n">
         <v>5847</v>
@@ -25744,7 +25744,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H875" t="n">
         <v>3194</v>
@@ -25802,7 +25802,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G877" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H877" t="n">
         <v>13736</v>
@@ -25947,7 +25947,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G882" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H882" t="n">
         <v>15378</v>
@@ -25976,7 +25976,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G883" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H883" t="n">
         <v>18373</v>
@@ -26034,7 +26034,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G885" t="n">
-        <v>3.68573904037476</v>
+        <v>3.6857385635376</v>
       </c>
       <c r="H885" t="n">
         <v>8364</v>
@@ -26063,7 +26063,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G886" t="n">
-        <v>3.73864436149597</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H886" t="n">
         <v>2531</v>
@@ -26092,7 +26092,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G887" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H887" t="n">
         <v>5091</v>
@@ -26121,7 +26121,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G888" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H888" t="n">
         <v>8519</v>
@@ -26150,7 +26150,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H889" t="n">
         <v>14342</v>
@@ -26179,7 +26179,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G890" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H890" t="n">
         <v>20433</v>
@@ -26208,7 +26208,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G891" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H891" t="n">
         <v>58437</v>
@@ -26266,7 +26266,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G893" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H893" t="n">
         <v>22381</v>
@@ -26353,7 +26353,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G896" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H896" t="n">
         <v>7640</v>
@@ -26440,7 +26440,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G899" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H899" t="n">
         <v>25714</v>
@@ -26498,7 +26498,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G901" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H901" t="n">
         <v>17900</v>
@@ -26527,7 +26527,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G902" t="n">
-        <v>3.73864436149597</v>
+        <v>3.73864412307739</v>
       </c>
       <c r="H902" t="n">
         <v>44451</v>
@@ -26556,7 +26556,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H903" t="n">
         <v>25646</v>
@@ -26585,7 +26585,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G904" t="n">
-        <v>3.80918502807617</v>
+        <v>3.80918455123901</v>
       </c>
       <c r="H904" t="n">
         <v>39491</v>
@@ -26672,7 +26672,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G907" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H907" t="n">
         <v>7190</v>
@@ -26730,7 +26730,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G909" t="n">
-        <v>3.77391457557678</v>
+        <v>3.77391481399536</v>
       </c>
       <c r="H909" t="n">
         <v>700</v>
@@ -26788,7 +26788,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H911" t="n">
         <v>85</v>
@@ -26846,7 +26846,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H913" t="n">
         <v>1250</v>
@@ -26875,7 +26875,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G914" t="n">
-        <v>3.86209011077881</v>
+        <v>3.86209034919739</v>
       </c>
       <c r="H914" t="n">
         <v>1050</v>
@@ -26933,7 +26933,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H916" t="n">
         <v>35</v>
@@ -27020,7 +27020,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G919" t="n">
-        <v>3.826819896698</v>
+        <v>3.82681965827942</v>
       </c>
       <c r="H919" t="n">
         <v>1905</v>
@@ -27049,7 +27049,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H920" t="n">
         <v>8574</v>
@@ -27136,7 +27136,7 @@
         <v>4.44000005722046</v>
       </c>
       <c r="G923" t="n">
-        <v>3.91499543190002</v>
+        <v>3.9149956703186</v>
       </c>
       <c r="H923" t="n">
         <v>10338</v>
@@ -27194,7 +27194,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H925" t="n">
         <v>2087</v>
@@ -27223,7 +27223,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>3.93263053894043</v>
+        <v>3.93263030052185</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H927" t="n">
         <v>1386</v>
@@ -27281,7 +27281,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G928" t="n">
-        <v>3.98553562164307</v>
+        <v>3.98553609848022</v>
       </c>
       <c r="H928" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H930" t="n">
         <v>125</v>
@@ -27397,7 +27397,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G932" t="n">
-        <v>3.95026564598083</v>
+        <v>3.95026540756226</v>
       </c>
       <c r="H932" t="n">
         <v>468</v>
@@ -27455,7 +27455,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G934" t="n">
-        <v>4.1795220375061</v>
+        <v>4.17952156066895</v>
       </c>
       <c r="H934" t="n">
         <v>5727</v>
@@ -27571,7 +27571,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G938" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H938" t="n">
         <v>10491</v>
@@ -27629,7 +27629,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G940" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H940" t="n">
         <v>194</v>
@@ -27716,7 +27716,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G943" t="n">
-        <v>4.28533315658569</v>
+        <v>4.28533267974854</v>
       </c>
       <c r="H943" t="n">
         <v>1635</v>
@@ -27745,7 +27745,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G944" t="n">
-        <v>4.2324275970459</v>
+        <v>4.23242807388306</v>
       </c>
       <c r="H944" t="n">
         <v>8544</v>
@@ -28093,7 +28093,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>4.33823776245117</v>
+        <v>4.33823823928833</v>
       </c>
       <c r="H956" t="n">
         <v>800</v>
@@ -28238,7 +28238,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G961" t="n">
-        <v>4.45286703109741</v>
+        <v>4.45286655426025</v>
       </c>
       <c r="H961" t="n">
         <v>1299</v>
@@ -46415,7 +46415,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="E1588" t="n">
-        <v>6.15000009536743</v>
+        <v>6.09999990463257</v>
       </c>
       <c r="F1588" t="n">
         <v>6.09999990463257</v>
@@ -46427,6 +46427,35 @@
         <v>708</v>
       </c>
       <c r="I1588" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1589" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1589" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D1589" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1589" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="G1589" t="n">
+        <v>6.15000009536743</v>
+      </c>
+      <c r="H1589" t="n">
+        <v>5973</v>
+      </c>
+      <c r="I1589" t="s">
         <v>9</v>
       </c>
     </row>
